--- a/client_gamedata/ios/iosExp.xlsx
+++ b/client_gamedata/ios/iosExp.xlsx
@@ -1450,7 +1450,7 @@
         <v>audioclip_sfx_b0015_jp.ab</v>
       </c>
       <c r="C53">
-        <v>116862</v>
+        <v>116861</v>
       </c>
       <c r="D53" t="str">
         <v>Stage_1</v>
@@ -1470,7 +1470,7 @@
         <v>audioclip_sfx_b0028_jp.ab</v>
       </c>
       <c r="C54">
-        <v>875307</v>
+        <v>875308</v>
       </c>
       <c r="D54" t="str">
         <v>Stage_1</v>
@@ -1770,7 +1770,7 @@
         <v>audioclip_sfx_h0006_jp.ab</v>
       </c>
       <c r="C69">
-        <v>1013615</v>
+        <v>1013616</v>
       </c>
       <c r="D69" t="str">
         <v>Stage_1</v>
@@ -1790,7 +1790,7 @@
         <v>audioclip_sfx_h0007_jp.ab</v>
       </c>
       <c r="C70">
-        <v>678624</v>
+        <v>678623</v>
       </c>
       <c r="D70" t="str">
         <v>Stage_1</v>
@@ -1810,7 +1810,7 @@
         <v>audioclip_sfx_h0008_jp.ab</v>
       </c>
       <c r="C71">
-        <v>349414</v>
+        <v>349413</v>
       </c>
       <c r="D71" t="str">
         <v>Stage_1</v>
@@ -1850,7 +1850,7 @@
         <v>audioclip_sfx_h0010_jp.ab</v>
       </c>
       <c r="C73">
-        <v>1074573</v>
+        <v>1074575</v>
       </c>
       <c r="D73" t="str">
         <v>Stage_1</v>
@@ -1870,7 +1870,7 @@
         <v>audioclip_sfx_h0012_jp.ab</v>
       </c>
       <c r="C74">
-        <v>740115</v>
+        <v>740114</v>
       </c>
       <c r="D74" t="str">
         <v>Stage_1</v>
@@ -1890,7 +1890,7 @@
         <v>audioclip_sfx_h0013_jp.ab</v>
       </c>
       <c r="C75">
-        <v>940882</v>
+        <v>940883</v>
       </c>
       <c r="D75" t="str">
         <v>Stage_1</v>
@@ -1910,7 +1910,7 @@
         <v>audioclip_sfx_h0014_jp.ab</v>
       </c>
       <c r="C76">
-        <v>446591</v>
+        <v>446594</v>
       </c>
       <c r="D76" t="str">
         <v>Stage_1</v>
@@ -1950,7 +1950,7 @@
         <v>audioclip_sfx_h0018_jp.ab</v>
       </c>
       <c r="C78">
-        <v>891813</v>
+        <v>891814</v>
       </c>
       <c r="D78" t="str">
         <v>Stage_1</v>
@@ -1990,7 +1990,7 @@
         <v>audioclip_sfx_h0021_jp.ab</v>
       </c>
       <c r="C80">
-        <v>1196247</v>
+        <v>1196249</v>
       </c>
       <c r="D80" t="str">
         <v>Stage_1</v>
@@ -2030,7 +2030,7 @@
         <v>audioclip_sfx_h0023_jp.ab</v>
       </c>
       <c r="C82">
-        <v>1374152</v>
+        <v>1374151</v>
       </c>
       <c r="D82" t="str">
         <v>Stage_1</v>
@@ -2050,7 +2050,7 @@
         <v>audioclip_sfx_h0024_jp.ab</v>
       </c>
       <c r="C83">
-        <v>1572148</v>
+        <v>1572146</v>
       </c>
       <c r="D83" t="str">
         <v>Stage_1</v>
@@ -2090,7 +2090,7 @@
         <v>audioclip_sfx_h0029_jp.ab</v>
       </c>
       <c r="C85">
-        <v>1291353</v>
+        <v>1291354</v>
       </c>
       <c r="D85" t="str">
         <v>Stage_1</v>
@@ -2110,7 +2110,7 @@
         <v>audioclip_sfx_h0030_jp.ab</v>
       </c>
       <c r="C86">
-        <v>1189230</v>
+        <v>1189229</v>
       </c>
       <c r="D86" t="str">
         <v>Stage_1</v>
@@ -2170,7 +2170,7 @@
         <v>audioclip_sfx_h0036_jp.ab</v>
       </c>
       <c r="C89">
-        <v>743619</v>
+        <v>743617</v>
       </c>
       <c r="D89" t="str">
         <v>Stage_1</v>
@@ -2190,7 +2190,7 @@
         <v>audioclip_sfx_h0038_jp.ab</v>
       </c>
       <c r="C90">
-        <v>611356</v>
+        <v>611357</v>
       </c>
       <c r="D90" t="str">
         <v>Stage_1</v>
@@ -2250,7 +2250,7 @@
         <v>audioclip_sfx_h0042_jp.ab</v>
       </c>
       <c r="C93">
-        <v>955384</v>
+        <v>955385</v>
       </c>
       <c r="D93" t="str">
         <v>Stage_1</v>
@@ -2290,7 +2290,7 @@
         <v>audioclip_sfx_h0044_jp.ab</v>
       </c>
       <c r="C95">
-        <v>619213</v>
+        <v>619212</v>
       </c>
       <c r="D95" t="str">
         <v>Stage_1</v>
@@ -2350,7 +2350,7 @@
         <v>audioclip_sfx_h0048_jp.ab</v>
       </c>
       <c r="C98">
-        <v>1635040</v>
+        <v>1635041</v>
       </c>
       <c r="D98" t="str">
         <v>Stage_1</v>
@@ -2370,7 +2370,7 @@
         <v>audioclip_sfx_h0073_jp.ab</v>
       </c>
       <c r="C99">
-        <v>276294</v>
+        <v>276295</v>
       </c>
       <c r="D99" t="str">
         <v>Stage_1</v>
@@ -2430,7 +2430,7 @@
         <v>audioclip_sfx_h0133_jp.ab</v>
       </c>
       <c r="C102">
-        <v>1334023</v>
+        <v>1334024</v>
       </c>
       <c r="D102" t="str">
         <v>Stage_1</v>
@@ -2470,7 +2470,7 @@
         <v>audioclip_sfx_h0135_jp.ab</v>
       </c>
       <c r="C104">
-        <v>2285418</v>
+        <v>2285419</v>
       </c>
       <c r="D104" t="str">
         <v>Stage_1</v>
@@ -2490,7 +2490,7 @@
         <v>audioclip_sfx_h0136_jp.ab</v>
       </c>
       <c r="C105">
-        <v>1316079</v>
+        <v>1316078</v>
       </c>
       <c r="D105" t="str">
         <v>Stage_1</v>
@@ -2530,7 +2530,7 @@
         <v>audioclip_sfx_h0138_jp.ab</v>
       </c>
       <c r="C107">
-        <v>1236789</v>
+        <v>1236790</v>
       </c>
       <c r="D107" t="str">
         <v>Stage_1</v>
@@ -2550,7 +2550,7 @@
         <v>audioclip_sfx_h0150_jp.ab</v>
       </c>
       <c r="C108">
-        <v>2757250</v>
+        <v>2757249</v>
       </c>
       <c r="D108" t="str">
         <v>Stage_1</v>
@@ -2570,7 +2570,7 @@
         <v>audioclip_sfx_h0151_jp.ab</v>
       </c>
       <c r="C109">
-        <v>1924709</v>
+        <v>1924706</v>
       </c>
       <c r="D109" t="str">
         <v>Stage_1</v>
@@ -2590,7 +2590,7 @@
         <v>audioclip_sfx_h0152_jp.ab</v>
       </c>
       <c r="C110">
-        <v>1987358</v>
+        <v>1987359</v>
       </c>
       <c r="D110" t="str">
         <v>Stage_1</v>
@@ -2670,7 +2670,7 @@
         <v>audioclip_sfx_h0161_jp.ab</v>
       </c>
       <c r="C114">
-        <v>1944101</v>
+        <v>1944102</v>
       </c>
       <c r="D114" t="str">
         <v>Stage_1</v>
@@ -2690,7 +2690,7 @@
         <v>audioclip_sfx_h0163_jp.ab</v>
       </c>
       <c r="C115">
-        <v>1305067</v>
+        <v>1305069</v>
       </c>
       <c r="D115" t="str">
         <v>Stage_1</v>
@@ -2710,7 +2710,7 @@
         <v>audioclip_sfx_h0164_jp.ab</v>
       </c>
       <c r="C116">
-        <v>966708</v>
+        <v>966705</v>
       </c>
       <c r="D116" t="str">
         <v>Stage_1</v>
@@ -2750,7 +2750,7 @@
         <v>audioclip_sfx_h0166_jp.ab</v>
       </c>
       <c r="C118">
-        <v>735094</v>
+        <v>735096</v>
       </c>
       <c r="D118" t="str">
         <v>Stage_1</v>
@@ -2810,7 +2810,7 @@
         <v>audioclip_sfx_h0169_jp.ab</v>
       </c>
       <c r="C121">
-        <v>929592</v>
+        <v>929593</v>
       </c>
       <c r="D121" t="str">
         <v>Stage_1</v>
@@ -2830,7 +2830,7 @@
         <v>audioclip_sfx_h0170_jp.ab</v>
       </c>
       <c r="C122">
-        <v>1438188</v>
+        <v>1438190</v>
       </c>
       <c r="D122" t="str">
         <v>Stage_1</v>
@@ -2850,7 +2850,7 @@
         <v>audioclip_sfx_h0171_jp.ab</v>
       </c>
       <c r="C123">
-        <v>1738274</v>
+        <v>1738273</v>
       </c>
       <c r="D123" t="str">
         <v>Stage_1</v>
@@ -2870,7 +2870,7 @@
         <v>audioclip_sfx_h0172_jp.ab</v>
       </c>
       <c r="C124">
-        <v>1379888</v>
+        <v>1379889</v>
       </c>
       <c r="D124" t="str">
         <v>Stage_1</v>
@@ -2890,7 +2890,7 @@
         <v>audioclip_sfx_h0174_jp.ab</v>
       </c>
       <c r="C125">
-        <v>1668214</v>
+        <v>1668215</v>
       </c>
       <c r="D125" t="str">
         <v>Stage_1</v>
@@ -2910,7 +2910,7 @@
         <v>audioclip_sfx_h0175_jp.ab</v>
       </c>
       <c r="C126">
-        <v>1253485</v>
+        <v>1253486</v>
       </c>
       <c r="D126" t="str">
         <v>Stage_1</v>
@@ -2970,7 +2970,7 @@
         <v>audioclip_sfx_h0179_jp.ab</v>
       </c>
       <c r="C129">
-        <v>1837992</v>
+        <v>1837986</v>
       </c>
       <c r="D129" t="str">
         <v>Stage_1</v>
@@ -2990,7 +2990,7 @@
         <v>audioclip_sfx_h0183_jp.ab</v>
       </c>
       <c r="C130">
-        <v>2327470</v>
+        <v>2327471</v>
       </c>
       <c r="D130" t="str">
         <v>Stage_1</v>
@@ -3010,7 +3010,7 @@
         <v>audioclip_sfx_h0185_jp.ab</v>
       </c>
       <c r="C131">
-        <v>1563968</v>
+        <v>1563971</v>
       </c>
       <c r="D131" t="str">
         <v>Stage_1</v>
@@ -3030,7 +3030,7 @@
         <v>audioclip_sfx_h0186_jp.ab</v>
       </c>
       <c r="C132">
-        <v>1892916</v>
+        <v>1892917</v>
       </c>
       <c r="D132" t="str">
         <v>Stage_1</v>
@@ -3050,7 +3050,7 @@
         <v>audioclip_sfx_h0190_jp.ab</v>
       </c>
       <c r="C133">
-        <v>2643057</v>
+        <v>2643056</v>
       </c>
       <c r="D133" t="str">
         <v>Stage_1</v>
@@ -3110,7 +3110,7 @@
         <v>audioclip_sfx_h0193_jp.ab</v>
       </c>
       <c r="C136">
-        <v>1562442</v>
+        <v>1562440</v>
       </c>
       <c r="D136" t="str">
         <v>Stage_1</v>
@@ -3210,7 +3210,7 @@
         <v>audioclip_sfx_h0199_jp.ab</v>
       </c>
       <c r="C141">
-        <v>922796</v>
+        <v>922797</v>
       </c>
       <c r="D141" t="str">
         <v>Stage_1</v>
@@ -3290,7 +3290,7 @@
         <v>audioclip_sfx_h0208_jp.ab</v>
       </c>
       <c r="C145">
-        <v>774137</v>
+        <v>774135</v>
       </c>
       <c r="D145" t="str">
         <v>Stage_1</v>
@@ -3310,7 +3310,7 @@
         <v>audioclip_sfx_h0209_jp.ab</v>
       </c>
       <c r="C146">
-        <v>1046540</v>
+        <v>1046541</v>
       </c>
       <c r="D146" t="str">
         <v>Stage_1</v>
@@ -3390,7 +3390,7 @@
         <v>audioclip_sfx_h0216_jp.ab</v>
       </c>
       <c r="C150">
-        <v>1220952</v>
+        <v>1220953</v>
       </c>
       <c r="D150" t="str">
         <v>Stage_1</v>
@@ -3470,7 +3470,7 @@
         <v>audioclip_sfx_h0221_jp.ab</v>
       </c>
       <c r="C154">
-        <v>1054459</v>
+        <v>1054460</v>
       </c>
       <c r="D154" t="str">
         <v>Stage_1</v>
@@ -3490,7 +3490,7 @@
         <v>audioclip_sfx_h0224_jp.ab</v>
       </c>
       <c r="C155">
-        <v>1031308</v>
+        <v>1031309</v>
       </c>
       <c r="D155" t="str">
         <v>Stage_1</v>
@@ -3510,7 +3510,7 @@
         <v>audioclip_sfx_h0226_jp.ab</v>
       </c>
       <c r="C156">
-        <v>1134473</v>
+        <v>1134470</v>
       </c>
       <c r="D156" t="str">
         <v>Stage_1</v>
@@ -3570,7 +3570,7 @@
         <v>audioclip_sfx_h0232_jp.ab</v>
       </c>
       <c r="C159">
-        <v>1390239</v>
+        <v>1390240</v>
       </c>
       <c r="D159" t="str">
         <v>Stage_1</v>
@@ -3590,7 +3590,7 @@
         <v>audioclip_sfx_h0233_jp.ab</v>
       </c>
       <c r="C160">
-        <v>1911212</v>
+        <v>1911213</v>
       </c>
       <c r="D160" t="str">
         <v>Stage_1</v>
@@ -3650,7 +3650,7 @@
         <v>audioclip_sfx_h0236_jp.ab</v>
       </c>
       <c r="C163">
-        <v>2245980</v>
+        <v>2245978</v>
       </c>
       <c r="D163" t="str">
         <v>Stage_1</v>
@@ -3670,7 +3670,7 @@
         <v>audioclip_sfx_h0237_jp.ab</v>
       </c>
       <c r="C164">
-        <v>2431132</v>
+        <v>2431131</v>
       </c>
       <c r="D164" t="str">
         <v>Stage_1</v>
@@ -3730,7 +3730,7 @@
         <v>audioclip_sfx_h0240_jp.ab</v>
       </c>
       <c r="C167">
-        <v>924349</v>
+        <v>924348</v>
       </c>
       <c r="D167" t="str">
         <v>Stage_1</v>
@@ -3750,7 +3750,7 @@
         <v>audioclip_sfx_h0241_jp.ab</v>
       </c>
       <c r="C168">
-        <v>1125056</v>
+        <v>1125057</v>
       </c>
       <c r="D168" t="str">
         <v>Stage_1</v>
@@ -3830,7 +3830,7 @@
         <v>audioclip_sfx_h0247_jp.ab</v>
       </c>
       <c r="C172">
-        <v>939767</v>
+        <v>939768</v>
       </c>
       <c r="D172" t="str">
         <v>Stage_1</v>
@@ -3850,7 +3850,7 @@
         <v>audioclip_sfx_h0248_jp.ab</v>
       </c>
       <c r="C173">
-        <v>1234716</v>
+        <v>1234718</v>
       </c>
       <c r="D173" t="str">
         <v>Stage_1</v>
@@ -3870,7 +3870,7 @@
         <v>audioclip_sfx_h0249_jp.ab</v>
       </c>
       <c r="C174">
-        <v>899109</v>
+        <v>899106</v>
       </c>
       <c r="D174" t="str">
         <v>Stage_1</v>
@@ -3890,7 +3890,7 @@
         <v>audioclip_sfx_h0253_jp.ab</v>
       </c>
       <c r="C175">
-        <v>1011101</v>
+        <v>1011102</v>
       </c>
       <c r="D175" t="str">
         <v>Stage_1</v>
@@ -3970,7 +3970,7 @@
         <v>audioclip_sfx_h0259_jp.ab</v>
       </c>
       <c r="C179">
-        <v>1446712</v>
+        <v>1446713</v>
       </c>
       <c r="D179" t="str">
         <v>Stage_1</v>
@@ -4230,7 +4230,7 @@
         <v>audioclip_sfx_r0034_jp.ab</v>
       </c>
       <c r="C192">
-        <v>1390722</v>
+        <v>1390720</v>
       </c>
       <c r="D192" t="str">
         <v>Stage_1</v>
@@ -4250,7 +4250,7 @@
         <v>audioclip_sfx_r0160_jp.ab</v>
       </c>
       <c r="C193">
-        <v>4141827</v>
+        <v>4141826</v>
       </c>
       <c r="D193" t="str">
         <v>Stage_1</v>
@@ -4310,7 +4310,7 @@
         <v>audioclip_sfx_t0017_jp.ab</v>
       </c>
       <c r="C196">
-        <v>883185</v>
+        <v>883191</v>
       </c>
       <c r="D196" t="str">
         <v>Stage_1</v>
@@ -4330,7 +4330,7 @@
         <v>audioclip_sfx_t0026_jp.ab</v>
       </c>
       <c r="C197">
-        <v>903966</v>
+        <v>903967</v>
       </c>
       <c r="D197" t="str">
         <v>Stage_1</v>
@@ -4370,7 +4370,7 @@
         <v>audioclip_sfx_t0032_jp.ab</v>
       </c>
       <c r="C199">
-        <v>995097</v>
+        <v>995099</v>
       </c>
       <c r="D199" t="str">
         <v>Stage_1</v>
@@ -4450,7 +4450,7 @@
         <v>audioclip_sfx_t0049_jp.ab</v>
       </c>
       <c r="C203">
-        <v>1950974</v>
+        <v>1950972</v>
       </c>
       <c r="D203" t="str">
         <v>Stage_1</v>
@@ -4470,7 +4470,7 @@
         <v>audioclip_sfx_t0153_jp.ab</v>
       </c>
       <c r="C204">
-        <v>2974172</v>
+        <v>2974171</v>
       </c>
       <c r="D204" t="str">
         <v>Stage_1</v>
@@ -4510,7 +4510,7 @@
         <v>audioclip_sfx_t0156_jp.ab</v>
       </c>
       <c r="C206">
-        <v>2340708</v>
+        <v>2340709</v>
       </c>
       <c r="D206" t="str">
         <v>Stage_1</v>
@@ -4530,7 +4530,7 @@
         <v>audioclip_sfx_t0158_jp.ab</v>
       </c>
       <c r="C207">
-        <v>1950990</v>
+        <v>1950993</v>
       </c>
       <c r="D207" t="str">
         <v>Stage_1</v>
@@ -4670,7 +4670,7 @@
         <v>audioclip_sfx_t0189_jp.ab</v>
       </c>
       <c r="C214">
-        <v>2403908</v>
+        <v>2403911</v>
       </c>
       <c r="D214" t="str">
         <v>Stage_1</v>
@@ -4790,7 +4790,7 @@
         <v>audioclip_sfx_t0222_jp.ab</v>
       </c>
       <c r="C220">
-        <v>781279</v>
+        <v>781280</v>
       </c>
       <c r="D220" t="str">
         <v>Stage_1</v>
@@ -4930,7 +4930,7 @@
         <v>audioclip_sfx_t0246_jp.ab</v>
       </c>
       <c r="C227">
-        <v>890769</v>
+        <v>890771</v>
       </c>
       <c r="D227" t="str">
         <v>Stage_1</v>
@@ -4990,7 +4990,7 @@
         <v>audioclip_sfx_t0252_jp.ab</v>
       </c>
       <c r="C230">
-        <v>2885316</v>
+        <v>2885317</v>
       </c>
       <c r="D230" t="str">
         <v>Stage_1</v>
@@ -5090,7 +5090,7 @@
         <v>audioclip_sfx_t3189_jp.ab</v>
       </c>
       <c r="C235">
-        <v>316226</v>
+        <v>316225</v>
       </c>
       <c r="D235" t="str">
         <v>Stage_1</v>
@@ -5110,7 +5110,7 @@
         <v>audioclip_sfx_t3191_jp.ab</v>
       </c>
       <c r="C236">
-        <v>164050</v>
+        <v>164051</v>
       </c>
       <c r="D236" t="str">
         <v>Stage_1</v>
@@ -5170,7 +5170,7 @@
         <v>audioclip_sfx_t3403_jp.ab</v>
       </c>
       <c r="C239">
-        <v>288968</v>
+        <v>288969</v>
       </c>
       <c r="D239" t="str">
         <v>Stage_1</v>
@@ -5750,7 +5750,7 @@
         <v>character_largeimage_h0024.ab</v>
       </c>
       <c r="C268">
-        <v>3281918</v>
+        <v>3281917</v>
       </c>
       <c r="D268" t="str">
         <v>Stage_1</v>
@@ -8170,7 +8170,7 @@
         <v>character_largeimage_t0180.ab</v>
       </c>
       <c r="C389">
-        <v>2585586</v>
+        <v>2585585</v>
       </c>
       <c r="D389" t="str">
         <v>Stage_1</v>

--- a/client_gamedata/ios/iosExp.xlsx
+++ b/client_gamedata/ios/iosExp.xlsx
@@ -450,7 +450,7 @@
         <v>audioclip_sfx_10_jp.ab</v>
       </c>
       <c r="C3">
-        <v>61211</v>
+        <v>61210</v>
       </c>
       <c r="D3" t="str">
         <v>Stage_1</v>
@@ -670,7 +670,7 @@
         <v>audioclip_sfx_20_jp.ab</v>
       </c>
       <c r="C14">
-        <v>147265</v>
+        <v>147264</v>
       </c>
       <c r="D14" t="str">
         <v>Stage_1</v>
@@ -1450,7 +1450,7 @@
         <v>audioclip_sfx_b0015_jp.ab</v>
       </c>
       <c r="C53">
-        <v>116861</v>
+        <v>116862</v>
       </c>
       <c r="D53" t="str">
         <v>Stage_1</v>
@@ -1510,7 +1510,7 @@
         <v>audioclip_sfx_b0202_jp.ab</v>
       </c>
       <c r="C56">
-        <v>1272281</v>
+        <v>1272282</v>
       </c>
       <c r="D56" t="str">
         <v>Stage_1</v>
@@ -1570,7 +1570,7 @@
         <v>audioclip_sfx_e0002_jp.ab</v>
       </c>
       <c r="C59">
-        <v>662050</v>
+        <v>662049</v>
       </c>
       <c r="D59" t="str">
         <v>Stage_1</v>
@@ -1590,7 +1590,7 @@
         <v>audioclip_sfx_e0046_jp.ab</v>
       </c>
       <c r="C60">
-        <v>3100225</v>
+        <v>3100224</v>
       </c>
       <c r="D60" t="str">
         <v>Stage_1</v>
@@ -1630,7 +1630,7 @@
         <v>audioclip_sfx_e3497_jp.ab</v>
       </c>
       <c r="C62">
-        <v>250850</v>
+        <v>250849</v>
       </c>
       <c r="D62" t="str">
         <v>Stage_1</v>
@@ -1770,7 +1770,7 @@
         <v>audioclip_sfx_h0006_jp.ab</v>
       </c>
       <c r="C69">
-        <v>1013616</v>
+        <v>1013615</v>
       </c>
       <c r="D69" t="str">
         <v>Stage_1</v>
@@ -1830,7 +1830,7 @@
         <v>audioclip_sfx_h0009_jp.ab</v>
       </c>
       <c r="C72">
-        <v>453782</v>
+        <v>453780</v>
       </c>
       <c r="D72" t="str">
         <v>Stage_1</v>
@@ -1870,7 +1870,7 @@
         <v>audioclip_sfx_h0012_jp.ab</v>
       </c>
       <c r="C74">
-        <v>740114</v>
+        <v>740117</v>
       </c>
       <c r="D74" t="str">
         <v>Stage_1</v>
@@ -1890,7 +1890,7 @@
         <v>audioclip_sfx_h0013_jp.ab</v>
       </c>
       <c r="C75">
-        <v>940883</v>
+        <v>940881</v>
       </c>
       <c r="D75" t="str">
         <v>Stage_1</v>
@@ -1910,7 +1910,7 @@
         <v>audioclip_sfx_h0014_jp.ab</v>
       </c>
       <c r="C76">
-        <v>446594</v>
+        <v>446591</v>
       </c>
       <c r="D76" t="str">
         <v>Stage_1</v>
@@ -1930,7 +1930,7 @@
         <v>audioclip_sfx_h0016_jp.ab</v>
       </c>
       <c r="C77">
-        <v>698680</v>
+        <v>698679</v>
       </c>
       <c r="D77" t="str">
         <v>Stage_1</v>
@@ -1950,7 +1950,7 @@
         <v>audioclip_sfx_h0018_jp.ab</v>
       </c>
       <c r="C78">
-        <v>891814</v>
+        <v>891813</v>
       </c>
       <c r="D78" t="str">
         <v>Stage_1</v>
@@ -1990,7 +1990,7 @@
         <v>audioclip_sfx_h0021_jp.ab</v>
       </c>
       <c r="C80">
-        <v>1196249</v>
+        <v>1196247</v>
       </c>
       <c r="D80" t="str">
         <v>Stage_1</v>
@@ -2030,7 +2030,7 @@
         <v>audioclip_sfx_h0023_jp.ab</v>
       </c>
       <c r="C82">
-        <v>1374151</v>
+        <v>1374152</v>
       </c>
       <c r="D82" t="str">
         <v>Stage_1</v>
@@ -2050,7 +2050,7 @@
         <v>audioclip_sfx_h0024_jp.ab</v>
       </c>
       <c r="C83">
-        <v>1572146</v>
+        <v>1572148</v>
       </c>
       <c r="D83" t="str">
         <v>Stage_1</v>
@@ -2070,7 +2070,7 @@
         <v>audioclip_sfx_h0025_jp.ab</v>
       </c>
       <c r="C84">
-        <v>938020</v>
+        <v>938018</v>
       </c>
       <c r="D84" t="str">
         <v>Stage_1</v>
@@ -2090,7 +2090,7 @@
         <v>audioclip_sfx_h0029_jp.ab</v>
       </c>
       <c r="C85">
-        <v>1291354</v>
+        <v>1291353</v>
       </c>
       <c r="D85" t="str">
         <v>Stage_1</v>
@@ -2110,7 +2110,7 @@
         <v>audioclip_sfx_h0030_jp.ab</v>
       </c>
       <c r="C86">
-        <v>1189229</v>
+        <v>1189228</v>
       </c>
       <c r="D86" t="str">
         <v>Stage_1</v>
@@ -2130,7 +2130,7 @@
         <v>audioclip_sfx_h0031_jp.ab</v>
       </c>
       <c r="C87">
-        <v>1039749</v>
+        <v>1039750</v>
       </c>
       <c r="D87" t="str">
         <v>Stage_1</v>
@@ -2170,7 +2170,7 @@
         <v>audioclip_sfx_h0036_jp.ab</v>
       </c>
       <c r="C89">
-        <v>743617</v>
+        <v>743620</v>
       </c>
       <c r="D89" t="str">
         <v>Stage_1</v>
@@ -2190,7 +2190,7 @@
         <v>audioclip_sfx_h0038_jp.ab</v>
       </c>
       <c r="C90">
-        <v>611357</v>
+        <v>611358</v>
       </c>
       <c r="D90" t="str">
         <v>Stage_1</v>
@@ -2250,7 +2250,7 @@
         <v>audioclip_sfx_h0042_jp.ab</v>
       </c>
       <c r="C93">
-        <v>955385</v>
+        <v>955386</v>
       </c>
       <c r="D93" t="str">
         <v>Stage_1</v>
@@ -2270,7 +2270,7 @@
         <v>audioclip_sfx_h0043_jp.ab</v>
       </c>
       <c r="C94">
-        <v>2421241</v>
+        <v>2421243</v>
       </c>
       <c r="D94" t="str">
         <v>Stage_1</v>
@@ -2350,7 +2350,7 @@
         <v>audioclip_sfx_h0048_jp.ab</v>
       </c>
       <c r="C98">
-        <v>1635041</v>
+        <v>1635039</v>
       </c>
       <c r="D98" t="str">
         <v>Stage_1</v>
@@ -2390,7 +2390,7 @@
         <v>audioclip_sfx_h0097_jp.ab</v>
       </c>
       <c r="C100">
-        <v>2057511</v>
+        <v>2057508</v>
       </c>
       <c r="D100" t="str">
         <v>Stage_1</v>
@@ -2430,7 +2430,7 @@
         <v>audioclip_sfx_h0133_jp.ab</v>
       </c>
       <c r="C102">
-        <v>1334024</v>
+        <v>1334023</v>
       </c>
       <c r="D102" t="str">
         <v>Stage_1</v>
@@ -2450,7 +2450,7 @@
         <v>audioclip_sfx_h0134_jp.ab</v>
       </c>
       <c r="C103">
-        <v>1204318</v>
+        <v>1204319</v>
       </c>
       <c r="D103" t="str">
         <v>Stage_1</v>
@@ -2490,7 +2490,7 @@
         <v>audioclip_sfx_h0136_jp.ab</v>
       </c>
       <c r="C105">
-        <v>1316078</v>
+        <v>1316076</v>
       </c>
       <c r="D105" t="str">
         <v>Stage_1</v>
@@ -2510,7 +2510,7 @@
         <v>audioclip_sfx_h0137_jp.ab</v>
       </c>
       <c r="C106">
-        <v>2046305</v>
+        <v>2046304</v>
       </c>
       <c r="D106" t="str">
         <v>Stage_1</v>
@@ -2570,7 +2570,7 @@
         <v>audioclip_sfx_h0151_jp.ab</v>
       </c>
       <c r="C109">
-        <v>1924706</v>
+        <v>1924705</v>
       </c>
       <c r="D109" t="str">
         <v>Stage_1</v>
@@ -2590,7 +2590,7 @@
         <v>audioclip_sfx_h0152_jp.ab</v>
       </c>
       <c r="C110">
-        <v>1987359</v>
+        <v>1987360</v>
       </c>
       <c r="D110" t="str">
         <v>Stage_1</v>
@@ -2650,7 +2650,7 @@
         <v>audioclip_sfx_h0159_jp.ab</v>
       </c>
       <c r="C113">
-        <v>1893112</v>
+        <v>1893113</v>
       </c>
       <c r="D113" t="str">
         <v>Stage_1</v>
@@ -2670,7 +2670,7 @@
         <v>audioclip_sfx_h0161_jp.ab</v>
       </c>
       <c r="C114">
-        <v>1944102</v>
+        <v>1944101</v>
       </c>
       <c r="D114" t="str">
         <v>Stage_1</v>
@@ -2690,7 +2690,7 @@
         <v>audioclip_sfx_h0163_jp.ab</v>
       </c>
       <c r="C115">
-        <v>1305069</v>
+        <v>1305067</v>
       </c>
       <c r="D115" t="str">
         <v>Stage_1</v>
@@ -2710,7 +2710,7 @@
         <v>audioclip_sfx_h0164_jp.ab</v>
       </c>
       <c r="C116">
-        <v>966705</v>
+        <v>966707</v>
       </c>
       <c r="D116" t="str">
         <v>Stage_1</v>
@@ -2730,7 +2730,7 @@
         <v>audioclip_sfx_h0165_jp.ab</v>
       </c>
       <c r="C117">
-        <v>1022204</v>
+        <v>1022205</v>
       </c>
       <c r="D117" t="str">
         <v>Stage_1</v>
@@ -2750,7 +2750,7 @@
         <v>audioclip_sfx_h0166_jp.ab</v>
       </c>
       <c r="C118">
-        <v>735096</v>
+        <v>735094</v>
       </c>
       <c r="D118" t="str">
         <v>Stage_1</v>
@@ -2810,7 +2810,7 @@
         <v>audioclip_sfx_h0169_jp.ab</v>
       </c>
       <c r="C121">
-        <v>929593</v>
+        <v>929592</v>
       </c>
       <c r="D121" t="str">
         <v>Stage_1</v>
@@ -2830,7 +2830,7 @@
         <v>audioclip_sfx_h0170_jp.ab</v>
       </c>
       <c r="C122">
-        <v>1438190</v>
+        <v>1438191</v>
       </c>
       <c r="D122" t="str">
         <v>Stage_1</v>
@@ -2850,7 +2850,7 @@
         <v>audioclip_sfx_h0171_jp.ab</v>
       </c>
       <c r="C123">
-        <v>1738273</v>
+        <v>1738274</v>
       </c>
       <c r="D123" t="str">
         <v>Stage_1</v>
@@ -2890,7 +2890,7 @@
         <v>audioclip_sfx_h0174_jp.ab</v>
       </c>
       <c r="C125">
-        <v>1668215</v>
+        <v>1668214</v>
       </c>
       <c r="D125" t="str">
         <v>Stage_1</v>
@@ -2970,7 +2970,7 @@
         <v>audioclip_sfx_h0179_jp.ab</v>
       </c>
       <c r="C129">
-        <v>1837986</v>
+        <v>1837987</v>
       </c>
       <c r="D129" t="str">
         <v>Stage_1</v>
@@ -2990,7 +2990,7 @@
         <v>audioclip_sfx_h0183_jp.ab</v>
       </c>
       <c r="C130">
-        <v>2327471</v>
+        <v>2327470</v>
       </c>
       <c r="D130" t="str">
         <v>Stage_1</v>
@@ -3010,7 +3010,7 @@
         <v>audioclip_sfx_h0185_jp.ab</v>
       </c>
       <c r="C131">
-        <v>1563971</v>
+        <v>1563967</v>
       </c>
       <c r="D131" t="str">
         <v>Stage_1</v>
@@ -3030,7 +3030,7 @@
         <v>audioclip_sfx_h0186_jp.ab</v>
       </c>
       <c r="C132">
-        <v>1892917</v>
+        <v>1892918</v>
       </c>
       <c r="D132" t="str">
         <v>Stage_1</v>
@@ -3050,7 +3050,7 @@
         <v>audioclip_sfx_h0190_jp.ab</v>
       </c>
       <c r="C133">
-        <v>2643056</v>
+        <v>2643059</v>
       </c>
       <c r="D133" t="str">
         <v>Stage_1</v>
@@ -3250,7 +3250,7 @@
         <v>audioclip_sfx_h0201_jp.ab</v>
       </c>
       <c r="C143">
-        <v>810575</v>
+        <v>810576</v>
       </c>
       <c r="D143" t="str">
         <v>Stage_1</v>
@@ -3310,7 +3310,7 @@
         <v>audioclip_sfx_h0209_jp.ab</v>
       </c>
       <c r="C146">
-        <v>1046541</v>
+        <v>1046540</v>
       </c>
       <c r="D146" t="str">
         <v>Stage_1</v>
@@ -3370,7 +3370,7 @@
         <v>audioclip_sfx_h0215_jp.ab</v>
       </c>
       <c r="C149">
-        <v>1225722</v>
+        <v>1225724</v>
       </c>
       <c r="D149" t="str">
         <v>Stage_1</v>
@@ -3390,7 +3390,7 @@
         <v>audioclip_sfx_h0216_jp.ab</v>
       </c>
       <c r="C150">
-        <v>1220953</v>
+        <v>1220952</v>
       </c>
       <c r="D150" t="str">
         <v>Stage_1</v>
@@ -3430,7 +3430,7 @@
         <v>audioclip_sfx_h0219_jp.ab</v>
       </c>
       <c r="C152">
-        <v>977561</v>
+        <v>977562</v>
       </c>
       <c r="D152" t="str">
         <v>Stage_1</v>
@@ -3490,7 +3490,7 @@
         <v>audioclip_sfx_h0224_jp.ab</v>
       </c>
       <c r="C155">
-        <v>1031309</v>
+        <v>1031308</v>
       </c>
       <c r="D155" t="str">
         <v>Stage_1</v>
@@ -3550,7 +3550,7 @@
         <v>audioclip_sfx_h0230_jp.ab</v>
       </c>
       <c r="C158">
-        <v>1022961</v>
+        <v>1022962</v>
       </c>
       <c r="D158" t="str">
         <v>Stage_1</v>
@@ -3570,7 +3570,7 @@
         <v>audioclip_sfx_h0232_jp.ab</v>
       </c>
       <c r="C159">
-        <v>1390240</v>
+        <v>1390239</v>
       </c>
       <c r="D159" t="str">
         <v>Stage_1</v>
@@ -3590,7 +3590,7 @@
         <v>audioclip_sfx_h0233_jp.ab</v>
       </c>
       <c r="C160">
-        <v>1911213</v>
+        <v>1911214</v>
       </c>
       <c r="D160" t="str">
         <v>Stage_1</v>
@@ -3630,7 +3630,7 @@
         <v>audioclip_sfx_h0235_jp.ab</v>
       </c>
       <c r="C162">
-        <v>2384176</v>
+        <v>2384177</v>
       </c>
       <c r="D162" t="str">
         <v>Stage_1</v>
@@ -3650,7 +3650,7 @@
         <v>audioclip_sfx_h0236_jp.ab</v>
       </c>
       <c r="C163">
-        <v>2245978</v>
+        <v>2245974</v>
       </c>
       <c r="D163" t="str">
         <v>Stage_1</v>
@@ -3670,7 +3670,7 @@
         <v>audioclip_sfx_h0237_jp.ab</v>
       </c>
       <c r="C164">
-        <v>2431131</v>
+        <v>2431130</v>
       </c>
       <c r="D164" t="str">
         <v>Stage_1</v>
@@ -3730,7 +3730,7 @@
         <v>audioclip_sfx_h0240_jp.ab</v>
       </c>
       <c r="C167">
-        <v>924348</v>
+        <v>924349</v>
       </c>
       <c r="D167" t="str">
         <v>Stage_1</v>
@@ -3750,7 +3750,7 @@
         <v>audioclip_sfx_h0241_jp.ab</v>
       </c>
       <c r="C168">
-        <v>1125057</v>
+        <v>1125056</v>
       </c>
       <c r="D168" t="str">
         <v>Stage_1</v>
@@ -3790,7 +3790,7 @@
         <v>audioclip_sfx_h0244_jp.ab</v>
       </c>
       <c r="C170">
-        <v>1110559</v>
+        <v>1110561</v>
       </c>
       <c r="D170" t="str">
         <v>Stage_1</v>
@@ -3870,7 +3870,7 @@
         <v>audioclip_sfx_h0249_jp.ab</v>
       </c>
       <c r="C174">
-        <v>899106</v>
+        <v>899107</v>
       </c>
       <c r="D174" t="str">
         <v>Stage_1</v>
@@ -3890,7 +3890,7 @@
         <v>audioclip_sfx_h0253_jp.ab</v>
       </c>
       <c r="C175">
-        <v>1011102</v>
+        <v>1011101</v>
       </c>
       <c r="D175" t="str">
         <v>Stage_1</v>
@@ -3950,7 +3950,7 @@
         <v>audioclip_sfx_h0257_jp.ab</v>
       </c>
       <c r="C178">
-        <v>1131207</v>
+        <v>1131208</v>
       </c>
       <c r="D178" t="str">
         <v>Stage_1</v>
@@ -3970,7 +3970,7 @@
         <v>audioclip_sfx_h0259_jp.ab</v>
       </c>
       <c r="C179">
-        <v>1446713</v>
+        <v>1446712</v>
       </c>
       <c r="D179" t="str">
         <v>Stage_1</v>
@@ -3990,7 +3990,7 @@
         <v>audioclip_sfx_h0261_jp.ab</v>
       </c>
       <c r="C180">
-        <v>1220853</v>
+        <v>1220852</v>
       </c>
       <c r="D180" t="str">
         <v>Stage_1</v>
@@ -4230,7 +4230,7 @@
         <v>audioclip_sfx_r0034_jp.ab</v>
       </c>
       <c r="C192">
-        <v>1390720</v>
+        <v>1390719</v>
       </c>
       <c r="D192" t="str">
         <v>Stage_1</v>
@@ -4250,7 +4250,7 @@
         <v>audioclip_sfx_r0160_jp.ab</v>
       </c>
       <c r="C193">
-        <v>4141826</v>
+        <v>4141828</v>
       </c>
       <c r="D193" t="str">
         <v>Stage_1</v>
@@ -4310,7 +4310,7 @@
         <v>audioclip_sfx_t0017_jp.ab</v>
       </c>
       <c r="C196">
-        <v>883191</v>
+        <v>883190</v>
       </c>
       <c r="D196" t="str">
         <v>Stage_1</v>
@@ -4350,7 +4350,7 @@
         <v>audioclip_sfx_t0027_jp.ab</v>
       </c>
       <c r="C198">
-        <v>1396256</v>
+        <v>1396255</v>
       </c>
       <c r="D198" t="str">
         <v>Stage_1</v>
@@ -4370,7 +4370,7 @@
         <v>audioclip_sfx_t0032_jp.ab</v>
       </c>
       <c r="C199">
-        <v>995099</v>
+        <v>995097</v>
       </c>
       <c r="D199" t="str">
         <v>Stage_1</v>
@@ -4450,7 +4450,7 @@
         <v>audioclip_sfx_t0049_jp.ab</v>
       </c>
       <c r="C203">
-        <v>1950972</v>
+        <v>1950975</v>
       </c>
       <c r="D203" t="str">
         <v>Stage_1</v>
@@ -4470,7 +4470,7 @@
         <v>audioclip_sfx_t0153_jp.ab</v>
       </c>
       <c r="C204">
-        <v>2974171</v>
+        <v>2974173</v>
       </c>
       <c r="D204" t="str">
         <v>Stage_1</v>
@@ -4490,7 +4490,7 @@
         <v>audioclip_sfx_t0155_jp.ab</v>
       </c>
       <c r="C205">
-        <v>1992961</v>
+        <v>1992960</v>
       </c>
       <c r="D205" t="str">
         <v>Stage_1</v>
@@ -4510,7 +4510,7 @@
         <v>audioclip_sfx_t0156_jp.ab</v>
       </c>
       <c r="C206">
-        <v>2340709</v>
+        <v>2340708</v>
       </c>
       <c r="D206" t="str">
         <v>Stage_1</v>
@@ -4530,7 +4530,7 @@
         <v>audioclip_sfx_t0158_jp.ab</v>
       </c>
       <c r="C207">
-        <v>1950993</v>
+        <v>1950996</v>
       </c>
       <c r="D207" t="str">
         <v>Stage_1</v>
@@ -4550,7 +4550,7 @@
         <v>audioclip_sfx_t0180_jp.ab</v>
       </c>
       <c r="C208">
-        <v>2527578</v>
+        <v>2527577</v>
       </c>
       <c r="D208" t="str">
         <v>Stage_1</v>
@@ -4570,7 +4570,7 @@
         <v>audioclip_sfx_t0181_jp.ab</v>
       </c>
       <c r="C209">
-        <v>2120059</v>
+        <v>2120060</v>
       </c>
       <c r="D209" t="str">
         <v>Stage_1</v>
@@ -4590,7 +4590,7 @@
         <v>audioclip_sfx_t0182_jp.ab</v>
       </c>
       <c r="C210">
-        <v>1952766</v>
+        <v>1952767</v>
       </c>
       <c r="D210" t="str">
         <v>Stage_1</v>
@@ -4670,7 +4670,7 @@
         <v>audioclip_sfx_t0189_jp.ab</v>
       </c>
       <c r="C214">
-        <v>2403911</v>
+        <v>2403908</v>
       </c>
       <c r="D214" t="str">
         <v>Stage_1</v>
@@ -4790,7 +4790,7 @@
         <v>audioclip_sfx_t0222_jp.ab</v>
       </c>
       <c r="C220">
-        <v>781280</v>
+        <v>781279</v>
       </c>
       <c r="D220" t="str">
         <v>Stage_1</v>
@@ -4870,7 +4870,7 @@
         <v>audioclip_sfx_t0229_jp.ab</v>
       </c>
       <c r="C224">
-        <v>1117663</v>
+        <v>1117664</v>
       </c>
       <c r="D224" t="str">
         <v>Stage_1</v>
@@ -4890,7 +4890,7 @@
         <v>audioclip_sfx_t0231_jp.ab</v>
       </c>
       <c r="C225">
-        <v>1242758</v>
+        <v>1242757</v>
       </c>
       <c r="D225" t="str">
         <v>Stage_1</v>
@@ -4910,7 +4910,7 @@
         <v>audioclip_sfx_t0242_jp.ab</v>
       </c>
       <c r="C226">
-        <v>955690</v>
+        <v>955689</v>
       </c>
       <c r="D226" t="str">
         <v>Stage_1</v>
@@ -4990,7 +4990,7 @@
         <v>audioclip_sfx_t0252_jp.ab</v>
       </c>
       <c r="C230">
-        <v>2885317</v>
+        <v>2885316</v>
       </c>
       <c r="D230" t="str">
         <v>Stage_1</v>
@@ -5170,7 +5170,7 @@
         <v>audioclip_sfx_t3403_jp.ab</v>
       </c>
       <c r="C239">
-        <v>288969</v>
+        <v>288968</v>
       </c>
       <c r="D239" t="str">
         <v>Stage_1</v>
@@ -5190,7 +5190,7 @@
         <v>audioclip_sfx_t3407_jp.ab</v>
       </c>
       <c r="C240">
-        <v>270580</v>
+        <v>270581</v>
       </c>
       <c r="D240" t="str">
         <v>Stage_1</v>
@@ -5410,7 +5410,7 @@
         <v>character_largeimage_h0003.ab</v>
       </c>
       <c r="C251">
-        <v>3975188</v>
+        <v>3975187</v>
       </c>
       <c r="D251" t="str">
         <v>Stage_1</v>
@@ -5790,7 +5790,7 @@
         <v>character_largeimage_h0029.ab</v>
       </c>
       <c r="C270">
-        <v>3878946</v>
+        <v>3878944</v>
       </c>
       <c r="D270" t="str">
         <v>Stage_1</v>
@@ -8170,7 +8170,7 @@
         <v>character_largeimage_t0180.ab</v>
       </c>
       <c r="C389">
-        <v>2585585</v>
+        <v>2585586</v>
       </c>
       <c r="D389" t="str">
         <v>Stage_1</v>

--- a/client_gamedata/ios/iosExp.xlsx
+++ b/client_gamedata/ios/iosExp.xlsx
@@ -1190,7 +1190,7 @@
         <v>audioclip_sfx_44_jp.ab</v>
       </c>
       <c r="C40">
-        <v>123386</v>
+        <v>123385</v>
       </c>
       <c r="D40" t="str">
         <v>Stage_1</v>
@@ -1450,7 +1450,7 @@
         <v>audioclip_sfx_b0015_jp.ab</v>
       </c>
       <c r="C53">
-        <v>116862</v>
+        <v>116863</v>
       </c>
       <c r="D53" t="str">
         <v>Stage_1</v>
@@ -1510,7 +1510,7 @@
         <v>audioclip_sfx_b0202_jp.ab</v>
       </c>
       <c r="C56">
-        <v>1272282</v>
+        <v>1272281</v>
       </c>
       <c r="D56" t="str">
         <v>Stage_1</v>
@@ -1570,7 +1570,7 @@
         <v>audioclip_sfx_e0002_jp.ab</v>
       </c>
       <c r="C59">
-        <v>662049</v>
+        <v>662050</v>
       </c>
       <c r="D59" t="str">
         <v>Stage_1</v>
@@ -1790,7 +1790,7 @@
         <v>audioclip_sfx_h0007_jp.ab</v>
       </c>
       <c r="C70">
-        <v>678623</v>
+        <v>678622</v>
       </c>
       <c r="D70" t="str">
         <v>Stage_1</v>
@@ -1810,7 +1810,7 @@
         <v>audioclip_sfx_h0008_jp.ab</v>
       </c>
       <c r="C71">
-        <v>349413</v>
+        <v>349414</v>
       </c>
       <c r="D71" t="str">
         <v>Stage_1</v>
@@ -1830,7 +1830,7 @@
         <v>audioclip_sfx_h0009_jp.ab</v>
       </c>
       <c r="C72">
-        <v>453780</v>
+        <v>453781</v>
       </c>
       <c r="D72" t="str">
         <v>Stage_1</v>
@@ -1870,7 +1870,7 @@
         <v>audioclip_sfx_h0012_jp.ab</v>
       </c>
       <c r="C74">
-        <v>740117</v>
+        <v>740115</v>
       </c>
       <c r="D74" t="str">
         <v>Stage_1</v>
@@ -1910,7 +1910,7 @@
         <v>audioclip_sfx_h0014_jp.ab</v>
       </c>
       <c r="C76">
-        <v>446591</v>
+        <v>446593</v>
       </c>
       <c r="D76" t="str">
         <v>Stage_1</v>
@@ -1990,7 +1990,7 @@
         <v>audioclip_sfx_h0021_jp.ab</v>
       </c>
       <c r="C80">
-        <v>1196247</v>
+        <v>1196248</v>
       </c>
       <c r="D80" t="str">
         <v>Stage_1</v>
@@ -2030,7 +2030,7 @@
         <v>audioclip_sfx_h0023_jp.ab</v>
       </c>
       <c r="C82">
-        <v>1374152</v>
+        <v>1374151</v>
       </c>
       <c r="D82" t="str">
         <v>Stage_1</v>
@@ -2050,7 +2050,7 @@
         <v>audioclip_sfx_h0024_jp.ab</v>
       </c>
       <c r="C83">
-        <v>1572148</v>
+        <v>1572146</v>
       </c>
       <c r="D83" t="str">
         <v>Stage_1</v>
@@ -2110,7 +2110,7 @@
         <v>audioclip_sfx_h0030_jp.ab</v>
       </c>
       <c r="C86">
-        <v>1189228</v>
+        <v>1189230</v>
       </c>
       <c r="D86" t="str">
         <v>Stage_1</v>
@@ -2130,7 +2130,7 @@
         <v>audioclip_sfx_h0031_jp.ab</v>
       </c>
       <c r="C87">
-        <v>1039750</v>
+        <v>1039749</v>
       </c>
       <c r="D87" t="str">
         <v>Stage_1</v>
@@ -2170,7 +2170,7 @@
         <v>audioclip_sfx_h0036_jp.ab</v>
       </c>
       <c r="C89">
-        <v>743620</v>
+        <v>743619</v>
       </c>
       <c r="D89" t="str">
         <v>Stage_1</v>
@@ -2190,7 +2190,7 @@
         <v>audioclip_sfx_h0038_jp.ab</v>
       </c>
       <c r="C90">
-        <v>611358</v>
+        <v>611356</v>
       </c>
       <c r="D90" t="str">
         <v>Stage_1</v>
@@ -2290,7 +2290,7 @@
         <v>audioclip_sfx_h0044_jp.ab</v>
       </c>
       <c r="C95">
-        <v>619212</v>
+        <v>619213</v>
       </c>
       <c r="D95" t="str">
         <v>Stage_1</v>
@@ -2350,7 +2350,7 @@
         <v>audioclip_sfx_h0048_jp.ab</v>
       </c>
       <c r="C98">
-        <v>1635039</v>
+        <v>1635041</v>
       </c>
       <c r="D98" t="str">
         <v>Stage_1</v>
@@ -2390,7 +2390,7 @@
         <v>audioclip_sfx_h0097_jp.ab</v>
       </c>
       <c r="C100">
-        <v>2057508</v>
+        <v>2057511</v>
       </c>
       <c r="D100" t="str">
         <v>Stage_1</v>
@@ -2430,7 +2430,7 @@
         <v>audioclip_sfx_h0133_jp.ab</v>
       </c>
       <c r="C102">
-        <v>1334023</v>
+        <v>1334024</v>
       </c>
       <c r="D102" t="str">
         <v>Stage_1</v>
@@ -2490,7 +2490,7 @@
         <v>audioclip_sfx_h0136_jp.ab</v>
       </c>
       <c r="C105">
-        <v>1316076</v>
+        <v>1316078</v>
       </c>
       <c r="D105" t="str">
         <v>Stage_1</v>
@@ -2530,7 +2530,7 @@
         <v>audioclip_sfx_h0138_jp.ab</v>
       </c>
       <c r="C107">
-        <v>1236790</v>
+        <v>1236789</v>
       </c>
       <c r="D107" t="str">
         <v>Stage_1</v>
@@ -2550,7 +2550,7 @@
         <v>audioclip_sfx_h0150_jp.ab</v>
       </c>
       <c r="C108">
-        <v>2757249</v>
+        <v>2757248</v>
       </c>
       <c r="D108" t="str">
         <v>Stage_1</v>
@@ -2570,7 +2570,7 @@
         <v>audioclip_sfx_h0151_jp.ab</v>
       </c>
       <c r="C109">
-        <v>1924705</v>
+        <v>1924708</v>
       </c>
       <c r="D109" t="str">
         <v>Stage_1</v>
@@ -2590,7 +2590,7 @@
         <v>audioclip_sfx_h0152_jp.ab</v>
       </c>
       <c r="C110">
-        <v>1987360</v>
+        <v>1987358</v>
       </c>
       <c r="D110" t="str">
         <v>Stage_1</v>
@@ -2630,7 +2630,7 @@
         <v>audioclip_sfx_h0157_jp.ab</v>
       </c>
       <c r="C112">
-        <v>1681371</v>
+        <v>1681370</v>
       </c>
       <c r="D112" t="str">
         <v>Stage_1</v>
@@ -2650,7 +2650,7 @@
         <v>audioclip_sfx_h0159_jp.ab</v>
       </c>
       <c r="C113">
-        <v>1893113</v>
+        <v>1893115</v>
       </c>
       <c r="D113" t="str">
         <v>Stage_1</v>
@@ -2770,7 +2770,7 @@
         <v>audioclip_sfx_h0167_jp.ab</v>
       </c>
       <c r="C119">
-        <v>884679</v>
+        <v>884678</v>
       </c>
       <c r="D119" t="str">
         <v>Stage_1</v>
@@ -2810,7 +2810,7 @@
         <v>audioclip_sfx_h0169_jp.ab</v>
       </c>
       <c r="C121">
-        <v>929592</v>
+        <v>929591</v>
       </c>
       <c r="D121" t="str">
         <v>Stage_1</v>
@@ -2830,7 +2830,7 @@
         <v>audioclip_sfx_h0170_jp.ab</v>
       </c>
       <c r="C122">
-        <v>1438191</v>
+        <v>1438192</v>
       </c>
       <c r="D122" t="str">
         <v>Stage_1</v>
@@ -2850,7 +2850,7 @@
         <v>audioclip_sfx_h0171_jp.ab</v>
       </c>
       <c r="C123">
-        <v>1738274</v>
+        <v>1738273</v>
       </c>
       <c r="D123" t="str">
         <v>Stage_1</v>
@@ -2910,7 +2910,7 @@
         <v>audioclip_sfx_h0175_jp.ab</v>
       </c>
       <c r="C126">
-        <v>1253486</v>
+        <v>1253487</v>
       </c>
       <c r="D126" t="str">
         <v>Stage_1</v>
@@ -3010,7 +3010,7 @@
         <v>audioclip_sfx_h0185_jp.ab</v>
       </c>
       <c r="C131">
-        <v>1563967</v>
+        <v>1563968</v>
       </c>
       <c r="D131" t="str">
         <v>Stage_1</v>
@@ -3030,7 +3030,7 @@
         <v>audioclip_sfx_h0186_jp.ab</v>
       </c>
       <c r="C132">
-        <v>1892918</v>
+        <v>1892917</v>
       </c>
       <c r="D132" t="str">
         <v>Stage_1</v>
@@ -3050,7 +3050,7 @@
         <v>audioclip_sfx_h0190_jp.ab</v>
       </c>
       <c r="C133">
-        <v>2643059</v>
+        <v>2643057</v>
       </c>
       <c r="D133" t="str">
         <v>Stage_1</v>
@@ -3150,7 +3150,7 @@
         <v>audioclip_sfx_h0196_jp.ab</v>
       </c>
       <c r="C138">
-        <v>1046814</v>
+        <v>1046813</v>
       </c>
       <c r="D138" t="str">
         <v>Stage_1</v>
@@ -3190,7 +3190,7 @@
         <v>audioclip_sfx_h0198_jp.ab</v>
       </c>
       <c r="C140">
-        <v>1081025</v>
+        <v>1081026</v>
       </c>
       <c r="D140" t="str">
         <v>Stage_1</v>
@@ -3290,7 +3290,7 @@
         <v>audioclip_sfx_h0208_jp.ab</v>
       </c>
       <c r="C145">
-        <v>774135</v>
+        <v>774137</v>
       </c>
       <c r="D145" t="str">
         <v>Stage_1</v>
@@ -3310,7 +3310,7 @@
         <v>audioclip_sfx_h0209_jp.ab</v>
       </c>
       <c r="C146">
-        <v>1046540</v>
+        <v>1046541</v>
       </c>
       <c r="D146" t="str">
         <v>Stage_1</v>
@@ -3430,7 +3430,7 @@
         <v>audioclip_sfx_h0219_jp.ab</v>
       </c>
       <c r="C152">
-        <v>977562</v>
+        <v>977561</v>
       </c>
       <c r="D152" t="str">
         <v>Stage_1</v>
@@ -3450,7 +3450,7 @@
         <v>audioclip_sfx_h0220_jp.ab</v>
       </c>
       <c r="C153">
-        <v>1002160</v>
+        <v>1002159</v>
       </c>
       <c r="D153" t="str">
         <v>Stage_1</v>
@@ -3470,7 +3470,7 @@
         <v>audioclip_sfx_h0221_jp.ab</v>
       </c>
       <c r="C154">
-        <v>1054460</v>
+        <v>1054459</v>
       </c>
       <c r="D154" t="str">
         <v>Stage_1</v>
@@ -3490,7 +3490,7 @@
         <v>audioclip_sfx_h0224_jp.ab</v>
       </c>
       <c r="C155">
-        <v>1031308</v>
+        <v>1031309</v>
       </c>
       <c r="D155" t="str">
         <v>Stage_1</v>
@@ -3550,7 +3550,7 @@
         <v>audioclip_sfx_h0230_jp.ab</v>
       </c>
       <c r="C158">
-        <v>1022962</v>
+        <v>1022960</v>
       </c>
       <c r="D158" t="str">
         <v>Stage_1</v>
@@ -3570,7 +3570,7 @@
         <v>audioclip_sfx_h0232_jp.ab</v>
       </c>
       <c r="C159">
-        <v>1390239</v>
+        <v>1390240</v>
       </c>
       <c r="D159" t="str">
         <v>Stage_1</v>
@@ -3590,7 +3590,7 @@
         <v>audioclip_sfx_h0233_jp.ab</v>
       </c>
       <c r="C160">
-        <v>1911214</v>
+        <v>1911213</v>
       </c>
       <c r="D160" t="str">
         <v>Stage_1</v>
@@ -3650,7 +3650,7 @@
         <v>audioclip_sfx_h0236_jp.ab</v>
       </c>
       <c r="C163">
-        <v>2245974</v>
+        <v>2245978</v>
       </c>
       <c r="D163" t="str">
         <v>Stage_1</v>
@@ -3670,7 +3670,7 @@
         <v>audioclip_sfx_h0237_jp.ab</v>
       </c>
       <c r="C164">
-        <v>2431130</v>
+        <v>2431132</v>
       </c>
       <c r="D164" t="str">
         <v>Stage_1</v>
@@ -3690,7 +3690,7 @@
         <v>audioclip_sfx_h0238_jp.ab</v>
       </c>
       <c r="C165">
-        <v>867922</v>
+        <v>867921</v>
       </c>
       <c r="D165" t="str">
         <v>Stage_1</v>
@@ -3710,7 +3710,7 @@
         <v>audioclip_sfx_h0239_jp.ab</v>
       </c>
       <c r="C166">
-        <v>5844653</v>
+        <v>5844651</v>
       </c>
       <c r="D166" t="str">
         <v>Stage_1</v>
@@ -3730,7 +3730,7 @@
         <v>audioclip_sfx_h0240_jp.ab</v>
       </c>
       <c r="C167">
-        <v>924349</v>
+        <v>924348</v>
       </c>
       <c r="D167" t="str">
         <v>Stage_1</v>
@@ -3790,7 +3790,7 @@
         <v>audioclip_sfx_h0244_jp.ab</v>
       </c>
       <c r="C170">
-        <v>1110561</v>
+        <v>1110560</v>
       </c>
       <c r="D170" t="str">
         <v>Stage_1</v>
@@ -3950,7 +3950,7 @@
         <v>audioclip_sfx_h0257_jp.ab</v>
       </c>
       <c r="C178">
-        <v>1131208</v>
+        <v>1131207</v>
       </c>
       <c r="D178" t="str">
         <v>Stage_1</v>
@@ -3970,7 +3970,7 @@
         <v>audioclip_sfx_h0259_jp.ab</v>
       </c>
       <c r="C179">
-        <v>1446712</v>
+        <v>1446713</v>
       </c>
       <c r="D179" t="str">
         <v>Stage_1</v>
@@ -3990,7 +3990,7 @@
         <v>audioclip_sfx_h0261_jp.ab</v>
       </c>
       <c r="C180">
-        <v>1220852</v>
+        <v>1220853</v>
       </c>
       <c r="D180" t="str">
         <v>Stage_1</v>
@@ -4010,7 +4010,7 @@
         <v>audioclip_sfx_h0262_jp.ab</v>
       </c>
       <c r="C181">
-        <v>1140808</v>
+        <v>1140807</v>
       </c>
       <c r="D181" t="str">
         <v>Stage_1</v>
@@ -4130,7 +4130,7 @@
         <v>audioclip_sfx_h0271_jp.ab</v>
       </c>
       <c r="C187">
-        <v>1584336</v>
+        <v>1584334</v>
       </c>
       <c r="D187" t="str">
         <v>Stage_1</v>
@@ -4230,7 +4230,7 @@
         <v>audioclip_sfx_r0034_jp.ab</v>
       </c>
       <c r="C192">
-        <v>1390719</v>
+        <v>1390722</v>
       </c>
       <c r="D192" t="str">
         <v>Stage_1</v>
@@ -4250,7 +4250,7 @@
         <v>audioclip_sfx_r0160_jp.ab</v>
       </c>
       <c r="C193">
-        <v>4141828</v>
+        <v>4141829</v>
       </c>
       <c r="D193" t="str">
         <v>Stage_1</v>
@@ -4270,7 +4270,7 @@
         <v>audioclip_sfx_r0173_jp.ab</v>
       </c>
       <c r="C194">
-        <v>1438364</v>
+        <v>1438365</v>
       </c>
       <c r="D194" t="str">
         <v>Stage_1</v>
@@ -4290,7 +4290,7 @@
         <v>audioclip_sfx_r0205_jp.ab</v>
       </c>
       <c r="C195">
-        <v>1066357</v>
+        <v>1066358</v>
       </c>
       <c r="D195" t="str">
         <v>Stage_1</v>
@@ -4310,7 +4310,7 @@
         <v>audioclip_sfx_t0017_jp.ab</v>
       </c>
       <c r="C196">
-        <v>883190</v>
+        <v>883186</v>
       </c>
       <c r="D196" t="str">
         <v>Stage_1</v>
@@ -4350,7 +4350,7 @@
         <v>audioclip_sfx_t0027_jp.ab</v>
       </c>
       <c r="C198">
-        <v>1396255</v>
+        <v>1396256</v>
       </c>
       <c r="D198" t="str">
         <v>Stage_1</v>
@@ -4370,7 +4370,7 @@
         <v>audioclip_sfx_t0032_jp.ab</v>
       </c>
       <c r="C199">
-        <v>995097</v>
+        <v>995100</v>
       </c>
       <c r="D199" t="str">
         <v>Stage_1</v>
@@ -4470,7 +4470,7 @@
         <v>audioclip_sfx_t0153_jp.ab</v>
       </c>
       <c r="C204">
-        <v>2974173</v>
+        <v>2974171</v>
       </c>
       <c r="D204" t="str">
         <v>Stage_1</v>
@@ -4490,7 +4490,7 @@
         <v>audioclip_sfx_t0155_jp.ab</v>
       </c>
       <c r="C205">
-        <v>1992960</v>
+        <v>1992962</v>
       </c>
       <c r="D205" t="str">
         <v>Stage_1</v>
@@ -4530,7 +4530,7 @@
         <v>audioclip_sfx_t0158_jp.ab</v>
       </c>
       <c r="C207">
-        <v>1950996</v>
+        <v>1950991</v>
       </c>
       <c r="D207" t="str">
         <v>Stage_1</v>
@@ -4550,7 +4550,7 @@
         <v>audioclip_sfx_t0180_jp.ab</v>
       </c>
       <c r="C208">
-        <v>2527577</v>
+        <v>2527578</v>
       </c>
       <c r="D208" t="str">
         <v>Stage_1</v>
@@ -4630,7 +4630,7 @@
         <v>audioclip_sfx_t0187_jp.ab</v>
       </c>
       <c r="C212">
-        <v>2460156</v>
+        <v>2460158</v>
       </c>
       <c r="D212" t="str">
         <v>Stage_1</v>
@@ -4650,7 +4650,7 @@
         <v>audioclip_sfx_t0188_jp.ab</v>
       </c>
       <c r="C213">
-        <v>1973760</v>
+        <v>1973756</v>
       </c>
       <c r="D213" t="str">
         <v>Stage_1</v>
@@ -4670,7 +4670,7 @@
         <v>audioclip_sfx_t0189_jp.ab</v>
       </c>
       <c r="C214">
-        <v>2403908</v>
+        <v>2403910</v>
       </c>
       <c r="D214" t="str">
         <v>Stage_1</v>
@@ -4790,7 +4790,7 @@
         <v>audioclip_sfx_t0222_jp.ab</v>
       </c>
       <c r="C220">
-        <v>781279</v>
+        <v>781278</v>
       </c>
       <c r="D220" t="str">
         <v>Stage_1</v>
@@ -4810,7 +4810,7 @@
         <v>audioclip_sfx_t0223_jp.ab</v>
       </c>
       <c r="C221">
-        <v>988345</v>
+        <v>988344</v>
       </c>
       <c r="D221" t="str">
         <v>Stage_1</v>
@@ -4870,7 +4870,7 @@
         <v>audioclip_sfx_t0229_jp.ab</v>
       </c>
       <c r="C224">
-        <v>1117664</v>
+        <v>1117663</v>
       </c>
       <c r="D224" t="str">
         <v>Stage_1</v>
@@ -4890,7 +4890,7 @@
         <v>audioclip_sfx_t0231_jp.ab</v>
       </c>
       <c r="C225">
-        <v>1242757</v>
+        <v>1242758</v>
       </c>
       <c r="D225" t="str">
         <v>Stage_1</v>
@@ -4930,7 +4930,7 @@
         <v>audioclip_sfx_t0246_jp.ab</v>
       </c>
       <c r="C227">
-        <v>890771</v>
+        <v>890769</v>
       </c>
       <c r="D227" t="str">
         <v>Stage_1</v>
@@ -5110,7 +5110,7 @@
         <v>audioclip_sfx_t3191_jp.ab</v>
       </c>
       <c r="C236">
-        <v>164051</v>
+        <v>164050</v>
       </c>
       <c r="D236" t="str">
         <v>Stage_1</v>
@@ -5130,7 +5130,7 @@
         <v>audioclip_sfx_t3259_jp.ab</v>
       </c>
       <c r="C237">
-        <v>214580</v>
+        <v>214579</v>
       </c>
       <c r="D237" t="str">
         <v>Stage_1</v>
@@ -5410,7 +5410,7 @@
         <v>character_largeimage_h0003.ab</v>
       </c>
       <c r="C251">
-        <v>3975187</v>
+        <v>3975188</v>
       </c>
       <c r="D251" t="str">
         <v>Stage_1</v>
@@ -5750,7 +5750,7 @@
         <v>character_largeimage_h0024.ab</v>
       </c>
       <c r="C268">
-        <v>3281917</v>
+        <v>3281918</v>
       </c>
       <c r="D268" t="str">
         <v>Stage_1</v>
@@ -8170,7 +8170,7 @@
         <v>character_largeimage_t0180.ab</v>
       </c>
       <c r="C389">
-        <v>2585586</v>
+        <v>2585585</v>
       </c>
       <c r="D389" t="str">
         <v>Stage_1</v>

--- a/client_gamedata/ios/iosExp.xlsx
+++ b/client_gamedata/ios/iosExp.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Assets" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Assets!$A$1:$F$417</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Assets!$A$1:$F$421</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F417"/>
+  <dimension ref="A1:F421"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -450,7 +450,7 @@
         <v>audioclip_sfx_10_jp.ab</v>
       </c>
       <c r="C3">
-        <v>61210</v>
+        <v>61211</v>
       </c>
       <c r="D3" t="str">
         <v>Stage_1</v>
@@ -1190,7 +1190,7 @@
         <v>audioclip_sfx_44_jp.ab</v>
       </c>
       <c r="C40">
-        <v>123385</v>
+        <v>123386</v>
       </c>
       <c r="D40" t="str">
         <v>Stage_1</v>
@@ -1450,7 +1450,7 @@
         <v>audioclip_sfx_b0015_jp.ab</v>
       </c>
       <c r="C53">
-        <v>116863</v>
+        <v>116861</v>
       </c>
       <c r="D53" t="str">
         <v>Stage_1</v>
@@ -1470,7 +1470,7 @@
         <v>audioclip_sfx_b0028_jp.ab</v>
       </c>
       <c r="C54">
-        <v>875308</v>
+        <v>875310</v>
       </c>
       <c r="D54" t="str">
         <v>Stage_1</v>
@@ -1490,7 +1490,7 @@
         <v>audioclip_sfx_b0037_jp.ab</v>
       </c>
       <c r="C55">
-        <v>2011714</v>
+        <v>2011713</v>
       </c>
       <c r="D55" t="str">
         <v>Stage_1</v>
@@ -1510,7 +1510,7 @@
         <v>audioclip_sfx_b0202_jp.ab</v>
       </c>
       <c r="C56">
-        <v>1272281</v>
+        <v>1272282</v>
       </c>
       <c r="D56" t="str">
         <v>Stage_1</v>
@@ -1550,7 +1550,7 @@
         <v>audioclip_sfx_b0267_jp.ab</v>
       </c>
       <c r="C58">
-        <v>1368973</v>
+        <v>1368974</v>
       </c>
       <c r="D58" t="str">
         <v>Stage_1</v>
@@ -1770,7 +1770,7 @@
         <v>audioclip_sfx_h0006_jp.ab</v>
       </c>
       <c r="C69">
-        <v>1013615</v>
+        <v>1013618</v>
       </c>
       <c r="D69" t="str">
         <v>Stage_1</v>
@@ -1790,7 +1790,7 @@
         <v>audioclip_sfx_h0007_jp.ab</v>
       </c>
       <c r="C70">
-        <v>678622</v>
+        <v>678624</v>
       </c>
       <c r="D70" t="str">
         <v>Stage_1</v>
@@ -1850,7 +1850,7 @@
         <v>audioclip_sfx_h0010_jp.ab</v>
       </c>
       <c r="C73">
-        <v>1074575</v>
+        <v>1074573</v>
       </c>
       <c r="D73" t="str">
         <v>Stage_1</v>
@@ -1890,7 +1890,7 @@
         <v>audioclip_sfx_h0013_jp.ab</v>
       </c>
       <c r="C75">
-        <v>940881</v>
+        <v>940885</v>
       </c>
       <c r="D75" t="str">
         <v>Stage_1</v>
@@ -1910,7 +1910,7 @@
         <v>audioclip_sfx_h0014_jp.ab</v>
       </c>
       <c r="C76">
-        <v>446593</v>
+        <v>446594</v>
       </c>
       <c r="D76" t="str">
         <v>Stage_1</v>
@@ -2050,7 +2050,7 @@
         <v>audioclip_sfx_h0024_jp.ab</v>
       </c>
       <c r="C83">
-        <v>1572146</v>
+        <v>1572148</v>
       </c>
       <c r="D83" t="str">
         <v>Stage_1</v>
@@ -2070,7 +2070,7 @@
         <v>audioclip_sfx_h0025_jp.ab</v>
       </c>
       <c r="C84">
-        <v>938018</v>
+        <v>938020</v>
       </c>
       <c r="D84" t="str">
         <v>Stage_1</v>
@@ -2110,7 +2110,7 @@
         <v>audioclip_sfx_h0030_jp.ab</v>
       </c>
       <c r="C86">
-        <v>1189230</v>
+        <v>1189227</v>
       </c>
       <c r="D86" t="str">
         <v>Stage_1</v>
@@ -2130,7 +2130,7 @@
         <v>audioclip_sfx_h0031_jp.ab</v>
       </c>
       <c r="C87">
-        <v>1039749</v>
+        <v>1039750</v>
       </c>
       <c r="D87" t="str">
         <v>Stage_1</v>
@@ -2150,7 +2150,7 @@
         <v>audioclip_sfx_h0035_jp.ab</v>
       </c>
       <c r="C88">
-        <v>785946</v>
+        <v>785945</v>
       </c>
       <c r="D88" t="str">
         <v>Stage_1</v>
@@ -2170,7 +2170,7 @@
         <v>audioclip_sfx_h0036_jp.ab</v>
       </c>
       <c r="C89">
-        <v>743619</v>
+        <v>743620</v>
       </c>
       <c r="D89" t="str">
         <v>Stage_1</v>
@@ -2190,7 +2190,7 @@
         <v>audioclip_sfx_h0038_jp.ab</v>
       </c>
       <c r="C90">
-        <v>611356</v>
+        <v>611357</v>
       </c>
       <c r="D90" t="str">
         <v>Stage_1</v>
@@ -2370,7 +2370,7 @@
         <v>audioclip_sfx_h0073_jp.ab</v>
       </c>
       <c r="C99">
-        <v>276295</v>
+        <v>276296</v>
       </c>
       <c r="D99" t="str">
         <v>Stage_1</v>
@@ -2390,7 +2390,7 @@
         <v>audioclip_sfx_h0097_jp.ab</v>
       </c>
       <c r="C100">
-        <v>2057511</v>
+        <v>2057509</v>
       </c>
       <c r="D100" t="str">
         <v>Stage_1</v>
@@ -2430,7 +2430,7 @@
         <v>audioclip_sfx_h0133_jp.ab</v>
       </c>
       <c r="C102">
-        <v>1334024</v>
+        <v>1334023</v>
       </c>
       <c r="D102" t="str">
         <v>Stage_1</v>
@@ -2470,7 +2470,7 @@
         <v>audioclip_sfx_h0135_jp.ab</v>
       </c>
       <c r="C104">
-        <v>2285419</v>
+        <v>2285418</v>
       </c>
       <c r="D104" t="str">
         <v>Stage_1</v>
@@ -2490,7 +2490,7 @@
         <v>audioclip_sfx_h0136_jp.ab</v>
       </c>
       <c r="C105">
-        <v>1316078</v>
+        <v>1316079</v>
       </c>
       <c r="D105" t="str">
         <v>Stage_1</v>
@@ -2530,7 +2530,7 @@
         <v>audioclip_sfx_h0138_jp.ab</v>
       </c>
       <c r="C107">
-        <v>1236789</v>
+        <v>1236791</v>
       </c>
       <c r="D107" t="str">
         <v>Stage_1</v>
@@ -2550,7 +2550,7 @@
         <v>audioclip_sfx_h0150_jp.ab</v>
       </c>
       <c r="C108">
-        <v>2757248</v>
+        <v>2757250</v>
       </c>
       <c r="D108" t="str">
         <v>Stage_1</v>
@@ -2590,7 +2590,7 @@
         <v>audioclip_sfx_h0152_jp.ab</v>
       </c>
       <c r="C110">
-        <v>1987358</v>
+        <v>1987359</v>
       </c>
       <c r="D110" t="str">
         <v>Stage_1</v>
@@ -2650,7 +2650,7 @@
         <v>audioclip_sfx_h0159_jp.ab</v>
       </c>
       <c r="C113">
-        <v>1893115</v>
+        <v>1893112</v>
       </c>
       <c r="D113" t="str">
         <v>Stage_1</v>
@@ -2670,7 +2670,7 @@
         <v>audioclip_sfx_h0161_jp.ab</v>
       </c>
       <c r="C114">
-        <v>1944101</v>
+        <v>1944102</v>
       </c>
       <c r="D114" t="str">
         <v>Stage_1</v>
@@ -2690,7 +2690,7 @@
         <v>audioclip_sfx_h0163_jp.ab</v>
       </c>
       <c r="C115">
-        <v>1305067</v>
+        <v>1305068</v>
       </c>
       <c r="D115" t="str">
         <v>Stage_1</v>
@@ -2770,7 +2770,7 @@
         <v>audioclip_sfx_h0167_jp.ab</v>
       </c>
       <c r="C119">
-        <v>884678</v>
+        <v>884679</v>
       </c>
       <c r="D119" t="str">
         <v>Stage_1</v>
@@ -2790,7 +2790,7 @@
         <v>audioclip_sfx_h0168_jp.ab</v>
       </c>
       <c r="C120">
-        <v>747236</v>
+        <v>747235</v>
       </c>
       <c r="D120" t="str">
         <v>Stage_1</v>
@@ -2850,7 +2850,7 @@
         <v>audioclip_sfx_h0171_jp.ab</v>
       </c>
       <c r="C123">
-        <v>1738273</v>
+        <v>1738274</v>
       </c>
       <c r="D123" t="str">
         <v>Stage_1</v>
@@ -2910,7 +2910,7 @@
         <v>audioclip_sfx_h0175_jp.ab</v>
       </c>
       <c r="C126">
-        <v>1253487</v>
+        <v>1253485</v>
       </c>
       <c r="D126" t="str">
         <v>Stage_1</v>
@@ -2970,7 +2970,7 @@
         <v>audioclip_sfx_h0179_jp.ab</v>
       </c>
       <c r="C129">
-        <v>1837987</v>
+        <v>1837988</v>
       </c>
       <c r="D129" t="str">
         <v>Stage_1</v>
@@ -3050,7 +3050,7 @@
         <v>audioclip_sfx_h0190_jp.ab</v>
       </c>
       <c r="C133">
-        <v>2643057</v>
+        <v>2643059</v>
       </c>
       <c r="D133" t="str">
         <v>Stage_1</v>
@@ -3250,7 +3250,7 @@
         <v>audioclip_sfx_h0201_jp.ab</v>
       </c>
       <c r="C143">
-        <v>810576</v>
+        <v>810575</v>
       </c>
       <c r="D143" t="str">
         <v>Stage_1</v>
@@ -3290,7 +3290,7 @@
         <v>audioclip_sfx_h0208_jp.ab</v>
       </c>
       <c r="C145">
-        <v>774137</v>
+        <v>774134</v>
       </c>
       <c r="D145" t="str">
         <v>Stage_1</v>
@@ -3310,7 +3310,7 @@
         <v>audioclip_sfx_h0209_jp.ab</v>
       </c>
       <c r="C146">
-        <v>1046541</v>
+        <v>1046540</v>
       </c>
       <c r="D146" t="str">
         <v>Stage_1</v>
@@ -3370,7 +3370,7 @@
         <v>audioclip_sfx_h0215_jp.ab</v>
       </c>
       <c r="C149">
-        <v>1225724</v>
+        <v>1225722</v>
       </c>
       <c r="D149" t="str">
         <v>Stage_1</v>
@@ -3450,7 +3450,7 @@
         <v>audioclip_sfx_h0220_jp.ab</v>
       </c>
       <c r="C153">
-        <v>1002159</v>
+        <v>1002160</v>
       </c>
       <c r="D153" t="str">
         <v>Stage_1</v>
@@ -3490,7 +3490,7 @@
         <v>audioclip_sfx_h0224_jp.ab</v>
       </c>
       <c r="C155">
-        <v>1031309</v>
+        <v>1031308</v>
       </c>
       <c r="D155" t="str">
         <v>Stage_1</v>
@@ -3510,7 +3510,7 @@
         <v>audioclip_sfx_h0226_jp.ab</v>
       </c>
       <c r="C156">
-        <v>1134470</v>
+        <v>1134472</v>
       </c>
       <c r="D156" t="str">
         <v>Stage_1</v>
@@ -3550,7 +3550,7 @@
         <v>audioclip_sfx_h0230_jp.ab</v>
       </c>
       <c r="C158">
-        <v>1022960</v>
+        <v>1022961</v>
       </c>
       <c r="D158" t="str">
         <v>Stage_1</v>
@@ -3630,7 +3630,7 @@
         <v>audioclip_sfx_h0235_jp.ab</v>
       </c>
       <c r="C162">
-        <v>2384177</v>
+        <v>2384176</v>
       </c>
       <c r="D162" t="str">
         <v>Stage_1</v>
@@ -3650,7 +3650,7 @@
         <v>audioclip_sfx_h0236_jp.ab</v>
       </c>
       <c r="C163">
-        <v>2245978</v>
+        <v>2245976</v>
       </c>
       <c r="D163" t="str">
         <v>Stage_1</v>
@@ -3690,7 +3690,7 @@
         <v>audioclip_sfx_h0238_jp.ab</v>
       </c>
       <c r="C165">
-        <v>867921</v>
+        <v>867922</v>
       </c>
       <c r="D165" t="str">
         <v>Stage_1</v>
@@ -3710,7 +3710,7 @@
         <v>audioclip_sfx_h0239_jp.ab</v>
       </c>
       <c r="C166">
-        <v>5844651</v>
+        <v>5844653</v>
       </c>
       <c r="D166" t="str">
         <v>Stage_1</v>
@@ -3750,7 +3750,7 @@
         <v>audioclip_sfx_h0241_jp.ab</v>
       </c>
       <c r="C168">
-        <v>1125056</v>
+        <v>1125057</v>
       </c>
       <c r="D168" t="str">
         <v>Stage_1</v>
@@ -3790,7 +3790,7 @@
         <v>audioclip_sfx_h0244_jp.ab</v>
       </c>
       <c r="C170">
-        <v>1110560</v>
+        <v>1110558</v>
       </c>
       <c r="D170" t="str">
         <v>Stage_1</v>
@@ -3830,7 +3830,7 @@
         <v>audioclip_sfx_h0247_jp.ab</v>
       </c>
       <c r="C172">
-        <v>939768</v>
+        <v>939767</v>
       </c>
       <c r="D172" t="str">
         <v>Stage_1</v>
@@ -3850,7 +3850,7 @@
         <v>audioclip_sfx_h0248_jp.ab</v>
       </c>
       <c r="C173">
-        <v>1234718</v>
+        <v>1234716</v>
       </c>
       <c r="D173" t="str">
         <v>Stage_1</v>
@@ -3870,7 +3870,7 @@
         <v>audioclip_sfx_h0249_jp.ab</v>
       </c>
       <c r="C174">
-        <v>899107</v>
+        <v>899109</v>
       </c>
       <c r="D174" t="str">
         <v>Stage_1</v>
@@ -3950,7 +3950,7 @@
         <v>audioclip_sfx_h0257_jp.ab</v>
       </c>
       <c r="C178">
-        <v>1131207</v>
+        <v>1131208</v>
       </c>
       <c r="D178" t="str">
         <v>Stage_1</v>
@@ -4010,7 +4010,7 @@
         <v>audioclip_sfx_h0262_jp.ab</v>
       </c>
       <c r="C181">
-        <v>1140807</v>
+        <v>1140808</v>
       </c>
       <c r="D181" t="str">
         <v>Stage_1</v>
@@ -4130,7 +4130,7 @@
         <v>audioclip_sfx_h0271_jp.ab</v>
       </c>
       <c r="C187">
-        <v>1584334</v>
+        <v>1584336</v>
       </c>
       <c r="D187" t="str">
         <v>Stage_1</v>
@@ -4270,7 +4270,7 @@
         <v>audioclip_sfx_r0173_jp.ab</v>
       </c>
       <c r="C194">
-        <v>1438365</v>
+        <v>1438364</v>
       </c>
       <c r="D194" t="str">
         <v>Stage_1</v>
@@ -4290,7 +4290,7 @@
         <v>audioclip_sfx_r0205_jp.ab</v>
       </c>
       <c r="C195">
-        <v>1066358</v>
+        <v>1066357</v>
       </c>
       <c r="D195" t="str">
         <v>Stage_1</v>
@@ -4330,7 +4330,7 @@
         <v>audioclip_sfx_t0026_jp.ab</v>
       </c>
       <c r="C197">
-        <v>903967</v>
+        <v>903966</v>
       </c>
       <c r="D197" t="str">
         <v>Stage_1</v>
@@ -4370,7 +4370,7 @@
         <v>audioclip_sfx_t0032_jp.ab</v>
       </c>
       <c r="C199">
-        <v>995100</v>
+        <v>995097</v>
       </c>
       <c r="D199" t="str">
         <v>Stage_1</v>
@@ -4450,7 +4450,7 @@
         <v>audioclip_sfx_t0049_jp.ab</v>
       </c>
       <c r="C203">
-        <v>1950975</v>
+        <v>1950972</v>
       </c>
       <c r="D203" t="str">
         <v>Stage_1</v>
@@ -4490,7 +4490,7 @@
         <v>audioclip_sfx_t0155_jp.ab</v>
       </c>
       <c r="C205">
-        <v>1992962</v>
+        <v>1992961</v>
       </c>
       <c r="D205" t="str">
         <v>Stage_1</v>
@@ -4530,7 +4530,7 @@
         <v>audioclip_sfx_t0158_jp.ab</v>
       </c>
       <c r="C207">
-        <v>1950991</v>
+        <v>1950990</v>
       </c>
       <c r="D207" t="str">
         <v>Stage_1</v>
@@ -4550,7 +4550,7 @@
         <v>audioclip_sfx_t0180_jp.ab</v>
       </c>
       <c r="C208">
-        <v>2527578</v>
+        <v>2527577</v>
       </c>
       <c r="D208" t="str">
         <v>Stage_1</v>
@@ -4630,7 +4630,7 @@
         <v>audioclip_sfx_t0187_jp.ab</v>
       </c>
       <c r="C212">
-        <v>2460158</v>
+        <v>2460157</v>
       </c>
       <c r="D212" t="str">
         <v>Stage_1</v>
@@ -4650,7 +4650,7 @@
         <v>audioclip_sfx_t0188_jp.ab</v>
       </c>
       <c r="C213">
-        <v>1973756</v>
+        <v>1973761</v>
       </c>
       <c r="D213" t="str">
         <v>Stage_1</v>
@@ -4790,7 +4790,7 @@
         <v>audioclip_sfx_t0222_jp.ab</v>
       </c>
       <c r="C220">
-        <v>781278</v>
+        <v>781279</v>
       </c>
       <c r="D220" t="str">
         <v>Stage_1</v>
@@ -4850,7 +4850,7 @@
         <v>audioclip_sfx_t0228_jp.ab</v>
       </c>
       <c r="C223">
-        <v>1009843</v>
+        <v>1009845</v>
       </c>
       <c r="D223" t="str">
         <v>Stage_1</v>
@@ -4870,7 +4870,7 @@
         <v>audioclip_sfx_t0229_jp.ab</v>
       </c>
       <c r="C224">
-        <v>1117663</v>
+        <v>1117664</v>
       </c>
       <c r="D224" t="str">
         <v>Stage_1</v>
@@ -4930,7 +4930,7 @@
         <v>audioclip_sfx_t0246_jp.ab</v>
       </c>
       <c r="C227">
-        <v>890769</v>
+        <v>890771</v>
       </c>
       <c r="D227" t="str">
         <v>Stage_1</v>
@@ -5064,13 +5064,13 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>audioclip_sfx_t0272_jp.ab</v>
+        <v>audioclip_sfx_t0269_jp.ab</v>
       </c>
       <c r="B234" t="str">
-        <v>audioclip_sfx_t0272_jp.ab</v>
+        <v>audioclip_sfx_t0269_jp.ab</v>
       </c>
       <c r="C234">
-        <v>1436659</v>
+        <v>1231700</v>
       </c>
       <c r="D234" t="str">
         <v>Stage_1</v>
@@ -5079,18 +5079,18 @@
         <v>0</v>
       </c>
       <c r="F234" t="str">
-        <v>3fbd499f369d479453c63104e49451bb58ffc5a320809a8764e869742fe3e29b</v>
+        <v>75159c8704f153ca9e4407ce585f5b2e6e24c82349549f6da9d7c7f66d5da6f2</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>audioclip_sfx_t3189_jp.ab</v>
+        <v>audioclip_sfx_t0272_jp.ab</v>
       </c>
       <c r="B235" t="str">
-        <v>audioclip_sfx_t3189_jp.ab</v>
+        <v>audioclip_sfx_t0272_jp.ab</v>
       </c>
       <c r="C235">
-        <v>316225</v>
+        <v>1436659</v>
       </c>
       <c r="D235" t="str">
         <v>Stage_1</v>
@@ -5099,18 +5099,18 @@
         <v>0</v>
       </c>
       <c r="F235" t="str">
-        <v>01cdfbbf9f77a918a2016333f70e047b3087ef54fd0477a4cbb298f6a9eb631d</v>
+        <v>3fbd499f369d479453c63104e49451bb58ffc5a320809a8764e869742fe3e29b</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>audioclip_sfx_t3191_jp.ab</v>
+        <v>audioclip_sfx_t0275_jp.ab</v>
       </c>
       <c r="B236" t="str">
-        <v>audioclip_sfx_t3191_jp.ab</v>
+        <v>audioclip_sfx_t0275_jp.ab</v>
       </c>
       <c r="C236">
-        <v>164050</v>
+        <v>175082</v>
       </c>
       <c r="D236" t="str">
         <v>Stage_1</v>
@@ -5119,18 +5119,18 @@
         <v>0</v>
       </c>
       <c r="F236" t="str">
-        <v>8abe3d521ebcb185fcce96a49bbc96df07257c26e4d0764e87c1936ced63e4b5</v>
+        <v>5e68602e3306cffa56ef70ee14bb1d7bb896075430251bddafe2a80bcb009ed3</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>audioclip_sfx_t3259_jp.ab</v>
+        <v>audioclip_sfx_t3189_jp.ab</v>
       </c>
       <c r="B237" t="str">
-        <v>audioclip_sfx_t3259_jp.ab</v>
+        <v>audioclip_sfx_t3189_jp.ab</v>
       </c>
       <c r="C237">
-        <v>214579</v>
+        <v>316225</v>
       </c>
       <c r="D237" t="str">
         <v>Stage_1</v>
@@ -5139,18 +5139,18 @@
         <v>0</v>
       </c>
       <c r="F237" t="str">
-        <v>d3418a4d00e7826aeec3b5f55296ba67194159666952d4f5645a7a3e3959bd33</v>
+        <v>01cdfbbf9f77a918a2016333f70e047b3087ef54fd0477a4cbb298f6a9eb631d</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>audioclip_sfx_t3260_jp.ab</v>
+        <v>audioclip_sfx_t3191_jp.ab</v>
       </c>
       <c r="B238" t="str">
-        <v>audioclip_sfx_t3260_jp.ab</v>
+        <v>audioclip_sfx_t3191_jp.ab</v>
       </c>
       <c r="C238">
-        <v>310407</v>
+        <v>164051</v>
       </c>
       <c r="D238" t="str">
         <v>Stage_1</v>
@@ -5159,18 +5159,18 @@
         <v>0</v>
       </c>
       <c r="F238" t="str">
-        <v>7922b41fbe5ace431e852e608c627644145a3374e7c72b17c7eb99e87d8a75f0</v>
+        <v>8abe3d521ebcb185fcce96a49bbc96df07257c26e4d0764e87c1936ced63e4b5</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>audioclip_sfx_t3403_jp.ab</v>
+        <v>audioclip_sfx_t3259_jp.ab</v>
       </c>
       <c r="B239" t="str">
-        <v>audioclip_sfx_t3403_jp.ab</v>
+        <v>audioclip_sfx_t3259_jp.ab</v>
       </c>
       <c r="C239">
-        <v>288968</v>
+        <v>214580</v>
       </c>
       <c r="D239" t="str">
         <v>Stage_1</v>
@@ -5179,18 +5179,18 @@
         <v>0</v>
       </c>
       <c r="F239" t="str">
-        <v>318ed1740220025f770750eae32fd2966f4ee57185327d8b16d06272c6fb1b72</v>
+        <v>d3418a4d00e7826aeec3b5f55296ba67194159666952d4f5645a7a3e3959bd33</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>audioclip_sfx_t3407_jp.ab</v>
+        <v>audioclip_sfx_t3260_jp.ab</v>
       </c>
       <c r="B240" t="str">
-        <v>audioclip_sfx_t3407_jp.ab</v>
+        <v>audioclip_sfx_t3260_jp.ab</v>
       </c>
       <c r="C240">
-        <v>270581</v>
+        <v>310407</v>
       </c>
       <c r="D240" t="str">
         <v>Stage_1</v>
@@ -5199,18 +5199,18 @@
         <v>0</v>
       </c>
       <c r="F240" t="str">
-        <v>d6d2fac1b1df16b394e326376d1b0328ebf898c00bfa98e4d483d55222f879a7</v>
+        <v>7922b41fbe5ace431e852e608c627644145a3374e7c72b17c7eb99e87d8a75f0</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>character_largeimage_b0001.ab</v>
+        <v>audioclip_sfx_t3403_jp.ab</v>
       </c>
       <c r="B241" t="str">
-        <v>character_largeimage_b0001.ab</v>
+        <v>audioclip_sfx_t3403_jp.ab</v>
       </c>
       <c r="C241">
-        <v>3127774</v>
+        <v>288969</v>
       </c>
       <c r="D241" t="str">
         <v>Stage_1</v>
@@ -5219,18 +5219,18 @@
         <v>0</v>
       </c>
       <c r="F241" t="str">
-        <v>78e784ceac79715e6f390d5b83f7fb527e8cb5b0404a6f1be45b313a5ba02dc1</v>
+        <v>318ed1740220025f770750eae32fd2966f4ee57185327d8b16d06272c6fb1b72</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>character_largeimage_b0015.ab</v>
+        <v>audioclip_sfx_t3407_jp.ab</v>
       </c>
       <c r="B242" t="str">
-        <v>character_largeimage_b0015.ab</v>
+        <v>audioclip_sfx_t3407_jp.ab</v>
       </c>
       <c r="C242">
-        <v>3331653</v>
+        <v>270581</v>
       </c>
       <c r="D242" t="str">
         <v>Stage_1</v>
@@ -5239,18 +5239,18 @@
         <v>0</v>
       </c>
       <c r="F242" t="str">
-        <v>dd04ef36d2763124089134dbe7458b80907450a71e52752c5290f0de6f4e7eae</v>
+        <v>d6d2fac1b1df16b394e326376d1b0328ebf898c00bfa98e4d483d55222f879a7</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>character_largeimage_b0028.ab</v>
+        <v>character_largeimage_b0001.ab</v>
       </c>
       <c r="B243" t="str">
-        <v>character_largeimage_b0028.ab</v>
+        <v>character_largeimage_b0001.ab</v>
       </c>
       <c r="C243">
-        <v>3412887</v>
+        <v>3127774</v>
       </c>
       <c r="D243" t="str">
         <v>Stage_1</v>
@@ -5259,18 +5259,18 @@
         <v>0</v>
       </c>
       <c r="F243" t="str">
-        <v>24f9a0b1ca8b96b3da27e0f1d94e381499f584471f56b3c2a7241ae4f6141d8c</v>
+        <v>78e784ceac79715e6f390d5b83f7fb527e8cb5b0404a6f1be45b313a5ba02dc1</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>character_largeimage_b0037.ab</v>
+        <v>character_largeimage_b0015.ab</v>
       </c>
       <c r="B244" t="str">
-        <v>character_largeimage_b0037.ab</v>
+        <v>character_largeimage_b0015.ab</v>
       </c>
       <c r="C244">
-        <v>4001030</v>
+        <v>3331653</v>
       </c>
       <c r="D244" t="str">
         <v>Stage_1</v>
@@ -5279,18 +5279,18 @@
         <v>0</v>
       </c>
       <c r="F244" t="str">
-        <v>1bb8cecd4d65d3465875868908bde0e58a0c63eb9afd917907feb7180b3b8914</v>
+        <v>dd04ef36d2763124089134dbe7458b80907450a71e52752c5290f0de6f4e7eae</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>character_largeimage_b0202.ab</v>
+        <v>character_largeimage_b0028.ab</v>
       </c>
       <c r="B245" t="str">
-        <v>character_largeimage_b0202.ab</v>
+        <v>character_largeimage_b0028.ab</v>
       </c>
       <c r="C245">
-        <v>790826</v>
+        <v>3412887</v>
       </c>
       <c r="D245" t="str">
         <v>Stage_1</v>
@@ -5299,18 +5299,18 @@
         <v>0</v>
       </c>
       <c r="F245" t="str">
-        <v>be4310c123d2b37d7bdd180f406795da17db9276c2abcf6d33c7f2d834798ba0</v>
+        <v>24f9a0b1ca8b96b3da27e0f1d94e381499f584471f56b3c2a7241ae4f6141d8c</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>character_largeimage_b0260.ab</v>
+        <v>character_largeimage_b0037.ab</v>
       </c>
       <c r="B246" t="str">
-        <v>character_largeimage_b0260.ab</v>
+        <v>character_largeimage_b0037.ab</v>
       </c>
       <c r="C246">
-        <v>809446</v>
+        <v>4001030</v>
       </c>
       <c r="D246" t="str">
         <v>Stage_1</v>
@@ -5319,18 +5319,18 @@
         <v>0</v>
       </c>
       <c r="F246" t="str">
-        <v>5545e61f9af50ea439bb9425d49679c265b4b04153e748be9d8dff61b7f46113</v>
+        <v>1bb8cecd4d65d3465875868908bde0e58a0c63eb9afd917907feb7180b3b8914</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>character_largeimage_b0267.ab</v>
+        <v>character_largeimage_b0202.ab</v>
       </c>
       <c r="B247" t="str">
-        <v>character_largeimage_b0267.ab</v>
+        <v>character_largeimage_b0202.ab</v>
       </c>
       <c r="C247">
-        <v>789052</v>
+        <v>790826</v>
       </c>
       <c r="D247" t="str">
         <v>Stage_1</v>
@@ -5339,18 +5339,18 @@
         <v>0</v>
       </c>
       <c r="F247" t="str">
-        <v>d2c5fdd38d13a1a6a6c8f4f19e0f84caaa156ea51ae041433dfd645d0b8e59f8</v>
+        <v>be4310c123d2b37d7bdd180f406795da17db9276c2abcf6d33c7f2d834798ba0</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>character_largeimage_e0002.ab</v>
+        <v>character_largeimage_b0260.ab</v>
       </c>
       <c r="B248" t="str">
-        <v>character_largeimage_e0002.ab</v>
+        <v>character_largeimage_b0260.ab</v>
       </c>
       <c r="C248">
-        <v>3558177</v>
+        <v>809446</v>
       </c>
       <c r="D248" t="str">
         <v>Stage_1</v>
@@ -5359,18 +5359,18 @@
         <v>0</v>
       </c>
       <c r="F248" t="str">
-        <v>a51d1503e3559c8ce675afeeed8f729155eed27a8fbebb35148b3dc87f8492e1</v>
+        <v>5545e61f9af50ea439bb9425d49679c265b4b04153e748be9d8dff61b7f46113</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>character_largeimage_e0046.ab</v>
+        <v>character_largeimage_b0267.ab</v>
       </c>
       <c r="B249" t="str">
-        <v>character_largeimage_e0046.ab</v>
+        <v>character_largeimage_b0267.ab</v>
       </c>
       <c r="C249">
-        <v>797567</v>
+        <v>789052</v>
       </c>
       <c r="D249" t="str">
         <v>Stage_1</v>
@@ -5379,18 +5379,18 @@
         <v>0</v>
       </c>
       <c r="F249" t="str">
-        <v>a59b46fa5f54c534a9098787a6bf734026c5260a26fe4ed54fab45eb22d26dd3</v>
+        <v>d2c5fdd38d13a1a6a6c8f4f19e0f84caaa156ea51ae041433dfd645d0b8e59f8</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>character_largeimage_h0000.ab</v>
+        <v>character_largeimage_e0002.ab</v>
       </c>
       <c r="B250" t="str">
-        <v>character_largeimage_h0000.ab</v>
+        <v>character_largeimage_e0002.ab</v>
       </c>
       <c r="C250">
-        <v>208090</v>
+        <v>3558177</v>
       </c>
       <c r="D250" t="str">
         <v>Stage_1</v>
@@ -5399,18 +5399,18 @@
         <v>0</v>
       </c>
       <c r="F250" t="str">
-        <v>a83767d3a6a982d3509d5ed4c329a744963271116b14d342654d3bd0bc612c66</v>
+        <v>a51d1503e3559c8ce675afeeed8f729155eed27a8fbebb35148b3dc87f8492e1</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>character_largeimage_h0003.ab</v>
+        <v>character_largeimage_e0046.ab</v>
       </c>
       <c r="B251" t="str">
-        <v>character_largeimage_h0003.ab</v>
+        <v>character_largeimage_e0046.ab</v>
       </c>
       <c r="C251">
-        <v>3975188</v>
+        <v>797567</v>
       </c>
       <c r="D251" t="str">
         <v>Stage_1</v>
@@ -5419,18 +5419,18 @@
         <v>0</v>
       </c>
       <c r="F251" t="str">
-        <v>c7a8bfc4a28e3f884b3fd89a9d5988d4b86952038ef16422caddaee083cf9588</v>
+        <v>a59b46fa5f54c534a9098787a6bf734026c5260a26fe4ed54fab45eb22d26dd3</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>character_largeimage_h0004.ab</v>
+        <v>character_largeimage_h0000.ab</v>
       </c>
       <c r="B252" t="str">
-        <v>character_largeimage_h0004.ab</v>
+        <v>character_largeimage_h0000.ab</v>
       </c>
       <c r="C252">
-        <v>4306043</v>
+        <v>208090</v>
       </c>
       <c r="D252" t="str">
         <v>Stage_1</v>
@@ -5439,18 +5439,18 @@
         <v>0</v>
       </c>
       <c r="F252" t="str">
-        <v>8b2ed468e2fcba7d477e3da1fe08a3c2d69c7a5b700f1e557d14a5b1a72ba120</v>
+        <v>a83767d3a6a982d3509d5ed4c329a744963271116b14d342654d3bd0bc612c66</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>character_largeimage_h0005.ab</v>
+        <v>character_largeimage_h0003.ab</v>
       </c>
       <c r="B253" t="str">
-        <v>character_largeimage_h0005.ab</v>
+        <v>character_largeimage_h0003.ab</v>
       </c>
       <c r="C253">
-        <v>3547758</v>
+        <v>3975187</v>
       </c>
       <c r="D253" t="str">
         <v>Stage_1</v>
@@ -5459,18 +5459,18 @@
         <v>0</v>
       </c>
       <c r="F253" t="str">
-        <v>e3fca3c426d6ee0a3cf9dd6f304f8f25d2fef2a9b1ae6de05627d3db37e3fc6a</v>
+        <v>c7a8bfc4a28e3f884b3fd89a9d5988d4b86952038ef16422caddaee083cf9588</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>character_largeimage_h0006.ab</v>
+        <v>character_largeimage_h0004.ab</v>
       </c>
       <c r="B254" t="str">
-        <v>character_largeimage_h0006.ab</v>
+        <v>character_largeimage_h0004.ab</v>
       </c>
       <c r="C254">
-        <v>3671173</v>
+        <v>4306043</v>
       </c>
       <c r="D254" t="str">
         <v>Stage_1</v>
@@ -5479,18 +5479,18 @@
         <v>0</v>
       </c>
       <c r="F254" t="str">
-        <v>b5b543aee2a4ed561a42e5107bbea10ef79b2ad93842b832eb235533f7ca4f99</v>
+        <v>8b2ed468e2fcba7d477e3da1fe08a3c2d69c7a5b700f1e557d14a5b1a72ba120</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>character_largeimage_h0007.ab</v>
+        <v>character_largeimage_h0005.ab</v>
       </c>
       <c r="B255" t="str">
-        <v>character_largeimage_h0007.ab</v>
+        <v>character_largeimage_h0005.ab</v>
       </c>
       <c r="C255">
-        <v>803840</v>
+        <v>3547758</v>
       </c>
       <c r="D255" t="str">
         <v>Stage_1</v>
@@ -5499,18 +5499,18 @@
         <v>0</v>
       </c>
       <c r="F255" t="str">
-        <v>e7a218ee7d7a55f01a0e251a424c46bcf384be8b50176d5cac868f9da0dde6d7</v>
+        <v>e3fca3c426d6ee0a3cf9dd6f304f8f25d2fef2a9b1ae6de05627d3db37e3fc6a</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>character_largeimage_h0008.ab</v>
+        <v>character_largeimage_h0006.ab</v>
       </c>
       <c r="B256" t="str">
-        <v>character_largeimage_h0008.ab</v>
+        <v>character_largeimage_h0006.ab</v>
       </c>
       <c r="C256">
-        <v>713224</v>
+        <v>3671173</v>
       </c>
       <c r="D256" t="str">
         <v>Stage_1</v>
@@ -5519,18 +5519,18 @@
         <v>0</v>
       </c>
       <c r="F256" t="str">
-        <v>bbc9c213346cd9c77b113965f05ffa7d0b05ac187f68681435bf67674b00e146</v>
+        <v>b5b543aee2a4ed561a42e5107bbea10ef79b2ad93842b832eb235533f7ca4f99</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>character_largeimage_h0009.ab</v>
+        <v>character_largeimage_h0007.ab</v>
       </c>
       <c r="B257" t="str">
-        <v>character_largeimage_h0009.ab</v>
+        <v>character_largeimage_h0007.ab</v>
       </c>
       <c r="C257">
-        <v>831282</v>
+        <v>803840</v>
       </c>
       <c r="D257" t="str">
         <v>Stage_1</v>
@@ -5539,18 +5539,18 @@
         <v>0</v>
       </c>
       <c r="F257" t="str">
-        <v>c38406c3168894ab382175e94b7976eb5ea0caf4f1d7a22fe7b3860d8dc0759e</v>
+        <v>e7a218ee7d7a55f01a0e251a424c46bcf384be8b50176d5cac868f9da0dde6d7</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>character_largeimage_h0010.ab</v>
+        <v>character_largeimage_h0008.ab</v>
       </c>
       <c r="B258" t="str">
-        <v>character_largeimage_h0010.ab</v>
+        <v>character_largeimage_h0008.ab</v>
       </c>
       <c r="C258">
-        <v>4679298</v>
+        <v>713224</v>
       </c>
       <c r="D258" t="str">
         <v>Stage_1</v>
@@ -5559,18 +5559,18 @@
         <v>0</v>
       </c>
       <c r="F258" t="str">
-        <v>6f4c0ef7a8999f67fbe814d23dd3f4bdd1d22cc0f44a0f13a9953615ce2d6580</v>
+        <v>bbc9c213346cd9c77b113965f05ffa7d0b05ac187f68681435bf67674b00e146</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>character_largeimage_h0012.ab</v>
+        <v>character_largeimage_h0009.ab</v>
       </c>
       <c r="B259" t="str">
-        <v>character_largeimage_h0012.ab</v>
+        <v>character_largeimage_h0009.ab</v>
       </c>
       <c r="C259">
-        <v>823851</v>
+        <v>831282</v>
       </c>
       <c r="D259" t="str">
         <v>Stage_1</v>
@@ -5579,18 +5579,18 @@
         <v>0</v>
       </c>
       <c r="F259" t="str">
-        <v>8ce801de023c56fbb01494c4ca701ac2a955973683af0de63eb113c470fe54c3</v>
+        <v>c38406c3168894ab382175e94b7976eb5ea0caf4f1d7a22fe7b3860d8dc0759e</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>character_largeimage_h0013.ab</v>
+        <v>character_largeimage_h0010.ab</v>
       </c>
       <c r="B260" t="str">
-        <v>character_largeimage_h0013.ab</v>
+        <v>character_largeimage_h0010.ab</v>
       </c>
       <c r="C260">
-        <v>730593</v>
+        <v>4679298</v>
       </c>
       <c r="D260" t="str">
         <v>Stage_1</v>
@@ -5599,18 +5599,18 @@
         <v>0</v>
       </c>
       <c r="F260" t="str">
-        <v>70018ef62ee1aa1a3b56fd711fb01a33ba58f72ed71b0ee34e169894cad9a529</v>
+        <v>6f4c0ef7a8999f67fbe814d23dd3f4bdd1d22cc0f44a0f13a9953615ce2d6580</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>character_largeimage_h0014.ab</v>
+        <v>character_largeimage_h0012.ab</v>
       </c>
       <c r="B261" t="str">
-        <v>character_largeimage_h0014.ab</v>
+        <v>character_largeimage_h0012.ab</v>
       </c>
       <c r="C261">
-        <v>808031</v>
+        <v>823851</v>
       </c>
       <c r="D261" t="str">
         <v>Stage_1</v>
@@ -5619,18 +5619,18 @@
         <v>0</v>
       </c>
       <c r="F261" t="str">
-        <v>da212d22735b71006f7bbebd8d2cf847ddf21d859344229cddf9f6ccf80c5372</v>
+        <v>8ce801de023c56fbb01494c4ca701ac2a955973683af0de63eb113c470fe54c3</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>character_largeimage_h0016.ab</v>
+        <v>character_largeimage_h0013.ab</v>
       </c>
       <c r="B262" t="str">
-        <v>character_largeimage_h0016.ab</v>
+        <v>character_largeimage_h0013.ab</v>
       </c>
       <c r="C262">
-        <v>758977</v>
+        <v>730593</v>
       </c>
       <c r="D262" t="str">
         <v>Stage_1</v>
@@ -5639,18 +5639,18 @@
         <v>0</v>
       </c>
       <c r="F262" t="str">
-        <v>8b88365c69bb5344a0f0022c3e0ae2283422666aca080b856f449d7397992782</v>
+        <v>70018ef62ee1aa1a3b56fd711fb01a33ba58f72ed71b0ee34e169894cad9a529</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>character_largeimage_h0018.ab</v>
+        <v>character_largeimage_h0014.ab</v>
       </c>
       <c r="B263" t="str">
-        <v>character_largeimage_h0018.ab</v>
+        <v>character_largeimage_h0014.ab</v>
       </c>
       <c r="C263">
-        <v>4615070</v>
+        <v>808031</v>
       </c>
       <c r="D263" t="str">
         <v>Stage_1</v>
@@ -5659,18 +5659,18 @@
         <v>0</v>
       </c>
       <c r="F263" t="str">
-        <v>78559c267f1b3412982acc007d76441d8b75e93eb4bfcdb0e95485e9ecd87318</v>
+        <v>da212d22735b71006f7bbebd8d2cf847ddf21d859344229cddf9f6ccf80c5372</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>character_largeimage_h0020.ab</v>
+        <v>character_largeimage_h0016.ab</v>
       </c>
       <c r="B264" t="str">
-        <v>character_largeimage_h0020.ab</v>
+        <v>character_largeimage_h0016.ab</v>
       </c>
       <c r="C264">
-        <v>3928747</v>
+        <v>758977</v>
       </c>
       <c r="D264" t="str">
         <v>Stage_1</v>
@@ -5679,18 +5679,18 @@
         <v>0</v>
       </c>
       <c r="F264" t="str">
-        <v>649021775c3d944ec66710dc2833a8df8f6e11c44878c62f3b931ff660a3c2da</v>
+        <v>8b88365c69bb5344a0f0022c3e0ae2283422666aca080b856f449d7397992782</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>character_largeimage_h0021.ab</v>
+        <v>character_largeimage_h0018.ab</v>
       </c>
       <c r="B265" t="str">
-        <v>character_largeimage_h0021.ab</v>
+        <v>character_largeimage_h0018.ab</v>
       </c>
       <c r="C265">
-        <v>4234934</v>
+        <v>4615070</v>
       </c>
       <c r="D265" t="str">
         <v>Stage_1</v>
@@ -5699,18 +5699,18 @@
         <v>0</v>
       </c>
       <c r="F265" t="str">
-        <v>95f82d1cb182f0d594eb6125d7b4f828b8e2b54c03c6a9b2a8a2688ae2b427ef</v>
+        <v>78559c267f1b3412982acc007d76441d8b75e93eb4bfcdb0e95485e9ecd87318</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>character_largeimage_h0022.ab</v>
+        <v>character_largeimage_h0020.ab</v>
       </c>
       <c r="B266" t="str">
-        <v>character_largeimage_h0022.ab</v>
+        <v>character_largeimage_h0020.ab</v>
       </c>
       <c r="C266">
-        <v>4332457</v>
+        <v>3928747</v>
       </c>
       <c r="D266" t="str">
         <v>Stage_1</v>
@@ -5719,18 +5719,18 @@
         <v>0</v>
       </c>
       <c r="F266" t="str">
-        <v>4d633e8de21a01527f9364d84f44895010d4a5dec9f0ede8402c19749280609a</v>
+        <v>649021775c3d944ec66710dc2833a8df8f6e11c44878c62f3b931ff660a3c2da</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>character_largeimage_h0023.ab</v>
+        <v>character_largeimage_h0021.ab</v>
       </c>
       <c r="B267" t="str">
-        <v>character_largeimage_h0023.ab</v>
+        <v>character_largeimage_h0021.ab</v>
       </c>
       <c r="C267">
-        <v>3265010</v>
+        <v>4234934</v>
       </c>
       <c r="D267" t="str">
         <v>Stage_1</v>
@@ -5739,18 +5739,18 @@
         <v>0</v>
       </c>
       <c r="F267" t="str">
-        <v>ffdbdb5c7c3a5f8aec334500f40226b14d82ac63ff43d51fa83131e6be67c680</v>
+        <v>95f82d1cb182f0d594eb6125d7b4f828b8e2b54c03c6a9b2a8a2688ae2b427ef</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>character_largeimage_h0024.ab</v>
+        <v>character_largeimage_h0022.ab</v>
       </c>
       <c r="B268" t="str">
-        <v>character_largeimage_h0024.ab</v>
+        <v>character_largeimage_h0022.ab</v>
       </c>
       <c r="C268">
-        <v>3281918</v>
+        <v>4332457</v>
       </c>
       <c r="D268" t="str">
         <v>Stage_1</v>
@@ -5759,18 +5759,18 @@
         <v>0</v>
       </c>
       <c r="F268" t="str">
-        <v>055d98eaa385323f6b431d57d9158c227ec5ff8f3fa628b8fdac15595b44a475</v>
+        <v>4d633e8de21a01527f9364d84f44895010d4a5dec9f0ede8402c19749280609a</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>character_largeimage_h0025.ab</v>
+        <v>character_largeimage_h0023.ab</v>
       </c>
       <c r="B269" t="str">
-        <v>character_largeimage_h0025.ab</v>
+        <v>character_largeimage_h0023.ab</v>
       </c>
       <c r="C269">
-        <v>3268737</v>
+        <v>3265010</v>
       </c>
       <c r="D269" t="str">
         <v>Stage_1</v>
@@ -5779,18 +5779,18 @@
         <v>0</v>
       </c>
       <c r="F269" t="str">
-        <v>2a72b0b0d6249cd756219728440dca77f1388f67427663ba12f8ddac14f3a5c5</v>
+        <v>ffdbdb5c7c3a5f8aec334500f40226b14d82ac63ff43d51fa83131e6be67c680</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>character_largeimage_h0029.ab</v>
+        <v>character_largeimage_h0024.ab</v>
       </c>
       <c r="B270" t="str">
-        <v>character_largeimage_h0029.ab</v>
+        <v>character_largeimage_h0024.ab</v>
       </c>
       <c r="C270">
-        <v>3878944</v>
+        <v>3281917</v>
       </c>
       <c r="D270" t="str">
         <v>Stage_1</v>
@@ -5799,18 +5799,18 @@
         <v>0</v>
       </c>
       <c r="F270" t="str">
-        <v>4d62229cbd284aa9391c2ae5728483edcdd7c3664570bc6980b143987362b95d</v>
+        <v>055d98eaa385323f6b431d57d9158c227ec5ff8f3fa628b8fdac15595b44a475</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>character_largeimage_h0030.ab</v>
+        <v>character_largeimage_h0025.ab</v>
       </c>
       <c r="B271" t="str">
-        <v>character_largeimage_h0030.ab</v>
+        <v>character_largeimage_h0025.ab</v>
       </c>
       <c r="C271">
-        <v>3068963</v>
+        <v>3268737</v>
       </c>
       <c r="D271" t="str">
         <v>Stage_1</v>
@@ -5819,18 +5819,18 @@
         <v>0</v>
       </c>
       <c r="F271" t="str">
-        <v>d43431a351343bcce91b2b6839f9998d1c36be4e3f4f103a9b7bed45056690a6</v>
+        <v>2a72b0b0d6249cd756219728440dca77f1388f67427663ba12f8ddac14f3a5c5</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>character_largeimage_h0031.ab</v>
+        <v>character_largeimage_h0029.ab</v>
       </c>
       <c r="B272" t="str">
-        <v>character_largeimage_h0031.ab</v>
+        <v>character_largeimage_h0029.ab</v>
       </c>
       <c r="C272">
-        <v>3311210</v>
+        <v>3878944</v>
       </c>
       <c r="D272" t="str">
         <v>Stage_1</v>
@@ -5839,18 +5839,18 @@
         <v>0</v>
       </c>
       <c r="F272" t="str">
-        <v>f844caa4342233c882176f4b3d3b5df3aa38df5704837c4e17b36f772a18fe85</v>
+        <v>4d62229cbd284aa9391c2ae5728483edcdd7c3664570bc6980b143987362b95d</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>character_largeimage_h0035.ab</v>
+        <v>character_largeimage_h0030.ab</v>
       </c>
       <c r="B273" t="str">
-        <v>character_largeimage_h0035.ab</v>
+        <v>character_largeimage_h0030.ab</v>
       </c>
       <c r="C273">
-        <v>3958978</v>
+        <v>3068963</v>
       </c>
       <c r="D273" t="str">
         <v>Stage_1</v>
@@ -5859,18 +5859,18 @@
         <v>0</v>
       </c>
       <c r="F273" t="str">
-        <v>5a7f4c68dffa0013111cececfe93648f43ea44a9d2ecc2f353cf7b7c8cb8f59c</v>
+        <v>d43431a351343bcce91b2b6839f9998d1c36be4e3f4f103a9b7bed45056690a6</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>character_largeimage_h0036.ab</v>
+        <v>character_largeimage_h0031.ab</v>
       </c>
       <c r="B274" t="str">
-        <v>character_largeimage_h0036.ab</v>
+        <v>character_largeimage_h0031.ab</v>
       </c>
       <c r="C274">
-        <v>2916298</v>
+        <v>3311210</v>
       </c>
       <c r="D274" t="str">
         <v>Stage_1</v>
@@ -5879,18 +5879,18 @@
         <v>0</v>
       </c>
       <c r="F274" t="str">
-        <v>b9696daa9252dec4261611f1f256637ee51cb3b8b33d0b92cfd3bba149001c6e</v>
+        <v>f844caa4342233c882176f4b3d3b5df3aa38df5704837c4e17b36f772a18fe85</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>character_largeimage_h0038.ab</v>
+        <v>character_largeimage_h0035.ab</v>
       </c>
       <c r="B275" t="str">
-        <v>character_largeimage_h0038.ab</v>
+        <v>character_largeimage_h0035.ab</v>
       </c>
       <c r="C275">
-        <v>855003</v>
+        <v>3958978</v>
       </c>
       <c r="D275" t="str">
         <v>Stage_1</v>
@@ -5899,18 +5899,18 @@
         <v>0</v>
       </c>
       <c r="F275" t="str">
-        <v>289b0ed905365cd5e8cb89fe42ac33d47e5f572cfc93a7419bb99f39ea7341d1</v>
+        <v>5a7f4c68dffa0013111cececfe93648f43ea44a9d2ecc2f353cf7b7c8cb8f59c</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>character_largeimage_h0040.ab</v>
+        <v>character_largeimage_h0036.ab</v>
       </c>
       <c r="B276" t="str">
-        <v>character_largeimage_h0040.ab</v>
+        <v>character_largeimage_h0036.ab</v>
       </c>
       <c r="C276">
-        <v>834045</v>
+        <v>2916298</v>
       </c>
       <c r="D276" t="str">
         <v>Stage_1</v>
@@ -5919,18 +5919,18 @@
         <v>0</v>
       </c>
       <c r="F276" t="str">
-        <v>6b42ad4bbc2598a1f1702e175d9bf9f511e485fa19f3fa86a86c22eb8cc7f23e</v>
+        <v>b9696daa9252dec4261611f1f256637ee51cb3b8b33d0b92cfd3bba149001c6e</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>character_largeimage_h0041.ab</v>
+        <v>character_largeimage_h0038.ab</v>
       </c>
       <c r="B277" t="str">
-        <v>character_largeimage_h0041.ab</v>
+        <v>character_largeimage_h0038.ab</v>
       </c>
       <c r="C277">
-        <v>799261</v>
+        <v>855003</v>
       </c>
       <c r="D277" t="str">
         <v>Stage_1</v>
@@ -5939,18 +5939,18 @@
         <v>0</v>
       </c>
       <c r="F277" t="str">
-        <v>5f1d547ddd7b8ce59a4e005ebe350bdc99957ad7f687d685d31014cccf81c0fc</v>
+        <v>289b0ed905365cd5e8cb89fe42ac33d47e5f572cfc93a7419bb99f39ea7341d1</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>character_largeimage_h0042.ab</v>
+        <v>character_largeimage_h0040.ab</v>
       </c>
       <c r="B278" t="str">
-        <v>character_largeimage_h0042.ab</v>
+        <v>character_largeimage_h0040.ab</v>
       </c>
       <c r="C278">
-        <v>777116</v>
+        <v>834045</v>
       </c>
       <c r="D278" t="str">
         <v>Stage_1</v>
@@ -5959,18 +5959,18 @@
         <v>0</v>
       </c>
       <c r="F278" t="str">
-        <v>ec22258063c80e1c82446b8a02dd46be8a92091df93f324eb9cf423dbee75c4a</v>
+        <v>6b42ad4bbc2598a1f1702e175d9bf9f511e485fa19f3fa86a86c22eb8cc7f23e</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>character_largeimage_h0043.ab</v>
+        <v>character_largeimage_h0041.ab</v>
       </c>
       <c r="B279" t="str">
-        <v>character_largeimage_h0043.ab</v>
+        <v>character_largeimage_h0041.ab</v>
       </c>
       <c r="C279">
-        <v>4131491</v>
+        <v>799261</v>
       </c>
       <c r="D279" t="str">
         <v>Stage_1</v>
@@ -5979,18 +5979,18 @@
         <v>0</v>
       </c>
       <c r="F279" t="str">
-        <v>2e3087d8674c5bff6c4f6a7957f7b459bfefc77083b6fa9050da6c234e5fcd06</v>
+        <v>5f1d547ddd7b8ce59a4e005ebe350bdc99957ad7f687d685d31014cccf81c0fc</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>character_largeimage_h0045.ab</v>
+        <v>character_largeimage_h0042.ab</v>
       </c>
       <c r="B280" t="str">
-        <v>character_largeimage_h0045.ab</v>
+        <v>character_largeimage_h0042.ab</v>
       </c>
       <c r="C280">
-        <v>806083</v>
+        <v>777116</v>
       </c>
       <c r="D280" t="str">
         <v>Stage_1</v>
@@ -5999,18 +5999,18 @@
         <v>0</v>
       </c>
       <c r="F280" t="str">
-        <v>75ea8ae022a44b3b64d866c990239078893ea0883aa85a84522e0d99fff85500</v>
+        <v>ec22258063c80e1c82446b8a02dd46be8a92091df93f324eb9cf423dbee75c4a</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>character_largeimage_h0047.ab</v>
+        <v>character_largeimage_h0043.ab</v>
       </c>
       <c r="B281" t="str">
-        <v>character_largeimage_h0047.ab</v>
+        <v>character_largeimage_h0043.ab</v>
       </c>
       <c r="C281">
-        <v>4289279</v>
+        <v>4131491</v>
       </c>
       <c r="D281" t="str">
         <v>Stage_1</v>
@@ -6019,18 +6019,18 @@
         <v>0</v>
       </c>
       <c r="F281" t="str">
-        <v>3f3f9d99623d7683093487b65cfd461be53bd2b8153a9419bb9880bf3086fee3</v>
+        <v>2e3087d8674c5bff6c4f6a7957f7b459bfefc77083b6fa9050da6c234e5fcd06</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>character_largeimage_h0048.ab</v>
+        <v>character_largeimage_h0045.ab</v>
       </c>
       <c r="B282" t="str">
-        <v>character_largeimage_h0048.ab</v>
+        <v>character_largeimage_h0045.ab</v>
       </c>
       <c r="C282">
-        <v>3816882</v>
+        <v>806083</v>
       </c>
       <c r="D282" t="str">
         <v>Stage_1</v>
@@ -6039,18 +6039,18 @@
         <v>0</v>
       </c>
       <c r="F282" t="str">
-        <v>e342bcc9d451f54427e9e676142ce9d3e42283c78c64adf074fd6754f8b711c9</v>
+        <v>75ea8ae022a44b3b64d866c990239078893ea0883aa85a84522e0d99fff85500</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>character_largeimage_h0097.ab</v>
+        <v>character_largeimage_h0047.ab</v>
       </c>
       <c r="B283" t="str">
-        <v>character_largeimage_h0097.ab</v>
+        <v>character_largeimage_h0047.ab</v>
       </c>
       <c r="C283">
-        <v>5051199</v>
+        <v>4289279</v>
       </c>
       <c r="D283" t="str">
         <v>Stage_1</v>
@@ -6059,18 +6059,18 @@
         <v>0</v>
       </c>
       <c r="F283" t="str">
-        <v>a85ef6c19ca8f47ed76b9c9f22aa8d48512b3d1dc156cdb37fdebe8d80ff9e1a</v>
+        <v>3f3f9d99623d7683093487b65cfd461be53bd2b8153a9419bb9880bf3086fee3</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>character_largeimage_h0133.ab</v>
+        <v>character_largeimage_h0048.ab</v>
       </c>
       <c r="B284" t="str">
-        <v>character_largeimage_h0133.ab</v>
+        <v>character_largeimage_h0048.ab</v>
       </c>
       <c r="C284">
-        <v>4176002</v>
+        <v>3816882</v>
       </c>
       <c r="D284" t="str">
         <v>Stage_1</v>
@@ -6079,18 +6079,18 @@
         <v>0</v>
       </c>
       <c r="F284" t="str">
-        <v>206d98bef7c96e960896ee8ee4a7b90e71f4c30bd73f9833cbe46d246c450f78</v>
+        <v>e342bcc9d451f54427e9e676142ce9d3e42283c78c64adf074fd6754f8b711c9</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>character_largeimage_h0134.ab</v>
+        <v>character_largeimage_h0097.ab</v>
       </c>
       <c r="B285" t="str">
-        <v>character_largeimage_h0134.ab</v>
+        <v>character_largeimage_h0097.ab</v>
       </c>
       <c r="C285">
-        <v>4242518</v>
+        <v>5051199</v>
       </c>
       <c r="D285" t="str">
         <v>Stage_1</v>
@@ -6099,18 +6099,18 @@
         <v>0</v>
       </c>
       <c r="F285" t="str">
-        <v>824b86c0e40aefc0770c167f978bc2fd4c1925a9efe1e9691c60a2eb5122c14e</v>
+        <v>a85ef6c19ca8f47ed76b9c9f22aa8d48512b3d1dc156cdb37fdebe8d80ff9e1a</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>character_largeimage_h0135.ab</v>
+        <v>character_largeimage_h0133.ab</v>
       </c>
       <c r="B286" t="str">
-        <v>character_largeimage_h0135.ab</v>
+        <v>character_largeimage_h0133.ab</v>
       </c>
       <c r="C286">
-        <v>3266671</v>
+        <v>4176002</v>
       </c>
       <c r="D286" t="str">
         <v>Stage_1</v>
@@ -6119,18 +6119,18 @@
         <v>0</v>
       </c>
       <c r="F286" t="str">
-        <v>6242bc0a6af6955ac2a0a8d31fee0a742dd006425a34614572a0ff0a6cf3ac30</v>
+        <v>206d98bef7c96e960896ee8ee4a7b90e71f4c30bd73f9833cbe46d246c450f78</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>character_largeimage_h0136.ab</v>
+        <v>character_largeimage_h0134.ab</v>
       </c>
       <c r="B287" t="str">
-        <v>character_largeimage_h0136.ab</v>
+        <v>character_largeimage_h0134.ab</v>
       </c>
       <c r="C287">
-        <v>3395405</v>
+        <v>4242518</v>
       </c>
       <c r="D287" t="str">
         <v>Stage_1</v>
@@ -6139,18 +6139,18 @@
         <v>0</v>
       </c>
       <c r="F287" t="str">
-        <v>c07b0a8e238a880228b5a27ac66e50bd4cd42ef64dd35769fbadb7ef4f9419aa</v>
+        <v>824b86c0e40aefc0770c167f978bc2fd4c1925a9efe1e9691c60a2eb5122c14e</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>character_largeimage_h0137.ab</v>
+        <v>character_largeimage_h0135.ab</v>
       </c>
       <c r="B288" t="str">
-        <v>character_largeimage_h0137.ab</v>
+        <v>character_largeimage_h0135.ab</v>
       </c>
       <c r="C288">
-        <v>5218305</v>
+        <v>3266671</v>
       </c>
       <c r="D288" t="str">
         <v>Stage_1</v>
@@ -6159,18 +6159,18 @@
         <v>0</v>
       </c>
       <c r="F288" t="str">
-        <v>0202ec87f638f3fd76d7a98dd5eb291a5d0c8125ded3ecb47f078dccd09f3a0b</v>
+        <v>6242bc0a6af6955ac2a0a8d31fee0a742dd006425a34614572a0ff0a6cf3ac30</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>character_largeimage_h0138.ab</v>
+        <v>character_largeimage_h0136.ab</v>
       </c>
       <c r="B289" t="str">
-        <v>character_largeimage_h0138.ab</v>
+        <v>character_largeimage_h0136.ab</v>
       </c>
       <c r="C289">
-        <v>4004656</v>
+        <v>3395405</v>
       </c>
       <c r="D289" t="str">
         <v>Stage_1</v>
@@ -6179,18 +6179,18 @@
         <v>0</v>
       </c>
       <c r="F289" t="str">
-        <v>61e12aaabe2c59ab60d879b18a7d8b89b7ddf9a8a71498e190e883353f7167c5</v>
+        <v>c07b0a8e238a880228b5a27ac66e50bd4cd42ef64dd35769fbadb7ef4f9419aa</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>character_largeimage_h0150.ab</v>
+        <v>character_largeimage_h0137.ab</v>
       </c>
       <c r="B290" t="str">
-        <v>character_largeimage_h0150.ab</v>
+        <v>character_largeimage_h0137.ab</v>
       </c>
       <c r="C290">
-        <v>4037956</v>
+        <v>5218305</v>
       </c>
       <c r="D290" t="str">
         <v>Stage_1</v>
@@ -6199,18 +6199,18 @@
         <v>0</v>
       </c>
       <c r="F290" t="str">
-        <v>d7d2064c4b7799f6f05c0bea7820d77879988674b6cbb863fc6ffff294516853</v>
+        <v>0202ec87f638f3fd76d7a98dd5eb291a5d0c8125ded3ecb47f078dccd09f3a0b</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>character_largeimage_h0151.ab</v>
+        <v>character_largeimage_h0138.ab</v>
       </c>
       <c r="B291" t="str">
-        <v>character_largeimage_h0151.ab</v>
+        <v>character_largeimage_h0138.ab</v>
       </c>
       <c r="C291">
-        <v>2589817</v>
+        <v>4004656</v>
       </c>
       <c r="D291" t="str">
         <v>Stage_1</v>
@@ -6219,18 +6219,18 @@
         <v>0</v>
       </c>
       <c r="F291" t="str">
-        <v>e319306d4c24fd23c4a7473ad0c6218a96d6abcbf8062198b2d17c4362a88c65</v>
+        <v>61e12aaabe2c59ab60d879b18a7d8b89b7ddf9a8a71498e190e883353f7167c5</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>character_largeimage_h0152.ab</v>
+        <v>character_largeimage_h0150.ab</v>
       </c>
       <c r="B292" t="str">
-        <v>character_largeimage_h0152.ab</v>
+        <v>character_largeimage_h0150.ab</v>
       </c>
       <c r="C292">
-        <v>3232149</v>
+        <v>4037956</v>
       </c>
       <c r="D292" t="str">
         <v>Stage_1</v>
@@ -6239,18 +6239,18 @@
         <v>0</v>
       </c>
       <c r="F292" t="str">
-        <v>3d27bb9df8d360989f595c83964e2a94d8e5fd22b8f7a6c1193e7c4cc257a6dd</v>
+        <v>d7d2064c4b7799f6f05c0bea7820d77879988674b6cbb863fc6ffff294516853</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>character_largeimage_h0154.ab</v>
+        <v>character_largeimage_h0151.ab</v>
       </c>
       <c r="B293" t="str">
-        <v>character_largeimage_h0154.ab</v>
+        <v>character_largeimage_h0151.ab</v>
       </c>
       <c r="C293">
-        <v>3117108</v>
+        <v>2589817</v>
       </c>
       <c r="D293" t="str">
         <v>Stage_1</v>
@@ -6259,18 +6259,18 @@
         <v>0</v>
       </c>
       <c r="F293" t="str">
-        <v>2ce3ea84a16615d2d212b5c34a99171686d2a4e36cff83cf509ebbfb367e0b2d</v>
+        <v>e319306d4c24fd23c4a7473ad0c6218a96d6abcbf8062198b2d17c4362a88c65</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>character_largeimage_h0157.ab</v>
+        <v>character_largeimage_h0152.ab</v>
       </c>
       <c r="B294" t="str">
-        <v>character_largeimage_h0157.ab</v>
+        <v>character_largeimage_h0152.ab</v>
       </c>
       <c r="C294">
-        <v>4175238</v>
+        <v>3232149</v>
       </c>
       <c r="D294" t="str">
         <v>Stage_1</v>
@@ -6279,18 +6279,18 @@
         <v>0</v>
       </c>
       <c r="F294" t="str">
-        <v>54cf04627438a03b859ddb2f4687af86522a3814168449e0f183e1fc0bb2a847</v>
+        <v>3d27bb9df8d360989f595c83964e2a94d8e5fd22b8f7a6c1193e7c4cc257a6dd</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>character_largeimage_h0159.ab</v>
+        <v>character_largeimage_h0154.ab</v>
       </c>
       <c r="B295" t="str">
-        <v>character_largeimage_h0159.ab</v>
+        <v>character_largeimage_h0154.ab</v>
       </c>
       <c r="C295">
-        <v>3438941</v>
+        <v>3117108</v>
       </c>
       <c r="D295" t="str">
         <v>Stage_1</v>
@@ -6299,18 +6299,18 @@
         <v>0</v>
       </c>
       <c r="F295" t="str">
-        <v>69896b88d7b878ed3a9ae0ccaac412a1dcead089da47686152318321fd1de238</v>
+        <v>2ce3ea84a16615d2d212b5c34a99171686d2a4e36cff83cf509ebbfb367e0b2d</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>character_largeimage_h0161.ab</v>
+        <v>character_largeimage_h0157.ab</v>
       </c>
       <c r="B296" t="str">
-        <v>character_largeimage_h0161.ab</v>
+        <v>character_largeimage_h0157.ab</v>
       </c>
       <c r="C296">
-        <v>4097341</v>
+        <v>4175238</v>
       </c>
       <c r="D296" t="str">
         <v>Stage_1</v>
@@ -6319,18 +6319,18 @@
         <v>0</v>
       </c>
       <c r="F296" t="str">
-        <v>a660b7d68977f955ba7ceced1adadab138e4fc76cc5208da43d9369b9dc59e23</v>
+        <v>54cf04627438a03b859ddb2f4687af86522a3814168449e0f183e1fc0bb2a847</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>character_largeimage_h0162.ab</v>
+        <v>character_largeimage_h0159.ab</v>
       </c>
       <c r="B297" t="str">
-        <v>character_largeimage_h0162.ab</v>
+        <v>character_largeimage_h0159.ab</v>
       </c>
       <c r="C297">
-        <v>750978</v>
+        <v>3438941</v>
       </c>
       <c r="D297" t="str">
         <v>Stage_1</v>
@@ -6339,18 +6339,18 @@
         <v>0</v>
       </c>
       <c r="F297" t="str">
-        <v>38de7487f089a655ef8ef162c0d101525d83e7f406dabf459b3a9c8390380122</v>
+        <v>69896b88d7b878ed3a9ae0ccaac412a1dcead089da47686152318321fd1de238</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>character_largeimage_h0163.ab</v>
+        <v>character_largeimage_h0161.ab</v>
       </c>
       <c r="B298" t="str">
-        <v>character_largeimage_h0163.ab</v>
+        <v>character_largeimage_h0161.ab</v>
       </c>
       <c r="C298">
-        <v>2078410</v>
+        <v>4097341</v>
       </c>
       <c r="D298" t="str">
         <v>Stage_1</v>
@@ -6359,18 +6359,18 @@
         <v>0</v>
       </c>
       <c r="F298" t="str">
-        <v>6cb30643d3b6c9be725cce1f64f07b98426ba01da9ad3e9b127862d8b8dbccf8</v>
+        <v>a660b7d68977f955ba7ceced1adadab138e4fc76cc5208da43d9369b9dc59e23</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>character_largeimage_h0164.ab</v>
+        <v>character_largeimage_h0162.ab</v>
       </c>
       <c r="B299" t="str">
-        <v>character_largeimage_h0164.ab</v>
+        <v>character_largeimage_h0162.ab</v>
       </c>
       <c r="C299">
-        <v>562150</v>
+        <v>750978</v>
       </c>
       <c r="D299" t="str">
         <v>Stage_1</v>
@@ -6379,18 +6379,18 @@
         <v>0</v>
       </c>
       <c r="F299" t="str">
-        <v>8950a764fe423f950c36d8d8c330f207f071139213a0be60bebb3ded5fe329cd</v>
+        <v>38de7487f089a655ef8ef162c0d101525d83e7f406dabf459b3a9c8390380122</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>character_largeimage_h0165.ab</v>
+        <v>character_largeimage_h0163.ab</v>
       </c>
       <c r="B300" t="str">
-        <v>character_largeimage_h0165.ab</v>
+        <v>character_largeimage_h0163.ab</v>
       </c>
       <c r="C300">
-        <v>796221</v>
+        <v>2078410</v>
       </c>
       <c r="D300" t="str">
         <v>Stage_1</v>
@@ -6399,18 +6399,18 @@
         <v>0</v>
       </c>
       <c r="F300" t="str">
-        <v>1e0a607d278479f68829b034dc3e31e3ff73f88dee2ff778c5c4398d845d97e6</v>
+        <v>6cb30643d3b6c9be725cce1f64f07b98426ba01da9ad3e9b127862d8b8dbccf8</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>character_largeimage_h0166.ab</v>
+        <v>character_largeimage_h0164.ab</v>
       </c>
       <c r="B301" t="str">
-        <v>character_largeimage_h0166.ab</v>
+        <v>character_largeimage_h0164.ab</v>
       </c>
       <c r="C301">
-        <v>770702</v>
+        <v>562150</v>
       </c>
       <c r="D301" t="str">
         <v>Stage_1</v>
@@ -6419,18 +6419,18 @@
         <v>0</v>
       </c>
       <c r="F301" t="str">
-        <v>e434b87a3241dae1f7d81acd86f8102e93895ec6ab30272f57fd9721c6d1bcfa</v>
+        <v>8950a764fe423f950c36d8d8c330f207f071139213a0be60bebb3ded5fe329cd</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>character_largeimage_h0167.ab</v>
+        <v>character_largeimage_h0165.ab</v>
       </c>
       <c r="B302" t="str">
-        <v>character_largeimage_h0167.ab</v>
+        <v>character_largeimage_h0165.ab</v>
       </c>
       <c r="C302">
-        <v>820636</v>
+        <v>796221</v>
       </c>
       <c r="D302" t="str">
         <v>Stage_1</v>
@@ -6439,18 +6439,18 @@
         <v>0</v>
       </c>
       <c r="F302" t="str">
-        <v>c5d28976c731cae2d777b0675466878565052af34c557d71d7009162fbe813e8</v>
+        <v>1e0a607d278479f68829b034dc3e31e3ff73f88dee2ff778c5c4398d845d97e6</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>character_largeimage_h0168.ab</v>
+        <v>character_largeimage_h0166.ab</v>
       </c>
       <c r="B303" t="str">
-        <v>character_largeimage_h0168.ab</v>
+        <v>character_largeimage_h0166.ab</v>
       </c>
       <c r="C303">
-        <v>817925</v>
+        <v>770702</v>
       </c>
       <c r="D303" t="str">
         <v>Stage_1</v>
@@ -6459,18 +6459,18 @@
         <v>0</v>
       </c>
       <c r="F303" t="str">
-        <v>d596388ecc3145e4279aed0ec7f8b25c8a5abbfeaf17c76560902f42fd6fd46c</v>
+        <v>e434b87a3241dae1f7d81acd86f8102e93895ec6ab30272f57fd9721c6d1bcfa</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>character_largeimage_h0169.ab</v>
+        <v>character_largeimage_h0167.ab</v>
       </c>
       <c r="B304" t="str">
-        <v>character_largeimage_h0169.ab</v>
+        <v>character_largeimage_h0167.ab</v>
       </c>
       <c r="C304">
-        <v>830548</v>
+        <v>820636</v>
       </c>
       <c r="D304" t="str">
         <v>Stage_1</v>
@@ -6479,18 +6479,18 @@
         <v>0</v>
       </c>
       <c r="F304" t="str">
-        <v>694f5ecefeccf73e0d79fcbde42e9a7552d32c2dc69d3894af27e1b92e9c9327</v>
+        <v>c5d28976c731cae2d777b0675466878565052af34c557d71d7009162fbe813e8</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>character_largeimage_h0170.ab</v>
+        <v>character_largeimage_h0168.ab</v>
       </c>
       <c r="B305" t="str">
-        <v>character_largeimage_h0170.ab</v>
+        <v>character_largeimage_h0168.ab</v>
       </c>
       <c r="C305">
-        <v>802577</v>
+        <v>817925</v>
       </c>
       <c r="D305" t="str">
         <v>Stage_1</v>
@@ -6499,18 +6499,18 @@
         <v>0</v>
       </c>
       <c r="F305" t="str">
-        <v>22ce1b1174d04d190ad9105ae99b8268e4b5b4bce7d43dbd7bac3a6930162aa5</v>
+        <v>d596388ecc3145e4279aed0ec7f8b25c8a5abbfeaf17c76560902f42fd6fd46c</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>character_largeimage_h0171.ab</v>
+        <v>character_largeimage_h0169.ab</v>
       </c>
       <c r="B306" t="str">
-        <v>character_largeimage_h0171.ab</v>
+        <v>character_largeimage_h0169.ab</v>
       </c>
       <c r="C306">
-        <v>782755</v>
+        <v>830548</v>
       </c>
       <c r="D306" t="str">
         <v>Stage_1</v>
@@ -6519,18 +6519,18 @@
         <v>0</v>
       </c>
       <c r="F306" t="str">
-        <v>fa33b1b6747266a27a42f0fe654fadc5c45d1b7ca97b1b8f2d52b3b0d3c7c647</v>
+        <v>694f5ecefeccf73e0d79fcbde42e9a7552d32c2dc69d3894af27e1b92e9c9327</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>character_largeimage_h0172.ab</v>
+        <v>character_largeimage_h0170.ab</v>
       </c>
       <c r="B307" t="str">
-        <v>character_largeimage_h0172.ab</v>
+        <v>character_largeimage_h0170.ab</v>
       </c>
       <c r="C307">
-        <v>783966</v>
+        <v>802577</v>
       </c>
       <c r="D307" t="str">
         <v>Stage_1</v>
@@ -6539,18 +6539,18 @@
         <v>0</v>
       </c>
       <c r="F307" t="str">
-        <v>6c80e0e30faa685a6e8861942e4283309563a109980a7b43ad0f6c8f7b3fd812</v>
+        <v>22ce1b1174d04d190ad9105ae99b8268e4b5b4bce7d43dbd7bac3a6930162aa5</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>character_largeimage_h0174.ab</v>
+        <v>character_largeimage_h0171.ab</v>
       </c>
       <c r="B308" t="str">
-        <v>character_largeimage_h0174.ab</v>
+        <v>character_largeimage_h0171.ab</v>
       </c>
       <c r="C308">
-        <v>818586</v>
+        <v>782755</v>
       </c>
       <c r="D308" t="str">
         <v>Stage_1</v>
@@ -6559,18 +6559,18 @@
         <v>0</v>
       </c>
       <c r="F308" t="str">
-        <v>4189f28a4927c0faa536e86f0b2978390507c7e2a3f7182854f18827713a9ae6</v>
+        <v>fa33b1b6747266a27a42f0fe654fadc5c45d1b7ca97b1b8f2d52b3b0d3c7c647</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>character_largeimage_h0175.ab</v>
+        <v>character_largeimage_h0172.ab</v>
       </c>
       <c r="B309" t="str">
-        <v>character_largeimage_h0175.ab</v>
+        <v>character_largeimage_h0172.ab</v>
       </c>
       <c r="C309">
-        <v>804643</v>
+        <v>783966</v>
       </c>
       <c r="D309" t="str">
         <v>Stage_1</v>
@@ -6579,18 +6579,18 @@
         <v>0</v>
       </c>
       <c r="F309" t="str">
-        <v>5779e4f64a588b7ba406c3f77cbe5a7623a881612f260d82d0fdd015454ce4e5</v>
+        <v>6c80e0e30faa685a6e8861942e4283309563a109980a7b43ad0f6c8f7b3fd812</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>character_largeimage_h0176.ab</v>
+        <v>character_largeimage_h0174.ab</v>
       </c>
       <c r="B310" t="str">
-        <v>character_largeimage_h0176.ab</v>
+        <v>character_largeimage_h0174.ab</v>
       </c>
       <c r="C310">
-        <v>815725</v>
+        <v>818586</v>
       </c>
       <c r="D310" t="str">
         <v>Stage_1</v>
@@ -6599,18 +6599,18 @@
         <v>0</v>
       </c>
       <c r="F310" t="str">
-        <v>670e37924a1dc65b3257f7ea9ea57af53ef77c50e363aa558450edda73a3971e</v>
+        <v>4189f28a4927c0faa536e86f0b2978390507c7e2a3f7182854f18827713a9ae6</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>character_largeimage_h0177.ab</v>
+        <v>character_largeimage_h0175.ab</v>
       </c>
       <c r="B311" t="str">
-        <v>character_largeimage_h0177.ab</v>
+        <v>character_largeimage_h0175.ab</v>
       </c>
       <c r="C311">
-        <v>787384</v>
+        <v>804643</v>
       </c>
       <c r="D311" t="str">
         <v>Stage_1</v>
@@ -6619,18 +6619,18 @@
         <v>0</v>
       </c>
       <c r="F311" t="str">
-        <v>72c7aa064bb39180b9f70c05d799875beb09b87e0863e05312f2b613f6296aaa</v>
+        <v>5779e4f64a588b7ba406c3f77cbe5a7623a881612f260d82d0fdd015454ce4e5</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>character_largeimage_h0179.ab</v>
+        <v>character_largeimage_h0176.ab</v>
       </c>
       <c r="B312" t="str">
-        <v>character_largeimage_h0179.ab</v>
+        <v>character_largeimage_h0176.ab</v>
       </c>
       <c r="C312">
-        <v>3226990</v>
+        <v>815725</v>
       </c>
       <c r="D312" t="str">
         <v>Stage_1</v>
@@ -6639,18 +6639,18 @@
         <v>0</v>
       </c>
       <c r="F312" t="str">
-        <v>78cff653adce00a0271b9b386462b605c5155aa5328a916a2c1e7472ef53800b</v>
+        <v>670e37924a1dc65b3257f7ea9ea57af53ef77c50e363aa558450edda73a3971e</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>character_largeimage_h0183.ab</v>
+        <v>character_largeimage_h0177.ab</v>
       </c>
       <c r="B313" t="str">
-        <v>character_largeimage_h0183.ab</v>
+        <v>character_largeimage_h0177.ab</v>
       </c>
       <c r="C313">
-        <v>3520720</v>
+        <v>787384</v>
       </c>
       <c r="D313" t="str">
         <v>Stage_1</v>
@@ -6659,18 +6659,18 @@
         <v>0</v>
       </c>
       <c r="F313" t="str">
-        <v>f0b995ef5d339afb76d7292b967c27ba26b3f240505eddecf275b18d014acabe</v>
+        <v>72c7aa064bb39180b9f70c05d799875beb09b87e0863e05312f2b613f6296aaa</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>character_largeimage_h0185.ab</v>
+        <v>character_largeimage_h0179.ab</v>
       </c>
       <c r="B314" t="str">
-        <v>character_largeimage_h0185.ab</v>
+        <v>character_largeimage_h0179.ab</v>
       </c>
       <c r="C314">
-        <v>2771089</v>
+        <v>3226990</v>
       </c>
       <c r="D314" t="str">
         <v>Stage_1</v>
@@ -6679,18 +6679,18 @@
         <v>0</v>
       </c>
       <c r="F314" t="str">
-        <v>bfa55cdf6f0750acee979cdf5cdc7840f4de769c34b7e38431644cf7a21ae6ba</v>
+        <v>78cff653adce00a0271b9b386462b605c5155aa5328a916a2c1e7472ef53800b</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>character_largeimage_h0186.ab</v>
+        <v>character_largeimage_h0183.ab</v>
       </c>
       <c r="B315" t="str">
-        <v>character_largeimage_h0186.ab</v>
+        <v>character_largeimage_h0183.ab</v>
       </c>
       <c r="C315">
-        <v>3669448</v>
+        <v>3520720</v>
       </c>
       <c r="D315" t="str">
         <v>Stage_1</v>
@@ -6699,18 +6699,18 @@
         <v>0</v>
       </c>
       <c r="F315" t="str">
-        <v>d9f408df598bbed9f98731ebbbc24dd54c87d8faf6db4f9f6ed0bbdc627164f9</v>
+        <v>f0b995ef5d339afb76d7292b967c27ba26b3f240505eddecf275b18d014acabe</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>character_largeimage_h0190.ab</v>
+        <v>character_largeimage_h0185.ab</v>
       </c>
       <c r="B316" t="str">
-        <v>character_largeimage_h0190.ab</v>
+        <v>character_largeimage_h0185.ab</v>
       </c>
       <c r="C316">
-        <v>3422472</v>
+        <v>2771089</v>
       </c>
       <c r="D316" t="str">
         <v>Stage_1</v>
@@ -6719,18 +6719,18 @@
         <v>0</v>
       </c>
       <c r="F316" t="str">
-        <v>6a96ed9bc7dae9b6a94560a7a2a2c4c968aa9c666608866700784adbd28efe9e</v>
+        <v>bfa55cdf6f0750acee979cdf5cdc7840f4de769c34b7e38431644cf7a21ae6ba</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>character_largeimage_h0191.ab</v>
+        <v>character_largeimage_h0186.ab</v>
       </c>
       <c r="B317" t="str">
-        <v>character_largeimage_h0191.ab</v>
+        <v>character_largeimage_h0186.ab</v>
       </c>
       <c r="C317">
-        <v>808827</v>
+        <v>3669448</v>
       </c>
       <c r="D317" t="str">
         <v>Stage_1</v>
@@ -6739,18 +6739,18 @@
         <v>0</v>
       </c>
       <c r="F317" t="str">
-        <v>b849caca8249392ed9cb5fbc69ad00daebd22a57c5dbe8dd0ef8e36a983745d0</v>
+        <v>d9f408df598bbed9f98731ebbbc24dd54c87d8faf6db4f9f6ed0bbdc627164f9</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>character_largeimage_h0192.ab</v>
+        <v>character_largeimage_h0190.ab</v>
       </c>
       <c r="B318" t="str">
-        <v>character_largeimage_h0192.ab</v>
+        <v>character_largeimage_h0190.ab</v>
       </c>
       <c r="C318">
-        <v>792810</v>
+        <v>3422472</v>
       </c>
       <c r="D318" t="str">
         <v>Stage_1</v>
@@ -6759,18 +6759,18 @@
         <v>0</v>
       </c>
       <c r="F318" t="str">
-        <v>2b02b549d1958dcd7765bd6847f70978d863dd130ffa8e646f5fdc031cdc8351</v>
+        <v>6a96ed9bc7dae9b6a94560a7a2a2c4c968aa9c666608866700784adbd28efe9e</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>character_largeimage_h0193.ab</v>
+        <v>character_largeimage_h0191.ab</v>
       </c>
       <c r="B319" t="str">
-        <v>character_largeimage_h0193.ab</v>
+        <v>character_largeimage_h0191.ab</v>
       </c>
       <c r="C319">
-        <v>725025</v>
+        <v>808827</v>
       </c>
       <c r="D319" t="str">
         <v>Stage_1</v>
@@ -6779,18 +6779,18 @@
         <v>0</v>
       </c>
       <c r="F319" t="str">
-        <v>c54d37a9842bc35f6a53430f7b78bf25398c17e364d4fd7af908f2f9e6a41a4a</v>
+        <v>b849caca8249392ed9cb5fbc69ad00daebd22a57c5dbe8dd0ef8e36a983745d0</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>character_largeimage_h0194.ab</v>
+        <v>character_largeimage_h0192.ab</v>
       </c>
       <c r="B320" t="str">
-        <v>character_largeimage_h0194.ab</v>
+        <v>character_largeimage_h0192.ab</v>
       </c>
       <c r="C320">
-        <v>785465</v>
+        <v>792810</v>
       </c>
       <c r="D320" t="str">
         <v>Stage_1</v>
@@ -6799,18 +6799,18 @@
         <v>0</v>
       </c>
       <c r="F320" t="str">
-        <v>36cc8950d881f726e02b7e855085ff44ade33666176018a788d9faec4f87090f</v>
+        <v>2b02b549d1958dcd7765bd6847f70978d863dd130ffa8e646f5fdc031cdc8351</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>character_largeimage_h0196.ab</v>
+        <v>character_largeimage_h0193.ab</v>
       </c>
       <c r="B321" t="str">
-        <v>character_largeimage_h0196.ab</v>
+        <v>character_largeimage_h0193.ab</v>
       </c>
       <c r="C321">
-        <v>815412</v>
+        <v>725025</v>
       </c>
       <c r="D321" t="str">
         <v>Stage_1</v>
@@ -6819,18 +6819,18 @@
         <v>0</v>
       </c>
       <c r="F321" t="str">
-        <v>6a6748aa0319948886214cb8c63c8cec143ea660d596ef8d6d978fdd3511b82a</v>
+        <v>c54d37a9842bc35f6a53430f7b78bf25398c17e364d4fd7af908f2f9e6a41a4a</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>character_largeimage_h0197.ab</v>
+        <v>character_largeimage_h0194.ab</v>
       </c>
       <c r="B322" t="str">
-        <v>character_largeimage_h0197.ab</v>
+        <v>character_largeimage_h0194.ab</v>
       </c>
       <c r="C322">
-        <v>798179</v>
+        <v>785465</v>
       </c>
       <c r="D322" t="str">
         <v>Stage_1</v>
@@ -6839,18 +6839,18 @@
         <v>0</v>
       </c>
       <c r="F322" t="str">
-        <v>c7d74889421f50783e19f16bfee0461d528a543471b9b45ae4aa772b774876c0</v>
+        <v>36cc8950d881f726e02b7e855085ff44ade33666176018a788d9faec4f87090f</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>character_largeimage_h0198.ab</v>
+        <v>character_largeimage_h0196.ab</v>
       </c>
       <c r="B323" t="str">
-        <v>character_largeimage_h0198.ab</v>
+        <v>character_largeimage_h0196.ab</v>
       </c>
       <c r="C323">
-        <v>781740</v>
+        <v>815412</v>
       </c>
       <c r="D323" t="str">
         <v>Stage_1</v>
@@ -6859,18 +6859,18 @@
         <v>0</v>
       </c>
       <c r="F323" t="str">
-        <v>2055d9937e4e0b0a8811536085a0478651eb0f01fc6dfec0c170ac2391a1d44b</v>
+        <v>6a6748aa0319948886214cb8c63c8cec143ea660d596ef8d6d978fdd3511b82a</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>character_largeimage_h0199.ab</v>
+        <v>character_largeimage_h0197.ab</v>
       </c>
       <c r="B324" t="str">
-        <v>character_largeimage_h0199.ab</v>
+        <v>character_largeimage_h0197.ab</v>
       </c>
       <c r="C324">
-        <v>723932</v>
+        <v>798179</v>
       </c>
       <c r="D324" t="str">
         <v>Stage_1</v>
@@ -6879,18 +6879,18 @@
         <v>0</v>
       </c>
       <c r="F324" t="str">
-        <v>54fb809610bab1d842ba2f6c9092c659035994f46801d54970375ee2ea3c5dac</v>
+        <v>c7d74889421f50783e19f16bfee0461d528a543471b9b45ae4aa772b774876c0</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>character_largeimage_h0200.ab</v>
+        <v>character_largeimage_h0198.ab</v>
       </c>
       <c r="B325" t="str">
-        <v>character_largeimage_h0200.ab</v>
+        <v>character_largeimage_h0198.ab</v>
       </c>
       <c r="C325">
-        <v>817588</v>
+        <v>781740</v>
       </c>
       <c r="D325" t="str">
         <v>Stage_1</v>
@@ -6899,18 +6899,18 @@
         <v>0</v>
       </c>
       <c r="F325" t="str">
-        <v>b19a3f8eb2a00ec2e2fafcdb4ae347a5e27c5d935a48a989071d64f8daa7c711</v>
+        <v>2055d9937e4e0b0a8811536085a0478651eb0f01fc6dfec0c170ac2391a1d44b</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>character_largeimage_h0201.ab</v>
+        <v>character_largeimage_h0199.ab</v>
       </c>
       <c r="B326" t="str">
-        <v>character_largeimage_h0201.ab</v>
+        <v>character_largeimage_h0199.ab</v>
       </c>
       <c r="C326">
-        <v>835275</v>
+        <v>723932</v>
       </c>
       <c r="D326" t="str">
         <v>Stage_1</v>
@@ -6919,18 +6919,18 @@
         <v>0</v>
       </c>
       <c r="F326" t="str">
-        <v>976aa2fcf5e09deb4a3ab659fb8a8e9afc3c27bbb832920dde15ea1cb2d990db</v>
+        <v>54fb809610bab1d842ba2f6c9092c659035994f46801d54970375ee2ea3c5dac</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>character_largeimage_h0203.ab</v>
+        <v>character_largeimage_h0200.ab</v>
       </c>
       <c r="B327" t="str">
-        <v>character_largeimage_h0203.ab</v>
+        <v>character_largeimage_h0200.ab</v>
       </c>
       <c r="C327">
-        <v>810774</v>
+        <v>817588</v>
       </c>
       <c r="D327" t="str">
         <v>Stage_1</v>
@@ -6939,18 +6939,18 @@
         <v>0</v>
       </c>
       <c r="F327" t="str">
-        <v>8a135d2928943c0ee8f93db24bb041ac0925554dfa5e69c1d8ed784c1517bab2</v>
+        <v>b19a3f8eb2a00ec2e2fafcdb4ae347a5e27c5d935a48a989071d64f8daa7c711</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>character_largeimage_h0208.ab</v>
+        <v>character_largeimage_h0201.ab</v>
       </c>
       <c r="B328" t="str">
-        <v>character_largeimage_h0208.ab</v>
+        <v>character_largeimage_h0201.ab</v>
       </c>
       <c r="C328">
-        <v>782587</v>
+        <v>835275</v>
       </c>
       <c r="D328" t="str">
         <v>Stage_1</v>
@@ -6959,18 +6959,18 @@
         <v>0</v>
       </c>
       <c r="F328" t="str">
-        <v>c8b75ce568e328d85fb21c02c1ab9c4309d261e1771ad612854e065b528e80b6</v>
+        <v>976aa2fcf5e09deb4a3ab659fb8a8e9afc3c27bbb832920dde15ea1cb2d990db</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>character_largeimage_h0209.ab</v>
+        <v>character_largeimage_h0203.ab</v>
       </c>
       <c r="B329" t="str">
-        <v>character_largeimage_h0209.ab</v>
+        <v>character_largeimage_h0203.ab</v>
       </c>
       <c r="C329">
-        <v>832318</v>
+        <v>810774</v>
       </c>
       <c r="D329" t="str">
         <v>Stage_1</v>
@@ -6979,18 +6979,18 @@
         <v>0</v>
       </c>
       <c r="F329" t="str">
-        <v>551c9d38c10aaa35dc668fa95d4ab634ea90021e999ec43e3b3692a33f37308c</v>
+        <v>8a135d2928943c0ee8f93db24bb041ac0925554dfa5e69c1d8ed784c1517bab2</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>character_largeimage_h0210.ab</v>
+        <v>character_largeimage_h0208.ab</v>
       </c>
       <c r="B330" t="str">
-        <v>character_largeimage_h0210.ab</v>
+        <v>character_largeimage_h0208.ab</v>
       </c>
       <c r="C330">
-        <v>825127</v>
+        <v>782587</v>
       </c>
       <c r="D330" t="str">
         <v>Stage_1</v>
@@ -6999,18 +6999,18 @@
         <v>0</v>
       </c>
       <c r="F330" t="str">
-        <v>8589c6aa5e2a1402cd077069b6a7c5b7963e4990bf24ef1ae425fa5b6fe77851</v>
+        <v>c8b75ce568e328d85fb21c02c1ab9c4309d261e1771ad612854e065b528e80b6</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>character_largeimage_h0213.ab</v>
+        <v>character_largeimage_h0209.ab</v>
       </c>
       <c r="B331" t="str">
-        <v>character_largeimage_h0213.ab</v>
+        <v>character_largeimage_h0209.ab</v>
       </c>
       <c r="C331">
-        <v>765539</v>
+        <v>832318</v>
       </c>
       <c r="D331" t="str">
         <v>Stage_1</v>
@@ -7019,18 +7019,18 @@
         <v>0</v>
       </c>
       <c r="F331" t="str">
-        <v>7ceaafb884feff69f0cad1625495c0b9623b4abcdb13918dee5ec9782b9e7c6f</v>
+        <v>551c9d38c10aaa35dc668fa95d4ab634ea90021e999ec43e3b3692a33f37308c</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>character_largeimage_h0215.ab</v>
+        <v>character_largeimage_h0210.ab</v>
       </c>
       <c r="B332" t="str">
-        <v>character_largeimage_h0215.ab</v>
+        <v>character_largeimage_h0210.ab</v>
       </c>
       <c r="C332">
-        <v>759394</v>
+        <v>825127</v>
       </c>
       <c r="D332" t="str">
         <v>Stage_1</v>
@@ -7039,18 +7039,18 @@
         <v>0</v>
       </c>
       <c r="F332" t="str">
-        <v>8e6f4b217298f11e5493e50b5f41aefd8b49f8f0d3d68747e30ebde5fcb495af</v>
+        <v>8589c6aa5e2a1402cd077069b6a7c5b7963e4990bf24ef1ae425fa5b6fe77851</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>character_largeimage_h0216.ab</v>
+        <v>character_largeimage_h0213.ab</v>
       </c>
       <c r="B333" t="str">
-        <v>character_largeimage_h0216.ab</v>
+        <v>character_largeimage_h0213.ab</v>
       </c>
       <c r="C333">
-        <v>736440</v>
+        <v>765539</v>
       </c>
       <c r="D333" t="str">
         <v>Stage_1</v>
@@ -7059,18 +7059,18 @@
         <v>0</v>
       </c>
       <c r="F333" t="str">
-        <v>1ba74f46cf112a8fbabd9dbe94f3e47c6b8fae0f59caf2cbd33d263176d536eb</v>
+        <v>7ceaafb884feff69f0cad1625495c0b9623b4abcdb13918dee5ec9782b9e7c6f</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>character_largeimage_h0217.ab</v>
+        <v>character_largeimage_h0215.ab</v>
       </c>
       <c r="B334" t="str">
-        <v>character_largeimage_h0217.ab</v>
+        <v>character_largeimage_h0215.ab</v>
       </c>
       <c r="C334">
-        <v>828877</v>
+        <v>759394</v>
       </c>
       <c r="D334" t="str">
         <v>Stage_1</v>
@@ -7079,18 +7079,18 @@
         <v>0</v>
       </c>
       <c r="F334" t="str">
-        <v>84f2c50e0b0f149fc2a5da0a87b10af733ba6c544daf4e3f9dd4c2c2e702fe60</v>
+        <v>8e6f4b217298f11e5493e50b5f41aefd8b49f8f0d3d68747e30ebde5fcb495af</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>character_largeimage_h0219.ab</v>
+        <v>character_largeimage_h0216.ab</v>
       </c>
       <c r="B335" t="str">
-        <v>character_largeimage_h0219.ab</v>
+        <v>character_largeimage_h0216.ab</v>
       </c>
       <c r="C335">
-        <v>817529</v>
+        <v>736440</v>
       </c>
       <c r="D335" t="str">
         <v>Stage_1</v>
@@ -7099,18 +7099,18 @@
         <v>0</v>
       </c>
       <c r="F335" t="str">
-        <v>87101cadb86464c4b19e924805d524f2a1700367f5a505fb1ae5f7bc289886f2</v>
+        <v>1ba74f46cf112a8fbabd9dbe94f3e47c6b8fae0f59caf2cbd33d263176d536eb</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>character_largeimage_h0220.ab</v>
+        <v>character_largeimage_h0217.ab</v>
       </c>
       <c r="B336" t="str">
-        <v>character_largeimage_h0220.ab</v>
+        <v>character_largeimage_h0217.ab</v>
       </c>
       <c r="C336">
-        <v>689304</v>
+        <v>828877</v>
       </c>
       <c r="D336" t="str">
         <v>Stage_1</v>
@@ -7119,18 +7119,18 @@
         <v>0</v>
       </c>
       <c r="F336" t="str">
-        <v>0838c201cac6aa71480937da9424b05a4dfbe7d617bb0811c64a08f8fbc44329</v>
+        <v>84f2c50e0b0f149fc2a5da0a87b10af733ba6c544daf4e3f9dd4c2c2e702fe60</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>character_largeimage_h0221.ab</v>
+        <v>character_largeimage_h0219.ab</v>
       </c>
       <c r="B337" t="str">
-        <v>character_largeimage_h0221.ab</v>
+        <v>character_largeimage_h0219.ab</v>
       </c>
       <c r="C337">
-        <v>774852</v>
+        <v>817529</v>
       </c>
       <c r="D337" t="str">
         <v>Stage_1</v>
@@ -7139,18 +7139,18 @@
         <v>0</v>
       </c>
       <c r="F337" t="str">
-        <v>260c6ef2907458fb0b24e79b4fdc8f2daf248b54e954c202b89e87fa45a79917</v>
+        <v>87101cadb86464c4b19e924805d524f2a1700367f5a505fb1ae5f7bc289886f2</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>character_largeimage_h0224.ab</v>
+        <v>character_largeimage_h0220.ab</v>
       </c>
       <c r="B338" t="str">
-        <v>character_largeimage_h0224.ab</v>
+        <v>character_largeimage_h0220.ab</v>
       </c>
       <c r="C338">
-        <v>734210</v>
+        <v>689304</v>
       </c>
       <c r="D338" t="str">
         <v>Stage_1</v>
@@ -7159,18 +7159,18 @@
         <v>0</v>
       </c>
       <c r="F338" t="str">
-        <v>8f88f1319c7298174ac3aa8a82b6986761610cbb74ef14c82c7e1ede1fc0b15d</v>
+        <v>0838c201cac6aa71480937da9424b05a4dfbe7d617bb0811c64a08f8fbc44329</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>character_largeimage_h0226.ab</v>
+        <v>character_largeimage_h0221.ab</v>
       </c>
       <c r="B339" t="str">
-        <v>character_largeimage_h0226.ab</v>
+        <v>character_largeimage_h0221.ab</v>
       </c>
       <c r="C339">
-        <v>761235</v>
+        <v>774852</v>
       </c>
       <c r="D339" t="str">
         <v>Stage_1</v>
@@ -7179,18 +7179,18 @@
         <v>0</v>
       </c>
       <c r="F339" t="str">
-        <v>6bc4336199b83047446c82c6a230574f05b6e130a41d9f33770766aeac9436f2</v>
+        <v>260c6ef2907458fb0b24e79b4fdc8f2daf248b54e954c202b89e87fa45a79917</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>character_largeimage_h0227.ab</v>
+        <v>character_largeimage_h0224.ab</v>
       </c>
       <c r="B340" t="str">
-        <v>character_largeimage_h0227.ab</v>
+        <v>character_largeimage_h0224.ab</v>
       </c>
       <c r="C340">
-        <v>786760</v>
+        <v>734210</v>
       </c>
       <c r="D340" t="str">
         <v>Stage_1</v>
@@ -7199,18 +7199,18 @@
         <v>0</v>
       </c>
       <c r="F340" t="str">
-        <v>0ec3a2ddea2c5f14762b1d53cf2a6c9b959342b7c2d7cb8c53f5de78389a1a9f</v>
+        <v>8f88f1319c7298174ac3aa8a82b6986761610cbb74ef14c82c7e1ede1fc0b15d</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>character_largeimage_h0230.ab</v>
+        <v>character_largeimage_h0226.ab</v>
       </c>
       <c r="B341" t="str">
-        <v>character_largeimage_h0230.ab</v>
+        <v>character_largeimage_h0226.ab</v>
       </c>
       <c r="C341">
-        <v>795281</v>
+        <v>761235</v>
       </c>
       <c r="D341" t="str">
         <v>Stage_1</v>
@@ -7219,18 +7219,18 @@
         <v>0</v>
       </c>
       <c r="F341" t="str">
-        <v>29ca1d6c0d021948d89276ee888dd3f034a0a0efe30c90a4af695d44e14e409d</v>
+        <v>6bc4336199b83047446c82c6a230574f05b6e130a41d9f33770766aeac9436f2</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>character_largeimage_h0232.ab</v>
+        <v>character_largeimage_h0227.ab</v>
       </c>
       <c r="B342" t="str">
-        <v>character_largeimage_h0232.ab</v>
+        <v>character_largeimage_h0227.ab</v>
       </c>
       <c r="C342">
-        <v>2084078</v>
+        <v>786760</v>
       </c>
       <c r="D342" t="str">
         <v>Stage_1</v>
@@ -7239,18 +7239,18 @@
         <v>0</v>
       </c>
       <c r="F342" t="str">
-        <v>dfe3d19d68019845ae4ece6c9574a5495c0a7e2d7b2bd5731672a07a39334105</v>
+        <v>0ec3a2ddea2c5f14762b1d53cf2a6c9b959342b7c2d7cb8c53f5de78389a1a9f</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>character_largeimage_h0233.ab</v>
+        <v>character_largeimage_h0230.ab</v>
       </c>
       <c r="B343" t="str">
-        <v>character_largeimage_h0233.ab</v>
+        <v>character_largeimage_h0230.ab</v>
       </c>
       <c r="C343">
-        <v>3216689</v>
+        <v>795281</v>
       </c>
       <c r="D343" t="str">
         <v>Stage_1</v>
@@ -7259,18 +7259,18 @@
         <v>0</v>
       </c>
       <c r="F343" t="str">
-        <v>aef3828cf7528b7b93a7e0d7408ad22b191692c1de64519b9f768867bc7b11a4</v>
+        <v>29ca1d6c0d021948d89276ee888dd3f034a0a0efe30c90a4af695d44e14e409d</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>character_largeimage_h0234.ab</v>
+        <v>character_largeimage_h0232.ab</v>
       </c>
       <c r="B344" t="str">
-        <v>character_largeimage_h0234.ab</v>
+        <v>character_largeimage_h0232.ab</v>
       </c>
       <c r="C344">
-        <v>3069501</v>
+        <v>2084078</v>
       </c>
       <c r="D344" t="str">
         <v>Stage_1</v>
@@ -7279,18 +7279,18 @@
         <v>0</v>
       </c>
       <c r="F344" t="str">
-        <v>b2537f99faf6708c1597ef8c25e62f4355e6f32459e915e721ed323c337327f5</v>
+        <v>dfe3d19d68019845ae4ece6c9574a5495c0a7e2d7b2bd5731672a07a39334105</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>character_largeimage_h0235.ab</v>
+        <v>character_largeimage_h0233.ab</v>
       </c>
       <c r="B345" t="str">
-        <v>character_largeimage_h0235.ab</v>
+        <v>character_largeimage_h0233.ab</v>
       </c>
       <c r="C345">
-        <v>2226899</v>
+        <v>3216689</v>
       </c>
       <c r="D345" t="str">
         <v>Stage_1</v>
@@ -7299,18 +7299,18 @@
         <v>0</v>
       </c>
       <c r="F345" t="str">
-        <v>465a56a4e220bd39de58cf59e525a9aa2450c8f08870c2d8368c8fd7339d7ac1</v>
+        <v>aef3828cf7528b7b93a7e0d7408ad22b191692c1de64519b9f768867bc7b11a4</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>character_largeimage_h0236.ab</v>
+        <v>character_largeimage_h0234.ab</v>
       </c>
       <c r="B346" t="str">
-        <v>character_largeimage_h0236.ab</v>
+        <v>character_largeimage_h0234.ab</v>
       </c>
       <c r="C346">
-        <v>2098839</v>
+        <v>3069501</v>
       </c>
       <c r="D346" t="str">
         <v>Stage_1</v>
@@ -7319,18 +7319,18 @@
         <v>0</v>
       </c>
       <c r="F346" t="str">
-        <v>861fe308f08e7ddd65e35b46d651cf70e0bf5a6ece93c69910f51b1910bc60b5</v>
+        <v>b2537f99faf6708c1597ef8c25e62f4355e6f32459e915e721ed323c337327f5</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>character_largeimage_h0237.ab</v>
+        <v>character_largeimage_h0235.ab</v>
       </c>
       <c r="B347" t="str">
-        <v>character_largeimage_h0237.ab</v>
+        <v>character_largeimage_h0235.ab</v>
       </c>
       <c r="C347">
-        <v>2342886</v>
+        <v>2226899</v>
       </c>
       <c r="D347" t="str">
         <v>Stage_1</v>
@@ -7339,18 +7339,18 @@
         <v>0</v>
       </c>
       <c r="F347" t="str">
-        <v>8e06426b9ef92077864f5f81f17f7da0e94162e7d8d2e1b0da5e5b0492ef2638</v>
+        <v>465a56a4e220bd39de58cf59e525a9aa2450c8f08870c2d8368c8fd7339d7ac1</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>character_largeimage_h0238.ab</v>
+        <v>character_largeimage_h0236.ab</v>
       </c>
       <c r="B348" t="str">
-        <v>character_largeimage_h0238.ab</v>
+        <v>character_largeimage_h0236.ab</v>
       </c>
       <c r="C348">
-        <v>848742</v>
+        <v>2098839</v>
       </c>
       <c r="D348" t="str">
         <v>Stage_1</v>
@@ -7359,18 +7359,18 @@
         <v>0</v>
       </c>
       <c r="F348" t="str">
-        <v>eebcd817999436e6de65383cf189412ca4c12f9058f159cae52fef68555ccbbe</v>
+        <v>861fe308f08e7ddd65e35b46d651cf70e0bf5a6ece93c69910f51b1910bc60b5</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>character_largeimage_h0239.ab</v>
+        <v>character_largeimage_h0237.ab</v>
       </c>
       <c r="B349" t="str">
-        <v>character_largeimage_h0239.ab</v>
+        <v>character_largeimage_h0237.ab</v>
       </c>
       <c r="C349">
-        <v>812643</v>
+        <v>2342886</v>
       </c>
       <c r="D349" t="str">
         <v>Stage_1</v>
@@ -7379,18 +7379,18 @@
         <v>0</v>
       </c>
       <c r="F349" t="str">
-        <v>a53f4a28d98d240b9ebf9ab9a21802b22ca3f01a9cbe43c7605471e8b69e8c22</v>
+        <v>8e06426b9ef92077864f5f81f17f7da0e94162e7d8d2e1b0da5e5b0492ef2638</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>character_largeimage_h0240.ab</v>
+        <v>character_largeimage_h0238.ab</v>
       </c>
       <c r="B350" t="str">
-        <v>character_largeimage_h0240.ab</v>
+        <v>character_largeimage_h0238.ab</v>
       </c>
       <c r="C350">
-        <v>819235</v>
+        <v>848742</v>
       </c>
       <c r="D350" t="str">
         <v>Stage_1</v>
@@ -7399,18 +7399,18 @@
         <v>0</v>
       </c>
       <c r="F350" t="str">
-        <v>416f932b7f7a15646a65e059ebb8f7a18b000b78fcdbdf6f5b0f6e99feee60a4</v>
+        <v>eebcd817999436e6de65383cf189412ca4c12f9058f159cae52fef68555ccbbe</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>character_largeimage_h0241.ab</v>
+        <v>character_largeimage_h0239.ab</v>
       </c>
       <c r="B351" t="str">
-        <v>character_largeimage_h0241.ab</v>
+        <v>character_largeimage_h0239.ab</v>
       </c>
       <c r="C351">
-        <v>824553</v>
+        <v>812643</v>
       </c>
       <c r="D351" t="str">
         <v>Stage_1</v>
@@ -7419,18 +7419,18 @@
         <v>0</v>
       </c>
       <c r="F351" t="str">
-        <v>0b513268be4ebfb7b998c19702c89e727831fcc9a6c44799632362eae33a7917</v>
+        <v>a53f4a28d98d240b9ebf9ab9a21802b22ca3f01a9cbe43c7605471e8b69e8c22</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>character_largeimage_h0243.ab</v>
+        <v>character_largeimage_h0240.ab</v>
       </c>
       <c r="B352" t="str">
-        <v>character_largeimage_h0243.ab</v>
+        <v>character_largeimage_h0240.ab</v>
       </c>
       <c r="C352">
-        <v>810706</v>
+        <v>819235</v>
       </c>
       <c r="D352" t="str">
         <v>Stage_1</v>
@@ -7439,18 +7439,18 @@
         <v>0</v>
       </c>
       <c r="F352" t="str">
-        <v>cb1bfb37585c135009aab9b0583e3d251dabfdd75817f9cb75d7b54ab1d86778</v>
+        <v>416f932b7f7a15646a65e059ebb8f7a18b000b78fcdbdf6f5b0f6e99feee60a4</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>character_largeimage_h0244.ab</v>
+        <v>character_largeimage_h0241.ab</v>
       </c>
       <c r="B353" t="str">
-        <v>character_largeimage_h0244.ab</v>
+        <v>character_largeimage_h0241.ab</v>
       </c>
       <c r="C353">
-        <v>778524</v>
+        <v>824553</v>
       </c>
       <c r="D353" t="str">
         <v>Stage_1</v>
@@ -7459,18 +7459,18 @@
         <v>0</v>
       </c>
       <c r="F353" t="str">
-        <v>41a7d16ec3600f10cab4dee7f9c437082021de8e22902f3b82af1db8c5b220fb</v>
+        <v>0b513268be4ebfb7b998c19702c89e727831fcc9a6c44799632362eae33a7917</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>character_largeimage_h0245.ab</v>
+        <v>character_largeimage_h0243.ab</v>
       </c>
       <c r="B354" t="str">
-        <v>character_largeimage_h0245.ab</v>
+        <v>character_largeimage_h0243.ab</v>
       </c>
       <c r="C354">
-        <v>795404</v>
+        <v>810706</v>
       </c>
       <c r="D354" t="str">
         <v>Stage_1</v>
@@ -7479,18 +7479,18 @@
         <v>0</v>
       </c>
       <c r="F354" t="str">
-        <v>22925c8d03dde32eb604d7ecfd799e03d9032c974272d0823790b7d6b18967ba</v>
+        <v>cb1bfb37585c135009aab9b0583e3d251dabfdd75817f9cb75d7b54ab1d86778</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>character_largeimage_h0247.ab</v>
+        <v>character_largeimage_h0244.ab</v>
       </c>
       <c r="B355" t="str">
-        <v>character_largeimage_h0247.ab</v>
+        <v>character_largeimage_h0244.ab</v>
       </c>
       <c r="C355">
-        <v>837487</v>
+        <v>778524</v>
       </c>
       <c r="D355" t="str">
         <v>Stage_1</v>
@@ -7499,18 +7499,18 @@
         <v>0</v>
       </c>
       <c r="F355" t="str">
-        <v>ef401029e4a4b055b381ebbe633554d5daf4a3e23b60c62b852b185c4c663bf5</v>
+        <v>41a7d16ec3600f10cab4dee7f9c437082021de8e22902f3b82af1db8c5b220fb</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>character_largeimage_h0248.ab</v>
+        <v>character_largeimage_h0245.ab</v>
       </c>
       <c r="B356" t="str">
-        <v>character_largeimage_h0248.ab</v>
+        <v>character_largeimage_h0245.ab</v>
       </c>
       <c r="C356">
-        <v>836258</v>
+        <v>795404</v>
       </c>
       <c r="D356" t="str">
         <v>Stage_1</v>
@@ -7519,18 +7519,18 @@
         <v>0</v>
       </c>
       <c r="F356" t="str">
-        <v>f8dc41278c1bfbb1635e74efb4ceb293b4de54b87f0626cf7e2b6c0f4972b150</v>
+        <v>22925c8d03dde32eb604d7ecfd799e03d9032c974272d0823790b7d6b18967ba</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>character_largeimage_h0249.ab</v>
+        <v>character_largeimage_h0247.ab</v>
       </c>
       <c r="B357" t="str">
-        <v>character_largeimage_h0249.ab</v>
+        <v>character_largeimage_h0247.ab</v>
       </c>
       <c r="C357">
-        <v>839134</v>
+        <v>837487</v>
       </c>
       <c r="D357" t="str">
         <v>Stage_1</v>
@@ -7539,18 +7539,18 @@
         <v>0</v>
       </c>
       <c r="F357" t="str">
-        <v>9b91af750de18d7afe93e1d3cba66a0bdd3c7db49a03c5ebcf3b8c44fee32fc4</v>
+        <v>ef401029e4a4b055b381ebbe633554d5daf4a3e23b60c62b852b185c4c663bf5</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>character_largeimage_h0253.ab</v>
+        <v>character_largeimage_h0248.ab</v>
       </c>
       <c r="B358" t="str">
-        <v>character_largeimage_h0253.ab</v>
+        <v>character_largeimage_h0248.ab</v>
       </c>
       <c r="C358">
-        <v>823722</v>
+        <v>836258</v>
       </c>
       <c r="D358" t="str">
         <v>Stage_1</v>
@@ -7559,18 +7559,18 @@
         <v>0</v>
       </c>
       <c r="F358" t="str">
-        <v>9c5c84a37c920c2e4b79f9013c9c5db129735e6375cc195a90117b4cf7802999</v>
+        <v>f8dc41278c1bfbb1635e74efb4ceb293b4de54b87f0626cf7e2b6c0f4972b150</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>character_largeimage_h0255.ab</v>
+        <v>character_largeimage_h0249.ab</v>
       </c>
       <c r="B359" t="str">
-        <v>character_largeimage_h0255.ab</v>
+        <v>character_largeimage_h0249.ab</v>
       </c>
       <c r="C359">
-        <v>800474</v>
+        <v>839134</v>
       </c>
       <c r="D359" t="str">
         <v>Stage_1</v>
@@ -7579,18 +7579,18 @@
         <v>0</v>
       </c>
       <c r="F359" t="str">
-        <v>450ab00dbd5b8f991797ab6c83f3ee7cb54290e9971ebd6d51273ff327ed5e15</v>
+        <v>9b91af750de18d7afe93e1d3cba66a0bdd3c7db49a03c5ebcf3b8c44fee32fc4</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>character_largeimage_h0256.ab</v>
+        <v>character_largeimage_h0253.ab</v>
       </c>
       <c r="B360" t="str">
-        <v>character_largeimage_h0256.ab</v>
+        <v>character_largeimage_h0253.ab</v>
       </c>
       <c r="C360">
-        <v>805509</v>
+        <v>823722</v>
       </c>
       <c r="D360" t="str">
         <v>Stage_1</v>
@@ -7599,18 +7599,18 @@
         <v>0</v>
       </c>
       <c r="F360" t="str">
-        <v>297c419fbd877b05bfc9add448ff76132757333cae20eccc028647aea7da7255</v>
+        <v>9c5c84a37c920c2e4b79f9013c9c5db129735e6375cc195a90117b4cf7802999</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>character_largeimage_h0257.ab</v>
+        <v>character_largeimage_h0255.ab</v>
       </c>
       <c r="B361" t="str">
-        <v>character_largeimage_h0257.ab</v>
+        <v>character_largeimage_h0255.ab</v>
       </c>
       <c r="C361">
-        <v>808381</v>
+        <v>800474</v>
       </c>
       <c r="D361" t="str">
         <v>Stage_1</v>
@@ -7619,18 +7619,18 @@
         <v>0</v>
       </c>
       <c r="F361" t="str">
-        <v>d05147b2b6be03ef2ce9c9de4dec8d3ff71bd96053222a4f476707092d75fa72</v>
+        <v>450ab00dbd5b8f991797ab6c83f3ee7cb54290e9971ebd6d51273ff327ed5e15</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>character_largeimage_h0259.ab</v>
+        <v>character_largeimage_h0256.ab</v>
       </c>
       <c r="B362" t="str">
-        <v>character_largeimage_h0259.ab</v>
+        <v>character_largeimage_h0256.ab</v>
       </c>
       <c r="C362">
-        <v>810068</v>
+        <v>805509</v>
       </c>
       <c r="D362" t="str">
         <v>Stage_1</v>
@@ -7639,18 +7639,18 @@
         <v>0</v>
       </c>
       <c r="F362" t="str">
-        <v>172c2c74277241aa72cedda739d55d17e54f6959a7474b0780a9ed33d03daa33</v>
+        <v>297c419fbd877b05bfc9add448ff76132757333cae20eccc028647aea7da7255</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>character_largeimage_h0261.ab</v>
+        <v>character_largeimage_h0257.ab</v>
       </c>
       <c r="B363" t="str">
-        <v>character_largeimage_h0261.ab</v>
+        <v>character_largeimage_h0257.ab</v>
       </c>
       <c r="C363">
-        <v>785275</v>
+        <v>808381</v>
       </c>
       <c r="D363" t="str">
         <v>Stage_1</v>
@@ -7659,18 +7659,18 @@
         <v>0</v>
       </c>
       <c r="F363" t="str">
-        <v>03b89947a2d5dbfe670810747d52ec50f06c25e91ffe38907f479d65efb03148</v>
+        <v>d05147b2b6be03ef2ce9c9de4dec8d3ff71bd96053222a4f476707092d75fa72</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>character_largeimage_h0262.ab</v>
+        <v>character_largeimage_h0259.ab</v>
       </c>
       <c r="B364" t="str">
-        <v>character_largeimage_h0262.ab</v>
+        <v>character_largeimage_h0259.ab</v>
       </c>
       <c r="C364">
-        <v>847775</v>
+        <v>810068</v>
       </c>
       <c r="D364" t="str">
         <v>Stage_1</v>
@@ -7679,18 +7679,18 @@
         <v>0</v>
       </c>
       <c r="F364" t="str">
-        <v>42dc7a9aeedfb2f6754bbff5a20c0649221fbd710df2fb2229837dbf798d580a</v>
+        <v>172c2c74277241aa72cedda739d55d17e54f6959a7474b0780a9ed33d03daa33</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>character_largeimage_h0264.ab</v>
+        <v>character_largeimage_h0261.ab</v>
       </c>
       <c r="B365" t="str">
-        <v>character_largeimage_h0264.ab</v>
+        <v>character_largeimage_h0261.ab</v>
       </c>
       <c r="C365">
-        <v>718190</v>
+        <v>785275</v>
       </c>
       <c r="D365" t="str">
         <v>Stage_1</v>
@@ -7699,18 +7699,18 @@
         <v>0</v>
       </c>
       <c r="F365" t="str">
-        <v>ab84d41ed01d417a5c5cd0109bca96e438f4f56f3472560b99958ac4137677ca</v>
+        <v>03b89947a2d5dbfe670810747d52ec50f06c25e91ffe38907f479d65efb03148</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>character_largeimage_h0265.ab</v>
+        <v>character_largeimage_h0262.ab</v>
       </c>
       <c r="B366" t="str">
-        <v>character_largeimage_h0265.ab</v>
+        <v>character_largeimage_h0262.ab</v>
       </c>
       <c r="C366">
-        <v>795432</v>
+        <v>847775</v>
       </c>
       <c r="D366" t="str">
         <v>Stage_1</v>
@@ -7719,18 +7719,18 @@
         <v>0</v>
       </c>
       <c r="F366" t="str">
-        <v>43942d89eafcb8381ae779ac97b86df469078014bca34c2803baa9d16040a97e</v>
+        <v>42dc7a9aeedfb2f6754bbff5a20c0649221fbd710df2fb2229837dbf798d580a</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>character_largeimage_h0266.ab</v>
+        <v>character_largeimage_h0264.ab</v>
       </c>
       <c r="B367" t="str">
-        <v>character_largeimage_h0266.ab</v>
+        <v>character_largeimage_h0264.ab</v>
       </c>
       <c r="C367">
-        <v>808588</v>
+        <v>718190</v>
       </c>
       <c r="D367" t="str">
         <v>Stage_1</v>
@@ -7739,18 +7739,18 @@
         <v>0</v>
       </c>
       <c r="F367" t="str">
-        <v>ed1bd287702b2f736b9ad9fb7524ec06f5777b21a9511818d78a3ad00dc9d423</v>
+        <v>ab84d41ed01d417a5c5cd0109bca96e438f4f56f3472560b99958ac4137677ca</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>character_largeimage_h0268.ab</v>
+        <v>character_largeimage_h0265.ab</v>
       </c>
       <c r="B368" t="str">
-        <v>character_largeimage_h0268.ab</v>
+        <v>character_largeimage_h0265.ab</v>
       </c>
       <c r="C368">
-        <v>778224</v>
+        <v>795432</v>
       </c>
       <c r="D368" t="str">
         <v>Stage_1</v>
@@ -7759,18 +7759,18 @@
         <v>0</v>
       </c>
       <c r="F368" t="str">
-        <v>8c545650dd20c9e32120149543dd24e79058d125aa0ccf95c1033e80b8078919</v>
+        <v>43942d89eafcb8381ae779ac97b86df469078014bca34c2803baa9d16040a97e</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>character_largeimage_h0270.ab</v>
+        <v>character_largeimage_h0266.ab</v>
       </c>
       <c r="B369" t="str">
-        <v>character_largeimage_h0270.ab</v>
+        <v>character_largeimage_h0266.ab</v>
       </c>
       <c r="C369">
-        <v>789665</v>
+        <v>808588</v>
       </c>
       <c r="D369" t="str">
         <v>Stage_1</v>
@@ -7779,18 +7779,18 @@
         <v>0</v>
       </c>
       <c r="F369" t="str">
-        <v>1061859969e3ff3ae1b28bcaa8c6e3a8aa5203c6699e037ab0a1a30dd0ea1e6d</v>
+        <v>ed1bd287702b2f736b9ad9fb7524ec06f5777b21a9511818d78a3ad00dc9d423</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>character_largeimage_h0271.ab</v>
+        <v>character_largeimage_h0268.ab</v>
       </c>
       <c r="B370" t="str">
-        <v>character_largeimage_h0271.ab</v>
+        <v>character_largeimage_h0268.ab</v>
       </c>
       <c r="C370">
-        <v>820733</v>
+        <v>778224</v>
       </c>
       <c r="D370" t="str">
         <v>Stage_1</v>
@@ -7799,18 +7799,18 @@
         <v>0</v>
       </c>
       <c r="F370" t="str">
-        <v>04260aa0eb4d75fb007447059b3aaed6316a2c062babec302361c33db8578284</v>
+        <v>8c545650dd20c9e32120149543dd24e79058d125aa0ccf95c1033e80b8078919</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>character_largeimage_h0274.ab</v>
+        <v>character_largeimage_h0270.ab</v>
       </c>
       <c r="B371" t="str">
-        <v>character_largeimage_h0274.ab</v>
+        <v>character_largeimage_h0270.ab</v>
       </c>
       <c r="C371">
-        <v>786408</v>
+        <v>789665</v>
       </c>
       <c r="D371" t="str">
         <v>Stage_1</v>
@@ -7819,18 +7819,18 @@
         <v>0</v>
       </c>
       <c r="F371" t="str">
-        <v>380ab4b4093260b3f77f48c03c65173f484970d7e9d7a55b9067faa0eb6b662d</v>
+        <v>1061859969e3ff3ae1b28bcaa8c6e3a8aa5203c6699e037ab0a1a30dd0ea1e6d</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>character_largeimage_m0011.ab</v>
+        <v>character_largeimage_h0271.ab</v>
       </c>
       <c r="B372" t="str">
-        <v>character_largeimage_m0011.ab</v>
+        <v>character_largeimage_h0271.ab</v>
       </c>
       <c r="C372">
-        <v>3645563</v>
+        <v>820733</v>
       </c>
       <c r="D372" t="str">
         <v>Stage_1</v>
@@ -7839,18 +7839,18 @@
         <v>0</v>
       </c>
       <c r="F372" t="str">
-        <v>6d163c0aa3de03702199280db17c4bbe2fddeea97fa709543044a1864c59ac4e</v>
+        <v>04260aa0eb4d75fb007447059b3aaed6316a2c062babec302361c33db8578284</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>character_largeimage_r0034.ab</v>
+        <v>character_largeimage_h0274.ab</v>
       </c>
       <c r="B373" t="str">
-        <v>character_largeimage_r0034.ab</v>
+        <v>character_largeimage_h0274.ab</v>
       </c>
       <c r="C373">
-        <v>3192016</v>
+        <v>786408</v>
       </c>
       <c r="D373" t="str">
         <v>Stage_1</v>
@@ -7859,18 +7859,18 @@
         <v>0</v>
       </c>
       <c r="F373" t="str">
-        <v>a95c21cd1ab779a63db9047ad68d79e913fce1d1229cd60959433c515fa2b15f</v>
+        <v>380ab4b4093260b3f77f48c03c65173f484970d7e9d7a55b9067faa0eb6b662d</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>character_largeimage_r0160.ab</v>
+        <v>character_largeimage_m0011.ab</v>
       </c>
       <c r="B374" t="str">
-        <v>character_largeimage_r0160.ab</v>
+        <v>character_largeimage_m0011.ab</v>
       </c>
       <c r="C374">
-        <v>4547639</v>
+        <v>3645563</v>
       </c>
       <c r="D374" t="str">
         <v>Stage_1</v>
@@ -7879,18 +7879,18 @@
         <v>0</v>
       </c>
       <c r="F374" t="str">
-        <v>964ea8e902241d88c58f2ac99db9982703da97b02c7609af5438b4a03a8a0efe</v>
+        <v>6d163c0aa3de03702199280db17c4bbe2fddeea97fa709543044a1864c59ac4e</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>character_largeimage_r0173.ab</v>
+        <v>character_largeimage_r0034.ab</v>
       </c>
       <c r="B375" t="str">
-        <v>character_largeimage_r0173.ab</v>
+        <v>character_largeimage_r0034.ab</v>
       </c>
       <c r="C375">
-        <v>783778</v>
+        <v>3192016</v>
       </c>
       <c r="D375" t="str">
         <v>Stage_1</v>
@@ -7899,18 +7899,18 @@
         <v>0</v>
       </c>
       <c r="F375" t="str">
-        <v>8195c3708ce8e882a3d95cb265160b057eb3bf5d286f64493dab9ff905fdaab6</v>
+        <v>a95c21cd1ab779a63db9047ad68d79e913fce1d1229cd60959433c515fa2b15f</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>character_largeimage_r0205.ab</v>
+        <v>character_largeimage_r0160.ab</v>
       </c>
       <c r="B376" t="str">
-        <v>character_largeimage_r0205.ab</v>
+        <v>character_largeimage_r0160.ab</v>
       </c>
       <c r="C376">
-        <v>835262</v>
+        <v>4547639</v>
       </c>
       <c r="D376" t="str">
         <v>Stage_1</v>
@@ -7919,18 +7919,18 @@
         <v>0</v>
       </c>
       <c r="F376" t="str">
-        <v>527e90522ce04f745056b9caedcb86a53d46219da877b5661b2d167770d26dcb</v>
+        <v>964ea8e902241d88c58f2ac99db9982703da97b02c7609af5438b4a03a8a0efe</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>character_largeimage_t0017.ab</v>
+        <v>character_largeimage_r0173.ab</v>
       </c>
       <c r="B377" t="str">
-        <v>character_largeimage_t0017.ab</v>
+        <v>character_largeimage_r0173.ab</v>
       </c>
       <c r="C377">
-        <v>5048467</v>
+        <v>783778</v>
       </c>
       <c r="D377" t="str">
         <v>Stage_1</v>
@@ -7939,18 +7939,18 @@
         <v>0</v>
       </c>
       <c r="F377" t="str">
-        <v>569f2fd821c168371bd7ba0fad110a99c067d9153288ec5b7dc7dba7fadbef87</v>
+        <v>8195c3708ce8e882a3d95cb265160b057eb3bf5d286f64493dab9ff905fdaab6</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>character_largeimage_t0026.ab</v>
+        <v>character_largeimage_r0205.ab</v>
       </c>
       <c r="B378" t="str">
-        <v>character_largeimage_t0026.ab</v>
+        <v>character_largeimage_r0205.ab</v>
       </c>
       <c r="C378">
-        <v>3324659</v>
+        <v>835262</v>
       </c>
       <c r="D378" t="str">
         <v>Stage_1</v>
@@ -7959,18 +7959,18 @@
         <v>0</v>
       </c>
       <c r="F378" t="str">
-        <v>3f68cff42a6b9b5f70e4727bbbc4ca79a4b5e3f36eabee4e6ac677e471042212</v>
+        <v>527e90522ce04f745056b9caedcb86a53d46219da877b5661b2d167770d26dcb</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>character_largeimage_t0027.ab</v>
+        <v>character_largeimage_t0017.ab</v>
       </c>
       <c r="B379" t="str">
-        <v>character_largeimage_t0027.ab</v>
+        <v>character_largeimage_t0017.ab</v>
       </c>
       <c r="C379">
-        <v>3241554</v>
+        <v>5048467</v>
       </c>
       <c r="D379" t="str">
         <v>Stage_1</v>
@@ -7979,18 +7979,18 @@
         <v>0</v>
       </c>
       <c r="F379" t="str">
-        <v>5c1ed78edf2589ba18b2fd63c792819e2092273556283005ee4e832864ad3852</v>
+        <v>569f2fd821c168371bd7ba0fad110a99c067d9153288ec5b7dc7dba7fadbef87</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>character_largeimage_t0032.ab</v>
+        <v>character_largeimage_t0026.ab</v>
       </c>
       <c r="B380" t="str">
-        <v>character_largeimage_t0032.ab</v>
+        <v>character_largeimage_t0026.ab</v>
       </c>
       <c r="C380">
-        <v>3632341</v>
+        <v>3324659</v>
       </c>
       <c r="D380" t="str">
         <v>Stage_1</v>
@@ -7999,18 +7999,18 @@
         <v>0</v>
       </c>
       <c r="F380" t="str">
-        <v>3f275335ed88fbd6088516a978efb3cd60af951a07bbdb0cd82a834ccaccbc07</v>
+        <v>3f68cff42a6b9b5f70e4727bbbc4ca79a4b5e3f36eabee4e6ac677e471042212</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>character_largeimage_t0033.ab</v>
+        <v>character_largeimage_t0027.ab</v>
       </c>
       <c r="B381" t="str">
-        <v>character_largeimage_t0033.ab</v>
+        <v>character_largeimage_t0027.ab</v>
       </c>
       <c r="C381">
-        <v>3771149</v>
+        <v>3241554</v>
       </c>
       <c r="D381" t="str">
         <v>Stage_1</v>
@@ -8019,18 +8019,18 @@
         <v>0</v>
       </c>
       <c r="F381" t="str">
-        <v>26a7366f49bb32607c93b69268e6fc0693e08fef6296452290871b2fb08fc2c7</v>
+        <v>5c1ed78edf2589ba18b2fd63c792819e2092273556283005ee4e832864ad3852</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>character_largeimage_t0039.ab</v>
+        <v>character_largeimage_t0032.ab</v>
       </c>
       <c r="B382" t="str">
-        <v>character_largeimage_t0039.ab</v>
+        <v>character_largeimage_t0032.ab</v>
       </c>
       <c r="C382">
-        <v>813283</v>
+        <v>3632341</v>
       </c>
       <c r="D382" t="str">
         <v>Stage_1</v>
@@ -8039,18 +8039,18 @@
         <v>0</v>
       </c>
       <c r="F382" t="str">
-        <v>5350ab84baed9d974062a833ee3cabfdea3208b429a787505b7863cd88d02e59</v>
+        <v>3f275335ed88fbd6088516a978efb3cd60af951a07bbdb0cd82a834ccaccbc07</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>character_largeimage_t0044.ab</v>
+        <v>character_largeimage_t0033.ab</v>
       </c>
       <c r="B383" t="str">
-        <v>character_largeimage_t0044.ab</v>
+        <v>character_largeimage_t0033.ab</v>
       </c>
       <c r="C383">
-        <v>791961</v>
+        <v>3771149</v>
       </c>
       <c r="D383" t="str">
         <v>Stage_1</v>
@@ -8059,18 +8059,18 @@
         <v>0</v>
       </c>
       <c r="F383" t="str">
-        <v>eb3fb4c4fbec62853ced6c63348bda093239167910e1975c24786721e5c36945</v>
+        <v>26a7366f49bb32607c93b69268e6fc0693e08fef6296452290871b2fb08fc2c7</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>character_largeimage_t0049.ab</v>
+        <v>character_largeimage_t0039.ab</v>
       </c>
       <c r="B384" t="str">
-        <v>character_largeimage_t0049.ab</v>
+        <v>character_largeimage_t0039.ab</v>
       </c>
       <c r="C384">
-        <v>2772613</v>
+        <v>813283</v>
       </c>
       <c r="D384" t="str">
         <v>Stage_1</v>
@@ -8079,18 +8079,18 @@
         <v>0</v>
       </c>
       <c r="F384" t="str">
-        <v>95bcb0bd9154f014e06084d19d720ac2bac3315b2829a51f748bab806188e50e</v>
+        <v>5350ab84baed9d974062a833ee3cabfdea3208b429a787505b7863cd88d02e59</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>character_largeimage_t0153.ab</v>
+        <v>character_largeimage_t0044.ab</v>
       </c>
       <c r="B385" t="str">
-        <v>character_largeimage_t0153.ab</v>
+        <v>character_largeimage_t0044.ab</v>
       </c>
       <c r="C385">
-        <v>2756611</v>
+        <v>791961</v>
       </c>
       <c r="D385" t="str">
         <v>Stage_1</v>
@@ -8099,18 +8099,18 @@
         <v>0</v>
       </c>
       <c r="F385" t="str">
-        <v>3c97d4a5953e712f3dfdd8ab30d02f527616fcb3d801dd8b86b3c0cf522a0eef</v>
+        <v>eb3fb4c4fbec62853ced6c63348bda093239167910e1975c24786721e5c36945</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>character_largeimage_t0155.ab</v>
+        <v>character_largeimage_t0049.ab</v>
       </c>
       <c r="B386" t="str">
-        <v>character_largeimage_t0155.ab</v>
+        <v>character_largeimage_t0049.ab</v>
       </c>
       <c r="C386">
-        <v>4381513</v>
+        <v>2772613</v>
       </c>
       <c r="D386" t="str">
         <v>Stage_1</v>
@@ -8119,18 +8119,18 @@
         <v>0</v>
       </c>
       <c r="F386" t="str">
-        <v>38ad3eaafbadfa98327d0d5542f2f0d88f7f31f659055e6d5d7f5d8ecadaaf25</v>
+        <v>95bcb0bd9154f014e06084d19d720ac2bac3315b2829a51f748bab806188e50e</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>character_largeimage_t0156.ab</v>
+        <v>character_largeimage_t0153.ab</v>
       </c>
       <c r="B387" t="str">
-        <v>character_largeimage_t0156.ab</v>
+        <v>character_largeimage_t0153.ab</v>
       </c>
       <c r="C387">
-        <v>2462163</v>
+        <v>2756611</v>
       </c>
       <c r="D387" t="str">
         <v>Stage_1</v>
@@ -8139,18 +8139,18 @@
         <v>0</v>
       </c>
       <c r="F387" t="str">
-        <v>d47db6ea8061d6508d44fdbc8629a568db3385a88c1f450c53188c37a306fbd1</v>
+        <v>3c97d4a5953e712f3dfdd8ab30d02f527616fcb3d801dd8b86b3c0cf522a0eef</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>character_largeimage_t0158.ab</v>
+        <v>character_largeimage_t0155.ab</v>
       </c>
       <c r="B388" t="str">
-        <v>character_largeimage_t0158.ab</v>
+        <v>character_largeimage_t0155.ab</v>
       </c>
       <c r="C388">
-        <v>5260995</v>
+        <v>4381513</v>
       </c>
       <c r="D388" t="str">
         <v>Stage_1</v>
@@ -8159,18 +8159,18 @@
         <v>0</v>
       </c>
       <c r="F388" t="str">
-        <v>60e32e2c51b82894f308157ead5044b1e8a536bc973703711b4f8eb6ab332f30</v>
+        <v>38ad3eaafbadfa98327d0d5542f2f0d88f7f31f659055e6d5d7f5d8ecadaaf25</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>character_largeimage_t0180.ab</v>
+        <v>character_largeimage_t0156.ab</v>
       </c>
       <c r="B389" t="str">
-        <v>character_largeimage_t0180.ab</v>
+        <v>character_largeimage_t0156.ab</v>
       </c>
       <c r="C389">
-        <v>2585585</v>
+        <v>2462163</v>
       </c>
       <c r="D389" t="str">
         <v>Stage_1</v>
@@ -8179,18 +8179,18 @@
         <v>0</v>
       </c>
       <c r="F389" t="str">
-        <v>c5811705c032100ad1a16583021dca2fb02a11ed596ad6f58b79f2775150edc1</v>
+        <v>d47db6ea8061d6508d44fdbc8629a568db3385a88c1f450c53188c37a306fbd1</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>character_largeimage_t0181.ab</v>
+        <v>character_largeimage_t0158.ab</v>
       </c>
       <c r="B390" t="str">
-        <v>character_largeimage_t0181.ab</v>
+        <v>character_largeimage_t0158.ab</v>
       </c>
       <c r="C390">
-        <v>3294655</v>
+        <v>5260995</v>
       </c>
       <c r="D390" t="str">
         <v>Stage_1</v>
@@ -8199,18 +8199,18 @@
         <v>0</v>
       </c>
       <c r="F390" t="str">
-        <v>3ce7bff8c5c6bff24697ac51035be274c30bba43c89704245ba4d5ece12532a8</v>
+        <v>60e32e2c51b82894f308157ead5044b1e8a536bc973703711b4f8eb6ab332f30</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>character_largeimage_t0182.ab</v>
+        <v>character_largeimage_t0180.ab</v>
       </c>
       <c r="B391" t="str">
-        <v>character_largeimage_t0182.ab</v>
+        <v>character_largeimage_t0180.ab</v>
       </c>
       <c r="C391">
-        <v>2283005</v>
+        <v>2585586</v>
       </c>
       <c r="D391" t="str">
         <v>Stage_1</v>
@@ -8219,18 +8219,18 @@
         <v>0</v>
       </c>
       <c r="F391" t="str">
-        <v>f08896641300c346a1e73ed169d426147c629133d6b99fc0d0b053d6f89dea33</v>
+        <v>c5811705c032100ad1a16583021dca2fb02a11ed596ad6f58b79f2775150edc1</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>character_largeimage_t0184.ab</v>
+        <v>character_largeimage_t0181.ab</v>
       </c>
       <c r="B392" t="str">
-        <v>character_largeimage_t0184.ab</v>
+        <v>character_largeimage_t0181.ab</v>
       </c>
       <c r="C392">
-        <v>2289827</v>
+        <v>3294655</v>
       </c>
       <c r="D392" t="str">
         <v>Stage_1</v>
@@ -8239,18 +8239,18 @@
         <v>0</v>
       </c>
       <c r="F392" t="str">
-        <v>aa09e9c0a10976e05321eeed5a37397f867e1377acd71dc4e3d2d5d1417daf28</v>
+        <v>3ce7bff8c5c6bff24697ac51035be274c30bba43c89704245ba4d5ece12532a8</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>character_largeimage_t0187.ab</v>
+        <v>character_largeimage_t0182.ab</v>
       </c>
       <c r="B393" t="str">
-        <v>character_largeimage_t0187.ab</v>
+        <v>character_largeimage_t0182.ab</v>
       </c>
       <c r="C393">
-        <v>2887185</v>
+        <v>2283005</v>
       </c>
       <c r="D393" t="str">
         <v>Stage_1</v>
@@ -8259,18 +8259,18 @@
         <v>0</v>
       </c>
       <c r="F393" t="str">
-        <v>84cffe40a80fe5c71df8f44503bbdce8bbffb4c01dc57012fb621fc40fd4230d</v>
+        <v>f08896641300c346a1e73ed169d426147c629133d6b99fc0d0b053d6f89dea33</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>character_largeimage_t0188.ab</v>
+        <v>character_largeimage_t0184.ab</v>
       </c>
       <c r="B394" t="str">
-        <v>character_largeimage_t0188.ab</v>
+        <v>character_largeimage_t0184.ab</v>
       </c>
       <c r="C394">
-        <v>2744938</v>
+        <v>2289827</v>
       </c>
       <c r="D394" t="str">
         <v>Stage_1</v>
@@ -8279,18 +8279,18 @@
         <v>0</v>
       </c>
       <c r="F394" t="str">
-        <v>4f854b7d0c3b92905dd2311a69ab83cea017de02730b719a6608464f27e269d4</v>
+        <v>aa09e9c0a10976e05321eeed5a37397f867e1377acd71dc4e3d2d5d1417daf28</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>character_largeimage_t0189.ab</v>
+        <v>character_largeimage_t0187.ab</v>
       </c>
       <c r="B395" t="str">
-        <v>character_largeimage_t0189.ab</v>
+        <v>character_largeimage_t0187.ab</v>
       </c>
       <c r="C395">
-        <v>4473711</v>
+        <v>2887185</v>
       </c>
       <c r="D395" t="str">
         <v>Stage_1</v>
@@ -8299,18 +8299,18 @@
         <v>0</v>
       </c>
       <c r="F395" t="str">
-        <v>8fc73aa493d889c8325fbef52adf15dac0c8ee19e212564b6ae16b08b266144f</v>
+        <v>84cffe40a80fe5c71df8f44503bbdce8bbffb4c01dc57012fb621fc40fd4230d</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>character_largeimage_t0204.ab</v>
+        <v>character_largeimage_t0188.ab</v>
       </c>
       <c r="B396" t="str">
-        <v>character_largeimage_t0204.ab</v>
+        <v>character_largeimage_t0188.ab</v>
       </c>
       <c r="C396">
-        <v>839510</v>
+        <v>2744938</v>
       </c>
       <c r="D396" t="str">
         <v>Stage_1</v>
@@ -8319,18 +8319,18 @@
         <v>0</v>
       </c>
       <c r="F396" t="str">
-        <v>3339401d70ded15a0020af038f486a0d2a6e2bf7e4ca29d2fc52483eba92f982</v>
+        <v>4f854b7d0c3b92905dd2311a69ab83cea017de02730b719a6608464f27e269d4</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>character_largeimage_t0207.ab</v>
+        <v>character_largeimage_t0189.ab</v>
       </c>
       <c r="B397" t="str">
-        <v>character_largeimage_t0207.ab</v>
+        <v>character_largeimage_t0189.ab</v>
       </c>
       <c r="C397">
-        <v>788109</v>
+        <v>4473711</v>
       </c>
       <c r="D397" t="str">
         <v>Stage_1</v>
@@ -8339,18 +8339,18 @@
         <v>0</v>
       </c>
       <c r="F397" t="str">
-        <v>884a61acb6fc59583fb23f817ab1ee2aad0b3edba982eb01c5e3d4409e1db73f</v>
+        <v>8fc73aa493d889c8325fbef52adf15dac0c8ee19e212564b6ae16b08b266144f</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>character_largeimage_t0212.ab</v>
+        <v>character_largeimage_t0204.ab</v>
       </c>
       <c r="B398" t="str">
-        <v>character_largeimage_t0212.ab</v>
+        <v>character_largeimage_t0204.ab</v>
       </c>
       <c r="C398">
-        <v>843123</v>
+        <v>839510</v>
       </c>
       <c r="D398" t="str">
         <v>Stage_1</v>
@@ -8359,18 +8359,18 @@
         <v>0</v>
       </c>
       <c r="F398" t="str">
-        <v>e442a6b286187dcc18ca56751536e1758d5953d5b913e759d2ed412148611a38</v>
+        <v>3339401d70ded15a0020af038f486a0d2a6e2bf7e4ca29d2fc52483eba92f982</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>character_largeimage_t0214.ab</v>
+        <v>character_largeimage_t0207.ab</v>
       </c>
       <c r="B399" t="str">
-        <v>character_largeimage_t0214.ab</v>
+        <v>character_largeimage_t0207.ab</v>
       </c>
       <c r="C399">
-        <v>828387</v>
+        <v>788109</v>
       </c>
       <c r="D399" t="str">
         <v>Stage_1</v>
@@ -8379,18 +8379,18 @@
         <v>0</v>
       </c>
       <c r="F399" t="str">
-        <v>342fd529c964664d600e232cd94bd8b1675ded9c1b64945ef103993a6b5b300c</v>
+        <v>884a61acb6fc59583fb23f817ab1ee2aad0b3edba982eb01c5e3d4409e1db73f</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>character_largeimage_t0218.ab</v>
+        <v>character_largeimage_t0212.ab</v>
       </c>
       <c r="B400" t="str">
-        <v>character_largeimage_t0218.ab</v>
+        <v>character_largeimage_t0212.ab</v>
       </c>
       <c r="C400">
-        <v>811612</v>
+        <v>843123</v>
       </c>
       <c r="D400" t="str">
         <v>Stage_1</v>
@@ -8399,18 +8399,18 @@
         <v>0</v>
       </c>
       <c r="F400" t="str">
-        <v>bda0c6f7dc7407f7c344f85b171a48370f75519c50e728784f647c83169bd94c</v>
+        <v>e442a6b286187dcc18ca56751536e1758d5953d5b913e759d2ed412148611a38</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>character_largeimage_t0222.ab</v>
+        <v>character_largeimage_t0214.ab</v>
       </c>
       <c r="B401" t="str">
-        <v>character_largeimage_t0222.ab</v>
+        <v>character_largeimage_t0214.ab</v>
       </c>
       <c r="C401">
-        <v>774259</v>
+        <v>828387</v>
       </c>
       <c r="D401" t="str">
         <v>Stage_1</v>
@@ -8419,18 +8419,18 @@
         <v>0</v>
       </c>
       <c r="F401" t="str">
-        <v>8ab646da7e9d3f088d7b6a87436ba651ca2f50198534bb4838143a45e096932e</v>
+        <v>342fd529c964664d600e232cd94bd8b1675ded9c1b64945ef103993a6b5b300c</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>character_largeimage_t0223.ab</v>
+        <v>character_largeimage_t0218.ab</v>
       </c>
       <c r="B402" t="str">
-        <v>character_largeimage_t0223.ab</v>
+        <v>character_largeimage_t0218.ab</v>
       </c>
       <c r="C402">
-        <v>844248</v>
+        <v>811612</v>
       </c>
       <c r="D402" t="str">
         <v>Stage_1</v>
@@ -8439,18 +8439,18 @@
         <v>0</v>
       </c>
       <c r="F402" t="str">
-        <v>18c1161759d4a71ed98ffc241b6626b1e001387f1a6c5ce54150f250abf64248</v>
+        <v>bda0c6f7dc7407f7c344f85b171a48370f75519c50e728784f647c83169bd94c</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>character_largeimage_t0225.ab</v>
+        <v>character_largeimage_t0222.ab</v>
       </c>
       <c r="B403" t="str">
-        <v>character_largeimage_t0225.ab</v>
+        <v>character_largeimage_t0222.ab</v>
       </c>
       <c r="C403">
-        <v>815023</v>
+        <v>774259</v>
       </c>
       <c r="D403" t="str">
         <v>Stage_1</v>
@@ -8459,18 +8459,18 @@
         <v>0</v>
       </c>
       <c r="F403" t="str">
-        <v>f2a096a766a2689633f4d106cf0a6a439a759aea742a118791bd76a6648f267d</v>
+        <v>8ab646da7e9d3f088d7b6a87436ba651ca2f50198534bb4838143a45e096932e</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>character_largeimage_t0228.ab</v>
+        <v>character_largeimage_t0223.ab</v>
       </c>
       <c r="B404" t="str">
-        <v>character_largeimage_t0228.ab</v>
+        <v>character_largeimage_t0223.ab</v>
       </c>
       <c r="C404">
-        <v>829894</v>
+        <v>844248</v>
       </c>
       <c r="D404" t="str">
         <v>Stage_1</v>
@@ -8479,18 +8479,18 @@
         <v>0</v>
       </c>
       <c r="F404" t="str">
-        <v>94f3e6cc4c0a6a79f10a543d83f614303bc3a05333d39f4403ef896f4dcf07f5</v>
+        <v>18c1161759d4a71ed98ffc241b6626b1e001387f1a6c5ce54150f250abf64248</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>character_largeimage_t0229.ab</v>
+        <v>character_largeimage_t0225.ab</v>
       </c>
       <c r="B405" t="str">
-        <v>character_largeimage_t0229.ab</v>
+        <v>character_largeimage_t0225.ab</v>
       </c>
       <c r="C405">
-        <v>1662213</v>
+        <v>815023</v>
       </c>
       <c r="D405" t="str">
         <v>Stage_1</v>
@@ -8499,18 +8499,18 @@
         <v>0</v>
       </c>
       <c r="F405" t="str">
-        <v>69e6216c55eeaaab8fd283f59f25c316734a73644b13941d4d1fe1e1c31f8c1f</v>
+        <v>f2a096a766a2689633f4d106cf0a6a439a759aea742a118791bd76a6648f267d</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>character_largeimage_t0231.ab</v>
+        <v>character_largeimage_t0228.ab</v>
       </c>
       <c r="B406" t="str">
-        <v>character_largeimage_t0231.ab</v>
+        <v>character_largeimage_t0228.ab</v>
       </c>
       <c r="C406">
-        <v>823425</v>
+        <v>829894</v>
       </c>
       <c r="D406" t="str">
         <v>Stage_1</v>
@@ -8519,18 +8519,18 @@
         <v>0</v>
       </c>
       <c r="F406" t="str">
-        <v>3cb4f02d9303d1a2b5fc53ad0acd0aa27db034c6c97e9bef02dacf3febc0eee6</v>
+        <v>94f3e6cc4c0a6a79f10a543d83f614303bc3a05333d39f4403ef896f4dcf07f5</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>character_largeimage_t0242.ab</v>
+        <v>character_largeimage_t0229.ab</v>
       </c>
       <c r="B407" t="str">
-        <v>character_largeimage_t0242.ab</v>
+        <v>character_largeimage_t0229.ab</v>
       </c>
       <c r="C407">
-        <v>777670</v>
+        <v>1662213</v>
       </c>
       <c r="D407" t="str">
         <v>Stage_1</v>
@@ -8539,18 +8539,18 @@
         <v>0</v>
       </c>
       <c r="F407" t="str">
-        <v>7c281124753083a4db690ee47b450f4f89e3d56fc805d995ace8e49efa5bc50f</v>
+        <v>69e6216c55eeaaab8fd283f59f25c316734a73644b13941d4d1fe1e1c31f8c1f</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>character_largeimage_t0246.ab</v>
+        <v>character_largeimage_t0231.ab</v>
       </c>
       <c r="B408" t="str">
-        <v>character_largeimage_t0246.ab</v>
+        <v>character_largeimage_t0231.ab</v>
       </c>
       <c r="C408">
-        <v>819675</v>
+        <v>823425</v>
       </c>
       <c r="D408" t="str">
         <v>Stage_1</v>
@@ -8559,18 +8559,18 @@
         <v>0</v>
       </c>
       <c r="F408" t="str">
-        <v>c9ff420c4cd5404f687592c9851a9c3c9b90d6aba4ec3215e4213794c4ec8651</v>
+        <v>3cb4f02d9303d1a2b5fc53ad0acd0aa27db034c6c97e9bef02dacf3febc0eee6</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>character_largeimage_t0250.ab</v>
+        <v>character_largeimage_t0242.ab</v>
       </c>
       <c r="B409" t="str">
-        <v>character_largeimage_t0250.ab</v>
+        <v>character_largeimage_t0242.ab</v>
       </c>
       <c r="C409">
-        <v>835064</v>
+        <v>777670</v>
       </c>
       <c r="D409" t="str">
         <v>Stage_1</v>
@@ -8579,18 +8579,18 @@
         <v>0</v>
       </c>
       <c r="F409" t="str">
-        <v>cabd53f65c1283e0ac5773bc89f0d3baf8df60f587a2629bb61ff5df5f38e998</v>
+        <v>7c281124753083a4db690ee47b450f4f89e3d56fc805d995ace8e49efa5bc50f</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>character_largeimage_t0251.ab</v>
+        <v>character_largeimage_t0246.ab</v>
       </c>
       <c r="B410" t="str">
-        <v>character_largeimage_t0251.ab</v>
+        <v>character_largeimage_t0246.ab</v>
       </c>
       <c r="C410">
-        <v>817439</v>
+        <v>819675</v>
       </c>
       <c r="D410" t="str">
         <v>Stage_1</v>
@@ -8599,18 +8599,18 @@
         <v>0</v>
       </c>
       <c r="F410" t="str">
-        <v>35de9505e776e1b88eff26e7adc6f554d89c0d74424c46ac4d6b966cac281dae</v>
+        <v>c9ff420c4cd5404f687592c9851a9c3c9b90d6aba4ec3215e4213794c4ec8651</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>character_largeimage_t0252.ab</v>
+        <v>character_largeimage_t0250.ab</v>
       </c>
       <c r="B411" t="str">
-        <v>character_largeimage_t0252.ab</v>
+        <v>character_largeimage_t0250.ab</v>
       </c>
       <c r="C411">
-        <v>3182222</v>
+        <v>835064</v>
       </c>
       <c r="D411" t="str">
         <v>Stage_1</v>
@@ -8619,18 +8619,18 @@
         <v>0</v>
       </c>
       <c r="F411" t="str">
-        <v>041e2f53d9fa84b5baeb43cbf5b681fe1c1a09fc422e5db7e8abc8f70bc26348</v>
+        <v>cabd53f65c1283e0ac5773bc89f0d3baf8df60f587a2629bb61ff5df5f38e998</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>character_largeimage_t0254.ab</v>
+        <v>character_largeimage_t0251.ab</v>
       </c>
       <c r="B412" t="str">
-        <v>character_largeimage_t0254.ab</v>
+        <v>character_largeimage_t0251.ab</v>
       </c>
       <c r="C412">
-        <v>821577</v>
+        <v>817439</v>
       </c>
       <c r="D412" t="str">
         <v>Stage_1</v>
@@ -8639,18 +8639,18 @@
         <v>0</v>
       </c>
       <c r="F412" t="str">
-        <v>0ec094e49c6f0bef8aeec78857eeaae95127b56d79ef9f59be4ec966f8258c66</v>
+        <v>35de9505e776e1b88eff26e7adc6f554d89c0d74424c46ac4d6b966cac281dae</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>character_largeimage_t0258.ab</v>
+        <v>character_largeimage_t0252.ab</v>
       </c>
       <c r="B413" t="str">
-        <v>character_largeimage_t0258.ab</v>
+        <v>character_largeimage_t0252.ab</v>
       </c>
       <c r="C413">
-        <v>799096</v>
+        <v>3182222</v>
       </c>
       <c r="D413" t="str">
         <v>Stage_1</v>
@@ -8659,18 +8659,18 @@
         <v>0</v>
       </c>
       <c r="F413" t="str">
-        <v>18672ae7cdd8fbc33c3c3fb113d9cc3cb1797d9336d487d7d2cc71564bb4a621</v>
+        <v>041e2f53d9fa84b5baeb43cbf5b681fe1c1a09fc422e5db7e8abc8f70bc26348</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>character_largeimage_t0263.ab</v>
+        <v>character_largeimage_t0254.ab</v>
       </c>
       <c r="B414" t="str">
-        <v>character_largeimage_t0263.ab</v>
+        <v>character_largeimage_t0254.ab</v>
       </c>
       <c r="C414">
-        <v>819892</v>
+        <v>821577</v>
       </c>
       <c r="D414" t="str">
         <v>Stage_1</v>
@@ -8679,18 +8679,18 @@
         <v>0</v>
       </c>
       <c r="F414" t="str">
-        <v>e8bb91ba644af38d3523e9355cc207668ab626f2304399ef855def2eeb181356</v>
+        <v>0ec094e49c6f0bef8aeec78857eeaae95127b56d79ef9f59be4ec966f8258c66</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>character_largeimage_t0272.ab</v>
+        <v>character_largeimage_t0258.ab</v>
       </c>
       <c r="B415" t="str">
-        <v>character_largeimage_t0272.ab</v>
+        <v>character_largeimage_t0258.ab</v>
       </c>
       <c r="C415">
-        <v>760703</v>
+        <v>799096</v>
       </c>
       <c r="D415" t="str">
         <v>Stage_1</v>
@@ -8699,18 +8699,18 @@
         <v>0</v>
       </c>
       <c r="F415" t="str">
-        <v>04b23476caf6f2275bb0febbf34b0f90581a1b778c8e54f1dd604efcb8283da8</v>
+        <v>18672ae7cdd8fbc33c3c3fb113d9cc3cb1797d9336d487d7d2cc71564bb4a621</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>character_largeimage_uncategorized_0.ab</v>
+        <v>character_largeimage_t0263.ab</v>
       </c>
       <c r="B416" t="str">
-        <v>character_largeimage_uncategorized_0.ab</v>
+        <v>character_largeimage_t0263.ab</v>
       </c>
       <c r="C416">
-        <v>173461</v>
+        <v>819892</v>
       </c>
       <c r="D416" t="str">
         <v>Stage_1</v>
@@ -8719,33 +8719,113 @@
         <v>0</v>
       </c>
       <c r="F416" t="str">
-        <v>9c40f907ab459375c76b4a51919f83aa971bac3c394a4d64e8e549d7879abebf</v>
+        <v>e8bb91ba644af38d3523e9355cc207668ab626f2304399ef855def2eeb181356</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
+        <v>character_largeimage_t0269.ab</v>
+      </c>
+      <c r="B417" t="str">
+        <v>character_largeimage_t0269.ab</v>
+      </c>
+      <c r="C417">
+        <v>814551</v>
+      </c>
+      <c r="D417" t="str">
+        <v>Stage_1</v>
+      </c>
+      <c r="E417">
+        <v>0</v>
+      </c>
+      <c r="F417" t="str">
+        <v>5775eef9664188e2989b7a33985a416e66fca83d2960305dab4744621708d1e0</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="str">
+        <v>character_largeimage_t0272.ab</v>
+      </c>
+      <c r="B418" t="str">
+        <v>character_largeimage_t0272.ab</v>
+      </c>
+      <c r="C418">
+        <v>760703</v>
+      </c>
+      <c r="D418" t="str">
+        <v>Stage_1</v>
+      </c>
+      <c r="E418">
+        <v>0</v>
+      </c>
+      <c r="F418" t="str">
+        <v>04b23476caf6f2275bb0febbf34b0f90581a1b778c8e54f1dd604efcb8283da8</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="str">
+        <v>character_largeimage_t0275.ab</v>
+      </c>
+      <c r="B419" t="str">
+        <v>character_largeimage_t0275.ab</v>
+      </c>
+      <c r="C419">
+        <v>761709</v>
+      </c>
+      <c r="D419" t="str">
+        <v>Stage_1</v>
+      </c>
+      <c r="E419">
+        <v>0</v>
+      </c>
+      <c r="F419" t="str">
+        <v>8350830bdc61d2345550fec850c1f0b08043d91988e717e7291fc6ff4633abfa</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="str">
+        <v>character_largeimage_uncategorized_0.ab</v>
+      </c>
+      <c r="B420" t="str">
+        <v>character_largeimage_uncategorized_0.ab</v>
+      </c>
+      <c r="C420">
+        <v>173461</v>
+      </c>
+      <c r="D420" t="str">
+        <v>Stage_1</v>
+      </c>
+      <c r="E420">
+        <v>0</v>
+      </c>
+      <c r="F420" t="str">
+        <v>9c40f907ab459375c76b4a51919f83aa971bac3c394a4d64e8e549d7879abebf</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="str">
         <v>character_largeimage_uncategorized_3.ab</v>
       </c>
-      <c r="B417" t="str">
+      <c r="B421" t="str">
         <v>character_largeimage_uncategorized_3.ab</v>
       </c>
-      <c r="C417">
+      <c r="C421">
         <v>214292</v>
       </c>
-      <c r="D417" t="str">
-        <v>Stage_1</v>
-      </c>
-      <c r="E417">
-        <v>0</v>
-      </c>
-      <c r="F417" t="str">
+      <c r="D421" t="str">
+        <v>Stage_1</v>
+      </c>
+      <c r="E421">
+        <v>0</v>
+      </c>
+      <c r="F421" t="str">
         <v>baa10ce33b3b4d5a88452011578fd5a338303e27f2f7e58822f6cbbf2f359f10</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F417"/>
+  <autoFilter ref="A1:F421"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F417"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F421"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/client_gamedata/ios/iosExp.xlsx
+++ b/client_gamedata/ios/iosExp.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Assets" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Assets!$A$1:$F$421</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Assets!$A$1:$F$423</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F421"/>
+  <dimension ref="A1:F423"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -670,7 +670,7 @@
         <v>audioclip_sfx_20_jp.ab</v>
       </c>
       <c r="C14">
-        <v>147264</v>
+        <v>147265</v>
       </c>
       <c r="D14" t="str">
         <v>Stage_1</v>
@@ -1450,7 +1450,7 @@
         <v>audioclip_sfx_b0015_jp.ab</v>
       </c>
       <c r="C53">
-        <v>116861</v>
+        <v>116862</v>
       </c>
       <c r="D53" t="str">
         <v>Stage_1</v>
@@ -1470,7 +1470,7 @@
         <v>audioclip_sfx_b0028_jp.ab</v>
       </c>
       <c r="C54">
-        <v>875310</v>
+        <v>875309</v>
       </c>
       <c r="D54" t="str">
         <v>Stage_1</v>
@@ -1490,7 +1490,7 @@
         <v>audioclip_sfx_b0037_jp.ab</v>
       </c>
       <c r="C55">
-        <v>2011713</v>
+        <v>2011714</v>
       </c>
       <c r="D55" t="str">
         <v>Stage_1</v>
@@ -1510,7 +1510,7 @@
         <v>audioclip_sfx_b0202_jp.ab</v>
       </c>
       <c r="C56">
-        <v>1272282</v>
+        <v>1272281</v>
       </c>
       <c r="D56" t="str">
         <v>Stage_1</v>
@@ -1590,7 +1590,7 @@
         <v>audioclip_sfx_e0046_jp.ab</v>
       </c>
       <c r="C60">
-        <v>3100224</v>
+        <v>3100225</v>
       </c>
       <c r="D60" t="str">
         <v>Stage_1</v>
@@ -1630,7 +1630,7 @@
         <v>audioclip_sfx_e3497_jp.ab</v>
       </c>
       <c r="C62">
-        <v>250849</v>
+        <v>250851</v>
       </c>
       <c r="D62" t="str">
         <v>Stage_1</v>
@@ -1770,7 +1770,7 @@
         <v>audioclip_sfx_h0006_jp.ab</v>
       </c>
       <c r="C69">
-        <v>1013618</v>
+        <v>1013616</v>
       </c>
       <c r="D69" t="str">
         <v>Stage_1</v>
@@ -1790,7 +1790,7 @@
         <v>audioclip_sfx_h0007_jp.ab</v>
       </c>
       <c r="C70">
-        <v>678624</v>
+        <v>678623</v>
       </c>
       <c r="D70" t="str">
         <v>Stage_1</v>
@@ -1810,7 +1810,7 @@
         <v>audioclip_sfx_h0008_jp.ab</v>
       </c>
       <c r="C71">
-        <v>349414</v>
+        <v>349413</v>
       </c>
       <c r="D71" t="str">
         <v>Stage_1</v>
@@ -1830,7 +1830,7 @@
         <v>audioclip_sfx_h0009_jp.ab</v>
       </c>
       <c r="C72">
-        <v>453781</v>
+        <v>453783</v>
       </c>
       <c r="D72" t="str">
         <v>Stage_1</v>
@@ -1870,7 +1870,7 @@
         <v>audioclip_sfx_h0012_jp.ab</v>
       </c>
       <c r="C74">
-        <v>740115</v>
+        <v>740116</v>
       </c>
       <c r="D74" t="str">
         <v>Stage_1</v>
@@ -1910,7 +1910,7 @@
         <v>audioclip_sfx_h0014_jp.ab</v>
       </c>
       <c r="C76">
-        <v>446594</v>
+        <v>446592</v>
       </c>
       <c r="D76" t="str">
         <v>Stage_1</v>
@@ -2010,7 +2010,7 @@
         <v>audioclip_sfx_h0022_jp.ab</v>
       </c>
       <c r="C81">
-        <v>985555</v>
+        <v>985554</v>
       </c>
       <c r="D81" t="str">
         <v>Stage_1</v>
@@ -2030,7 +2030,7 @@
         <v>audioclip_sfx_h0023_jp.ab</v>
       </c>
       <c r="C82">
-        <v>1374151</v>
+        <v>1374152</v>
       </c>
       <c r="D82" t="str">
         <v>Stage_1</v>
@@ -2050,7 +2050,7 @@
         <v>audioclip_sfx_h0024_jp.ab</v>
       </c>
       <c r="C83">
-        <v>1572148</v>
+        <v>1572147</v>
       </c>
       <c r="D83" t="str">
         <v>Stage_1</v>
@@ -2110,7 +2110,7 @@
         <v>audioclip_sfx_h0030_jp.ab</v>
       </c>
       <c r="C86">
-        <v>1189227</v>
+        <v>1189229</v>
       </c>
       <c r="D86" t="str">
         <v>Stage_1</v>
@@ -2130,7 +2130,7 @@
         <v>audioclip_sfx_h0031_jp.ab</v>
       </c>
       <c r="C87">
-        <v>1039750</v>
+        <v>1039749</v>
       </c>
       <c r="D87" t="str">
         <v>Stage_1</v>
@@ -2150,7 +2150,7 @@
         <v>audioclip_sfx_h0035_jp.ab</v>
       </c>
       <c r="C88">
-        <v>785945</v>
+        <v>785946</v>
       </c>
       <c r="D88" t="str">
         <v>Stage_1</v>
@@ -2170,7 +2170,7 @@
         <v>audioclip_sfx_h0036_jp.ab</v>
       </c>
       <c r="C89">
-        <v>743620</v>
+        <v>743619</v>
       </c>
       <c r="D89" t="str">
         <v>Stage_1</v>
@@ -2190,7 +2190,7 @@
         <v>audioclip_sfx_h0038_jp.ab</v>
       </c>
       <c r="C90">
-        <v>611357</v>
+        <v>611356</v>
       </c>
       <c r="D90" t="str">
         <v>Stage_1</v>
@@ -2270,7 +2270,7 @@
         <v>audioclip_sfx_h0043_jp.ab</v>
       </c>
       <c r="C94">
-        <v>2421243</v>
+        <v>2421241</v>
       </c>
       <c r="D94" t="str">
         <v>Stage_1</v>
@@ -2310,7 +2310,7 @@
         <v>audioclip_sfx_h0045_jp.ab</v>
       </c>
       <c r="C96">
-        <v>538569</v>
+        <v>538568</v>
       </c>
       <c r="D96" t="str">
         <v>Stage_1</v>
@@ -2330,7 +2330,7 @@
         <v>audioclip_sfx_h0047_jp.ab</v>
       </c>
       <c r="C97">
-        <v>8510835</v>
+        <v>8510836</v>
       </c>
       <c r="D97" t="str">
         <v>Stage_1</v>
@@ -2370,7 +2370,7 @@
         <v>audioclip_sfx_h0073_jp.ab</v>
       </c>
       <c r="C99">
-        <v>276296</v>
+        <v>276295</v>
       </c>
       <c r="D99" t="str">
         <v>Stage_1</v>
@@ -2490,7 +2490,7 @@
         <v>audioclip_sfx_h0136_jp.ab</v>
       </c>
       <c r="C105">
-        <v>1316079</v>
+        <v>1316077</v>
       </c>
       <c r="D105" t="str">
         <v>Stage_1</v>
@@ -2530,7 +2530,7 @@
         <v>audioclip_sfx_h0138_jp.ab</v>
       </c>
       <c r="C107">
-        <v>1236791</v>
+        <v>1236790</v>
       </c>
       <c r="D107" t="str">
         <v>Stage_1</v>
@@ -2550,7 +2550,7 @@
         <v>audioclip_sfx_h0150_jp.ab</v>
       </c>
       <c r="C108">
-        <v>2757250</v>
+        <v>2757251</v>
       </c>
       <c r="D108" t="str">
         <v>Stage_1</v>
@@ -2570,7 +2570,7 @@
         <v>audioclip_sfx_h0151_jp.ab</v>
       </c>
       <c r="C109">
-        <v>1924708</v>
+        <v>1924706</v>
       </c>
       <c r="D109" t="str">
         <v>Stage_1</v>
@@ -2590,7 +2590,7 @@
         <v>audioclip_sfx_h0152_jp.ab</v>
       </c>
       <c r="C110">
-        <v>1987359</v>
+        <v>1987360</v>
       </c>
       <c r="D110" t="str">
         <v>Stage_1</v>
@@ -2630,7 +2630,7 @@
         <v>audioclip_sfx_h0157_jp.ab</v>
       </c>
       <c r="C112">
-        <v>1681370</v>
+        <v>1681371</v>
       </c>
       <c r="D112" t="str">
         <v>Stage_1</v>
@@ -2650,7 +2650,7 @@
         <v>audioclip_sfx_h0159_jp.ab</v>
       </c>
       <c r="C113">
-        <v>1893112</v>
+        <v>1893111</v>
       </c>
       <c r="D113" t="str">
         <v>Stage_1</v>
@@ -2670,7 +2670,7 @@
         <v>audioclip_sfx_h0161_jp.ab</v>
       </c>
       <c r="C114">
-        <v>1944102</v>
+        <v>1944103</v>
       </c>
       <c r="D114" t="str">
         <v>Stage_1</v>
@@ -2690,7 +2690,7 @@
         <v>audioclip_sfx_h0163_jp.ab</v>
       </c>
       <c r="C115">
-        <v>1305068</v>
+        <v>1305069</v>
       </c>
       <c r="D115" t="str">
         <v>Stage_1</v>
@@ -2750,7 +2750,7 @@
         <v>audioclip_sfx_h0166_jp.ab</v>
       </c>
       <c r="C118">
-        <v>735094</v>
+        <v>735096</v>
       </c>
       <c r="D118" t="str">
         <v>Stage_1</v>
@@ -2770,7 +2770,7 @@
         <v>audioclip_sfx_h0167_jp.ab</v>
       </c>
       <c r="C119">
-        <v>884679</v>
+        <v>884678</v>
       </c>
       <c r="D119" t="str">
         <v>Stage_1</v>
@@ -2790,7 +2790,7 @@
         <v>audioclip_sfx_h0168_jp.ab</v>
       </c>
       <c r="C120">
-        <v>747235</v>
+        <v>747236</v>
       </c>
       <c r="D120" t="str">
         <v>Stage_1</v>
@@ -2830,7 +2830,7 @@
         <v>audioclip_sfx_h0170_jp.ab</v>
       </c>
       <c r="C122">
-        <v>1438192</v>
+        <v>1438188</v>
       </c>
       <c r="D122" t="str">
         <v>Stage_1</v>
@@ -2850,7 +2850,7 @@
         <v>audioclip_sfx_h0171_jp.ab</v>
       </c>
       <c r="C123">
-        <v>1738274</v>
+        <v>1738273</v>
       </c>
       <c r="D123" t="str">
         <v>Stage_1</v>
@@ -2910,7 +2910,7 @@
         <v>audioclip_sfx_h0175_jp.ab</v>
       </c>
       <c r="C126">
-        <v>1253485</v>
+        <v>1253486</v>
       </c>
       <c r="D126" t="str">
         <v>Stage_1</v>
@@ -2970,7 +2970,7 @@
         <v>audioclip_sfx_h0179_jp.ab</v>
       </c>
       <c r="C129">
-        <v>1837988</v>
+        <v>1837989</v>
       </c>
       <c r="D129" t="str">
         <v>Stage_1</v>
@@ -3010,7 +3010,7 @@
         <v>audioclip_sfx_h0185_jp.ab</v>
       </c>
       <c r="C131">
-        <v>1563968</v>
+        <v>1563967</v>
       </c>
       <c r="D131" t="str">
         <v>Stage_1</v>
@@ -3030,7 +3030,7 @@
         <v>audioclip_sfx_h0186_jp.ab</v>
       </c>
       <c r="C132">
-        <v>1892917</v>
+        <v>1892919</v>
       </c>
       <c r="D132" t="str">
         <v>Stage_1</v>
@@ -3050,7 +3050,7 @@
         <v>audioclip_sfx_h0190_jp.ab</v>
       </c>
       <c r="C133">
-        <v>2643059</v>
+        <v>2643058</v>
       </c>
       <c r="D133" t="str">
         <v>Stage_1</v>
@@ -3150,7 +3150,7 @@
         <v>audioclip_sfx_h0196_jp.ab</v>
       </c>
       <c r="C138">
-        <v>1046813</v>
+        <v>1046812</v>
       </c>
       <c r="D138" t="str">
         <v>Stage_1</v>
@@ -3190,7 +3190,7 @@
         <v>audioclip_sfx_h0198_jp.ab</v>
       </c>
       <c r="C140">
-        <v>1081026</v>
+        <v>1081025</v>
       </c>
       <c r="D140" t="str">
         <v>Stage_1</v>
@@ -3290,7 +3290,7 @@
         <v>audioclip_sfx_h0208_jp.ab</v>
       </c>
       <c r="C145">
-        <v>774134</v>
+        <v>774137</v>
       </c>
       <c r="D145" t="str">
         <v>Stage_1</v>
@@ -3490,7 +3490,7 @@
         <v>audioclip_sfx_h0224_jp.ab</v>
       </c>
       <c r="C155">
-        <v>1031308</v>
+        <v>1031309</v>
       </c>
       <c r="D155" t="str">
         <v>Stage_1</v>
@@ -3550,7 +3550,7 @@
         <v>audioclip_sfx_h0230_jp.ab</v>
       </c>
       <c r="C158">
-        <v>1022961</v>
+        <v>1022962</v>
       </c>
       <c r="D158" t="str">
         <v>Stage_1</v>
@@ -3590,7 +3590,7 @@
         <v>audioclip_sfx_h0233_jp.ab</v>
       </c>
       <c r="C160">
-        <v>1911213</v>
+        <v>1911214</v>
       </c>
       <c r="D160" t="str">
         <v>Stage_1</v>
@@ -3650,7 +3650,7 @@
         <v>audioclip_sfx_h0236_jp.ab</v>
       </c>
       <c r="C163">
-        <v>2245976</v>
+        <v>2245978</v>
       </c>
       <c r="D163" t="str">
         <v>Stage_1</v>
@@ -3670,7 +3670,7 @@
         <v>audioclip_sfx_h0237_jp.ab</v>
       </c>
       <c r="C164">
-        <v>2431132</v>
+        <v>2431130</v>
       </c>
       <c r="D164" t="str">
         <v>Stage_1</v>
@@ -3750,7 +3750,7 @@
         <v>audioclip_sfx_h0241_jp.ab</v>
       </c>
       <c r="C168">
-        <v>1125057</v>
+        <v>1125056</v>
       </c>
       <c r="D168" t="str">
         <v>Stage_1</v>
@@ -3850,7 +3850,7 @@
         <v>audioclip_sfx_h0248_jp.ab</v>
       </c>
       <c r="C173">
-        <v>1234716</v>
+        <v>1234718</v>
       </c>
       <c r="D173" t="str">
         <v>Stage_1</v>
@@ -3870,7 +3870,7 @@
         <v>audioclip_sfx_h0249_jp.ab</v>
       </c>
       <c r="C174">
-        <v>899109</v>
+        <v>899107</v>
       </c>
       <c r="D174" t="str">
         <v>Stage_1</v>
@@ -3970,7 +3970,7 @@
         <v>audioclip_sfx_h0259_jp.ab</v>
       </c>
       <c r="C179">
-        <v>1446713</v>
+        <v>1446712</v>
       </c>
       <c r="D179" t="str">
         <v>Stage_1</v>
@@ -3990,7 +3990,7 @@
         <v>audioclip_sfx_h0261_jp.ab</v>
       </c>
       <c r="C180">
-        <v>1220853</v>
+        <v>1220852</v>
       </c>
       <c r="D180" t="str">
         <v>Stage_1</v>
@@ -4144,13 +4144,13 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>audioclip_sfx_h0274_jp.ab</v>
+        <v>audioclip_sfx_h0273_jp.ab</v>
       </c>
       <c r="B188" t="str">
-        <v>audioclip_sfx_h0274_jp.ab</v>
+        <v>audioclip_sfx_h0273_jp.ab</v>
       </c>
       <c r="C188">
-        <v>1539698</v>
+        <v>1372807</v>
       </c>
       <c r="D188" t="str">
         <v>Stage_1</v>
@@ -4159,18 +4159,18 @@
         <v>0</v>
       </c>
       <c r="F188" t="str">
-        <v>1af040bd1788fa17e98eb02c87f15e5ada55e3a2e5a70b2e56b505e3c5d85090</v>
+        <v>5fff5d907859c6321942ad5db651650d340e8a3ff72cd16eb8ec3f2c60d41c6c</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>audioclip_sfx_h3190_jp.ab</v>
+        <v>audioclip_sfx_h0274_jp.ab</v>
       </c>
       <c r="B189" t="str">
-        <v>audioclip_sfx_h3190_jp.ab</v>
+        <v>audioclip_sfx_h0274_jp.ab</v>
       </c>
       <c r="C189">
-        <v>274141</v>
+        <v>1539698</v>
       </c>
       <c r="D189" t="str">
         <v>Stage_1</v>
@@ -4179,18 +4179,18 @@
         <v>0</v>
       </c>
       <c r="F189" t="str">
-        <v>9eb4ecd3f3e085f0324fe131b664b0dd4662b72c3dc2fcf9d07102bf21c32b72</v>
+        <v>1af040bd1788fa17e98eb02c87f15e5ada55e3a2e5a70b2e56b505e3c5d85090</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>audioclip_sfx_h3401_jp.ab</v>
+        <v>audioclip_sfx_h3190_jp.ab</v>
       </c>
       <c r="B190" t="str">
-        <v>audioclip_sfx_h3401_jp.ab</v>
+        <v>audioclip_sfx_h3190_jp.ab</v>
       </c>
       <c r="C190">
-        <v>220278</v>
+        <v>274141</v>
       </c>
       <c r="D190" t="str">
         <v>Stage_1</v>
@@ -4199,18 +4199,18 @@
         <v>0</v>
       </c>
       <c r="F190" t="str">
-        <v>bfd1e4e5ecfbe76670e0cbcf8e995505ad8e5878e9a9dd0d01716b8b487c88c9</v>
+        <v>9eb4ecd3f3e085f0324fe131b664b0dd4662b72c3dc2fcf9d07102bf21c32b72</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>audioclip_sfx_m0011_jp.ab</v>
+        <v>audioclip_sfx_h3401_jp.ab</v>
       </c>
       <c r="B191" t="str">
-        <v>audioclip_sfx_m0011_jp.ab</v>
+        <v>audioclip_sfx_h3401_jp.ab</v>
       </c>
       <c r="C191">
-        <v>95939</v>
+        <v>220278</v>
       </c>
       <c r="D191" t="str">
         <v>Stage_1</v>
@@ -4219,18 +4219,18 @@
         <v>0</v>
       </c>
       <c r="F191" t="str">
-        <v>3b4b8786386c69943f0f359fc0ea0779db199f5f19ebc3f5248302686bd825f1</v>
+        <v>bfd1e4e5ecfbe76670e0cbcf8e995505ad8e5878e9a9dd0d01716b8b487c88c9</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>audioclip_sfx_r0034_jp.ab</v>
+        <v>audioclip_sfx_m0011_jp.ab</v>
       </c>
       <c r="B192" t="str">
-        <v>audioclip_sfx_r0034_jp.ab</v>
+        <v>audioclip_sfx_m0011_jp.ab</v>
       </c>
       <c r="C192">
-        <v>1390722</v>
+        <v>95939</v>
       </c>
       <c r="D192" t="str">
         <v>Stage_1</v>
@@ -4239,18 +4239,18 @@
         <v>0</v>
       </c>
       <c r="F192" t="str">
-        <v>4f71edf4bbd4c86e2d9f0bb49f2ef5275cd707aec9e30de127252d2bc84be384</v>
+        <v>3b4b8786386c69943f0f359fc0ea0779db199f5f19ebc3f5248302686bd825f1</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>audioclip_sfx_r0160_jp.ab</v>
+        <v>audioclip_sfx_r0034_jp.ab</v>
       </c>
       <c r="B193" t="str">
-        <v>audioclip_sfx_r0160_jp.ab</v>
+        <v>audioclip_sfx_r0034_jp.ab</v>
       </c>
       <c r="C193">
-        <v>4141829</v>
+        <v>1390720</v>
       </c>
       <c r="D193" t="str">
         <v>Stage_1</v>
@@ -4259,18 +4259,18 @@
         <v>0</v>
       </c>
       <c r="F193" t="str">
-        <v>53250ee3484ea26304c0a7fd112d551545735fdbe124452cac32da923cf3eccb</v>
+        <v>4f71edf4bbd4c86e2d9f0bb49f2ef5275cd707aec9e30de127252d2bc84be384</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>audioclip_sfx_r0173_jp.ab</v>
+        <v>audioclip_sfx_r0160_jp.ab</v>
       </c>
       <c r="B194" t="str">
-        <v>audioclip_sfx_r0173_jp.ab</v>
+        <v>audioclip_sfx_r0160_jp.ab</v>
       </c>
       <c r="C194">
-        <v>1438364</v>
+        <v>4141831</v>
       </c>
       <c r="D194" t="str">
         <v>Stage_1</v>
@@ -4279,18 +4279,18 @@
         <v>0</v>
       </c>
       <c r="F194" t="str">
-        <v>9ecc97c123ddd9aacf2f6ba002eabbbdf3b77e8dd505913f1ed17f488c97a29a</v>
+        <v>53250ee3484ea26304c0a7fd112d551545735fdbe124452cac32da923cf3eccb</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>audioclip_sfx_r0205_jp.ab</v>
+        <v>audioclip_sfx_r0173_jp.ab</v>
       </c>
       <c r="B195" t="str">
-        <v>audioclip_sfx_r0205_jp.ab</v>
+        <v>audioclip_sfx_r0173_jp.ab</v>
       </c>
       <c r="C195">
-        <v>1066357</v>
+        <v>1438363</v>
       </c>
       <c r="D195" t="str">
         <v>Stage_1</v>
@@ -4299,18 +4299,18 @@
         <v>0</v>
       </c>
       <c r="F195" t="str">
-        <v>c92555b7120ac235346b35f30da6753a28158b9840ca72b3cac3d7a23cecdfc2</v>
+        <v>9ecc97c123ddd9aacf2f6ba002eabbbdf3b77e8dd505913f1ed17f488c97a29a</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>audioclip_sfx_t0017_jp.ab</v>
+        <v>audioclip_sfx_r0205_jp.ab</v>
       </c>
       <c r="B196" t="str">
-        <v>audioclip_sfx_t0017_jp.ab</v>
+        <v>audioclip_sfx_r0205_jp.ab</v>
       </c>
       <c r="C196">
-        <v>883186</v>
+        <v>1066358</v>
       </c>
       <c r="D196" t="str">
         <v>Stage_1</v>
@@ -4319,18 +4319,18 @@
         <v>0</v>
       </c>
       <c r="F196" t="str">
-        <v>b70487cba84494f69cee47573fab52e375c8bd92af04044cfdc5818cbe84153d</v>
+        <v>c92555b7120ac235346b35f30da6753a28158b9840ca72b3cac3d7a23cecdfc2</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>audioclip_sfx_t0026_jp.ab</v>
+        <v>audioclip_sfx_t0017_jp.ab</v>
       </c>
       <c r="B197" t="str">
-        <v>audioclip_sfx_t0026_jp.ab</v>
+        <v>audioclip_sfx_t0017_jp.ab</v>
       </c>
       <c r="C197">
-        <v>903966</v>
+        <v>883188</v>
       </c>
       <c r="D197" t="str">
         <v>Stage_1</v>
@@ -4339,18 +4339,18 @@
         <v>0</v>
       </c>
       <c r="F197" t="str">
-        <v>2e9997e9cbd488446ab8e1dd429e313dc921fd5412e0eab5332297122bd1ca26</v>
+        <v>b70487cba84494f69cee47573fab52e375c8bd92af04044cfdc5818cbe84153d</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>audioclip_sfx_t0027_jp.ab</v>
+        <v>audioclip_sfx_t0026_jp.ab</v>
       </c>
       <c r="B198" t="str">
-        <v>audioclip_sfx_t0027_jp.ab</v>
+        <v>audioclip_sfx_t0026_jp.ab</v>
       </c>
       <c r="C198">
-        <v>1396256</v>
+        <v>903967</v>
       </c>
       <c r="D198" t="str">
         <v>Stage_1</v>
@@ -4359,18 +4359,18 @@
         <v>0</v>
       </c>
       <c r="F198" t="str">
-        <v>b15bdd7b76908dfea388b149103cb7a3bb8ddedb9d0b66e61a9bbdb4ed76c6bb</v>
+        <v>2e9997e9cbd488446ab8e1dd429e313dc921fd5412e0eab5332297122bd1ca26</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>audioclip_sfx_t0032_jp.ab</v>
+        <v>audioclip_sfx_t0027_jp.ab</v>
       </c>
       <c r="B199" t="str">
-        <v>audioclip_sfx_t0032_jp.ab</v>
+        <v>audioclip_sfx_t0027_jp.ab</v>
       </c>
       <c r="C199">
-        <v>995097</v>
+        <v>1396255</v>
       </c>
       <c r="D199" t="str">
         <v>Stage_1</v>
@@ -4379,18 +4379,18 @@
         <v>0</v>
       </c>
       <c r="F199" t="str">
-        <v>ba41a2a25880e9c9c32992a8d12134f3417542a623ef5796438664487de2dd84</v>
+        <v>b15bdd7b76908dfea388b149103cb7a3bb8ddedb9d0b66e61a9bbdb4ed76c6bb</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>audioclip_sfx_t0033_jp.ab</v>
+        <v>audioclip_sfx_t0032_jp.ab</v>
       </c>
       <c r="B200" t="str">
-        <v>audioclip_sfx_t0033_jp.ab</v>
+        <v>audioclip_sfx_t0032_jp.ab</v>
       </c>
       <c r="C200">
-        <v>1222455</v>
+        <v>995096</v>
       </c>
       <c r="D200" t="str">
         <v>Stage_1</v>
@@ -4399,18 +4399,18 @@
         <v>0</v>
       </c>
       <c r="F200" t="str">
-        <v>63963c9efe4a35bd1f713e9096337f19fd65c782f6a42ffe70e44f4b05fc8e64</v>
+        <v>ba41a2a25880e9c9c32992a8d12134f3417542a623ef5796438664487de2dd84</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>audioclip_sfx_t0039_jp.ab</v>
+        <v>audioclip_sfx_t0033_jp.ab</v>
       </c>
       <c r="B201" t="str">
-        <v>audioclip_sfx_t0039_jp.ab</v>
+        <v>audioclip_sfx_t0033_jp.ab</v>
       </c>
       <c r="C201">
-        <v>694991</v>
+        <v>1222456</v>
       </c>
       <c r="D201" t="str">
         <v>Stage_1</v>
@@ -4419,18 +4419,18 @@
         <v>0</v>
       </c>
       <c r="F201" t="str">
-        <v>a2e4375cd3ec14e8de1240ada61ea4bd86a4168a0f7da338bdf3289a455ace8d</v>
+        <v>63963c9efe4a35bd1f713e9096337f19fd65c782f6a42ffe70e44f4b05fc8e64</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>audioclip_sfx_t0044_jp.ab</v>
+        <v>audioclip_sfx_t0039_jp.ab</v>
       </c>
       <c r="B202" t="str">
-        <v>audioclip_sfx_t0044_jp.ab</v>
+        <v>audioclip_sfx_t0039_jp.ab</v>
       </c>
       <c r="C202">
-        <v>3841908</v>
+        <v>694991</v>
       </c>
       <c r="D202" t="str">
         <v>Stage_1</v>
@@ -4439,18 +4439,18 @@
         <v>0</v>
       </c>
       <c r="F202" t="str">
-        <v>91288f2a2fcc8e9d38b2516a9a0c2fc5655d888dbc2e871df9f5a39a9ffce823</v>
+        <v>a2e4375cd3ec14e8de1240ada61ea4bd86a4168a0f7da338bdf3289a455ace8d</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>audioclip_sfx_t0049_jp.ab</v>
+        <v>audioclip_sfx_t0044_jp.ab</v>
       </c>
       <c r="B203" t="str">
-        <v>audioclip_sfx_t0049_jp.ab</v>
+        <v>audioclip_sfx_t0044_jp.ab</v>
       </c>
       <c r="C203">
-        <v>1950972</v>
+        <v>3841908</v>
       </c>
       <c r="D203" t="str">
         <v>Stage_1</v>
@@ -4459,18 +4459,18 @@
         <v>0</v>
       </c>
       <c r="F203" t="str">
-        <v>67f07047bfa16f49fbf64d39e131045c4144ba87694de4e7f992355b9c299351</v>
+        <v>91288f2a2fcc8e9d38b2516a9a0c2fc5655d888dbc2e871df9f5a39a9ffce823</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>audioclip_sfx_t0153_jp.ab</v>
+        <v>audioclip_sfx_t0049_jp.ab</v>
       </c>
       <c r="B204" t="str">
-        <v>audioclip_sfx_t0153_jp.ab</v>
+        <v>audioclip_sfx_t0049_jp.ab</v>
       </c>
       <c r="C204">
-        <v>2974171</v>
+        <v>1950971</v>
       </c>
       <c r="D204" t="str">
         <v>Stage_1</v>
@@ -4479,18 +4479,18 @@
         <v>0</v>
       </c>
       <c r="F204" t="str">
-        <v>15235b6c85359ae5ee7667d431699e6c187e2ed3e93cf47a2a46349be09b4179</v>
+        <v>67f07047bfa16f49fbf64d39e131045c4144ba87694de4e7f992355b9c299351</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>audioclip_sfx_t0155_jp.ab</v>
+        <v>audioclip_sfx_t0153_jp.ab</v>
       </c>
       <c r="B205" t="str">
-        <v>audioclip_sfx_t0155_jp.ab</v>
+        <v>audioclip_sfx_t0153_jp.ab</v>
       </c>
       <c r="C205">
-        <v>1992961</v>
+        <v>2974172</v>
       </c>
       <c r="D205" t="str">
         <v>Stage_1</v>
@@ -4499,18 +4499,18 @@
         <v>0</v>
       </c>
       <c r="F205" t="str">
-        <v>7c84d1990a85f4779a7eda24c273846c81610aa0fe2813d34e8445ed38b16296</v>
+        <v>15235b6c85359ae5ee7667d431699e6c187e2ed3e93cf47a2a46349be09b4179</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>audioclip_sfx_t0156_jp.ab</v>
+        <v>audioclip_sfx_t0155_jp.ab</v>
       </c>
       <c r="B206" t="str">
-        <v>audioclip_sfx_t0156_jp.ab</v>
+        <v>audioclip_sfx_t0155_jp.ab</v>
       </c>
       <c r="C206">
-        <v>2340708</v>
+        <v>1992961</v>
       </c>
       <c r="D206" t="str">
         <v>Stage_1</v>
@@ -4519,18 +4519,18 @@
         <v>0</v>
       </c>
       <c r="F206" t="str">
-        <v>5c7114173bcc2aa7765ceeec641470a3748cba8820707c60590b601ffa9e7055</v>
+        <v>7c84d1990a85f4779a7eda24c273846c81610aa0fe2813d34e8445ed38b16296</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>audioclip_sfx_t0158_jp.ab</v>
+        <v>audioclip_sfx_t0156_jp.ab</v>
       </c>
       <c r="B207" t="str">
-        <v>audioclip_sfx_t0158_jp.ab</v>
+        <v>audioclip_sfx_t0156_jp.ab</v>
       </c>
       <c r="C207">
-        <v>1950990</v>
+        <v>2340708</v>
       </c>
       <c r="D207" t="str">
         <v>Stage_1</v>
@@ -4539,18 +4539,18 @@
         <v>0</v>
       </c>
       <c r="F207" t="str">
-        <v>e52de1bdb54e58c7e3ff0ad2ab16da9e6f5d9cc50b81d89beace7a56e732346d</v>
+        <v>5c7114173bcc2aa7765ceeec641470a3748cba8820707c60590b601ffa9e7055</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>audioclip_sfx_t0180_jp.ab</v>
+        <v>audioclip_sfx_t0158_jp.ab</v>
       </c>
       <c r="B208" t="str">
-        <v>audioclip_sfx_t0180_jp.ab</v>
+        <v>audioclip_sfx_t0158_jp.ab</v>
       </c>
       <c r="C208">
-        <v>2527577</v>
+        <v>1950991</v>
       </c>
       <c r="D208" t="str">
         <v>Stage_1</v>
@@ -4559,18 +4559,18 @@
         <v>0</v>
       </c>
       <c r="F208" t="str">
-        <v>6f31b6b3134e7be9114828c534a1bd1df6311033e5cde7af58e453a261307349</v>
+        <v>e52de1bdb54e58c7e3ff0ad2ab16da9e6f5d9cc50b81d89beace7a56e732346d</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>audioclip_sfx_t0181_jp.ab</v>
+        <v>audioclip_sfx_t0180_jp.ab</v>
       </c>
       <c r="B209" t="str">
-        <v>audioclip_sfx_t0181_jp.ab</v>
+        <v>audioclip_sfx_t0180_jp.ab</v>
       </c>
       <c r="C209">
-        <v>2120060</v>
+        <v>2527578</v>
       </c>
       <c r="D209" t="str">
         <v>Stage_1</v>
@@ -4579,18 +4579,18 @@
         <v>0</v>
       </c>
       <c r="F209" t="str">
-        <v>dafa9dbdf2f8f8a22b7186d59bc97ac7a5c45f7bd8f4b5d0a6060d3a7f0b9375</v>
+        <v>6f31b6b3134e7be9114828c534a1bd1df6311033e5cde7af58e453a261307349</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>audioclip_sfx_t0182_jp.ab</v>
+        <v>audioclip_sfx_t0181_jp.ab</v>
       </c>
       <c r="B210" t="str">
-        <v>audioclip_sfx_t0182_jp.ab</v>
+        <v>audioclip_sfx_t0181_jp.ab</v>
       </c>
       <c r="C210">
-        <v>1952767</v>
+        <v>2120059</v>
       </c>
       <c r="D210" t="str">
         <v>Stage_1</v>
@@ -4599,18 +4599,18 @@
         <v>0</v>
       </c>
       <c r="F210" t="str">
-        <v>c6062de6ae2cba59cbcc0cdb17d71b682a4cf7097952355c293ec991ad67657f</v>
+        <v>dafa9dbdf2f8f8a22b7186d59bc97ac7a5c45f7bd8f4b5d0a6060d3a7f0b9375</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>audioclip_sfx_t0184_jp.ab</v>
+        <v>audioclip_sfx_t0182_jp.ab</v>
       </c>
       <c r="B211" t="str">
-        <v>audioclip_sfx_t0184_jp.ab</v>
+        <v>audioclip_sfx_t0182_jp.ab</v>
       </c>
       <c r="C211">
-        <v>1736024</v>
+        <v>1952767</v>
       </c>
       <c r="D211" t="str">
         <v>Stage_1</v>
@@ -4619,18 +4619,18 @@
         <v>0</v>
       </c>
       <c r="F211" t="str">
-        <v>fac1fce0fd7de8c885aff7abb736d9580d0d9c03c7bcb811dda4c341e27b0b63</v>
+        <v>c6062de6ae2cba59cbcc0cdb17d71b682a4cf7097952355c293ec991ad67657f</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>audioclip_sfx_t0187_jp.ab</v>
+        <v>audioclip_sfx_t0184_jp.ab</v>
       </c>
       <c r="B212" t="str">
-        <v>audioclip_sfx_t0187_jp.ab</v>
+        <v>audioclip_sfx_t0184_jp.ab</v>
       </c>
       <c r="C212">
-        <v>2460157</v>
+        <v>1736024</v>
       </c>
       <c r="D212" t="str">
         <v>Stage_1</v>
@@ -4639,18 +4639,18 @@
         <v>0</v>
       </c>
       <c r="F212" t="str">
-        <v>c7515df8ff510981f8f8cf8b1ee59f740db4c11b7342c41539e5299ad250d8a2</v>
+        <v>fac1fce0fd7de8c885aff7abb736d9580d0d9c03c7bcb811dda4c341e27b0b63</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>audioclip_sfx_t0188_jp.ab</v>
+        <v>audioclip_sfx_t0187_jp.ab</v>
       </c>
       <c r="B213" t="str">
-        <v>audioclip_sfx_t0188_jp.ab</v>
+        <v>audioclip_sfx_t0187_jp.ab</v>
       </c>
       <c r="C213">
-        <v>1973761</v>
+        <v>2460157</v>
       </c>
       <c r="D213" t="str">
         <v>Stage_1</v>
@@ -4659,18 +4659,18 @@
         <v>0</v>
       </c>
       <c r="F213" t="str">
-        <v>29e965dcc6fc00f674215baf4b928c70be3f541088a6a5b986f879c73f5a5d42</v>
+        <v>c7515df8ff510981f8f8cf8b1ee59f740db4c11b7342c41539e5299ad250d8a2</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>audioclip_sfx_t0189_jp.ab</v>
+        <v>audioclip_sfx_t0188_jp.ab</v>
       </c>
       <c r="B214" t="str">
-        <v>audioclip_sfx_t0189_jp.ab</v>
+        <v>audioclip_sfx_t0188_jp.ab</v>
       </c>
       <c r="C214">
-        <v>2403910</v>
+        <v>1973760</v>
       </c>
       <c r="D214" t="str">
         <v>Stage_1</v>
@@ -4679,18 +4679,18 @@
         <v>0</v>
       </c>
       <c r="F214" t="str">
-        <v>b16c0ca313216b564f4b1e6eccb6e954925af42df5760bd9437c91e0a2061922</v>
+        <v>29e965dcc6fc00f674215baf4b928c70be3f541088a6a5b986f879c73f5a5d42</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>audioclip_sfx_t0204_jp.ab</v>
+        <v>audioclip_sfx_t0189_jp.ab</v>
       </c>
       <c r="B215" t="str">
-        <v>audioclip_sfx_t0204_jp.ab</v>
+        <v>audioclip_sfx_t0189_jp.ab</v>
       </c>
       <c r="C215">
-        <v>1290319</v>
+        <v>2403910</v>
       </c>
       <c r="D215" t="str">
         <v>Stage_1</v>
@@ -4699,18 +4699,18 @@
         <v>0</v>
       </c>
       <c r="F215" t="str">
-        <v>3cd8c7dae7a51d1482da70e02c1ec32b0e9414370658e14b4e45fc0e0665a4e9</v>
+        <v>b16c0ca313216b564f4b1e6eccb6e954925af42df5760bd9437c91e0a2061922</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>audioclip_sfx_t0207_jp.ab</v>
+        <v>audioclip_sfx_t0204_jp.ab</v>
       </c>
       <c r="B216" t="str">
-        <v>audioclip_sfx_t0207_jp.ab</v>
+        <v>audioclip_sfx_t0204_jp.ab</v>
       </c>
       <c r="C216">
-        <v>940739</v>
+        <v>1290319</v>
       </c>
       <c r="D216" t="str">
         <v>Stage_1</v>
@@ -4719,18 +4719,18 @@
         <v>0</v>
       </c>
       <c r="F216" t="str">
-        <v>6093f9e47c57dd3fc24f60af5f7622e81bacab91f35c0dacb54fcc1e2d36c7cf</v>
+        <v>3cd8c7dae7a51d1482da70e02c1ec32b0e9414370658e14b4e45fc0e0665a4e9</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>audioclip_sfx_t0212_jp.ab</v>
+        <v>audioclip_sfx_t0207_jp.ab</v>
       </c>
       <c r="B217" t="str">
-        <v>audioclip_sfx_t0212_jp.ab</v>
+        <v>audioclip_sfx_t0207_jp.ab</v>
       </c>
       <c r="C217">
-        <v>1484342</v>
+        <v>940739</v>
       </c>
       <c r="D217" t="str">
         <v>Stage_1</v>
@@ -4739,18 +4739,18 @@
         <v>0</v>
       </c>
       <c r="F217" t="str">
-        <v>e73e76ba60cbcfda52306bf47a263f3be4e0c31663be4278b999cff99d452011</v>
+        <v>6093f9e47c57dd3fc24f60af5f7622e81bacab91f35c0dacb54fcc1e2d36c7cf</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>audioclip_sfx_t0214_jp.ab</v>
+        <v>audioclip_sfx_t0212_jp.ab</v>
       </c>
       <c r="B218" t="str">
-        <v>audioclip_sfx_t0214_jp.ab</v>
+        <v>audioclip_sfx_t0212_jp.ab</v>
       </c>
       <c r="C218">
-        <v>1202868</v>
+        <v>1484342</v>
       </c>
       <c r="D218" t="str">
         <v>Stage_1</v>
@@ -4759,18 +4759,18 @@
         <v>0</v>
       </c>
       <c r="F218" t="str">
-        <v>8d2f29e299d4c8d0cb34579b5ae0b2de70efd1d3d394e38a5323bfbe75a553e7</v>
+        <v>e73e76ba60cbcfda52306bf47a263f3be4e0c31663be4278b999cff99d452011</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>audioclip_sfx_t0218_jp.ab</v>
+        <v>audioclip_sfx_t0214_jp.ab</v>
       </c>
       <c r="B219" t="str">
-        <v>audioclip_sfx_t0218_jp.ab</v>
+        <v>audioclip_sfx_t0214_jp.ab</v>
       </c>
       <c r="C219">
-        <v>619268</v>
+        <v>1202868</v>
       </c>
       <c r="D219" t="str">
         <v>Stage_1</v>
@@ -4779,18 +4779,18 @@
         <v>0</v>
       </c>
       <c r="F219" t="str">
-        <v>76c2f395f7dd3e6968171d854f1a945ff726837685d2a94e2a19c1fe8c217be8</v>
+        <v>8d2f29e299d4c8d0cb34579b5ae0b2de70efd1d3d394e38a5323bfbe75a553e7</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>audioclip_sfx_t0222_jp.ab</v>
+        <v>audioclip_sfx_t0218_jp.ab</v>
       </c>
       <c r="B220" t="str">
-        <v>audioclip_sfx_t0222_jp.ab</v>
+        <v>audioclip_sfx_t0218_jp.ab</v>
       </c>
       <c r="C220">
-        <v>781279</v>
+        <v>619268</v>
       </c>
       <c r="D220" t="str">
         <v>Stage_1</v>
@@ -4799,18 +4799,18 @@
         <v>0</v>
       </c>
       <c r="F220" t="str">
-        <v>c1be58c088b69a1fd1f997ba5f0d043bb187c8feb06162a49a38b291cde93ed5</v>
+        <v>76c2f395f7dd3e6968171d854f1a945ff726837685d2a94e2a19c1fe8c217be8</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>audioclip_sfx_t0223_jp.ab</v>
+        <v>audioclip_sfx_t0222_jp.ab</v>
       </c>
       <c r="B221" t="str">
-        <v>audioclip_sfx_t0223_jp.ab</v>
+        <v>audioclip_sfx_t0222_jp.ab</v>
       </c>
       <c r="C221">
-        <v>988344</v>
+        <v>781279</v>
       </c>
       <c r="D221" t="str">
         <v>Stage_1</v>
@@ -4819,18 +4819,18 @@
         <v>0</v>
       </c>
       <c r="F221" t="str">
-        <v>1f449da36a5721d749c0a977bfc07acd9568c1e47886840b5d6eca12d7ba7911</v>
+        <v>c1be58c088b69a1fd1f997ba5f0d043bb187c8feb06162a49a38b291cde93ed5</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>audioclip_sfx_t0225_jp.ab</v>
+        <v>audioclip_sfx_t0223_jp.ab</v>
       </c>
       <c r="B222" t="str">
-        <v>audioclip_sfx_t0225_jp.ab</v>
+        <v>audioclip_sfx_t0223_jp.ab</v>
       </c>
       <c r="C222">
-        <v>867411</v>
+        <v>988344</v>
       </c>
       <c r="D222" t="str">
         <v>Stage_1</v>
@@ -4839,18 +4839,18 @@
         <v>0</v>
       </c>
       <c r="F222" t="str">
-        <v>2403978508b152e347b3f46dda625a4f30324882f2594dd64dcade93354bca03</v>
+        <v>1f449da36a5721d749c0a977bfc07acd9568c1e47886840b5d6eca12d7ba7911</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>audioclip_sfx_t0228_jp.ab</v>
+        <v>audioclip_sfx_t0225_jp.ab</v>
       </c>
       <c r="B223" t="str">
-        <v>audioclip_sfx_t0228_jp.ab</v>
+        <v>audioclip_sfx_t0225_jp.ab</v>
       </c>
       <c r="C223">
-        <v>1009845</v>
+        <v>867411</v>
       </c>
       <c r="D223" t="str">
         <v>Stage_1</v>
@@ -4859,18 +4859,18 @@
         <v>0</v>
       </c>
       <c r="F223" t="str">
-        <v>c501f9ab00ed7a5a51aa0e3f5e6c69e2f59abe0a18f0989109e95f748974c93b</v>
+        <v>2403978508b152e347b3f46dda625a4f30324882f2594dd64dcade93354bca03</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>audioclip_sfx_t0229_jp.ab</v>
+        <v>audioclip_sfx_t0228_jp.ab</v>
       </c>
       <c r="B224" t="str">
-        <v>audioclip_sfx_t0229_jp.ab</v>
+        <v>audioclip_sfx_t0228_jp.ab</v>
       </c>
       <c r="C224">
-        <v>1117664</v>
+        <v>1009845</v>
       </c>
       <c r="D224" t="str">
         <v>Stage_1</v>
@@ -4879,18 +4879,18 @@
         <v>0</v>
       </c>
       <c r="F224" t="str">
-        <v>9f7f6b1d211cc28e51714ec88ca1c3e39dd93ff9915f15d9f74be6b519c65ede</v>
+        <v>c501f9ab00ed7a5a51aa0e3f5e6c69e2f59abe0a18f0989109e95f748974c93b</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>audioclip_sfx_t0231_jp.ab</v>
+        <v>audioclip_sfx_t0229_jp.ab</v>
       </c>
       <c r="B225" t="str">
-        <v>audioclip_sfx_t0231_jp.ab</v>
+        <v>audioclip_sfx_t0229_jp.ab</v>
       </c>
       <c r="C225">
-        <v>1242758</v>
+        <v>1117665</v>
       </c>
       <c r="D225" t="str">
         <v>Stage_1</v>
@@ -4899,18 +4899,18 @@
         <v>0</v>
       </c>
       <c r="F225" t="str">
-        <v>ce08981162e66466b4ee4e4da78ceb0ffc741426c58cd5e7fd42f26741c67bfb</v>
+        <v>9f7f6b1d211cc28e51714ec88ca1c3e39dd93ff9915f15d9f74be6b519c65ede</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>audioclip_sfx_t0242_jp.ab</v>
+        <v>audioclip_sfx_t0231_jp.ab</v>
       </c>
       <c r="B226" t="str">
-        <v>audioclip_sfx_t0242_jp.ab</v>
+        <v>audioclip_sfx_t0231_jp.ab</v>
       </c>
       <c r="C226">
-        <v>955689</v>
+        <v>1242758</v>
       </c>
       <c r="D226" t="str">
         <v>Stage_1</v>
@@ -4919,18 +4919,18 @@
         <v>0</v>
       </c>
       <c r="F226" t="str">
-        <v>b7ace3ce40220f62e3d18d05ec7660b190503c1030c184741d45181e67939878</v>
+        <v>ce08981162e66466b4ee4e4da78ceb0ffc741426c58cd5e7fd42f26741c67bfb</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>audioclip_sfx_t0246_jp.ab</v>
+        <v>audioclip_sfx_t0242_jp.ab</v>
       </c>
       <c r="B227" t="str">
-        <v>audioclip_sfx_t0246_jp.ab</v>
+        <v>audioclip_sfx_t0242_jp.ab</v>
       </c>
       <c r="C227">
-        <v>890771</v>
+        <v>955690</v>
       </c>
       <c r="D227" t="str">
         <v>Stage_1</v>
@@ -4939,18 +4939,18 @@
         <v>0</v>
       </c>
       <c r="F227" t="str">
-        <v>983311ac98117dad253ea5b6a92e1c836692f5f1be8f54da5e2c61e3f0085062</v>
+        <v>b7ace3ce40220f62e3d18d05ec7660b190503c1030c184741d45181e67939878</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>audioclip_sfx_t0250_jp.ab</v>
+        <v>audioclip_sfx_t0246_jp.ab</v>
       </c>
       <c r="B228" t="str">
-        <v>audioclip_sfx_t0250_jp.ab</v>
+        <v>audioclip_sfx_t0246_jp.ab</v>
       </c>
       <c r="C228">
-        <v>1509664</v>
+        <v>890771</v>
       </c>
       <c r="D228" t="str">
         <v>Stage_1</v>
@@ -4959,18 +4959,18 @@
         <v>0</v>
       </c>
       <c r="F228" t="str">
-        <v>1af58272bb08ddde51eb1ba60f0704e4df9b5465bdfeeac1ff193ce56384bdb3</v>
+        <v>983311ac98117dad253ea5b6a92e1c836692f5f1be8f54da5e2c61e3f0085062</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>audioclip_sfx_t0251_jp.ab</v>
+        <v>audioclip_sfx_t0250_jp.ab</v>
       </c>
       <c r="B229" t="str">
-        <v>audioclip_sfx_t0251_jp.ab</v>
+        <v>audioclip_sfx_t0250_jp.ab</v>
       </c>
       <c r="C229">
-        <v>1812579</v>
+        <v>1509664</v>
       </c>
       <c r="D229" t="str">
         <v>Stage_1</v>
@@ -4979,18 +4979,18 @@
         <v>0</v>
       </c>
       <c r="F229" t="str">
-        <v>83103a7a033808c88ac06462bb696421ca4aefe89e7096d385cd786c89d83f7e</v>
+        <v>1af58272bb08ddde51eb1ba60f0704e4df9b5465bdfeeac1ff193ce56384bdb3</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>audioclip_sfx_t0252_jp.ab</v>
+        <v>audioclip_sfx_t0251_jp.ab</v>
       </c>
       <c r="B230" t="str">
-        <v>audioclip_sfx_t0252_jp.ab</v>
+        <v>audioclip_sfx_t0251_jp.ab</v>
       </c>
       <c r="C230">
-        <v>2885316</v>
+        <v>1812579</v>
       </c>
       <c r="D230" t="str">
         <v>Stage_1</v>
@@ -4999,18 +4999,18 @@
         <v>0</v>
       </c>
       <c r="F230" t="str">
-        <v>148649f548044e6098a6642c2fa9ad1b9ff8e00150a71f5809dda3927fe4701f</v>
+        <v>83103a7a033808c88ac06462bb696421ca4aefe89e7096d385cd786c89d83f7e</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>audioclip_sfx_t0254_jp.ab</v>
+        <v>audioclip_sfx_t0252_jp.ab</v>
       </c>
       <c r="B231" t="str">
-        <v>audioclip_sfx_t0254_jp.ab</v>
+        <v>audioclip_sfx_t0252_jp.ab</v>
       </c>
       <c r="C231">
-        <v>1288917</v>
+        <v>2885317</v>
       </c>
       <c r="D231" t="str">
         <v>Stage_1</v>
@@ -5019,18 +5019,18 @@
         <v>0</v>
       </c>
       <c r="F231" t="str">
-        <v>d904be8b981ba87777b1f00a5a758bc50493dacb6f15c975bde4aebd7d563ca8</v>
+        <v>148649f548044e6098a6642c2fa9ad1b9ff8e00150a71f5809dda3927fe4701f</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>audioclip_sfx_t0258_jp.ab</v>
+        <v>audioclip_sfx_t0254_jp.ab</v>
       </c>
       <c r="B232" t="str">
-        <v>audioclip_sfx_t0258_jp.ab</v>
+        <v>audioclip_sfx_t0254_jp.ab</v>
       </c>
       <c r="C232">
-        <v>1912958</v>
+        <v>1288917</v>
       </c>
       <c r="D232" t="str">
         <v>Stage_1</v>
@@ -5039,18 +5039,18 @@
         <v>0</v>
       </c>
       <c r="F232" t="str">
-        <v>b5c1c04a2837264abf5aabfdb7cd0e6b28f8d9c1552e191d433be8dedb7018db</v>
+        <v>d904be8b981ba87777b1f00a5a758bc50493dacb6f15c975bde4aebd7d563ca8</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>audioclip_sfx_t0263_jp.ab</v>
+        <v>audioclip_sfx_t0258_jp.ab</v>
       </c>
       <c r="B233" t="str">
-        <v>audioclip_sfx_t0263_jp.ab</v>
+        <v>audioclip_sfx_t0258_jp.ab</v>
       </c>
       <c r="C233">
-        <v>1741544</v>
+        <v>1912958</v>
       </c>
       <c r="D233" t="str">
         <v>Stage_1</v>
@@ -5059,18 +5059,18 @@
         <v>0</v>
       </c>
       <c r="F233" t="str">
-        <v>a16fb8288cca9c4e0172e756e8f7970aebe0a540486a0136a7e7471ffb57dac4</v>
+        <v>b5c1c04a2837264abf5aabfdb7cd0e6b28f8d9c1552e191d433be8dedb7018db</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>audioclip_sfx_t0269_jp.ab</v>
+        <v>audioclip_sfx_t0263_jp.ab</v>
       </c>
       <c r="B234" t="str">
-        <v>audioclip_sfx_t0269_jp.ab</v>
+        <v>audioclip_sfx_t0263_jp.ab</v>
       </c>
       <c r="C234">
-        <v>1231700</v>
+        <v>1741544</v>
       </c>
       <c r="D234" t="str">
         <v>Stage_1</v>
@@ -5079,18 +5079,18 @@
         <v>0</v>
       </c>
       <c r="F234" t="str">
-        <v>75159c8704f153ca9e4407ce585f5b2e6e24c82349549f6da9d7c7f66d5da6f2</v>
+        <v>a16fb8288cca9c4e0172e756e8f7970aebe0a540486a0136a7e7471ffb57dac4</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>audioclip_sfx_t0272_jp.ab</v>
+        <v>audioclip_sfx_t0269_jp.ab</v>
       </c>
       <c r="B235" t="str">
-        <v>audioclip_sfx_t0272_jp.ab</v>
+        <v>audioclip_sfx_t0269_jp.ab</v>
       </c>
       <c r="C235">
-        <v>1436659</v>
+        <v>1231700</v>
       </c>
       <c r="D235" t="str">
         <v>Stage_1</v>
@@ -5099,18 +5099,18 @@
         <v>0</v>
       </c>
       <c r="F235" t="str">
-        <v>3fbd499f369d479453c63104e49451bb58ffc5a320809a8764e869742fe3e29b</v>
+        <v>75159c8704f153ca9e4407ce585f5b2e6e24c82349549f6da9d7c7f66d5da6f2</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>audioclip_sfx_t0275_jp.ab</v>
+        <v>audioclip_sfx_t0272_jp.ab</v>
       </c>
       <c r="B236" t="str">
-        <v>audioclip_sfx_t0275_jp.ab</v>
+        <v>audioclip_sfx_t0272_jp.ab</v>
       </c>
       <c r="C236">
-        <v>175082</v>
+        <v>1436659</v>
       </c>
       <c r="D236" t="str">
         <v>Stage_1</v>
@@ -5119,18 +5119,18 @@
         <v>0</v>
       </c>
       <c r="F236" t="str">
-        <v>5e68602e3306cffa56ef70ee14bb1d7bb896075430251bddafe2a80bcb009ed3</v>
+        <v>3fbd499f369d479453c63104e49451bb58ffc5a320809a8764e869742fe3e29b</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>audioclip_sfx_t3189_jp.ab</v>
+        <v>audioclip_sfx_t0275_jp.ab</v>
       </c>
       <c r="B237" t="str">
-        <v>audioclip_sfx_t3189_jp.ab</v>
+        <v>audioclip_sfx_t0275_jp.ab</v>
       </c>
       <c r="C237">
-        <v>316225</v>
+        <v>1172442</v>
       </c>
       <c r="D237" t="str">
         <v>Stage_1</v>
@@ -5139,18 +5139,18 @@
         <v>0</v>
       </c>
       <c r="F237" t="str">
-        <v>01cdfbbf9f77a918a2016333f70e047b3087ef54fd0477a4cbb298f6a9eb631d</v>
+        <v>b6f6edf00466592028c60ce90e74dd406334954362231570834a3b4eef0603ed</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>audioclip_sfx_t3191_jp.ab</v>
+        <v>audioclip_sfx_t3189_jp.ab</v>
       </c>
       <c r="B238" t="str">
-        <v>audioclip_sfx_t3191_jp.ab</v>
+        <v>audioclip_sfx_t3189_jp.ab</v>
       </c>
       <c r="C238">
-        <v>164051</v>
+        <v>316225</v>
       </c>
       <c r="D238" t="str">
         <v>Stage_1</v>
@@ -5159,18 +5159,18 @@
         <v>0</v>
       </c>
       <c r="F238" t="str">
-        <v>8abe3d521ebcb185fcce96a49bbc96df07257c26e4d0764e87c1936ced63e4b5</v>
+        <v>01cdfbbf9f77a918a2016333f70e047b3087ef54fd0477a4cbb298f6a9eb631d</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>audioclip_sfx_t3259_jp.ab</v>
+        <v>audioclip_sfx_t3191_jp.ab</v>
       </c>
       <c r="B239" t="str">
-        <v>audioclip_sfx_t3259_jp.ab</v>
+        <v>audioclip_sfx_t3191_jp.ab</v>
       </c>
       <c r="C239">
-        <v>214580</v>
+        <v>164051</v>
       </c>
       <c r="D239" t="str">
         <v>Stage_1</v>
@@ -5179,18 +5179,18 @@
         <v>0</v>
       </c>
       <c r="F239" t="str">
-        <v>d3418a4d00e7826aeec3b5f55296ba67194159666952d4f5645a7a3e3959bd33</v>
+        <v>8abe3d521ebcb185fcce96a49bbc96df07257c26e4d0764e87c1936ced63e4b5</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>audioclip_sfx_t3260_jp.ab</v>
+        <v>audioclip_sfx_t3259_jp.ab</v>
       </c>
       <c r="B240" t="str">
-        <v>audioclip_sfx_t3260_jp.ab</v>
+        <v>audioclip_sfx_t3259_jp.ab</v>
       </c>
       <c r="C240">
-        <v>310407</v>
+        <v>214579</v>
       </c>
       <c r="D240" t="str">
         <v>Stage_1</v>
@@ -5199,18 +5199,18 @@
         <v>0</v>
       </c>
       <c r="F240" t="str">
-        <v>7922b41fbe5ace431e852e608c627644145a3374e7c72b17c7eb99e87d8a75f0</v>
+        <v>d3418a4d00e7826aeec3b5f55296ba67194159666952d4f5645a7a3e3959bd33</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>audioclip_sfx_t3403_jp.ab</v>
+        <v>audioclip_sfx_t3260_jp.ab</v>
       </c>
       <c r="B241" t="str">
-        <v>audioclip_sfx_t3403_jp.ab</v>
+        <v>audioclip_sfx_t3260_jp.ab</v>
       </c>
       <c r="C241">
-        <v>288969</v>
+        <v>310407</v>
       </c>
       <c r="D241" t="str">
         <v>Stage_1</v>
@@ -5219,18 +5219,18 @@
         <v>0</v>
       </c>
       <c r="F241" t="str">
-        <v>318ed1740220025f770750eae32fd2966f4ee57185327d8b16d06272c6fb1b72</v>
+        <v>7922b41fbe5ace431e852e608c627644145a3374e7c72b17c7eb99e87d8a75f0</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>audioclip_sfx_t3407_jp.ab</v>
+        <v>audioclip_sfx_t3403_jp.ab</v>
       </c>
       <c r="B242" t="str">
-        <v>audioclip_sfx_t3407_jp.ab</v>
+        <v>audioclip_sfx_t3403_jp.ab</v>
       </c>
       <c r="C242">
-        <v>270581</v>
+        <v>288968</v>
       </c>
       <c r="D242" t="str">
         <v>Stage_1</v>
@@ -5239,18 +5239,18 @@
         <v>0</v>
       </c>
       <c r="F242" t="str">
-        <v>d6d2fac1b1df16b394e326376d1b0328ebf898c00bfa98e4d483d55222f879a7</v>
+        <v>318ed1740220025f770750eae32fd2966f4ee57185327d8b16d06272c6fb1b72</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>character_largeimage_b0001.ab</v>
+        <v>audioclip_sfx_t3407_jp.ab</v>
       </c>
       <c r="B243" t="str">
-        <v>character_largeimage_b0001.ab</v>
+        <v>audioclip_sfx_t3407_jp.ab</v>
       </c>
       <c r="C243">
-        <v>3127774</v>
+        <v>270580</v>
       </c>
       <c r="D243" t="str">
         <v>Stage_1</v>
@@ -5259,18 +5259,18 @@
         <v>0</v>
       </c>
       <c r="F243" t="str">
-        <v>78e784ceac79715e6f390d5b83f7fb527e8cb5b0404a6f1be45b313a5ba02dc1</v>
+        <v>d6d2fac1b1df16b394e326376d1b0328ebf898c00bfa98e4d483d55222f879a7</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>character_largeimage_b0015.ab</v>
+        <v>character_largeimage_b0001.ab</v>
       </c>
       <c r="B244" t="str">
-        <v>character_largeimage_b0015.ab</v>
+        <v>character_largeimage_b0001.ab</v>
       </c>
       <c r="C244">
-        <v>3331653</v>
+        <v>3127774</v>
       </c>
       <c r="D244" t="str">
         <v>Stage_1</v>
@@ -5279,18 +5279,18 @@
         <v>0</v>
       </c>
       <c r="F244" t="str">
-        <v>dd04ef36d2763124089134dbe7458b80907450a71e52752c5290f0de6f4e7eae</v>
+        <v>78e784ceac79715e6f390d5b83f7fb527e8cb5b0404a6f1be45b313a5ba02dc1</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>character_largeimage_b0028.ab</v>
+        <v>character_largeimage_b0015.ab</v>
       </c>
       <c r="B245" t="str">
-        <v>character_largeimage_b0028.ab</v>
+        <v>character_largeimage_b0015.ab</v>
       </c>
       <c r="C245">
-        <v>3412887</v>
+        <v>3331653</v>
       </c>
       <c r="D245" t="str">
         <v>Stage_1</v>
@@ -5299,18 +5299,18 @@
         <v>0</v>
       </c>
       <c r="F245" t="str">
-        <v>24f9a0b1ca8b96b3da27e0f1d94e381499f584471f56b3c2a7241ae4f6141d8c</v>
+        <v>dd04ef36d2763124089134dbe7458b80907450a71e52752c5290f0de6f4e7eae</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>character_largeimage_b0037.ab</v>
+        <v>character_largeimage_b0028.ab</v>
       </c>
       <c r="B246" t="str">
-        <v>character_largeimage_b0037.ab</v>
+        <v>character_largeimage_b0028.ab</v>
       </c>
       <c r="C246">
-        <v>4001030</v>
+        <v>3412887</v>
       </c>
       <c r="D246" t="str">
         <v>Stage_1</v>
@@ -5319,18 +5319,18 @@
         <v>0</v>
       </c>
       <c r="F246" t="str">
-        <v>1bb8cecd4d65d3465875868908bde0e58a0c63eb9afd917907feb7180b3b8914</v>
+        <v>24f9a0b1ca8b96b3da27e0f1d94e381499f584471f56b3c2a7241ae4f6141d8c</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>character_largeimage_b0202.ab</v>
+        <v>character_largeimage_b0037.ab</v>
       </c>
       <c r="B247" t="str">
-        <v>character_largeimage_b0202.ab</v>
+        <v>character_largeimage_b0037.ab</v>
       </c>
       <c r="C247">
-        <v>790826</v>
+        <v>4001030</v>
       </c>
       <c r="D247" t="str">
         <v>Stage_1</v>
@@ -5339,18 +5339,18 @@
         <v>0</v>
       </c>
       <c r="F247" t="str">
-        <v>be4310c123d2b37d7bdd180f406795da17db9276c2abcf6d33c7f2d834798ba0</v>
+        <v>1bb8cecd4d65d3465875868908bde0e58a0c63eb9afd917907feb7180b3b8914</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>character_largeimage_b0260.ab</v>
+        <v>character_largeimage_b0202.ab</v>
       </c>
       <c r="B248" t="str">
-        <v>character_largeimage_b0260.ab</v>
+        <v>character_largeimage_b0202.ab</v>
       </c>
       <c r="C248">
-        <v>809446</v>
+        <v>790826</v>
       </c>
       <c r="D248" t="str">
         <v>Stage_1</v>
@@ -5359,18 +5359,18 @@
         <v>0</v>
       </c>
       <c r="F248" t="str">
-        <v>5545e61f9af50ea439bb9425d49679c265b4b04153e748be9d8dff61b7f46113</v>
+        <v>be4310c123d2b37d7bdd180f406795da17db9276c2abcf6d33c7f2d834798ba0</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>character_largeimage_b0267.ab</v>
+        <v>character_largeimage_b0260.ab</v>
       </c>
       <c r="B249" t="str">
-        <v>character_largeimage_b0267.ab</v>
+        <v>character_largeimage_b0260.ab</v>
       </c>
       <c r="C249">
-        <v>789052</v>
+        <v>809446</v>
       </c>
       <c r="D249" t="str">
         <v>Stage_1</v>
@@ -5379,18 +5379,18 @@
         <v>0</v>
       </c>
       <c r="F249" t="str">
-        <v>d2c5fdd38d13a1a6a6c8f4f19e0f84caaa156ea51ae041433dfd645d0b8e59f8</v>
+        <v>5545e61f9af50ea439bb9425d49679c265b4b04153e748be9d8dff61b7f46113</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>character_largeimage_e0002.ab</v>
+        <v>character_largeimage_b0267.ab</v>
       </c>
       <c r="B250" t="str">
-        <v>character_largeimage_e0002.ab</v>
+        <v>character_largeimage_b0267.ab</v>
       </c>
       <c r="C250">
-        <v>3558177</v>
+        <v>789052</v>
       </c>
       <c r="D250" t="str">
         <v>Stage_1</v>
@@ -5399,18 +5399,18 @@
         <v>0</v>
       </c>
       <c r="F250" t="str">
-        <v>a51d1503e3559c8ce675afeeed8f729155eed27a8fbebb35148b3dc87f8492e1</v>
+        <v>d2c5fdd38d13a1a6a6c8f4f19e0f84caaa156ea51ae041433dfd645d0b8e59f8</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>character_largeimage_e0046.ab</v>
+        <v>character_largeimage_e0002.ab</v>
       </c>
       <c r="B251" t="str">
-        <v>character_largeimage_e0046.ab</v>
+        <v>character_largeimage_e0002.ab</v>
       </c>
       <c r="C251">
-        <v>797567</v>
+        <v>3558177</v>
       </c>
       <c r="D251" t="str">
         <v>Stage_1</v>
@@ -5419,18 +5419,18 @@
         <v>0</v>
       </c>
       <c r="F251" t="str">
-        <v>a59b46fa5f54c534a9098787a6bf734026c5260a26fe4ed54fab45eb22d26dd3</v>
+        <v>a51d1503e3559c8ce675afeeed8f729155eed27a8fbebb35148b3dc87f8492e1</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>character_largeimage_h0000.ab</v>
+        <v>character_largeimage_e0046.ab</v>
       </c>
       <c r="B252" t="str">
-        <v>character_largeimage_h0000.ab</v>
+        <v>character_largeimage_e0046.ab</v>
       </c>
       <c r="C252">
-        <v>208090</v>
+        <v>797567</v>
       </c>
       <c r="D252" t="str">
         <v>Stage_1</v>
@@ -5439,18 +5439,18 @@
         <v>0</v>
       </c>
       <c r="F252" t="str">
-        <v>a83767d3a6a982d3509d5ed4c329a744963271116b14d342654d3bd0bc612c66</v>
+        <v>a59b46fa5f54c534a9098787a6bf734026c5260a26fe4ed54fab45eb22d26dd3</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>character_largeimage_h0003.ab</v>
+        <v>character_largeimage_h0000.ab</v>
       </c>
       <c r="B253" t="str">
-        <v>character_largeimage_h0003.ab</v>
+        <v>character_largeimage_h0000.ab</v>
       </c>
       <c r="C253">
-        <v>3975187</v>
+        <v>208090</v>
       </c>
       <c r="D253" t="str">
         <v>Stage_1</v>
@@ -5459,18 +5459,18 @@
         <v>0</v>
       </c>
       <c r="F253" t="str">
-        <v>c7a8bfc4a28e3f884b3fd89a9d5988d4b86952038ef16422caddaee083cf9588</v>
+        <v>a83767d3a6a982d3509d5ed4c329a744963271116b14d342654d3bd0bc612c66</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>character_largeimage_h0004.ab</v>
+        <v>character_largeimage_h0003.ab</v>
       </c>
       <c r="B254" t="str">
-        <v>character_largeimage_h0004.ab</v>
+        <v>character_largeimage_h0003.ab</v>
       </c>
       <c r="C254">
-        <v>4306043</v>
+        <v>3975188</v>
       </c>
       <c r="D254" t="str">
         <v>Stage_1</v>
@@ -5479,18 +5479,18 @@
         <v>0</v>
       </c>
       <c r="F254" t="str">
-        <v>8b2ed468e2fcba7d477e3da1fe08a3c2d69c7a5b700f1e557d14a5b1a72ba120</v>
+        <v>c7a8bfc4a28e3f884b3fd89a9d5988d4b86952038ef16422caddaee083cf9588</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>character_largeimage_h0005.ab</v>
+        <v>character_largeimage_h0004.ab</v>
       </c>
       <c r="B255" t="str">
-        <v>character_largeimage_h0005.ab</v>
+        <v>character_largeimage_h0004.ab</v>
       </c>
       <c r="C255">
-        <v>3547758</v>
+        <v>4306043</v>
       </c>
       <c r="D255" t="str">
         <v>Stage_1</v>
@@ -5499,18 +5499,18 @@
         <v>0</v>
       </c>
       <c r="F255" t="str">
-        <v>e3fca3c426d6ee0a3cf9dd6f304f8f25d2fef2a9b1ae6de05627d3db37e3fc6a</v>
+        <v>8b2ed468e2fcba7d477e3da1fe08a3c2d69c7a5b700f1e557d14a5b1a72ba120</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>character_largeimage_h0006.ab</v>
+        <v>character_largeimage_h0005.ab</v>
       </c>
       <c r="B256" t="str">
-        <v>character_largeimage_h0006.ab</v>
+        <v>character_largeimage_h0005.ab</v>
       </c>
       <c r="C256">
-        <v>3671173</v>
+        <v>3547758</v>
       </c>
       <c r="D256" t="str">
         <v>Stage_1</v>
@@ -5519,18 +5519,18 @@
         <v>0</v>
       </c>
       <c r="F256" t="str">
-        <v>b5b543aee2a4ed561a42e5107bbea10ef79b2ad93842b832eb235533f7ca4f99</v>
+        <v>e3fca3c426d6ee0a3cf9dd6f304f8f25d2fef2a9b1ae6de05627d3db37e3fc6a</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>character_largeimage_h0007.ab</v>
+        <v>character_largeimage_h0006.ab</v>
       </c>
       <c r="B257" t="str">
-        <v>character_largeimage_h0007.ab</v>
+        <v>character_largeimage_h0006.ab</v>
       </c>
       <c r="C257">
-        <v>803840</v>
+        <v>3671173</v>
       </c>
       <c r="D257" t="str">
         <v>Stage_1</v>
@@ -5539,18 +5539,18 @@
         <v>0</v>
       </c>
       <c r="F257" t="str">
-        <v>e7a218ee7d7a55f01a0e251a424c46bcf384be8b50176d5cac868f9da0dde6d7</v>
+        <v>b5b543aee2a4ed561a42e5107bbea10ef79b2ad93842b832eb235533f7ca4f99</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>character_largeimage_h0008.ab</v>
+        <v>character_largeimage_h0007.ab</v>
       </c>
       <c r="B258" t="str">
-        <v>character_largeimage_h0008.ab</v>
+        <v>character_largeimage_h0007.ab</v>
       </c>
       <c r="C258">
-        <v>713224</v>
+        <v>803840</v>
       </c>
       <c r="D258" t="str">
         <v>Stage_1</v>
@@ -5559,18 +5559,18 @@
         <v>0</v>
       </c>
       <c r="F258" t="str">
-        <v>bbc9c213346cd9c77b113965f05ffa7d0b05ac187f68681435bf67674b00e146</v>
+        <v>e7a218ee7d7a55f01a0e251a424c46bcf384be8b50176d5cac868f9da0dde6d7</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>character_largeimage_h0009.ab</v>
+        <v>character_largeimage_h0008.ab</v>
       </c>
       <c r="B259" t="str">
-        <v>character_largeimage_h0009.ab</v>
+        <v>character_largeimage_h0008.ab</v>
       </c>
       <c r="C259">
-        <v>831282</v>
+        <v>713224</v>
       </c>
       <c r="D259" t="str">
         <v>Stage_1</v>
@@ -5579,18 +5579,18 @@
         <v>0</v>
       </c>
       <c r="F259" t="str">
-        <v>c38406c3168894ab382175e94b7976eb5ea0caf4f1d7a22fe7b3860d8dc0759e</v>
+        <v>bbc9c213346cd9c77b113965f05ffa7d0b05ac187f68681435bf67674b00e146</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>character_largeimage_h0010.ab</v>
+        <v>character_largeimage_h0009.ab</v>
       </c>
       <c r="B260" t="str">
-        <v>character_largeimage_h0010.ab</v>
+        <v>character_largeimage_h0009.ab</v>
       </c>
       <c r="C260">
-        <v>4679298</v>
+        <v>831282</v>
       </c>
       <c r="D260" t="str">
         <v>Stage_1</v>
@@ -5599,18 +5599,18 @@
         <v>0</v>
       </c>
       <c r="F260" t="str">
-        <v>6f4c0ef7a8999f67fbe814d23dd3f4bdd1d22cc0f44a0f13a9953615ce2d6580</v>
+        <v>c38406c3168894ab382175e94b7976eb5ea0caf4f1d7a22fe7b3860d8dc0759e</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>character_largeimage_h0012.ab</v>
+        <v>character_largeimage_h0010.ab</v>
       </c>
       <c r="B261" t="str">
-        <v>character_largeimage_h0012.ab</v>
+        <v>character_largeimage_h0010.ab</v>
       </c>
       <c r="C261">
-        <v>823851</v>
+        <v>4679298</v>
       </c>
       <c r="D261" t="str">
         <v>Stage_1</v>
@@ -5619,18 +5619,18 @@
         <v>0</v>
       </c>
       <c r="F261" t="str">
-        <v>8ce801de023c56fbb01494c4ca701ac2a955973683af0de63eb113c470fe54c3</v>
+        <v>6f4c0ef7a8999f67fbe814d23dd3f4bdd1d22cc0f44a0f13a9953615ce2d6580</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>character_largeimage_h0013.ab</v>
+        <v>character_largeimage_h0012.ab</v>
       </c>
       <c r="B262" t="str">
-        <v>character_largeimage_h0013.ab</v>
+        <v>character_largeimage_h0012.ab</v>
       </c>
       <c r="C262">
-        <v>730593</v>
+        <v>823851</v>
       </c>
       <c r="D262" t="str">
         <v>Stage_1</v>
@@ -5639,18 +5639,18 @@
         <v>0</v>
       </c>
       <c r="F262" t="str">
-        <v>70018ef62ee1aa1a3b56fd711fb01a33ba58f72ed71b0ee34e169894cad9a529</v>
+        <v>8ce801de023c56fbb01494c4ca701ac2a955973683af0de63eb113c470fe54c3</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>character_largeimage_h0014.ab</v>
+        <v>character_largeimage_h0013.ab</v>
       </c>
       <c r="B263" t="str">
-        <v>character_largeimage_h0014.ab</v>
+        <v>character_largeimage_h0013.ab</v>
       </c>
       <c r="C263">
-        <v>808031</v>
+        <v>730593</v>
       </c>
       <c r="D263" t="str">
         <v>Stage_1</v>
@@ -5659,18 +5659,18 @@
         <v>0</v>
       </c>
       <c r="F263" t="str">
-        <v>da212d22735b71006f7bbebd8d2cf847ddf21d859344229cddf9f6ccf80c5372</v>
+        <v>70018ef62ee1aa1a3b56fd711fb01a33ba58f72ed71b0ee34e169894cad9a529</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>character_largeimage_h0016.ab</v>
+        <v>character_largeimage_h0014.ab</v>
       </c>
       <c r="B264" t="str">
-        <v>character_largeimage_h0016.ab</v>
+        <v>character_largeimage_h0014.ab</v>
       </c>
       <c r="C264">
-        <v>758977</v>
+        <v>808031</v>
       </c>
       <c r="D264" t="str">
         <v>Stage_1</v>
@@ -5679,18 +5679,18 @@
         <v>0</v>
       </c>
       <c r="F264" t="str">
-        <v>8b88365c69bb5344a0f0022c3e0ae2283422666aca080b856f449d7397992782</v>
+        <v>da212d22735b71006f7bbebd8d2cf847ddf21d859344229cddf9f6ccf80c5372</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>character_largeimage_h0018.ab</v>
+        <v>character_largeimage_h0016.ab</v>
       </c>
       <c r="B265" t="str">
-        <v>character_largeimage_h0018.ab</v>
+        <v>character_largeimage_h0016.ab</v>
       </c>
       <c r="C265">
-        <v>4615070</v>
+        <v>758977</v>
       </c>
       <c r="D265" t="str">
         <v>Stage_1</v>
@@ -5699,18 +5699,18 @@
         <v>0</v>
       </c>
       <c r="F265" t="str">
-        <v>78559c267f1b3412982acc007d76441d8b75e93eb4bfcdb0e95485e9ecd87318</v>
+        <v>8b88365c69bb5344a0f0022c3e0ae2283422666aca080b856f449d7397992782</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>character_largeimage_h0020.ab</v>
+        <v>character_largeimage_h0018.ab</v>
       </c>
       <c r="B266" t="str">
-        <v>character_largeimage_h0020.ab</v>
+        <v>character_largeimage_h0018.ab</v>
       </c>
       <c r="C266">
-        <v>3928747</v>
+        <v>4615070</v>
       </c>
       <c r="D266" t="str">
         <v>Stage_1</v>
@@ -5719,18 +5719,18 @@
         <v>0</v>
       </c>
       <c r="F266" t="str">
-        <v>649021775c3d944ec66710dc2833a8df8f6e11c44878c62f3b931ff660a3c2da</v>
+        <v>78559c267f1b3412982acc007d76441d8b75e93eb4bfcdb0e95485e9ecd87318</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>character_largeimage_h0021.ab</v>
+        <v>character_largeimage_h0020.ab</v>
       </c>
       <c r="B267" t="str">
-        <v>character_largeimage_h0021.ab</v>
+        <v>character_largeimage_h0020.ab</v>
       </c>
       <c r="C267">
-        <v>4234934</v>
+        <v>3928747</v>
       </c>
       <c r="D267" t="str">
         <v>Stage_1</v>
@@ -5739,18 +5739,18 @@
         <v>0</v>
       </c>
       <c r="F267" t="str">
-        <v>95f82d1cb182f0d594eb6125d7b4f828b8e2b54c03c6a9b2a8a2688ae2b427ef</v>
+        <v>649021775c3d944ec66710dc2833a8df8f6e11c44878c62f3b931ff660a3c2da</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>character_largeimage_h0022.ab</v>
+        <v>character_largeimage_h0021.ab</v>
       </c>
       <c r="B268" t="str">
-        <v>character_largeimage_h0022.ab</v>
+        <v>character_largeimage_h0021.ab</v>
       </c>
       <c r="C268">
-        <v>4332457</v>
+        <v>4234934</v>
       </c>
       <c r="D268" t="str">
         <v>Stage_1</v>
@@ -5759,18 +5759,18 @@
         <v>0</v>
       </c>
       <c r="F268" t="str">
-        <v>4d633e8de21a01527f9364d84f44895010d4a5dec9f0ede8402c19749280609a</v>
+        <v>95f82d1cb182f0d594eb6125d7b4f828b8e2b54c03c6a9b2a8a2688ae2b427ef</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>character_largeimage_h0023.ab</v>
+        <v>character_largeimage_h0022.ab</v>
       </c>
       <c r="B269" t="str">
-        <v>character_largeimage_h0023.ab</v>
+        <v>character_largeimage_h0022.ab</v>
       </c>
       <c r="C269">
-        <v>3265010</v>
+        <v>4332457</v>
       </c>
       <c r="D269" t="str">
         <v>Stage_1</v>
@@ -5779,18 +5779,18 @@
         <v>0</v>
       </c>
       <c r="F269" t="str">
-        <v>ffdbdb5c7c3a5f8aec334500f40226b14d82ac63ff43d51fa83131e6be67c680</v>
+        <v>4d633e8de21a01527f9364d84f44895010d4a5dec9f0ede8402c19749280609a</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>character_largeimage_h0024.ab</v>
+        <v>character_largeimage_h0023.ab</v>
       </c>
       <c r="B270" t="str">
-        <v>character_largeimage_h0024.ab</v>
+        <v>character_largeimage_h0023.ab</v>
       </c>
       <c r="C270">
-        <v>3281917</v>
+        <v>3265010</v>
       </c>
       <c r="D270" t="str">
         <v>Stage_1</v>
@@ -5799,18 +5799,18 @@
         <v>0</v>
       </c>
       <c r="F270" t="str">
-        <v>055d98eaa385323f6b431d57d9158c227ec5ff8f3fa628b8fdac15595b44a475</v>
+        <v>ffdbdb5c7c3a5f8aec334500f40226b14d82ac63ff43d51fa83131e6be67c680</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>character_largeimage_h0025.ab</v>
+        <v>character_largeimage_h0024.ab</v>
       </c>
       <c r="B271" t="str">
-        <v>character_largeimage_h0025.ab</v>
+        <v>character_largeimage_h0024.ab</v>
       </c>
       <c r="C271">
-        <v>3268737</v>
+        <v>3281917</v>
       </c>
       <c r="D271" t="str">
         <v>Stage_1</v>
@@ -5819,18 +5819,18 @@
         <v>0</v>
       </c>
       <c r="F271" t="str">
-        <v>2a72b0b0d6249cd756219728440dca77f1388f67427663ba12f8ddac14f3a5c5</v>
+        <v>055d98eaa385323f6b431d57d9158c227ec5ff8f3fa628b8fdac15595b44a475</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>character_largeimage_h0029.ab</v>
+        <v>character_largeimage_h0025.ab</v>
       </c>
       <c r="B272" t="str">
-        <v>character_largeimage_h0029.ab</v>
+        <v>character_largeimage_h0025.ab</v>
       </c>
       <c r="C272">
-        <v>3878944</v>
+        <v>3268737</v>
       </c>
       <c r="D272" t="str">
         <v>Stage_1</v>
@@ -5839,18 +5839,18 @@
         <v>0</v>
       </c>
       <c r="F272" t="str">
-        <v>4d62229cbd284aa9391c2ae5728483edcdd7c3664570bc6980b143987362b95d</v>
+        <v>2a72b0b0d6249cd756219728440dca77f1388f67427663ba12f8ddac14f3a5c5</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>character_largeimage_h0030.ab</v>
+        <v>character_largeimage_h0029.ab</v>
       </c>
       <c r="B273" t="str">
-        <v>character_largeimage_h0030.ab</v>
+        <v>character_largeimage_h0029.ab</v>
       </c>
       <c r="C273">
-        <v>3068963</v>
+        <v>3878944</v>
       </c>
       <c r="D273" t="str">
         <v>Stage_1</v>
@@ -5859,18 +5859,18 @@
         <v>0</v>
       </c>
       <c r="F273" t="str">
-        <v>d43431a351343bcce91b2b6839f9998d1c36be4e3f4f103a9b7bed45056690a6</v>
+        <v>4d62229cbd284aa9391c2ae5728483edcdd7c3664570bc6980b143987362b95d</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>character_largeimage_h0031.ab</v>
+        <v>character_largeimage_h0030.ab</v>
       </c>
       <c r="B274" t="str">
-        <v>character_largeimage_h0031.ab</v>
+        <v>character_largeimage_h0030.ab</v>
       </c>
       <c r="C274">
-        <v>3311210</v>
+        <v>3068963</v>
       </c>
       <c r="D274" t="str">
         <v>Stage_1</v>
@@ -5879,18 +5879,18 @@
         <v>0</v>
       </c>
       <c r="F274" t="str">
-        <v>f844caa4342233c882176f4b3d3b5df3aa38df5704837c4e17b36f772a18fe85</v>
+        <v>d43431a351343bcce91b2b6839f9998d1c36be4e3f4f103a9b7bed45056690a6</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>character_largeimage_h0035.ab</v>
+        <v>character_largeimage_h0031.ab</v>
       </c>
       <c r="B275" t="str">
-        <v>character_largeimage_h0035.ab</v>
+        <v>character_largeimage_h0031.ab</v>
       </c>
       <c r="C275">
-        <v>3958978</v>
+        <v>3311210</v>
       </c>
       <c r="D275" t="str">
         <v>Stage_1</v>
@@ -5899,18 +5899,18 @@
         <v>0</v>
       </c>
       <c r="F275" t="str">
-        <v>5a7f4c68dffa0013111cececfe93648f43ea44a9d2ecc2f353cf7b7c8cb8f59c</v>
+        <v>f844caa4342233c882176f4b3d3b5df3aa38df5704837c4e17b36f772a18fe85</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>character_largeimage_h0036.ab</v>
+        <v>character_largeimage_h0035.ab</v>
       </c>
       <c r="B276" t="str">
-        <v>character_largeimage_h0036.ab</v>
+        <v>character_largeimage_h0035.ab</v>
       </c>
       <c r="C276">
-        <v>2916298</v>
+        <v>3958978</v>
       </c>
       <c r="D276" t="str">
         <v>Stage_1</v>
@@ -5919,18 +5919,18 @@
         <v>0</v>
       </c>
       <c r="F276" t="str">
-        <v>b9696daa9252dec4261611f1f256637ee51cb3b8b33d0b92cfd3bba149001c6e</v>
+        <v>5a7f4c68dffa0013111cececfe93648f43ea44a9d2ecc2f353cf7b7c8cb8f59c</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>character_largeimage_h0038.ab</v>
+        <v>character_largeimage_h0036.ab</v>
       </c>
       <c r="B277" t="str">
-        <v>character_largeimage_h0038.ab</v>
+        <v>character_largeimage_h0036.ab</v>
       </c>
       <c r="C277">
-        <v>855003</v>
+        <v>2916298</v>
       </c>
       <c r="D277" t="str">
         <v>Stage_1</v>
@@ -5939,18 +5939,18 @@
         <v>0</v>
       </c>
       <c r="F277" t="str">
-        <v>289b0ed905365cd5e8cb89fe42ac33d47e5f572cfc93a7419bb99f39ea7341d1</v>
+        <v>b9696daa9252dec4261611f1f256637ee51cb3b8b33d0b92cfd3bba149001c6e</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>character_largeimage_h0040.ab</v>
+        <v>character_largeimage_h0038.ab</v>
       </c>
       <c r="B278" t="str">
-        <v>character_largeimage_h0040.ab</v>
+        <v>character_largeimage_h0038.ab</v>
       </c>
       <c r="C278">
-        <v>834045</v>
+        <v>855003</v>
       </c>
       <c r="D278" t="str">
         <v>Stage_1</v>
@@ -5959,18 +5959,18 @@
         <v>0</v>
       </c>
       <c r="F278" t="str">
-        <v>6b42ad4bbc2598a1f1702e175d9bf9f511e485fa19f3fa86a86c22eb8cc7f23e</v>
+        <v>289b0ed905365cd5e8cb89fe42ac33d47e5f572cfc93a7419bb99f39ea7341d1</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>character_largeimage_h0041.ab</v>
+        <v>character_largeimage_h0040.ab</v>
       </c>
       <c r="B279" t="str">
-        <v>character_largeimage_h0041.ab</v>
+        <v>character_largeimage_h0040.ab</v>
       </c>
       <c r="C279">
-        <v>799261</v>
+        <v>834045</v>
       </c>
       <c r="D279" t="str">
         <v>Stage_1</v>
@@ -5979,18 +5979,18 @@
         <v>0</v>
       </c>
       <c r="F279" t="str">
-        <v>5f1d547ddd7b8ce59a4e005ebe350bdc99957ad7f687d685d31014cccf81c0fc</v>
+        <v>6b42ad4bbc2598a1f1702e175d9bf9f511e485fa19f3fa86a86c22eb8cc7f23e</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>character_largeimage_h0042.ab</v>
+        <v>character_largeimage_h0041.ab</v>
       </c>
       <c r="B280" t="str">
-        <v>character_largeimage_h0042.ab</v>
+        <v>character_largeimage_h0041.ab</v>
       </c>
       <c r="C280">
-        <v>777116</v>
+        <v>799261</v>
       </c>
       <c r="D280" t="str">
         <v>Stage_1</v>
@@ -5999,18 +5999,18 @@
         <v>0</v>
       </c>
       <c r="F280" t="str">
-        <v>ec22258063c80e1c82446b8a02dd46be8a92091df93f324eb9cf423dbee75c4a</v>
+        <v>5f1d547ddd7b8ce59a4e005ebe350bdc99957ad7f687d685d31014cccf81c0fc</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>character_largeimage_h0043.ab</v>
+        <v>character_largeimage_h0042.ab</v>
       </c>
       <c r="B281" t="str">
-        <v>character_largeimage_h0043.ab</v>
+        <v>character_largeimage_h0042.ab</v>
       </c>
       <c r="C281">
-        <v>4131491</v>
+        <v>777116</v>
       </c>
       <c r="D281" t="str">
         <v>Stage_1</v>
@@ -6019,18 +6019,18 @@
         <v>0</v>
       </c>
       <c r="F281" t="str">
-        <v>2e3087d8674c5bff6c4f6a7957f7b459bfefc77083b6fa9050da6c234e5fcd06</v>
+        <v>ec22258063c80e1c82446b8a02dd46be8a92091df93f324eb9cf423dbee75c4a</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>character_largeimage_h0045.ab</v>
+        <v>character_largeimage_h0043.ab</v>
       </c>
       <c r="B282" t="str">
-        <v>character_largeimage_h0045.ab</v>
+        <v>character_largeimage_h0043.ab</v>
       </c>
       <c r="C282">
-        <v>806083</v>
+        <v>4131491</v>
       </c>
       <c r="D282" t="str">
         <v>Stage_1</v>
@@ -6039,18 +6039,18 @@
         <v>0</v>
       </c>
       <c r="F282" t="str">
-        <v>75ea8ae022a44b3b64d866c990239078893ea0883aa85a84522e0d99fff85500</v>
+        <v>2e3087d8674c5bff6c4f6a7957f7b459bfefc77083b6fa9050da6c234e5fcd06</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>character_largeimage_h0047.ab</v>
+        <v>character_largeimage_h0045.ab</v>
       </c>
       <c r="B283" t="str">
-        <v>character_largeimage_h0047.ab</v>
+        <v>character_largeimage_h0045.ab</v>
       </c>
       <c r="C283">
-        <v>4289279</v>
+        <v>806083</v>
       </c>
       <c r="D283" t="str">
         <v>Stage_1</v>
@@ -6059,18 +6059,18 @@
         <v>0</v>
       </c>
       <c r="F283" t="str">
-        <v>3f3f9d99623d7683093487b65cfd461be53bd2b8153a9419bb9880bf3086fee3</v>
+        <v>75ea8ae022a44b3b64d866c990239078893ea0883aa85a84522e0d99fff85500</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>character_largeimage_h0048.ab</v>
+        <v>character_largeimage_h0047.ab</v>
       </c>
       <c r="B284" t="str">
-        <v>character_largeimage_h0048.ab</v>
+        <v>character_largeimage_h0047.ab</v>
       </c>
       <c r="C284">
-        <v>3816882</v>
+        <v>4289279</v>
       </c>
       <c r="D284" t="str">
         <v>Stage_1</v>
@@ -6079,18 +6079,18 @@
         <v>0</v>
       </c>
       <c r="F284" t="str">
-        <v>e342bcc9d451f54427e9e676142ce9d3e42283c78c64adf074fd6754f8b711c9</v>
+        <v>3f3f9d99623d7683093487b65cfd461be53bd2b8153a9419bb9880bf3086fee3</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>character_largeimage_h0097.ab</v>
+        <v>character_largeimage_h0048.ab</v>
       </c>
       <c r="B285" t="str">
-        <v>character_largeimage_h0097.ab</v>
+        <v>character_largeimage_h0048.ab</v>
       </c>
       <c r="C285">
-        <v>5051199</v>
+        <v>3816882</v>
       </c>
       <c r="D285" t="str">
         <v>Stage_1</v>
@@ -6099,18 +6099,18 @@
         <v>0</v>
       </c>
       <c r="F285" t="str">
-        <v>a85ef6c19ca8f47ed76b9c9f22aa8d48512b3d1dc156cdb37fdebe8d80ff9e1a</v>
+        <v>e342bcc9d451f54427e9e676142ce9d3e42283c78c64adf074fd6754f8b711c9</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>character_largeimage_h0133.ab</v>
+        <v>character_largeimage_h0097.ab</v>
       </c>
       <c r="B286" t="str">
-        <v>character_largeimage_h0133.ab</v>
+        <v>character_largeimage_h0097.ab</v>
       </c>
       <c r="C286">
-        <v>4176002</v>
+        <v>5051199</v>
       </c>
       <c r="D286" t="str">
         <v>Stage_1</v>
@@ -6119,18 +6119,18 @@
         <v>0</v>
       </c>
       <c r="F286" t="str">
-        <v>206d98bef7c96e960896ee8ee4a7b90e71f4c30bd73f9833cbe46d246c450f78</v>
+        <v>a85ef6c19ca8f47ed76b9c9f22aa8d48512b3d1dc156cdb37fdebe8d80ff9e1a</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>character_largeimage_h0134.ab</v>
+        <v>character_largeimage_h0133.ab</v>
       </c>
       <c r="B287" t="str">
-        <v>character_largeimage_h0134.ab</v>
+        <v>character_largeimage_h0133.ab</v>
       </c>
       <c r="C287">
-        <v>4242518</v>
+        <v>4176002</v>
       </c>
       <c r="D287" t="str">
         <v>Stage_1</v>
@@ -6139,18 +6139,18 @@
         <v>0</v>
       </c>
       <c r="F287" t="str">
-        <v>824b86c0e40aefc0770c167f978bc2fd4c1925a9efe1e9691c60a2eb5122c14e</v>
+        <v>206d98bef7c96e960896ee8ee4a7b90e71f4c30bd73f9833cbe46d246c450f78</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>character_largeimage_h0135.ab</v>
+        <v>character_largeimage_h0134.ab</v>
       </c>
       <c r="B288" t="str">
-        <v>character_largeimage_h0135.ab</v>
+        <v>character_largeimage_h0134.ab</v>
       </c>
       <c r="C288">
-        <v>3266671</v>
+        <v>4242518</v>
       </c>
       <c r="D288" t="str">
         <v>Stage_1</v>
@@ -6159,18 +6159,18 @@
         <v>0</v>
       </c>
       <c r="F288" t="str">
-        <v>6242bc0a6af6955ac2a0a8d31fee0a742dd006425a34614572a0ff0a6cf3ac30</v>
+        <v>824b86c0e40aefc0770c167f978bc2fd4c1925a9efe1e9691c60a2eb5122c14e</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>character_largeimage_h0136.ab</v>
+        <v>character_largeimage_h0135.ab</v>
       </c>
       <c r="B289" t="str">
-        <v>character_largeimage_h0136.ab</v>
+        <v>character_largeimage_h0135.ab</v>
       </c>
       <c r="C289">
-        <v>3395405</v>
+        <v>3266671</v>
       </c>
       <c r="D289" t="str">
         <v>Stage_1</v>
@@ -6179,18 +6179,18 @@
         <v>0</v>
       </c>
       <c r="F289" t="str">
-        <v>c07b0a8e238a880228b5a27ac66e50bd4cd42ef64dd35769fbadb7ef4f9419aa</v>
+        <v>6242bc0a6af6955ac2a0a8d31fee0a742dd006425a34614572a0ff0a6cf3ac30</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>character_largeimage_h0137.ab</v>
+        <v>character_largeimage_h0136.ab</v>
       </c>
       <c r="B290" t="str">
-        <v>character_largeimage_h0137.ab</v>
+        <v>character_largeimage_h0136.ab</v>
       </c>
       <c r="C290">
-        <v>5218305</v>
+        <v>3395405</v>
       </c>
       <c r="D290" t="str">
         <v>Stage_1</v>
@@ -6199,18 +6199,18 @@
         <v>0</v>
       </c>
       <c r="F290" t="str">
-        <v>0202ec87f638f3fd76d7a98dd5eb291a5d0c8125ded3ecb47f078dccd09f3a0b</v>
+        <v>c07b0a8e238a880228b5a27ac66e50bd4cd42ef64dd35769fbadb7ef4f9419aa</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>character_largeimage_h0138.ab</v>
+        <v>character_largeimage_h0137.ab</v>
       </c>
       <c r="B291" t="str">
-        <v>character_largeimage_h0138.ab</v>
+        <v>character_largeimage_h0137.ab</v>
       </c>
       <c r="C291">
-        <v>4004656</v>
+        <v>5218305</v>
       </c>
       <c r="D291" t="str">
         <v>Stage_1</v>
@@ -6219,18 +6219,18 @@
         <v>0</v>
       </c>
       <c r="F291" t="str">
-        <v>61e12aaabe2c59ab60d879b18a7d8b89b7ddf9a8a71498e190e883353f7167c5</v>
+        <v>0202ec87f638f3fd76d7a98dd5eb291a5d0c8125ded3ecb47f078dccd09f3a0b</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>character_largeimage_h0150.ab</v>
+        <v>character_largeimage_h0138.ab</v>
       </c>
       <c r="B292" t="str">
-        <v>character_largeimage_h0150.ab</v>
+        <v>character_largeimage_h0138.ab</v>
       </c>
       <c r="C292">
-        <v>4037956</v>
+        <v>4004656</v>
       </c>
       <c r="D292" t="str">
         <v>Stage_1</v>
@@ -6239,18 +6239,18 @@
         <v>0</v>
       </c>
       <c r="F292" t="str">
-        <v>d7d2064c4b7799f6f05c0bea7820d77879988674b6cbb863fc6ffff294516853</v>
+        <v>61e12aaabe2c59ab60d879b18a7d8b89b7ddf9a8a71498e190e883353f7167c5</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>character_largeimage_h0151.ab</v>
+        <v>character_largeimage_h0150.ab</v>
       </c>
       <c r="B293" t="str">
-        <v>character_largeimage_h0151.ab</v>
+        <v>character_largeimage_h0150.ab</v>
       </c>
       <c r="C293">
-        <v>2589817</v>
+        <v>4037956</v>
       </c>
       <c r="D293" t="str">
         <v>Stage_1</v>
@@ -6259,18 +6259,18 @@
         <v>0</v>
       </c>
       <c r="F293" t="str">
-        <v>e319306d4c24fd23c4a7473ad0c6218a96d6abcbf8062198b2d17c4362a88c65</v>
+        <v>d7d2064c4b7799f6f05c0bea7820d77879988674b6cbb863fc6ffff294516853</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>character_largeimage_h0152.ab</v>
+        <v>character_largeimage_h0151.ab</v>
       </c>
       <c r="B294" t="str">
-        <v>character_largeimage_h0152.ab</v>
+        <v>character_largeimage_h0151.ab</v>
       </c>
       <c r="C294">
-        <v>3232149</v>
+        <v>2589817</v>
       </c>
       <c r="D294" t="str">
         <v>Stage_1</v>
@@ -6279,18 +6279,18 @@
         <v>0</v>
       </c>
       <c r="F294" t="str">
-        <v>3d27bb9df8d360989f595c83964e2a94d8e5fd22b8f7a6c1193e7c4cc257a6dd</v>
+        <v>e319306d4c24fd23c4a7473ad0c6218a96d6abcbf8062198b2d17c4362a88c65</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>character_largeimage_h0154.ab</v>
+        <v>character_largeimage_h0152.ab</v>
       </c>
       <c r="B295" t="str">
-        <v>character_largeimage_h0154.ab</v>
+        <v>character_largeimage_h0152.ab</v>
       </c>
       <c r="C295">
-        <v>3117108</v>
+        <v>3232149</v>
       </c>
       <c r="D295" t="str">
         <v>Stage_1</v>
@@ -6299,18 +6299,18 @@
         <v>0</v>
       </c>
       <c r="F295" t="str">
-        <v>2ce3ea84a16615d2d212b5c34a99171686d2a4e36cff83cf509ebbfb367e0b2d</v>
+        <v>3d27bb9df8d360989f595c83964e2a94d8e5fd22b8f7a6c1193e7c4cc257a6dd</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>character_largeimage_h0157.ab</v>
+        <v>character_largeimage_h0154.ab</v>
       </c>
       <c r="B296" t="str">
-        <v>character_largeimage_h0157.ab</v>
+        <v>character_largeimage_h0154.ab</v>
       </c>
       <c r="C296">
-        <v>4175238</v>
+        <v>3117108</v>
       </c>
       <c r="D296" t="str">
         <v>Stage_1</v>
@@ -6319,18 +6319,18 @@
         <v>0</v>
       </c>
       <c r="F296" t="str">
-        <v>54cf04627438a03b859ddb2f4687af86522a3814168449e0f183e1fc0bb2a847</v>
+        <v>2ce3ea84a16615d2d212b5c34a99171686d2a4e36cff83cf509ebbfb367e0b2d</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>character_largeimage_h0159.ab</v>
+        <v>character_largeimage_h0157.ab</v>
       </c>
       <c r="B297" t="str">
-        <v>character_largeimage_h0159.ab</v>
+        <v>character_largeimage_h0157.ab</v>
       </c>
       <c r="C297">
-        <v>3438941</v>
+        <v>4175238</v>
       </c>
       <c r="D297" t="str">
         <v>Stage_1</v>
@@ -6339,18 +6339,18 @@
         <v>0</v>
       </c>
       <c r="F297" t="str">
-        <v>69896b88d7b878ed3a9ae0ccaac412a1dcead089da47686152318321fd1de238</v>
+        <v>54cf04627438a03b859ddb2f4687af86522a3814168449e0f183e1fc0bb2a847</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>character_largeimage_h0161.ab</v>
+        <v>character_largeimage_h0159.ab</v>
       </c>
       <c r="B298" t="str">
-        <v>character_largeimage_h0161.ab</v>
+        <v>character_largeimage_h0159.ab</v>
       </c>
       <c r="C298">
-        <v>4097341</v>
+        <v>3438941</v>
       </c>
       <c r="D298" t="str">
         <v>Stage_1</v>
@@ -6359,18 +6359,18 @@
         <v>0</v>
       </c>
       <c r="F298" t="str">
-        <v>a660b7d68977f955ba7ceced1adadab138e4fc76cc5208da43d9369b9dc59e23</v>
+        <v>69896b88d7b878ed3a9ae0ccaac412a1dcead089da47686152318321fd1de238</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>character_largeimage_h0162.ab</v>
+        <v>character_largeimage_h0161.ab</v>
       </c>
       <c r="B299" t="str">
-        <v>character_largeimage_h0162.ab</v>
+        <v>character_largeimage_h0161.ab</v>
       </c>
       <c r="C299">
-        <v>750978</v>
+        <v>4097341</v>
       </c>
       <c r="D299" t="str">
         <v>Stage_1</v>
@@ -6379,18 +6379,18 @@
         <v>0</v>
       </c>
       <c r="F299" t="str">
-        <v>38de7487f089a655ef8ef162c0d101525d83e7f406dabf459b3a9c8390380122</v>
+        <v>a660b7d68977f955ba7ceced1adadab138e4fc76cc5208da43d9369b9dc59e23</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>character_largeimage_h0163.ab</v>
+        <v>character_largeimage_h0162.ab</v>
       </c>
       <c r="B300" t="str">
-        <v>character_largeimage_h0163.ab</v>
+        <v>character_largeimage_h0162.ab</v>
       </c>
       <c r="C300">
-        <v>2078410</v>
+        <v>750978</v>
       </c>
       <c r="D300" t="str">
         <v>Stage_1</v>
@@ -6399,18 +6399,18 @@
         <v>0</v>
       </c>
       <c r="F300" t="str">
-        <v>6cb30643d3b6c9be725cce1f64f07b98426ba01da9ad3e9b127862d8b8dbccf8</v>
+        <v>38de7487f089a655ef8ef162c0d101525d83e7f406dabf459b3a9c8390380122</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>character_largeimage_h0164.ab</v>
+        <v>character_largeimage_h0163.ab</v>
       </c>
       <c r="B301" t="str">
-        <v>character_largeimage_h0164.ab</v>
+        <v>character_largeimage_h0163.ab</v>
       </c>
       <c r="C301">
-        <v>562150</v>
+        <v>2078410</v>
       </c>
       <c r="D301" t="str">
         <v>Stage_1</v>
@@ -6419,18 +6419,18 @@
         <v>0</v>
       </c>
       <c r="F301" t="str">
-        <v>8950a764fe423f950c36d8d8c330f207f071139213a0be60bebb3ded5fe329cd</v>
+        <v>6cb30643d3b6c9be725cce1f64f07b98426ba01da9ad3e9b127862d8b8dbccf8</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>character_largeimage_h0165.ab</v>
+        <v>character_largeimage_h0164.ab</v>
       </c>
       <c r="B302" t="str">
-        <v>character_largeimage_h0165.ab</v>
+        <v>character_largeimage_h0164.ab</v>
       </c>
       <c r="C302">
-        <v>796221</v>
+        <v>562150</v>
       </c>
       <c r="D302" t="str">
         <v>Stage_1</v>
@@ -6439,18 +6439,18 @@
         <v>0</v>
       </c>
       <c r="F302" t="str">
-        <v>1e0a607d278479f68829b034dc3e31e3ff73f88dee2ff778c5c4398d845d97e6</v>
+        <v>8950a764fe423f950c36d8d8c330f207f071139213a0be60bebb3ded5fe329cd</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>character_largeimage_h0166.ab</v>
+        <v>character_largeimage_h0165.ab</v>
       </c>
       <c r="B303" t="str">
-        <v>character_largeimage_h0166.ab</v>
+        <v>character_largeimage_h0165.ab</v>
       </c>
       <c r="C303">
-        <v>770702</v>
+        <v>796221</v>
       </c>
       <c r="D303" t="str">
         <v>Stage_1</v>
@@ -6459,18 +6459,18 @@
         <v>0</v>
       </c>
       <c r="F303" t="str">
-        <v>e434b87a3241dae1f7d81acd86f8102e93895ec6ab30272f57fd9721c6d1bcfa</v>
+        <v>1e0a607d278479f68829b034dc3e31e3ff73f88dee2ff778c5c4398d845d97e6</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>character_largeimage_h0167.ab</v>
+        <v>character_largeimage_h0166.ab</v>
       </c>
       <c r="B304" t="str">
-        <v>character_largeimage_h0167.ab</v>
+        <v>character_largeimage_h0166.ab</v>
       </c>
       <c r="C304">
-        <v>820636</v>
+        <v>770702</v>
       </c>
       <c r="D304" t="str">
         <v>Stage_1</v>
@@ -6479,18 +6479,18 @@
         <v>0</v>
       </c>
       <c r="F304" t="str">
-        <v>c5d28976c731cae2d777b0675466878565052af34c557d71d7009162fbe813e8</v>
+        <v>e434b87a3241dae1f7d81acd86f8102e93895ec6ab30272f57fd9721c6d1bcfa</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>character_largeimage_h0168.ab</v>
+        <v>character_largeimage_h0167.ab</v>
       </c>
       <c r="B305" t="str">
-        <v>character_largeimage_h0168.ab</v>
+        <v>character_largeimage_h0167.ab</v>
       </c>
       <c r="C305">
-        <v>817925</v>
+        <v>820636</v>
       </c>
       <c r="D305" t="str">
         <v>Stage_1</v>
@@ -6499,18 +6499,18 @@
         <v>0</v>
       </c>
       <c r="F305" t="str">
-        <v>d596388ecc3145e4279aed0ec7f8b25c8a5abbfeaf17c76560902f42fd6fd46c</v>
+        <v>c5d28976c731cae2d777b0675466878565052af34c557d71d7009162fbe813e8</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>character_largeimage_h0169.ab</v>
+        <v>character_largeimage_h0168.ab</v>
       </c>
       <c r="B306" t="str">
-        <v>character_largeimage_h0169.ab</v>
+        <v>character_largeimage_h0168.ab</v>
       </c>
       <c r="C306">
-        <v>830548</v>
+        <v>817925</v>
       </c>
       <c r="D306" t="str">
         <v>Stage_1</v>
@@ -6519,18 +6519,18 @@
         <v>0</v>
       </c>
       <c r="F306" t="str">
-        <v>694f5ecefeccf73e0d79fcbde42e9a7552d32c2dc69d3894af27e1b92e9c9327</v>
+        <v>d596388ecc3145e4279aed0ec7f8b25c8a5abbfeaf17c76560902f42fd6fd46c</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>character_largeimage_h0170.ab</v>
+        <v>character_largeimage_h0169.ab</v>
       </c>
       <c r="B307" t="str">
-        <v>character_largeimage_h0170.ab</v>
+        <v>character_largeimage_h0169.ab</v>
       </c>
       <c r="C307">
-        <v>802577</v>
+        <v>830548</v>
       </c>
       <c r="D307" t="str">
         <v>Stage_1</v>
@@ -6539,18 +6539,18 @@
         <v>0</v>
       </c>
       <c r="F307" t="str">
-        <v>22ce1b1174d04d190ad9105ae99b8268e4b5b4bce7d43dbd7bac3a6930162aa5</v>
+        <v>694f5ecefeccf73e0d79fcbde42e9a7552d32c2dc69d3894af27e1b92e9c9327</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>character_largeimage_h0171.ab</v>
+        <v>character_largeimage_h0170.ab</v>
       </c>
       <c r="B308" t="str">
-        <v>character_largeimage_h0171.ab</v>
+        <v>character_largeimage_h0170.ab</v>
       </c>
       <c r="C308">
-        <v>782755</v>
+        <v>802577</v>
       </c>
       <c r="D308" t="str">
         <v>Stage_1</v>
@@ -6559,18 +6559,18 @@
         <v>0</v>
       </c>
       <c r="F308" t="str">
-        <v>fa33b1b6747266a27a42f0fe654fadc5c45d1b7ca97b1b8f2d52b3b0d3c7c647</v>
+        <v>22ce1b1174d04d190ad9105ae99b8268e4b5b4bce7d43dbd7bac3a6930162aa5</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>character_largeimage_h0172.ab</v>
+        <v>character_largeimage_h0171.ab</v>
       </c>
       <c r="B309" t="str">
-        <v>character_largeimage_h0172.ab</v>
+        <v>character_largeimage_h0171.ab</v>
       </c>
       <c r="C309">
-        <v>783966</v>
+        <v>782755</v>
       </c>
       <c r="D309" t="str">
         <v>Stage_1</v>
@@ -6579,18 +6579,18 @@
         <v>0</v>
       </c>
       <c r="F309" t="str">
-        <v>6c80e0e30faa685a6e8861942e4283309563a109980a7b43ad0f6c8f7b3fd812</v>
+        <v>fa33b1b6747266a27a42f0fe654fadc5c45d1b7ca97b1b8f2d52b3b0d3c7c647</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>character_largeimage_h0174.ab</v>
+        <v>character_largeimage_h0172.ab</v>
       </c>
       <c r="B310" t="str">
-        <v>character_largeimage_h0174.ab</v>
+        <v>character_largeimage_h0172.ab</v>
       </c>
       <c r="C310">
-        <v>818586</v>
+        <v>783966</v>
       </c>
       <c r="D310" t="str">
         <v>Stage_1</v>
@@ -6599,18 +6599,18 @@
         <v>0</v>
       </c>
       <c r="F310" t="str">
-        <v>4189f28a4927c0faa536e86f0b2978390507c7e2a3f7182854f18827713a9ae6</v>
+        <v>6c80e0e30faa685a6e8861942e4283309563a109980a7b43ad0f6c8f7b3fd812</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>character_largeimage_h0175.ab</v>
+        <v>character_largeimage_h0174.ab</v>
       </c>
       <c r="B311" t="str">
-        <v>character_largeimage_h0175.ab</v>
+        <v>character_largeimage_h0174.ab</v>
       </c>
       <c r="C311">
-        <v>804643</v>
+        <v>818586</v>
       </c>
       <c r="D311" t="str">
         <v>Stage_1</v>
@@ -6619,18 +6619,18 @@
         <v>0</v>
       </c>
       <c r="F311" t="str">
-        <v>5779e4f64a588b7ba406c3f77cbe5a7623a881612f260d82d0fdd015454ce4e5</v>
+        <v>4189f28a4927c0faa536e86f0b2978390507c7e2a3f7182854f18827713a9ae6</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>character_largeimage_h0176.ab</v>
+        <v>character_largeimage_h0175.ab</v>
       </c>
       <c r="B312" t="str">
-        <v>character_largeimage_h0176.ab</v>
+        <v>character_largeimage_h0175.ab</v>
       </c>
       <c r="C312">
-        <v>815725</v>
+        <v>804643</v>
       </c>
       <c r="D312" t="str">
         <v>Stage_1</v>
@@ -6639,18 +6639,18 @@
         <v>0</v>
       </c>
       <c r="F312" t="str">
-        <v>670e37924a1dc65b3257f7ea9ea57af53ef77c50e363aa558450edda73a3971e</v>
+        <v>5779e4f64a588b7ba406c3f77cbe5a7623a881612f260d82d0fdd015454ce4e5</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>character_largeimage_h0177.ab</v>
+        <v>character_largeimage_h0176.ab</v>
       </c>
       <c r="B313" t="str">
-        <v>character_largeimage_h0177.ab</v>
+        <v>character_largeimage_h0176.ab</v>
       </c>
       <c r="C313">
-        <v>787384</v>
+        <v>815725</v>
       </c>
       <c r="D313" t="str">
         <v>Stage_1</v>
@@ -6659,18 +6659,18 @@
         <v>0</v>
       </c>
       <c r="F313" t="str">
-        <v>72c7aa064bb39180b9f70c05d799875beb09b87e0863e05312f2b613f6296aaa</v>
+        <v>670e37924a1dc65b3257f7ea9ea57af53ef77c50e363aa558450edda73a3971e</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>character_largeimage_h0179.ab</v>
+        <v>character_largeimage_h0177.ab</v>
       </c>
       <c r="B314" t="str">
-        <v>character_largeimage_h0179.ab</v>
+        <v>character_largeimage_h0177.ab</v>
       </c>
       <c r="C314">
-        <v>3226990</v>
+        <v>787384</v>
       </c>
       <c r="D314" t="str">
         <v>Stage_1</v>
@@ -6679,18 +6679,18 @@
         <v>0</v>
       </c>
       <c r="F314" t="str">
-        <v>78cff653adce00a0271b9b386462b605c5155aa5328a916a2c1e7472ef53800b</v>
+        <v>72c7aa064bb39180b9f70c05d799875beb09b87e0863e05312f2b613f6296aaa</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>character_largeimage_h0183.ab</v>
+        <v>character_largeimage_h0179.ab</v>
       </c>
       <c r="B315" t="str">
-        <v>character_largeimage_h0183.ab</v>
+        <v>character_largeimage_h0179.ab</v>
       </c>
       <c r="C315">
-        <v>3520720</v>
+        <v>3226990</v>
       </c>
       <c r="D315" t="str">
         <v>Stage_1</v>
@@ -6699,18 +6699,18 @@
         <v>0</v>
       </c>
       <c r="F315" t="str">
-        <v>f0b995ef5d339afb76d7292b967c27ba26b3f240505eddecf275b18d014acabe</v>
+        <v>78cff653adce00a0271b9b386462b605c5155aa5328a916a2c1e7472ef53800b</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>character_largeimage_h0185.ab</v>
+        <v>character_largeimage_h0183.ab</v>
       </c>
       <c r="B316" t="str">
-        <v>character_largeimage_h0185.ab</v>
+        <v>character_largeimage_h0183.ab</v>
       </c>
       <c r="C316">
-        <v>2771089</v>
+        <v>3520720</v>
       </c>
       <c r="D316" t="str">
         <v>Stage_1</v>
@@ -6719,18 +6719,18 @@
         <v>0</v>
       </c>
       <c r="F316" t="str">
-        <v>bfa55cdf6f0750acee979cdf5cdc7840f4de769c34b7e38431644cf7a21ae6ba</v>
+        <v>f0b995ef5d339afb76d7292b967c27ba26b3f240505eddecf275b18d014acabe</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>character_largeimage_h0186.ab</v>
+        <v>character_largeimage_h0185.ab</v>
       </c>
       <c r="B317" t="str">
-        <v>character_largeimage_h0186.ab</v>
+        <v>character_largeimage_h0185.ab</v>
       </c>
       <c r="C317">
-        <v>3669448</v>
+        <v>2771089</v>
       </c>
       <c r="D317" t="str">
         <v>Stage_1</v>
@@ -6739,18 +6739,18 @@
         <v>0</v>
       </c>
       <c r="F317" t="str">
-        <v>d9f408df598bbed9f98731ebbbc24dd54c87d8faf6db4f9f6ed0bbdc627164f9</v>
+        <v>bfa55cdf6f0750acee979cdf5cdc7840f4de769c34b7e38431644cf7a21ae6ba</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>character_largeimage_h0190.ab</v>
+        <v>character_largeimage_h0186.ab</v>
       </c>
       <c r="B318" t="str">
-        <v>character_largeimage_h0190.ab</v>
+        <v>character_largeimage_h0186.ab</v>
       </c>
       <c r="C318">
-        <v>3422472</v>
+        <v>3669448</v>
       </c>
       <c r="D318" t="str">
         <v>Stage_1</v>
@@ -6759,18 +6759,18 @@
         <v>0</v>
       </c>
       <c r="F318" t="str">
-        <v>6a96ed9bc7dae9b6a94560a7a2a2c4c968aa9c666608866700784adbd28efe9e</v>
+        <v>d9f408df598bbed9f98731ebbbc24dd54c87d8faf6db4f9f6ed0bbdc627164f9</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>character_largeimage_h0191.ab</v>
+        <v>character_largeimage_h0190.ab</v>
       </c>
       <c r="B319" t="str">
-        <v>character_largeimage_h0191.ab</v>
+        <v>character_largeimage_h0190.ab</v>
       </c>
       <c r="C319">
-        <v>808827</v>
+        <v>3422472</v>
       </c>
       <c r="D319" t="str">
         <v>Stage_1</v>
@@ -6779,18 +6779,18 @@
         <v>0</v>
       </c>
       <c r="F319" t="str">
-        <v>b849caca8249392ed9cb5fbc69ad00daebd22a57c5dbe8dd0ef8e36a983745d0</v>
+        <v>6a96ed9bc7dae9b6a94560a7a2a2c4c968aa9c666608866700784adbd28efe9e</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>character_largeimage_h0192.ab</v>
+        <v>character_largeimage_h0191.ab</v>
       </c>
       <c r="B320" t="str">
-        <v>character_largeimage_h0192.ab</v>
+        <v>character_largeimage_h0191.ab</v>
       </c>
       <c r="C320">
-        <v>792810</v>
+        <v>808827</v>
       </c>
       <c r="D320" t="str">
         <v>Stage_1</v>
@@ -6799,18 +6799,18 @@
         <v>0</v>
       </c>
       <c r="F320" t="str">
-        <v>2b02b549d1958dcd7765bd6847f70978d863dd130ffa8e646f5fdc031cdc8351</v>
+        <v>b849caca8249392ed9cb5fbc69ad00daebd22a57c5dbe8dd0ef8e36a983745d0</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>character_largeimage_h0193.ab</v>
+        <v>character_largeimage_h0192.ab</v>
       </c>
       <c r="B321" t="str">
-        <v>character_largeimage_h0193.ab</v>
+        <v>character_largeimage_h0192.ab</v>
       </c>
       <c r="C321">
-        <v>725025</v>
+        <v>792810</v>
       </c>
       <c r="D321" t="str">
         <v>Stage_1</v>
@@ -6819,18 +6819,18 @@
         <v>0</v>
       </c>
       <c r="F321" t="str">
-        <v>c54d37a9842bc35f6a53430f7b78bf25398c17e364d4fd7af908f2f9e6a41a4a</v>
+        <v>2b02b549d1958dcd7765bd6847f70978d863dd130ffa8e646f5fdc031cdc8351</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>character_largeimage_h0194.ab</v>
+        <v>character_largeimage_h0193.ab</v>
       </c>
       <c r="B322" t="str">
-        <v>character_largeimage_h0194.ab</v>
+        <v>character_largeimage_h0193.ab</v>
       </c>
       <c r="C322">
-        <v>785465</v>
+        <v>725025</v>
       </c>
       <c r="D322" t="str">
         <v>Stage_1</v>
@@ -6839,18 +6839,18 @@
         <v>0</v>
       </c>
       <c r="F322" t="str">
-        <v>36cc8950d881f726e02b7e855085ff44ade33666176018a788d9faec4f87090f</v>
+        <v>c54d37a9842bc35f6a53430f7b78bf25398c17e364d4fd7af908f2f9e6a41a4a</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>character_largeimage_h0196.ab</v>
+        <v>character_largeimage_h0194.ab</v>
       </c>
       <c r="B323" t="str">
-        <v>character_largeimage_h0196.ab</v>
+        <v>character_largeimage_h0194.ab</v>
       </c>
       <c r="C323">
-        <v>815412</v>
+        <v>785465</v>
       </c>
       <c r="D323" t="str">
         <v>Stage_1</v>
@@ -6859,18 +6859,18 @@
         <v>0</v>
       </c>
       <c r="F323" t="str">
-        <v>6a6748aa0319948886214cb8c63c8cec143ea660d596ef8d6d978fdd3511b82a</v>
+        <v>36cc8950d881f726e02b7e855085ff44ade33666176018a788d9faec4f87090f</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>character_largeimage_h0197.ab</v>
+        <v>character_largeimage_h0196.ab</v>
       </c>
       <c r="B324" t="str">
-        <v>character_largeimage_h0197.ab</v>
+        <v>character_largeimage_h0196.ab</v>
       </c>
       <c r="C324">
-        <v>798179</v>
+        <v>815412</v>
       </c>
       <c r="D324" t="str">
         <v>Stage_1</v>
@@ -6879,18 +6879,18 @@
         <v>0</v>
       </c>
       <c r="F324" t="str">
-        <v>c7d74889421f50783e19f16bfee0461d528a543471b9b45ae4aa772b774876c0</v>
+        <v>6a6748aa0319948886214cb8c63c8cec143ea660d596ef8d6d978fdd3511b82a</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>character_largeimage_h0198.ab</v>
+        <v>character_largeimage_h0197.ab</v>
       </c>
       <c r="B325" t="str">
-        <v>character_largeimage_h0198.ab</v>
+        <v>character_largeimage_h0197.ab</v>
       </c>
       <c r="C325">
-        <v>781740</v>
+        <v>798179</v>
       </c>
       <c r="D325" t="str">
         <v>Stage_1</v>
@@ -6899,18 +6899,18 @@
         <v>0</v>
       </c>
       <c r="F325" t="str">
-        <v>2055d9937e4e0b0a8811536085a0478651eb0f01fc6dfec0c170ac2391a1d44b</v>
+        <v>c7d74889421f50783e19f16bfee0461d528a543471b9b45ae4aa772b774876c0</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>character_largeimage_h0199.ab</v>
+        <v>character_largeimage_h0198.ab</v>
       </c>
       <c r="B326" t="str">
-        <v>character_largeimage_h0199.ab</v>
+        <v>character_largeimage_h0198.ab</v>
       </c>
       <c r="C326">
-        <v>723932</v>
+        <v>781740</v>
       </c>
       <c r="D326" t="str">
         <v>Stage_1</v>
@@ -6919,18 +6919,18 @@
         <v>0</v>
       </c>
       <c r="F326" t="str">
-        <v>54fb809610bab1d842ba2f6c9092c659035994f46801d54970375ee2ea3c5dac</v>
+        <v>2055d9937e4e0b0a8811536085a0478651eb0f01fc6dfec0c170ac2391a1d44b</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>character_largeimage_h0200.ab</v>
+        <v>character_largeimage_h0199.ab</v>
       </c>
       <c r="B327" t="str">
-        <v>character_largeimage_h0200.ab</v>
+        <v>character_largeimage_h0199.ab</v>
       </c>
       <c r="C327">
-        <v>817588</v>
+        <v>723932</v>
       </c>
       <c r="D327" t="str">
         <v>Stage_1</v>
@@ -6939,18 +6939,18 @@
         <v>0</v>
       </c>
       <c r="F327" t="str">
-        <v>b19a3f8eb2a00ec2e2fafcdb4ae347a5e27c5d935a48a989071d64f8daa7c711</v>
+        <v>54fb809610bab1d842ba2f6c9092c659035994f46801d54970375ee2ea3c5dac</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>character_largeimage_h0201.ab</v>
+        <v>character_largeimage_h0200.ab</v>
       </c>
       <c r="B328" t="str">
-        <v>character_largeimage_h0201.ab</v>
+        <v>character_largeimage_h0200.ab</v>
       </c>
       <c r="C328">
-        <v>835275</v>
+        <v>817588</v>
       </c>
       <c r="D328" t="str">
         <v>Stage_1</v>
@@ -6959,18 +6959,18 @@
         <v>0</v>
       </c>
       <c r="F328" t="str">
-        <v>976aa2fcf5e09deb4a3ab659fb8a8e9afc3c27bbb832920dde15ea1cb2d990db</v>
+        <v>b19a3f8eb2a00ec2e2fafcdb4ae347a5e27c5d935a48a989071d64f8daa7c711</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>character_largeimage_h0203.ab</v>
+        <v>character_largeimage_h0201.ab</v>
       </c>
       <c r="B329" t="str">
-        <v>character_largeimage_h0203.ab</v>
+        <v>character_largeimage_h0201.ab</v>
       </c>
       <c r="C329">
-        <v>810774</v>
+        <v>835275</v>
       </c>
       <c r="D329" t="str">
         <v>Stage_1</v>
@@ -6979,18 +6979,18 @@
         <v>0</v>
       </c>
       <c r="F329" t="str">
-        <v>8a135d2928943c0ee8f93db24bb041ac0925554dfa5e69c1d8ed784c1517bab2</v>
+        <v>976aa2fcf5e09deb4a3ab659fb8a8e9afc3c27bbb832920dde15ea1cb2d990db</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>character_largeimage_h0208.ab</v>
+        <v>character_largeimage_h0203.ab</v>
       </c>
       <c r="B330" t="str">
-        <v>character_largeimage_h0208.ab</v>
+        <v>character_largeimage_h0203.ab</v>
       </c>
       <c r="C330">
-        <v>782587</v>
+        <v>810774</v>
       </c>
       <c r="D330" t="str">
         <v>Stage_1</v>
@@ -6999,18 +6999,18 @@
         <v>0</v>
       </c>
       <c r="F330" t="str">
-        <v>c8b75ce568e328d85fb21c02c1ab9c4309d261e1771ad612854e065b528e80b6</v>
+        <v>8a135d2928943c0ee8f93db24bb041ac0925554dfa5e69c1d8ed784c1517bab2</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>character_largeimage_h0209.ab</v>
+        <v>character_largeimage_h0208.ab</v>
       </c>
       <c r="B331" t="str">
-        <v>character_largeimage_h0209.ab</v>
+        <v>character_largeimage_h0208.ab</v>
       </c>
       <c r="C331">
-        <v>832318</v>
+        <v>782587</v>
       </c>
       <c r="D331" t="str">
         <v>Stage_1</v>
@@ -7019,18 +7019,18 @@
         <v>0</v>
       </c>
       <c r="F331" t="str">
-        <v>551c9d38c10aaa35dc668fa95d4ab634ea90021e999ec43e3b3692a33f37308c</v>
+        <v>c8b75ce568e328d85fb21c02c1ab9c4309d261e1771ad612854e065b528e80b6</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>character_largeimage_h0210.ab</v>
+        <v>character_largeimage_h0209.ab</v>
       </c>
       <c r="B332" t="str">
-        <v>character_largeimage_h0210.ab</v>
+        <v>character_largeimage_h0209.ab</v>
       </c>
       <c r="C332">
-        <v>825127</v>
+        <v>832318</v>
       </c>
       <c r="D332" t="str">
         <v>Stage_1</v>
@@ -7039,18 +7039,18 @@
         <v>0</v>
       </c>
       <c r="F332" t="str">
-        <v>8589c6aa5e2a1402cd077069b6a7c5b7963e4990bf24ef1ae425fa5b6fe77851</v>
+        <v>551c9d38c10aaa35dc668fa95d4ab634ea90021e999ec43e3b3692a33f37308c</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>character_largeimage_h0213.ab</v>
+        <v>character_largeimage_h0210.ab</v>
       </c>
       <c r="B333" t="str">
-        <v>character_largeimage_h0213.ab</v>
+        <v>character_largeimage_h0210.ab</v>
       </c>
       <c r="C333">
-        <v>765539</v>
+        <v>825127</v>
       </c>
       <c r="D333" t="str">
         <v>Stage_1</v>
@@ -7059,18 +7059,18 @@
         <v>0</v>
       </c>
       <c r="F333" t="str">
-        <v>7ceaafb884feff69f0cad1625495c0b9623b4abcdb13918dee5ec9782b9e7c6f</v>
+        <v>8589c6aa5e2a1402cd077069b6a7c5b7963e4990bf24ef1ae425fa5b6fe77851</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>character_largeimage_h0215.ab</v>
+        <v>character_largeimage_h0213.ab</v>
       </c>
       <c r="B334" t="str">
-        <v>character_largeimage_h0215.ab</v>
+        <v>character_largeimage_h0213.ab</v>
       </c>
       <c r="C334">
-        <v>759394</v>
+        <v>765539</v>
       </c>
       <c r="D334" t="str">
         <v>Stage_1</v>
@@ -7079,18 +7079,18 @@
         <v>0</v>
       </c>
       <c r="F334" t="str">
-        <v>8e6f4b217298f11e5493e50b5f41aefd8b49f8f0d3d68747e30ebde5fcb495af</v>
+        <v>7ceaafb884feff69f0cad1625495c0b9623b4abcdb13918dee5ec9782b9e7c6f</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>character_largeimage_h0216.ab</v>
+        <v>character_largeimage_h0215.ab</v>
       </c>
       <c r="B335" t="str">
-        <v>character_largeimage_h0216.ab</v>
+        <v>character_largeimage_h0215.ab</v>
       </c>
       <c r="C335">
-        <v>736440</v>
+        <v>759394</v>
       </c>
       <c r="D335" t="str">
         <v>Stage_1</v>
@@ -7099,18 +7099,18 @@
         <v>0</v>
       </c>
       <c r="F335" t="str">
-        <v>1ba74f46cf112a8fbabd9dbe94f3e47c6b8fae0f59caf2cbd33d263176d536eb</v>
+        <v>8e6f4b217298f11e5493e50b5f41aefd8b49f8f0d3d68747e30ebde5fcb495af</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>character_largeimage_h0217.ab</v>
+        <v>character_largeimage_h0216.ab</v>
       </c>
       <c r="B336" t="str">
-        <v>character_largeimage_h0217.ab</v>
+        <v>character_largeimage_h0216.ab</v>
       </c>
       <c r="C336">
-        <v>828877</v>
+        <v>736440</v>
       </c>
       <c r="D336" t="str">
         <v>Stage_1</v>
@@ -7119,18 +7119,18 @@
         <v>0</v>
       </c>
       <c r="F336" t="str">
-        <v>84f2c50e0b0f149fc2a5da0a87b10af733ba6c544daf4e3f9dd4c2c2e702fe60</v>
+        <v>1ba74f46cf112a8fbabd9dbe94f3e47c6b8fae0f59caf2cbd33d263176d536eb</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>character_largeimage_h0219.ab</v>
+        <v>character_largeimage_h0217.ab</v>
       </c>
       <c r="B337" t="str">
-        <v>character_largeimage_h0219.ab</v>
+        <v>character_largeimage_h0217.ab</v>
       </c>
       <c r="C337">
-        <v>817529</v>
+        <v>828877</v>
       </c>
       <c r="D337" t="str">
         <v>Stage_1</v>
@@ -7139,18 +7139,18 @@
         <v>0</v>
       </c>
       <c r="F337" t="str">
-        <v>87101cadb86464c4b19e924805d524f2a1700367f5a505fb1ae5f7bc289886f2</v>
+        <v>84f2c50e0b0f149fc2a5da0a87b10af733ba6c544daf4e3f9dd4c2c2e702fe60</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>character_largeimage_h0220.ab</v>
+        <v>character_largeimage_h0219.ab</v>
       </c>
       <c r="B338" t="str">
-        <v>character_largeimage_h0220.ab</v>
+        <v>character_largeimage_h0219.ab</v>
       </c>
       <c r="C338">
-        <v>689304</v>
+        <v>817529</v>
       </c>
       <c r="D338" t="str">
         <v>Stage_1</v>
@@ -7159,18 +7159,18 @@
         <v>0</v>
       </c>
       <c r="F338" t="str">
-        <v>0838c201cac6aa71480937da9424b05a4dfbe7d617bb0811c64a08f8fbc44329</v>
+        <v>87101cadb86464c4b19e924805d524f2a1700367f5a505fb1ae5f7bc289886f2</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>character_largeimage_h0221.ab</v>
+        <v>character_largeimage_h0220.ab</v>
       </c>
       <c r="B339" t="str">
-        <v>character_largeimage_h0221.ab</v>
+        <v>character_largeimage_h0220.ab</v>
       </c>
       <c r="C339">
-        <v>774852</v>
+        <v>689304</v>
       </c>
       <c r="D339" t="str">
         <v>Stage_1</v>
@@ -7179,18 +7179,18 @@
         <v>0</v>
       </c>
       <c r="F339" t="str">
-        <v>260c6ef2907458fb0b24e79b4fdc8f2daf248b54e954c202b89e87fa45a79917</v>
+        <v>0838c201cac6aa71480937da9424b05a4dfbe7d617bb0811c64a08f8fbc44329</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>character_largeimage_h0224.ab</v>
+        <v>character_largeimage_h0221.ab</v>
       </c>
       <c r="B340" t="str">
-        <v>character_largeimage_h0224.ab</v>
+        <v>character_largeimage_h0221.ab</v>
       </c>
       <c r="C340">
-        <v>734210</v>
+        <v>774852</v>
       </c>
       <c r="D340" t="str">
         <v>Stage_1</v>
@@ -7199,18 +7199,18 @@
         <v>0</v>
       </c>
       <c r="F340" t="str">
-        <v>8f88f1319c7298174ac3aa8a82b6986761610cbb74ef14c82c7e1ede1fc0b15d</v>
+        <v>260c6ef2907458fb0b24e79b4fdc8f2daf248b54e954c202b89e87fa45a79917</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>character_largeimage_h0226.ab</v>
+        <v>character_largeimage_h0224.ab</v>
       </c>
       <c r="B341" t="str">
-        <v>character_largeimage_h0226.ab</v>
+        <v>character_largeimage_h0224.ab</v>
       </c>
       <c r="C341">
-        <v>761235</v>
+        <v>734210</v>
       </c>
       <c r="D341" t="str">
         <v>Stage_1</v>
@@ -7219,18 +7219,18 @@
         <v>0</v>
       </c>
       <c r="F341" t="str">
-        <v>6bc4336199b83047446c82c6a230574f05b6e130a41d9f33770766aeac9436f2</v>
+        <v>8f88f1319c7298174ac3aa8a82b6986761610cbb74ef14c82c7e1ede1fc0b15d</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>character_largeimage_h0227.ab</v>
+        <v>character_largeimage_h0226.ab</v>
       </c>
       <c r="B342" t="str">
-        <v>character_largeimage_h0227.ab</v>
+        <v>character_largeimage_h0226.ab</v>
       </c>
       <c r="C342">
-        <v>786760</v>
+        <v>761235</v>
       </c>
       <c r="D342" t="str">
         <v>Stage_1</v>
@@ -7239,18 +7239,18 @@
         <v>0</v>
       </c>
       <c r="F342" t="str">
-        <v>0ec3a2ddea2c5f14762b1d53cf2a6c9b959342b7c2d7cb8c53f5de78389a1a9f</v>
+        <v>6bc4336199b83047446c82c6a230574f05b6e130a41d9f33770766aeac9436f2</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>character_largeimage_h0230.ab</v>
+        <v>character_largeimage_h0227.ab</v>
       </c>
       <c r="B343" t="str">
-        <v>character_largeimage_h0230.ab</v>
+        <v>character_largeimage_h0227.ab</v>
       </c>
       <c r="C343">
-        <v>795281</v>
+        <v>786760</v>
       </c>
       <c r="D343" t="str">
         <v>Stage_1</v>
@@ -7259,18 +7259,18 @@
         <v>0</v>
       </c>
       <c r="F343" t="str">
-        <v>29ca1d6c0d021948d89276ee888dd3f034a0a0efe30c90a4af695d44e14e409d</v>
+        <v>0ec3a2ddea2c5f14762b1d53cf2a6c9b959342b7c2d7cb8c53f5de78389a1a9f</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>character_largeimage_h0232.ab</v>
+        <v>character_largeimage_h0230.ab</v>
       </c>
       <c r="B344" t="str">
-        <v>character_largeimage_h0232.ab</v>
+        <v>character_largeimage_h0230.ab</v>
       </c>
       <c r="C344">
-        <v>2084078</v>
+        <v>795281</v>
       </c>
       <c r="D344" t="str">
         <v>Stage_1</v>
@@ -7279,18 +7279,18 @@
         <v>0</v>
       </c>
       <c r="F344" t="str">
-        <v>dfe3d19d68019845ae4ece6c9574a5495c0a7e2d7b2bd5731672a07a39334105</v>
+        <v>29ca1d6c0d021948d89276ee888dd3f034a0a0efe30c90a4af695d44e14e409d</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>character_largeimage_h0233.ab</v>
+        <v>character_largeimage_h0232.ab</v>
       </c>
       <c r="B345" t="str">
-        <v>character_largeimage_h0233.ab</v>
+        <v>character_largeimage_h0232.ab</v>
       </c>
       <c r="C345">
-        <v>3216689</v>
+        <v>2084078</v>
       </c>
       <c r="D345" t="str">
         <v>Stage_1</v>
@@ -7299,18 +7299,18 @@
         <v>0</v>
       </c>
       <c r="F345" t="str">
-        <v>aef3828cf7528b7b93a7e0d7408ad22b191692c1de64519b9f768867bc7b11a4</v>
+        <v>dfe3d19d68019845ae4ece6c9574a5495c0a7e2d7b2bd5731672a07a39334105</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>character_largeimage_h0234.ab</v>
+        <v>character_largeimage_h0233.ab</v>
       </c>
       <c r="B346" t="str">
-        <v>character_largeimage_h0234.ab</v>
+        <v>character_largeimage_h0233.ab</v>
       </c>
       <c r="C346">
-        <v>3069501</v>
+        <v>3216689</v>
       </c>
       <c r="D346" t="str">
         <v>Stage_1</v>
@@ -7319,18 +7319,18 @@
         <v>0</v>
       </c>
       <c r="F346" t="str">
-        <v>b2537f99faf6708c1597ef8c25e62f4355e6f32459e915e721ed323c337327f5</v>
+        <v>aef3828cf7528b7b93a7e0d7408ad22b191692c1de64519b9f768867bc7b11a4</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>character_largeimage_h0235.ab</v>
+        <v>character_largeimage_h0234.ab</v>
       </c>
       <c r="B347" t="str">
-        <v>character_largeimage_h0235.ab</v>
+        <v>character_largeimage_h0234.ab</v>
       </c>
       <c r="C347">
-        <v>2226899</v>
+        <v>3069501</v>
       </c>
       <c r="D347" t="str">
         <v>Stage_1</v>
@@ -7339,18 +7339,18 @@
         <v>0</v>
       </c>
       <c r="F347" t="str">
-        <v>465a56a4e220bd39de58cf59e525a9aa2450c8f08870c2d8368c8fd7339d7ac1</v>
+        <v>b2537f99faf6708c1597ef8c25e62f4355e6f32459e915e721ed323c337327f5</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>character_largeimage_h0236.ab</v>
+        <v>character_largeimage_h0235.ab</v>
       </c>
       <c r="B348" t="str">
-        <v>character_largeimage_h0236.ab</v>
+        <v>character_largeimage_h0235.ab</v>
       </c>
       <c r="C348">
-        <v>2098839</v>
+        <v>2226899</v>
       </c>
       <c r="D348" t="str">
         <v>Stage_1</v>
@@ -7359,18 +7359,18 @@
         <v>0</v>
       </c>
       <c r="F348" t="str">
-        <v>861fe308f08e7ddd65e35b46d651cf70e0bf5a6ece93c69910f51b1910bc60b5</v>
+        <v>465a56a4e220bd39de58cf59e525a9aa2450c8f08870c2d8368c8fd7339d7ac1</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>character_largeimage_h0237.ab</v>
+        <v>character_largeimage_h0236.ab</v>
       </c>
       <c r="B349" t="str">
-        <v>character_largeimage_h0237.ab</v>
+        <v>character_largeimage_h0236.ab</v>
       </c>
       <c r="C349">
-        <v>2342886</v>
+        <v>2098839</v>
       </c>
       <c r="D349" t="str">
         <v>Stage_1</v>
@@ -7379,18 +7379,18 @@
         <v>0</v>
       </c>
       <c r="F349" t="str">
-        <v>8e06426b9ef92077864f5f81f17f7da0e94162e7d8d2e1b0da5e5b0492ef2638</v>
+        <v>861fe308f08e7ddd65e35b46d651cf70e0bf5a6ece93c69910f51b1910bc60b5</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>character_largeimage_h0238.ab</v>
+        <v>character_largeimage_h0237.ab</v>
       </c>
       <c r="B350" t="str">
-        <v>character_largeimage_h0238.ab</v>
+        <v>character_largeimage_h0237.ab</v>
       </c>
       <c r="C350">
-        <v>848742</v>
+        <v>2342886</v>
       </c>
       <c r="D350" t="str">
         <v>Stage_1</v>
@@ -7399,18 +7399,18 @@
         <v>0</v>
       </c>
       <c r="F350" t="str">
-        <v>eebcd817999436e6de65383cf189412ca4c12f9058f159cae52fef68555ccbbe</v>
+        <v>8e06426b9ef92077864f5f81f17f7da0e94162e7d8d2e1b0da5e5b0492ef2638</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>character_largeimage_h0239.ab</v>
+        <v>character_largeimage_h0238.ab</v>
       </c>
       <c r="B351" t="str">
-        <v>character_largeimage_h0239.ab</v>
+        <v>character_largeimage_h0238.ab</v>
       </c>
       <c r="C351">
-        <v>812643</v>
+        <v>848742</v>
       </c>
       <c r="D351" t="str">
         <v>Stage_1</v>
@@ -7419,18 +7419,18 @@
         <v>0</v>
       </c>
       <c r="F351" t="str">
-        <v>a53f4a28d98d240b9ebf9ab9a21802b22ca3f01a9cbe43c7605471e8b69e8c22</v>
+        <v>eebcd817999436e6de65383cf189412ca4c12f9058f159cae52fef68555ccbbe</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>character_largeimage_h0240.ab</v>
+        <v>character_largeimage_h0239.ab</v>
       </c>
       <c r="B352" t="str">
-        <v>character_largeimage_h0240.ab</v>
+        <v>character_largeimage_h0239.ab</v>
       </c>
       <c r="C352">
-        <v>819235</v>
+        <v>812643</v>
       </c>
       <c r="D352" t="str">
         <v>Stage_1</v>
@@ -7439,18 +7439,18 @@
         <v>0</v>
       </c>
       <c r="F352" t="str">
-        <v>416f932b7f7a15646a65e059ebb8f7a18b000b78fcdbdf6f5b0f6e99feee60a4</v>
+        <v>a53f4a28d98d240b9ebf9ab9a21802b22ca3f01a9cbe43c7605471e8b69e8c22</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>character_largeimage_h0241.ab</v>
+        <v>character_largeimage_h0240.ab</v>
       </c>
       <c r="B353" t="str">
-        <v>character_largeimage_h0241.ab</v>
+        <v>character_largeimage_h0240.ab</v>
       </c>
       <c r="C353">
-        <v>824553</v>
+        <v>819235</v>
       </c>
       <c r="D353" t="str">
         <v>Stage_1</v>
@@ -7459,18 +7459,18 @@
         <v>0</v>
       </c>
       <c r="F353" t="str">
-        <v>0b513268be4ebfb7b998c19702c89e727831fcc9a6c44799632362eae33a7917</v>
+        <v>416f932b7f7a15646a65e059ebb8f7a18b000b78fcdbdf6f5b0f6e99feee60a4</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>character_largeimage_h0243.ab</v>
+        <v>character_largeimage_h0241.ab</v>
       </c>
       <c r="B354" t="str">
-        <v>character_largeimage_h0243.ab</v>
+        <v>character_largeimage_h0241.ab</v>
       </c>
       <c r="C354">
-        <v>810706</v>
+        <v>824553</v>
       </c>
       <c r="D354" t="str">
         <v>Stage_1</v>
@@ -7479,18 +7479,18 @@
         <v>0</v>
       </c>
       <c r="F354" t="str">
-        <v>cb1bfb37585c135009aab9b0583e3d251dabfdd75817f9cb75d7b54ab1d86778</v>
+        <v>0b513268be4ebfb7b998c19702c89e727831fcc9a6c44799632362eae33a7917</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>character_largeimage_h0244.ab</v>
+        <v>character_largeimage_h0243.ab</v>
       </c>
       <c r="B355" t="str">
-        <v>character_largeimage_h0244.ab</v>
+        <v>character_largeimage_h0243.ab</v>
       </c>
       <c r="C355">
-        <v>778524</v>
+        <v>810706</v>
       </c>
       <c r="D355" t="str">
         <v>Stage_1</v>
@@ -7499,18 +7499,18 @@
         <v>0</v>
       </c>
       <c r="F355" t="str">
-        <v>41a7d16ec3600f10cab4dee7f9c437082021de8e22902f3b82af1db8c5b220fb</v>
+        <v>cb1bfb37585c135009aab9b0583e3d251dabfdd75817f9cb75d7b54ab1d86778</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>character_largeimage_h0245.ab</v>
+        <v>character_largeimage_h0244.ab</v>
       </c>
       <c r="B356" t="str">
-        <v>character_largeimage_h0245.ab</v>
+        <v>character_largeimage_h0244.ab</v>
       </c>
       <c r="C356">
-        <v>795404</v>
+        <v>778524</v>
       </c>
       <c r="D356" t="str">
         <v>Stage_1</v>
@@ -7519,18 +7519,18 @@
         <v>0</v>
       </c>
       <c r="F356" t="str">
-        <v>22925c8d03dde32eb604d7ecfd799e03d9032c974272d0823790b7d6b18967ba</v>
+        <v>41a7d16ec3600f10cab4dee7f9c437082021de8e22902f3b82af1db8c5b220fb</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>character_largeimage_h0247.ab</v>
+        <v>character_largeimage_h0245.ab</v>
       </c>
       <c r="B357" t="str">
-        <v>character_largeimage_h0247.ab</v>
+        <v>character_largeimage_h0245.ab</v>
       </c>
       <c r="C357">
-        <v>837487</v>
+        <v>795404</v>
       </c>
       <c r="D357" t="str">
         <v>Stage_1</v>
@@ -7539,18 +7539,18 @@
         <v>0</v>
       </c>
       <c r="F357" t="str">
-        <v>ef401029e4a4b055b381ebbe633554d5daf4a3e23b60c62b852b185c4c663bf5</v>
+        <v>22925c8d03dde32eb604d7ecfd799e03d9032c974272d0823790b7d6b18967ba</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>character_largeimage_h0248.ab</v>
+        <v>character_largeimage_h0247.ab</v>
       </c>
       <c r="B358" t="str">
-        <v>character_largeimage_h0248.ab</v>
+        <v>character_largeimage_h0247.ab</v>
       </c>
       <c r="C358">
-        <v>836258</v>
+        <v>837487</v>
       </c>
       <c r="D358" t="str">
         <v>Stage_1</v>
@@ -7559,18 +7559,18 @@
         <v>0</v>
       </c>
       <c r="F358" t="str">
-        <v>f8dc41278c1bfbb1635e74efb4ceb293b4de54b87f0626cf7e2b6c0f4972b150</v>
+        <v>ef401029e4a4b055b381ebbe633554d5daf4a3e23b60c62b852b185c4c663bf5</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>character_largeimage_h0249.ab</v>
+        <v>character_largeimage_h0248.ab</v>
       </c>
       <c r="B359" t="str">
-        <v>character_largeimage_h0249.ab</v>
+        <v>character_largeimage_h0248.ab</v>
       </c>
       <c r="C359">
-        <v>839134</v>
+        <v>836258</v>
       </c>
       <c r="D359" t="str">
         <v>Stage_1</v>
@@ -7579,18 +7579,18 @@
         <v>0</v>
       </c>
       <c r="F359" t="str">
-        <v>9b91af750de18d7afe93e1d3cba66a0bdd3c7db49a03c5ebcf3b8c44fee32fc4</v>
+        <v>f8dc41278c1bfbb1635e74efb4ceb293b4de54b87f0626cf7e2b6c0f4972b150</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>character_largeimage_h0253.ab</v>
+        <v>character_largeimage_h0249.ab</v>
       </c>
       <c r="B360" t="str">
-        <v>character_largeimage_h0253.ab</v>
+        <v>character_largeimage_h0249.ab</v>
       </c>
       <c r="C360">
-        <v>823722</v>
+        <v>839134</v>
       </c>
       <c r="D360" t="str">
         <v>Stage_1</v>
@@ -7599,18 +7599,18 @@
         <v>0</v>
       </c>
       <c r="F360" t="str">
-        <v>9c5c84a37c920c2e4b79f9013c9c5db129735e6375cc195a90117b4cf7802999</v>
+        <v>9b91af750de18d7afe93e1d3cba66a0bdd3c7db49a03c5ebcf3b8c44fee32fc4</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>character_largeimage_h0255.ab</v>
+        <v>character_largeimage_h0253.ab</v>
       </c>
       <c r="B361" t="str">
-        <v>character_largeimage_h0255.ab</v>
+        <v>character_largeimage_h0253.ab</v>
       </c>
       <c r="C361">
-        <v>800474</v>
+        <v>823722</v>
       </c>
       <c r="D361" t="str">
         <v>Stage_1</v>
@@ -7619,18 +7619,18 @@
         <v>0</v>
       </c>
       <c r="F361" t="str">
-        <v>450ab00dbd5b8f991797ab6c83f3ee7cb54290e9971ebd6d51273ff327ed5e15</v>
+        <v>9c5c84a37c920c2e4b79f9013c9c5db129735e6375cc195a90117b4cf7802999</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>character_largeimage_h0256.ab</v>
+        <v>character_largeimage_h0255.ab</v>
       </c>
       <c r="B362" t="str">
-        <v>character_largeimage_h0256.ab</v>
+        <v>character_largeimage_h0255.ab</v>
       </c>
       <c r="C362">
-        <v>805509</v>
+        <v>800474</v>
       </c>
       <c r="D362" t="str">
         <v>Stage_1</v>
@@ -7639,18 +7639,18 @@
         <v>0</v>
       </c>
       <c r="F362" t="str">
-        <v>297c419fbd877b05bfc9add448ff76132757333cae20eccc028647aea7da7255</v>
+        <v>450ab00dbd5b8f991797ab6c83f3ee7cb54290e9971ebd6d51273ff327ed5e15</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>character_largeimage_h0257.ab</v>
+        <v>character_largeimage_h0256.ab</v>
       </c>
       <c r="B363" t="str">
-        <v>character_largeimage_h0257.ab</v>
+        <v>character_largeimage_h0256.ab</v>
       </c>
       <c r="C363">
-        <v>808381</v>
+        <v>805509</v>
       </c>
       <c r="D363" t="str">
         <v>Stage_1</v>
@@ -7659,18 +7659,18 @@
         <v>0</v>
       </c>
       <c r="F363" t="str">
-        <v>d05147b2b6be03ef2ce9c9de4dec8d3ff71bd96053222a4f476707092d75fa72</v>
+        <v>297c419fbd877b05bfc9add448ff76132757333cae20eccc028647aea7da7255</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>character_largeimage_h0259.ab</v>
+        <v>character_largeimage_h0257.ab</v>
       </c>
       <c r="B364" t="str">
-        <v>character_largeimage_h0259.ab</v>
+        <v>character_largeimage_h0257.ab</v>
       </c>
       <c r="C364">
-        <v>810068</v>
+        <v>808381</v>
       </c>
       <c r="D364" t="str">
         <v>Stage_1</v>
@@ -7679,18 +7679,18 @@
         <v>0</v>
       </c>
       <c r="F364" t="str">
-        <v>172c2c74277241aa72cedda739d55d17e54f6959a7474b0780a9ed33d03daa33</v>
+        <v>d05147b2b6be03ef2ce9c9de4dec8d3ff71bd96053222a4f476707092d75fa72</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>character_largeimage_h0261.ab</v>
+        <v>character_largeimage_h0259.ab</v>
       </c>
       <c r="B365" t="str">
-        <v>character_largeimage_h0261.ab</v>
+        <v>character_largeimage_h0259.ab</v>
       </c>
       <c r="C365">
-        <v>785275</v>
+        <v>810068</v>
       </c>
       <c r="D365" t="str">
         <v>Stage_1</v>
@@ -7699,18 +7699,18 @@
         <v>0</v>
       </c>
       <c r="F365" t="str">
-        <v>03b89947a2d5dbfe670810747d52ec50f06c25e91ffe38907f479d65efb03148</v>
+        <v>172c2c74277241aa72cedda739d55d17e54f6959a7474b0780a9ed33d03daa33</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>character_largeimage_h0262.ab</v>
+        <v>character_largeimage_h0261.ab</v>
       </c>
       <c r="B366" t="str">
-        <v>character_largeimage_h0262.ab</v>
+        <v>character_largeimage_h0261.ab</v>
       </c>
       <c r="C366">
-        <v>847775</v>
+        <v>785275</v>
       </c>
       <c r="D366" t="str">
         <v>Stage_1</v>
@@ -7719,18 +7719,18 @@
         <v>0</v>
       </c>
       <c r="F366" t="str">
-        <v>42dc7a9aeedfb2f6754bbff5a20c0649221fbd710df2fb2229837dbf798d580a</v>
+        <v>03b89947a2d5dbfe670810747d52ec50f06c25e91ffe38907f479d65efb03148</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>character_largeimage_h0264.ab</v>
+        <v>character_largeimage_h0262.ab</v>
       </c>
       <c r="B367" t="str">
-        <v>character_largeimage_h0264.ab</v>
+        <v>character_largeimage_h0262.ab</v>
       </c>
       <c r="C367">
-        <v>718190</v>
+        <v>847775</v>
       </c>
       <c r="D367" t="str">
         <v>Stage_1</v>
@@ -7739,18 +7739,18 @@
         <v>0</v>
       </c>
       <c r="F367" t="str">
-        <v>ab84d41ed01d417a5c5cd0109bca96e438f4f56f3472560b99958ac4137677ca</v>
+        <v>42dc7a9aeedfb2f6754bbff5a20c0649221fbd710df2fb2229837dbf798d580a</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>character_largeimage_h0265.ab</v>
+        <v>character_largeimage_h0264.ab</v>
       </c>
       <c r="B368" t="str">
-        <v>character_largeimage_h0265.ab</v>
+        <v>character_largeimage_h0264.ab</v>
       </c>
       <c r="C368">
-        <v>795432</v>
+        <v>718190</v>
       </c>
       <c r="D368" t="str">
         <v>Stage_1</v>
@@ -7759,18 +7759,18 @@
         <v>0</v>
       </c>
       <c r="F368" t="str">
-        <v>43942d89eafcb8381ae779ac97b86df469078014bca34c2803baa9d16040a97e</v>
+        <v>ab84d41ed01d417a5c5cd0109bca96e438f4f56f3472560b99958ac4137677ca</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>character_largeimage_h0266.ab</v>
+        <v>character_largeimage_h0265.ab</v>
       </c>
       <c r="B369" t="str">
-        <v>character_largeimage_h0266.ab</v>
+        <v>character_largeimage_h0265.ab</v>
       </c>
       <c r="C369">
-        <v>808588</v>
+        <v>795432</v>
       </c>
       <c r="D369" t="str">
         <v>Stage_1</v>
@@ -7779,18 +7779,18 @@
         <v>0</v>
       </c>
       <c r="F369" t="str">
-        <v>ed1bd287702b2f736b9ad9fb7524ec06f5777b21a9511818d78a3ad00dc9d423</v>
+        <v>43942d89eafcb8381ae779ac97b86df469078014bca34c2803baa9d16040a97e</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>character_largeimage_h0268.ab</v>
+        <v>character_largeimage_h0266.ab</v>
       </c>
       <c r="B370" t="str">
-        <v>character_largeimage_h0268.ab</v>
+        <v>character_largeimage_h0266.ab</v>
       </c>
       <c r="C370">
-        <v>778224</v>
+        <v>808588</v>
       </c>
       <c r="D370" t="str">
         <v>Stage_1</v>
@@ -7799,18 +7799,18 @@
         <v>0</v>
       </c>
       <c r="F370" t="str">
-        <v>8c545650dd20c9e32120149543dd24e79058d125aa0ccf95c1033e80b8078919</v>
+        <v>ed1bd287702b2f736b9ad9fb7524ec06f5777b21a9511818d78a3ad00dc9d423</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>character_largeimage_h0270.ab</v>
+        <v>character_largeimage_h0268.ab</v>
       </c>
       <c r="B371" t="str">
-        <v>character_largeimage_h0270.ab</v>
+        <v>character_largeimage_h0268.ab</v>
       </c>
       <c r="C371">
-        <v>789665</v>
+        <v>778224</v>
       </c>
       <c r="D371" t="str">
         <v>Stage_1</v>
@@ -7819,18 +7819,18 @@
         <v>0</v>
       </c>
       <c r="F371" t="str">
-        <v>1061859969e3ff3ae1b28bcaa8c6e3a8aa5203c6699e037ab0a1a30dd0ea1e6d</v>
+        <v>8c545650dd20c9e32120149543dd24e79058d125aa0ccf95c1033e80b8078919</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>character_largeimage_h0271.ab</v>
+        <v>character_largeimage_h0270.ab</v>
       </c>
       <c r="B372" t="str">
-        <v>character_largeimage_h0271.ab</v>
+        <v>character_largeimage_h0270.ab</v>
       </c>
       <c r="C372">
-        <v>820733</v>
+        <v>789665</v>
       </c>
       <c r="D372" t="str">
         <v>Stage_1</v>
@@ -7839,18 +7839,18 @@
         <v>0</v>
       </c>
       <c r="F372" t="str">
-        <v>04260aa0eb4d75fb007447059b3aaed6316a2c062babec302361c33db8578284</v>
+        <v>1061859969e3ff3ae1b28bcaa8c6e3a8aa5203c6699e037ab0a1a30dd0ea1e6d</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>character_largeimage_h0274.ab</v>
+        <v>character_largeimage_h0271.ab</v>
       </c>
       <c r="B373" t="str">
-        <v>character_largeimage_h0274.ab</v>
+        <v>character_largeimage_h0271.ab</v>
       </c>
       <c r="C373">
-        <v>786408</v>
+        <v>820733</v>
       </c>
       <c r="D373" t="str">
         <v>Stage_1</v>
@@ -7859,18 +7859,18 @@
         <v>0</v>
       </c>
       <c r="F373" t="str">
-        <v>380ab4b4093260b3f77f48c03c65173f484970d7e9d7a55b9067faa0eb6b662d</v>
+        <v>04260aa0eb4d75fb007447059b3aaed6316a2c062babec302361c33db8578284</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>character_largeimage_m0011.ab</v>
+        <v>character_largeimage_h0273.ab</v>
       </c>
       <c r="B374" t="str">
-        <v>character_largeimage_m0011.ab</v>
+        <v>character_largeimage_h0273.ab</v>
       </c>
       <c r="C374">
-        <v>3645563</v>
+        <v>757725</v>
       </c>
       <c r="D374" t="str">
         <v>Stage_1</v>
@@ -7879,18 +7879,18 @@
         <v>0</v>
       </c>
       <c r="F374" t="str">
-        <v>6d163c0aa3de03702199280db17c4bbe2fddeea97fa709543044a1864c59ac4e</v>
+        <v>e451b622796765d79eda9a2e06ffe4673623d79ed334b834b1f3fbfa33e59da7</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>character_largeimage_r0034.ab</v>
+        <v>character_largeimage_h0274.ab</v>
       </c>
       <c r="B375" t="str">
-        <v>character_largeimage_r0034.ab</v>
+        <v>character_largeimage_h0274.ab</v>
       </c>
       <c r="C375">
-        <v>3192016</v>
+        <v>786408</v>
       </c>
       <c r="D375" t="str">
         <v>Stage_1</v>
@@ -7899,18 +7899,18 @@
         <v>0</v>
       </c>
       <c r="F375" t="str">
-        <v>a95c21cd1ab779a63db9047ad68d79e913fce1d1229cd60959433c515fa2b15f</v>
+        <v>380ab4b4093260b3f77f48c03c65173f484970d7e9d7a55b9067faa0eb6b662d</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>character_largeimage_r0160.ab</v>
+        <v>character_largeimage_m0011.ab</v>
       </c>
       <c r="B376" t="str">
-        <v>character_largeimage_r0160.ab</v>
+        <v>character_largeimage_m0011.ab</v>
       </c>
       <c r="C376">
-        <v>4547639</v>
+        <v>3645563</v>
       </c>
       <c r="D376" t="str">
         <v>Stage_1</v>
@@ -7919,18 +7919,18 @@
         <v>0</v>
       </c>
       <c r="F376" t="str">
-        <v>964ea8e902241d88c58f2ac99db9982703da97b02c7609af5438b4a03a8a0efe</v>
+        <v>6d163c0aa3de03702199280db17c4bbe2fddeea97fa709543044a1864c59ac4e</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>character_largeimage_r0173.ab</v>
+        <v>character_largeimage_r0034.ab</v>
       </c>
       <c r="B377" t="str">
-        <v>character_largeimage_r0173.ab</v>
+        <v>character_largeimage_r0034.ab</v>
       </c>
       <c r="C377">
-        <v>783778</v>
+        <v>3192016</v>
       </c>
       <c r="D377" t="str">
         <v>Stage_1</v>
@@ -7939,18 +7939,18 @@
         <v>0</v>
       </c>
       <c r="F377" t="str">
-        <v>8195c3708ce8e882a3d95cb265160b057eb3bf5d286f64493dab9ff905fdaab6</v>
+        <v>a95c21cd1ab779a63db9047ad68d79e913fce1d1229cd60959433c515fa2b15f</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>character_largeimage_r0205.ab</v>
+        <v>character_largeimage_r0160.ab</v>
       </c>
       <c r="B378" t="str">
-        <v>character_largeimage_r0205.ab</v>
+        <v>character_largeimage_r0160.ab</v>
       </c>
       <c r="C378">
-        <v>835262</v>
+        <v>4547639</v>
       </c>
       <c r="D378" t="str">
         <v>Stage_1</v>
@@ -7959,18 +7959,18 @@
         <v>0</v>
       </c>
       <c r="F378" t="str">
-        <v>527e90522ce04f745056b9caedcb86a53d46219da877b5661b2d167770d26dcb</v>
+        <v>964ea8e902241d88c58f2ac99db9982703da97b02c7609af5438b4a03a8a0efe</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>character_largeimage_t0017.ab</v>
+        <v>character_largeimage_r0173.ab</v>
       </c>
       <c r="B379" t="str">
-        <v>character_largeimage_t0017.ab</v>
+        <v>character_largeimage_r0173.ab</v>
       </c>
       <c r="C379">
-        <v>5048467</v>
+        <v>783778</v>
       </c>
       <c r="D379" t="str">
         <v>Stage_1</v>
@@ -7979,18 +7979,18 @@
         <v>0</v>
       </c>
       <c r="F379" t="str">
-        <v>569f2fd821c168371bd7ba0fad110a99c067d9153288ec5b7dc7dba7fadbef87</v>
+        <v>8195c3708ce8e882a3d95cb265160b057eb3bf5d286f64493dab9ff905fdaab6</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>character_largeimage_t0026.ab</v>
+        <v>character_largeimage_r0205.ab</v>
       </c>
       <c r="B380" t="str">
-        <v>character_largeimage_t0026.ab</v>
+        <v>character_largeimage_r0205.ab</v>
       </c>
       <c r="C380">
-        <v>3324659</v>
+        <v>835262</v>
       </c>
       <c r="D380" t="str">
         <v>Stage_1</v>
@@ -7999,18 +7999,18 @@
         <v>0</v>
       </c>
       <c r="F380" t="str">
-        <v>3f68cff42a6b9b5f70e4727bbbc4ca79a4b5e3f36eabee4e6ac677e471042212</v>
+        <v>527e90522ce04f745056b9caedcb86a53d46219da877b5661b2d167770d26dcb</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>character_largeimage_t0027.ab</v>
+        <v>character_largeimage_t0017.ab</v>
       </c>
       <c r="B381" t="str">
-        <v>character_largeimage_t0027.ab</v>
+        <v>character_largeimage_t0017.ab</v>
       </c>
       <c r="C381">
-        <v>3241554</v>
+        <v>5048467</v>
       </c>
       <c r="D381" t="str">
         <v>Stage_1</v>
@@ -8019,18 +8019,18 @@
         <v>0</v>
       </c>
       <c r="F381" t="str">
-        <v>5c1ed78edf2589ba18b2fd63c792819e2092273556283005ee4e832864ad3852</v>
+        <v>569f2fd821c168371bd7ba0fad110a99c067d9153288ec5b7dc7dba7fadbef87</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>character_largeimage_t0032.ab</v>
+        <v>character_largeimage_t0026.ab</v>
       </c>
       <c r="B382" t="str">
-        <v>character_largeimage_t0032.ab</v>
+        <v>character_largeimage_t0026.ab</v>
       </c>
       <c r="C382">
-        <v>3632341</v>
+        <v>3324659</v>
       </c>
       <c r="D382" t="str">
         <v>Stage_1</v>
@@ -8039,18 +8039,18 @@
         <v>0</v>
       </c>
       <c r="F382" t="str">
-        <v>3f275335ed88fbd6088516a978efb3cd60af951a07bbdb0cd82a834ccaccbc07</v>
+        <v>3f68cff42a6b9b5f70e4727bbbc4ca79a4b5e3f36eabee4e6ac677e471042212</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>character_largeimage_t0033.ab</v>
+        <v>character_largeimage_t0027.ab</v>
       </c>
       <c r="B383" t="str">
-        <v>character_largeimage_t0033.ab</v>
+        <v>character_largeimage_t0027.ab</v>
       </c>
       <c r="C383">
-        <v>3771149</v>
+        <v>3241554</v>
       </c>
       <c r="D383" t="str">
         <v>Stage_1</v>
@@ -8059,18 +8059,18 @@
         <v>0</v>
       </c>
       <c r="F383" t="str">
-        <v>26a7366f49bb32607c93b69268e6fc0693e08fef6296452290871b2fb08fc2c7</v>
+        <v>5c1ed78edf2589ba18b2fd63c792819e2092273556283005ee4e832864ad3852</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>character_largeimage_t0039.ab</v>
+        <v>character_largeimage_t0032.ab</v>
       </c>
       <c r="B384" t="str">
-        <v>character_largeimage_t0039.ab</v>
+        <v>character_largeimage_t0032.ab</v>
       </c>
       <c r="C384">
-        <v>813283</v>
+        <v>3632341</v>
       </c>
       <c r="D384" t="str">
         <v>Stage_1</v>
@@ -8079,18 +8079,18 @@
         <v>0</v>
       </c>
       <c r="F384" t="str">
-        <v>5350ab84baed9d974062a833ee3cabfdea3208b429a787505b7863cd88d02e59</v>
+        <v>3f275335ed88fbd6088516a978efb3cd60af951a07bbdb0cd82a834ccaccbc07</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>character_largeimage_t0044.ab</v>
+        <v>character_largeimage_t0033.ab</v>
       </c>
       <c r="B385" t="str">
-        <v>character_largeimage_t0044.ab</v>
+        <v>character_largeimage_t0033.ab</v>
       </c>
       <c r="C385">
-        <v>791961</v>
+        <v>3771149</v>
       </c>
       <c r="D385" t="str">
         <v>Stage_1</v>
@@ -8099,18 +8099,18 @@
         <v>0</v>
       </c>
       <c r="F385" t="str">
-        <v>eb3fb4c4fbec62853ced6c63348bda093239167910e1975c24786721e5c36945</v>
+        <v>26a7366f49bb32607c93b69268e6fc0693e08fef6296452290871b2fb08fc2c7</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>character_largeimage_t0049.ab</v>
+        <v>character_largeimage_t0039.ab</v>
       </c>
       <c r="B386" t="str">
-        <v>character_largeimage_t0049.ab</v>
+        <v>character_largeimage_t0039.ab</v>
       </c>
       <c r="C386">
-        <v>2772613</v>
+        <v>813283</v>
       </c>
       <c r="D386" t="str">
         <v>Stage_1</v>
@@ -8119,18 +8119,18 @@
         <v>0</v>
       </c>
       <c r="F386" t="str">
-        <v>95bcb0bd9154f014e06084d19d720ac2bac3315b2829a51f748bab806188e50e</v>
+        <v>5350ab84baed9d974062a833ee3cabfdea3208b429a787505b7863cd88d02e59</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>character_largeimage_t0153.ab</v>
+        <v>character_largeimage_t0044.ab</v>
       </c>
       <c r="B387" t="str">
-        <v>character_largeimage_t0153.ab</v>
+        <v>character_largeimage_t0044.ab</v>
       </c>
       <c r="C387">
-        <v>2756611</v>
+        <v>791961</v>
       </c>
       <c r="D387" t="str">
         <v>Stage_1</v>
@@ -8139,18 +8139,18 @@
         <v>0</v>
       </c>
       <c r="F387" t="str">
-        <v>3c97d4a5953e712f3dfdd8ab30d02f527616fcb3d801dd8b86b3c0cf522a0eef</v>
+        <v>eb3fb4c4fbec62853ced6c63348bda093239167910e1975c24786721e5c36945</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>character_largeimage_t0155.ab</v>
+        <v>character_largeimage_t0049.ab</v>
       </c>
       <c r="B388" t="str">
-        <v>character_largeimage_t0155.ab</v>
+        <v>character_largeimage_t0049.ab</v>
       </c>
       <c r="C388">
-        <v>4381513</v>
+        <v>2772613</v>
       </c>
       <c r="D388" t="str">
         <v>Stage_1</v>
@@ -8159,18 +8159,18 @@
         <v>0</v>
       </c>
       <c r="F388" t="str">
-        <v>38ad3eaafbadfa98327d0d5542f2f0d88f7f31f659055e6d5d7f5d8ecadaaf25</v>
+        <v>95bcb0bd9154f014e06084d19d720ac2bac3315b2829a51f748bab806188e50e</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>character_largeimage_t0156.ab</v>
+        <v>character_largeimage_t0153.ab</v>
       </c>
       <c r="B389" t="str">
-        <v>character_largeimage_t0156.ab</v>
+        <v>character_largeimage_t0153.ab</v>
       </c>
       <c r="C389">
-        <v>2462163</v>
+        <v>2756611</v>
       </c>
       <c r="D389" t="str">
         <v>Stage_1</v>
@@ -8179,18 +8179,18 @@
         <v>0</v>
       </c>
       <c r="F389" t="str">
-        <v>d47db6ea8061d6508d44fdbc8629a568db3385a88c1f450c53188c37a306fbd1</v>
+        <v>3c97d4a5953e712f3dfdd8ab30d02f527616fcb3d801dd8b86b3c0cf522a0eef</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>character_largeimage_t0158.ab</v>
+        <v>character_largeimage_t0155.ab</v>
       </c>
       <c r="B390" t="str">
-        <v>character_largeimage_t0158.ab</v>
+        <v>character_largeimage_t0155.ab</v>
       </c>
       <c r="C390">
-        <v>5260995</v>
+        <v>4381513</v>
       </c>
       <c r="D390" t="str">
         <v>Stage_1</v>
@@ -8199,18 +8199,18 @@
         <v>0</v>
       </c>
       <c r="F390" t="str">
-        <v>60e32e2c51b82894f308157ead5044b1e8a536bc973703711b4f8eb6ab332f30</v>
+        <v>38ad3eaafbadfa98327d0d5542f2f0d88f7f31f659055e6d5d7f5d8ecadaaf25</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>character_largeimage_t0180.ab</v>
+        <v>character_largeimage_t0156.ab</v>
       </c>
       <c r="B391" t="str">
-        <v>character_largeimage_t0180.ab</v>
+        <v>character_largeimage_t0156.ab</v>
       </c>
       <c r="C391">
-        <v>2585586</v>
+        <v>2462163</v>
       </c>
       <c r="D391" t="str">
         <v>Stage_1</v>
@@ -8219,18 +8219,18 @@
         <v>0</v>
       </c>
       <c r="F391" t="str">
-        <v>c5811705c032100ad1a16583021dca2fb02a11ed596ad6f58b79f2775150edc1</v>
+        <v>d47db6ea8061d6508d44fdbc8629a568db3385a88c1f450c53188c37a306fbd1</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>character_largeimage_t0181.ab</v>
+        <v>character_largeimage_t0158.ab</v>
       </c>
       <c r="B392" t="str">
-        <v>character_largeimage_t0181.ab</v>
+        <v>character_largeimage_t0158.ab</v>
       </c>
       <c r="C392">
-        <v>3294655</v>
+        <v>5260995</v>
       </c>
       <c r="D392" t="str">
         <v>Stage_1</v>
@@ -8239,18 +8239,18 @@
         <v>0</v>
       </c>
       <c r="F392" t="str">
-        <v>3ce7bff8c5c6bff24697ac51035be274c30bba43c89704245ba4d5ece12532a8</v>
+        <v>60e32e2c51b82894f308157ead5044b1e8a536bc973703711b4f8eb6ab332f30</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>character_largeimage_t0182.ab</v>
+        <v>character_largeimage_t0180.ab</v>
       </c>
       <c r="B393" t="str">
-        <v>character_largeimage_t0182.ab</v>
+        <v>character_largeimage_t0180.ab</v>
       </c>
       <c r="C393">
-        <v>2283005</v>
+        <v>2585585</v>
       </c>
       <c r="D393" t="str">
         <v>Stage_1</v>
@@ -8259,18 +8259,18 @@
         <v>0</v>
       </c>
       <c r="F393" t="str">
-        <v>f08896641300c346a1e73ed169d426147c629133d6b99fc0d0b053d6f89dea33</v>
+        <v>c5811705c032100ad1a16583021dca2fb02a11ed596ad6f58b79f2775150edc1</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>character_largeimage_t0184.ab</v>
+        <v>character_largeimage_t0181.ab</v>
       </c>
       <c r="B394" t="str">
-        <v>character_largeimage_t0184.ab</v>
+        <v>character_largeimage_t0181.ab</v>
       </c>
       <c r="C394">
-        <v>2289827</v>
+        <v>3294655</v>
       </c>
       <c r="D394" t="str">
         <v>Stage_1</v>
@@ -8279,18 +8279,18 @@
         <v>0</v>
       </c>
       <c r="F394" t="str">
-        <v>aa09e9c0a10976e05321eeed5a37397f867e1377acd71dc4e3d2d5d1417daf28</v>
+        <v>3ce7bff8c5c6bff24697ac51035be274c30bba43c89704245ba4d5ece12532a8</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>character_largeimage_t0187.ab</v>
+        <v>character_largeimage_t0182.ab</v>
       </c>
       <c r="B395" t="str">
-        <v>character_largeimage_t0187.ab</v>
+        <v>character_largeimage_t0182.ab</v>
       </c>
       <c r="C395">
-        <v>2887185</v>
+        <v>2283005</v>
       </c>
       <c r="D395" t="str">
         <v>Stage_1</v>
@@ -8299,18 +8299,18 @@
         <v>0</v>
       </c>
       <c r="F395" t="str">
-        <v>84cffe40a80fe5c71df8f44503bbdce8bbffb4c01dc57012fb621fc40fd4230d</v>
+        <v>f08896641300c346a1e73ed169d426147c629133d6b99fc0d0b053d6f89dea33</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>character_largeimage_t0188.ab</v>
+        <v>character_largeimage_t0184.ab</v>
       </c>
       <c r="B396" t="str">
-        <v>character_largeimage_t0188.ab</v>
+        <v>character_largeimage_t0184.ab</v>
       </c>
       <c r="C396">
-        <v>2744938</v>
+        <v>2289827</v>
       </c>
       <c r="D396" t="str">
         <v>Stage_1</v>
@@ -8319,18 +8319,18 @@
         <v>0</v>
       </c>
       <c r="F396" t="str">
-        <v>4f854b7d0c3b92905dd2311a69ab83cea017de02730b719a6608464f27e269d4</v>
+        <v>aa09e9c0a10976e05321eeed5a37397f867e1377acd71dc4e3d2d5d1417daf28</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>character_largeimage_t0189.ab</v>
+        <v>character_largeimage_t0187.ab</v>
       </c>
       <c r="B397" t="str">
-        <v>character_largeimage_t0189.ab</v>
+        <v>character_largeimage_t0187.ab</v>
       </c>
       <c r="C397">
-        <v>4473711</v>
+        <v>2887185</v>
       </c>
       <c r="D397" t="str">
         <v>Stage_1</v>
@@ -8339,18 +8339,18 @@
         <v>0</v>
       </c>
       <c r="F397" t="str">
-        <v>8fc73aa493d889c8325fbef52adf15dac0c8ee19e212564b6ae16b08b266144f</v>
+        <v>84cffe40a80fe5c71df8f44503bbdce8bbffb4c01dc57012fb621fc40fd4230d</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>character_largeimage_t0204.ab</v>
+        <v>character_largeimage_t0188.ab</v>
       </c>
       <c r="B398" t="str">
-        <v>character_largeimage_t0204.ab</v>
+        <v>character_largeimage_t0188.ab</v>
       </c>
       <c r="C398">
-        <v>839510</v>
+        <v>2744938</v>
       </c>
       <c r="D398" t="str">
         <v>Stage_1</v>
@@ -8359,18 +8359,18 @@
         <v>0</v>
       </c>
       <c r="F398" t="str">
-        <v>3339401d70ded15a0020af038f486a0d2a6e2bf7e4ca29d2fc52483eba92f982</v>
+        <v>4f854b7d0c3b92905dd2311a69ab83cea017de02730b719a6608464f27e269d4</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>character_largeimage_t0207.ab</v>
+        <v>character_largeimage_t0189.ab</v>
       </c>
       <c r="B399" t="str">
-        <v>character_largeimage_t0207.ab</v>
+        <v>character_largeimage_t0189.ab</v>
       </c>
       <c r="C399">
-        <v>788109</v>
+        <v>4473711</v>
       </c>
       <c r="D399" t="str">
         <v>Stage_1</v>
@@ -8379,18 +8379,18 @@
         <v>0</v>
       </c>
       <c r="F399" t="str">
-        <v>884a61acb6fc59583fb23f817ab1ee2aad0b3edba982eb01c5e3d4409e1db73f</v>
+        <v>8fc73aa493d889c8325fbef52adf15dac0c8ee19e212564b6ae16b08b266144f</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>character_largeimage_t0212.ab</v>
+        <v>character_largeimage_t0204.ab</v>
       </c>
       <c r="B400" t="str">
-        <v>character_largeimage_t0212.ab</v>
+        <v>character_largeimage_t0204.ab</v>
       </c>
       <c r="C400">
-        <v>843123</v>
+        <v>839510</v>
       </c>
       <c r="D400" t="str">
         <v>Stage_1</v>
@@ -8399,18 +8399,18 @@
         <v>0</v>
       </c>
       <c r="F400" t="str">
-        <v>e442a6b286187dcc18ca56751536e1758d5953d5b913e759d2ed412148611a38</v>
+        <v>3339401d70ded15a0020af038f486a0d2a6e2bf7e4ca29d2fc52483eba92f982</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>character_largeimage_t0214.ab</v>
+        <v>character_largeimage_t0207.ab</v>
       </c>
       <c r="B401" t="str">
-        <v>character_largeimage_t0214.ab</v>
+        <v>character_largeimage_t0207.ab</v>
       </c>
       <c r="C401">
-        <v>828387</v>
+        <v>788109</v>
       </c>
       <c r="D401" t="str">
         <v>Stage_1</v>
@@ -8419,18 +8419,18 @@
         <v>0</v>
       </c>
       <c r="F401" t="str">
-        <v>342fd529c964664d600e232cd94bd8b1675ded9c1b64945ef103993a6b5b300c</v>
+        <v>884a61acb6fc59583fb23f817ab1ee2aad0b3edba982eb01c5e3d4409e1db73f</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>character_largeimage_t0218.ab</v>
+        <v>character_largeimage_t0212.ab</v>
       </c>
       <c r="B402" t="str">
-        <v>character_largeimage_t0218.ab</v>
+        <v>character_largeimage_t0212.ab</v>
       </c>
       <c r="C402">
-        <v>811612</v>
+        <v>843123</v>
       </c>
       <c r="D402" t="str">
         <v>Stage_1</v>
@@ -8439,18 +8439,18 @@
         <v>0</v>
       </c>
       <c r="F402" t="str">
-        <v>bda0c6f7dc7407f7c344f85b171a48370f75519c50e728784f647c83169bd94c</v>
+        <v>e442a6b286187dcc18ca56751536e1758d5953d5b913e759d2ed412148611a38</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>character_largeimage_t0222.ab</v>
+        <v>character_largeimage_t0214.ab</v>
       </c>
       <c r="B403" t="str">
-        <v>character_largeimage_t0222.ab</v>
+        <v>character_largeimage_t0214.ab</v>
       </c>
       <c r="C403">
-        <v>774259</v>
+        <v>828387</v>
       </c>
       <c r="D403" t="str">
         <v>Stage_1</v>
@@ -8459,18 +8459,18 @@
         <v>0</v>
       </c>
       <c r="F403" t="str">
-        <v>8ab646da7e9d3f088d7b6a87436ba651ca2f50198534bb4838143a45e096932e</v>
+        <v>342fd529c964664d600e232cd94bd8b1675ded9c1b64945ef103993a6b5b300c</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>character_largeimage_t0223.ab</v>
+        <v>character_largeimage_t0218.ab</v>
       </c>
       <c r="B404" t="str">
-        <v>character_largeimage_t0223.ab</v>
+        <v>character_largeimage_t0218.ab</v>
       </c>
       <c r="C404">
-        <v>844248</v>
+        <v>811612</v>
       </c>
       <c r="D404" t="str">
         <v>Stage_1</v>
@@ -8479,18 +8479,18 @@
         <v>0</v>
       </c>
       <c r="F404" t="str">
-        <v>18c1161759d4a71ed98ffc241b6626b1e001387f1a6c5ce54150f250abf64248</v>
+        <v>bda0c6f7dc7407f7c344f85b171a48370f75519c50e728784f647c83169bd94c</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>character_largeimage_t0225.ab</v>
+        <v>character_largeimage_t0222.ab</v>
       </c>
       <c r="B405" t="str">
-        <v>character_largeimage_t0225.ab</v>
+        <v>character_largeimage_t0222.ab</v>
       </c>
       <c r="C405">
-        <v>815023</v>
+        <v>774259</v>
       </c>
       <c r="D405" t="str">
         <v>Stage_1</v>
@@ -8499,18 +8499,18 @@
         <v>0</v>
       </c>
       <c r="F405" t="str">
-        <v>f2a096a766a2689633f4d106cf0a6a439a759aea742a118791bd76a6648f267d</v>
+        <v>8ab646da7e9d3f088d7b6a87436ba651ca2f50198534bb4838143a45e096932e</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>character_largeimage_t0228.ab</v>
+        <v>character_largeimage_t0223.ab</v>
       </c>
       <c r="B406" t="str">
-        <v>character_largeimage_t0228.ab</v>
+        <v>character_largeimage_t0223.ab</v>
       </c>
       <c r="C406">
-        <v>829894</v>
+        <v>844248</v>
       </c>
       <c r="D406" t="str">
         <v>Stage_1</v>
@@ -8519,18 +8519,18 @@
         <v>0</v>
       </c>
       <c r="F406" t="str">
-        <v>94f3e6cc4c0a6a79f10a543d83f614303bc3a05333d39f4403ef896f4dcf07f5</v>
+        <v>18c1161759d4a71ed98ffc241b6626b1e001387f1a6c5ce54150f250abf64248</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>character_largeimage_t0229.ab</v>
+        <v>character_largeimage_t0225.ab</v>
       </c>
       <c r="B407" t="str">
-        <v>character_largeimage_t0229.ab</v>
+        <v>character_largeimage_t0225.ab</v>
       </c>
       <c r="C407">
-        <v>1662213</v>
+        <v>815023</v>
       </c>
       <c r="D407" t="str">
         <v>Stage_1</v>
@@ -8539,18 +8539,18 @@
         <v>0</v>
       </c>
       <c r="F407" t="str">
-        <v>69e6216c55eeaaab8fd283f59f25c316734a73644b13941d4d1fe1e1c31f8c1f</v>
+        <v>f2a096a766a2689633f4d106cf0a6a439a759aea742a118791bd76a6648f267d</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>character_largeimage_t0231.ab</v>
+        <v>character_largeimage_t0228.ab</v>
       </c>
       <c r="B408" t="str">
-        <v>character_largeimage_t0231.ab</v>
+        <v>character_largeimage_t0228.ab</v>
       </c>
       <c r="C408">
-        <v>823425</v>
+        <v>829894</v>
       </c>
       <c r="D408" t="str">
         <v>Stage_1</v>
@@ -8559,18 +8559,18 @@
         <v>0</v>
       </c>
       <c r="F408" t="str">
-        <v>3cb4f02d9303d1a2b5fc53ad0acd0aa27db034c6c97e9bef02dacf3febc0eee6</v>
+        <v>94f3e6cc4c0a6a79f10a543d83f614303bc3a05333d39f4403ef896f4dcf07f5</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>character_largeimage_t0242.ab</v>
+        <v>character_largeimage_t0229.ab</v>
       </c>
       <c r="B409" t="str">
-        <v>character_largeimage_t0242.ab</v>
+        <v>character_largeimage_t0229.ab</v>
       </c>
       <c r="C409">
-        <v>777670</v>
+        <v>1662213</v>
       </c>
       <c r="D409" t="str">
         <v>Stage_1</v>
@@ -8579,18 +8579,18 @@
         <v>0</v>
       </c>
       <c r="F409" t="str">
-        <v>7c281124753083a4db690ee47b450f4f89e3d56fc805d995ace8e49efa5bc50f</v>
+        <v>69e6216c55eeaaab8fd283f59f25c316734a73644b13941d4d1fe1e1c31f8c1f</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>character_largeimage_t0246.ab</v>
+        <v>character_largeimage_t0231.ab</v>
       </c>
       <c r="B410" t="str">
-        <v>character_largeimage_t0246.ab</v>
+        <v>character_largeimage_t0231.ab</v>
       </c>
       <c r="C410">
-        <v>819675</v>
+        <v>823425</v>
       </c>
       <c r="D410" t="str">
         <v>Stage_1</v>
@@ -8599,18 +8599,18 @@
         <v>0</v>
       </c>
       <c r="F410" t="str">
-        <v>c9ff420c4cd5404f687592c9851a9c3c9b90d6aba4ec3215e4213794c4ec8651</v>
+        <v>3cb4f02d9303d1a2b5fc53ad0acd0aa27db034c6c97e9bef02dacf3febc0eee6</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>character_largeimage_t0250.ab</v>
+        <v>character_largeimage_t0242.ab</v>
       </c>
       <c r="B411" t="str">
-        <v>character_largeimage_t0250.ab</v>
+        <v>character_largeimage_t0242.ab</v>
       </c>
       <c r="C411">
-        <v>835064</v>
+        <v>777670</v>
       </c>
       <c r="D411" t="str">
         <v>Stage_1</v>
@@ -8619,18 +8619,18 @@
         <v>0</v>
       </c>
       <c r="F411" t="str">
-        <v>cabd53f65c1283e0ac5773bc89f0d3baf8df60f587a2629bb61ff5df5f38e998</v>
+        <v>7c281124753083a4db690ee47b450f4f89e3d56fc805d995ace8e49efa5bc50f</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>character_largeimage_t0251.ab</v>
+        <v>character_largeimage_t0246.ab</v>
       </c>
       <c r="B412" t="str">
-        <v>character_largeimage_t0251.ab</v>
+        <v>character_largeimage_t0246.ab</v>
       </c>
       <c r="C412">
-        <v>817439</v>
+        <v>819675</v>
       </c>
       <c r="D412" t="str">
         <v>Stage_1</v>
@@ -8639,18 +8639,18 @@
         <v>0</v>
       </c>
       <c r="F412" t="str">
-        <v>35de9505e776e1b88eff26e7adc6f554d89c0d74424c46ac4d6b966cac281dae</v>
+        <v>c9ff420c4cd5404f687592c9851a9c3c9b90d6aba4ec3215e4213794c4ec8651</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>character_largeimage_t0252.ab</v>
+        <v>character_largeimage_t0250.ab</v>
       </c>
       <c r="B413" t="str">
-        <v>character_largeimage_t0252.ab</v>
+        <v>character_largeimage_t0250.ab</v>
       </c>
       <c r="C413">
-        <v>3182222</v>
+        <v>835064</v>
       </c>
       <c r="D413" t="str">
         <v>Stage_1</v>
@@ -8659,18 +8659,18 @@
         <v>0</v>
       </c>
       <c r="F413" t="str">
-        <v>041e2f53d9fa84b5baeb43cbf5b681fe1c1a09fc422e5db7e8abc8f70bc26348</v>
+        <v>cabd53f65c1283e0ac5773bc89f0d3baf8df60f587a2629bb61ff5df5f38e998</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>character_largeimage_t0254.ab</v>
+        <v>character_largeimage_t0251.ab</v>
       </c>
       <c r="B414" t="str">
-        <v>character_largeimage_t0254.ab</v>
+        <v>character_largeimage_t0251.ab</v>
       </c>
       <c r="C414">
-        <v>821577</v>
+        <v>817439</v>
       </c>
       <c r="D414" t="str">
         <v>Stage_1</v>
@@ -8679,18 +8679,18 @@
         <v>0</v>
       </c>
       <c r="F414" t="str">
-        <v>0ec094e49c6f0bef8aeec78857eeaae95127b56d79ef9f59be4ec966f8258c66</v>
+        <v>35de9505e776e1b88eff26e7adc6f554d89c0d74424c46ac4d6b966cac281dae</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>character_largeimage_t0258.ab</v>
+        <v>character_largeimage_t0252.ab</v>
       </c>
       <c r="B415" t="str">
-        <v>character_largeimage_t0258.ab</v>
+        <v>character_largeimage_t0252.ab</v>
       </c>
       <c r="C415">
-        <v>799096</v>
+        <v>3182222</v>
       </c>
       <c r="D415" t="str">
         <v>Stage_1</v>
@@ -8699,18 +8699,18 @@
         <v>0</v>
       </c>
       <c r="F415" t="str">
-        <v>18672ae7cdd8fbc33c3c3fb113d9cc3cb1797d9336d487d7d2cc71564bb4a621</v>
+        <v>041e2f53d9fa84b5baeb43cbf5b681fe1c1a09fc422e5db7e8abc8f70bc26348</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>character_largeimage_t0263.ab</v>
+        <v>character_largeimage_t0254.ab</v>
       </c>
       <c r="B416" t="str">
-        <v>character_largeimage_t0263.ab</v>
+        <v>character_largeimage_t0254.ab</v>
       </c>
       <c r="C416">
-        <v>819892</v>
+        <v>821577</v>
       </c>
       <c r="D416" t="str">
         <v>Stage_1</v>
@@ -8719,18 +8719,18 @@
         <v>0</v>
       </c>
       <c r="F416" t="str">
-        <v>e8bb91ba644af38d3523e9355cc207668ab626f2304399ef855def2eeb181356</v>
+        <v>0ec094e49c6f0bef8aeec78857eeaae95127b56d79ef9f59be4ec966f8258c66</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>character_largeimage_t0269.ab</v>
+        <v>character_largeimage_t0258.ab</v>
       </c>
       <c r="B417" t="str">
-        <v>character_largeimage_t0269.ab</v>
+        <v>character_largeimage_t0258.ab</v>
       </c>
       <c r="C417">
-        <v>814551</v>
+        <v>799096</v>
       </c>
       <c r="D417" t="str">
         <v>Stage_1</v>
@@ -8739,18 +8739,18 @@
         <v>0</v>
       </c>
       <c r="F417" t="str">
-        <v>5775eef9664188e2989b7a33985a416e66fca83d2960305dab4744621708d1e0</v>
+        <v>18672ae7cdd8fbc33c3c3fb113d9cc3cb1797d9336d487d7d2cc71564bb4a621</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>character_largeimage_t0272.ab</v>
+        <v>character_largeimage_t0263.ab</v>
       </c>
       <c r="B418" t="str">
-        <v>character_largeimage_t0272.ab</v>
+        <v>character_largeimage_t0263.ab</v>
       </c>
       <c r="C418">
-        <v>760703</v>
+        <v>819892</v>
       </c>
       <c r="D418" t="str">
         <v>Stage_1</v>
@@ -8759,18 +8759,18 @@
         <v>0</v>
       </c>
       <c r="F418" t="str">
-        <v>04b23476caf6f2275bb0febbf34b0f90581a1b778c8e54f1dd604efcb8283da8</v>
+        <v>e8bb91ba644af38d3523e9355cc207668ab626f2304399ef855def2eeb181356</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>character_largeimage_t0275.ab</v>
+        <v>character_largeimage_t0269.ab</v>
       </c>
       <c r="B419" t="str">
-        <v>character_largeimage_t0275.ab</v>
+        <v>character_largeimage_t0269.ab</v>
       </c>
       <c r="C419">
-        <v>761709</v>
+        <v>814551</v>
       </c>
       <c r="D419" t="str">
         <v>Stage_1</v>
@@ -8779,18 +8779,18 @@
         <v>0</v>
       </c>
       <c r="F419" t="str">
-        <v>8350830bdc61d2345550fec850c1f0b08043d91988e717e7291fc6ff4633abfa</v>
+        <v>5775eef9664188e2989b7a33985a416e66fca83d2960305dab4744621708d1e0</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>character_largeimage_uncategorized_0.ab</v>
+        <v>character_largeimage_t0272.ab</v>
       </c>
       <c r="B420" t="str">
-        <v>character_largeimage_uncategorized_0.ab</v>
+        <v>character_largeimage_t0272.ab</v>
       </c>
       <c r="C420">
-        <v>173461</v>
+        <v>760703</v>
       </c>
       <c r="D420" t="str">
         <v>Stage_1</v>
@@ -8799,33 +8799,73 @@
         <v>0</v>
       </c>
       <c r="F420" t="str">
-        <v>9c40f907ab459375c76b4a51919f83aa971bac3c394a4d64e8e549d7879abebf</v>
+        <v>04b23476caf6f2275bb0febbf34b0f90581a1b778c8e54f1dd604efcb8283da8</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
+        <v>character_largeimage_t0275.ab</v>
+      </c>
+      <c r="B421" t="str">
+        <v>character_largeimage_t0275.ab</v>
+      </c>
+      <c r="C421">
+        <v>761709</v>
+      </c>
+      <c r="D421" t="str">
+        <v>Stage_1</v>
+      </c>
+      <c r="E421">
+        <v>0</v>
+      </c>
+      <c r="F421" t="str">
+        <v>8350830bdc61d2345550fec850c1f0b08043d91988e717e7291fc6ff4633abfa</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="str">
+        <v>character_largeimage_uncategorized_0.ab</v>
+      </c>
+      <c r="B422" t="str">
+        <v>character_largeimage_uncategorized_0.ab</v>
+      </c>
+      <c r="C422">
+        <v>173461</v>
+      </c>
+      <c r="D422" t="str">
+        <v>Stage_1</v>
+      </c>
+      <c r="E422">
+        <v>0</v>
+      </c>
+      <c r="F422" t="str">
+        <v>9c40f907ab459375c76b4a51919f83aa971bac3c394a4d64e8e549d7879abebf</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="str">
         <v>character_largeimage_uncategorized_3.ab</v>
       </c>
-      <c r="B421" t="str">
+      <c r="B423" t="str">
         <v>character_largeimage_uncategorized_3.ab</v>
       </c>
-      <c r="C421">
+      <c r="C423">
         <v>214292</v>
       </c>
-      <c r="D421" t="str">
-        <v>Stage_1</v>
-      </c>
-      <c r="E421">
-        <v>0</v>
-      </c>
-      <c r="F421" t="str">
+      <c r="D423" t="str">
+        <v>Stage_1</v>
+      </c>
+      <c r="E423">
+        <v>0</v>
+      </c>
+      <c r="F423" t="str">
         <v>baa10ce33b3b4d5a88452011578fd5a338303e27f2f7e58822f6cbbf2f359f10</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F421"/>
+  <autoFilter ref="A1:F423"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F421"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F423"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/client_gamedata/ios/iosExp.xlsx
+++ b/client_gamedata/ios/iosExp.xlsx
@@ -450,7 +450,7 @@
         <v>audioclip_sfx_10_jp.ab</v>
       </c>
       <c r="C3">
-        <v>61211</v>
+        <v>61210</v>
       </c>
       <c r="D3" t="str">
         <v>Stage_1</v>
@@ -1470,7 +1470,7 @@
         <v>audioclip_sfx_b0028_jp.ab</v>
       </c>
       <c r="C54">
-        <v>875309</v>
+        <v>875308</v>
       </c>
       <c r="D54" t="str">
         <v>Stage_1</v>
@@ -1490,7 +1490,7 @@
         <v>audioclip_sfx_b0037_jp.ab</v>
       </c>
       <c r="C55">
-        <v>2011714</v>
+        <v>2011713</v>
       </c>
       <c r="D55" t="str">
         <v>Stage_1</v>
@@ -1510,7 +1510,7 @@
         <v>audioclip_sfx_b0202_jp.ab</v>
       </c>
       <c r="C56">
-        <v>1272281</v>
+        <v>1272282</v>
       </c>
       <c r="D56" t="str">
         <v>Stage_1</v>
@@ -1630,7 +1630,7 @@
         <v>audioclip_sfx_e3497_jp.ab</v>
       </c>
       <c r="C62">
-        <v>250851</v>
+        <v>250850</v>
       </c>
       <c r="D62" t="str">
         <v>Stage_1</v>
@@ -1710,7 +1710,7 @@
         <v>audioclip_sfx_h0003_jp.ab</v>
       </c>
       <c r="C66">
-        <v>643327</v>
+        <v>643325</v>
       </c>
       <c r="D66" t="str">
         <v>Stage_1</v>
@@ -1770,7 +1770,7 @@
         <v>audioclip_sfx_h0006_jp.ab</v>
       </c>
       <c r="C69">
-        <v>1013616</v>
+        <v>1013615</v>
       </c>
       <c r="D69" t="str">
         <v>Stage_1</v>
@@ -1830,7 +1830,7 @@
         <v>audioclip_sfx_h0009_jp.ab</v>
       </c>
       <c r="C72">
-        <v>453783</v>
+        <v>453780</v>
       </c>
       <c r="D72" t="str">
         <v>Stage_1</v>
@@ -1850,7 +1850,7 @@
         <v>audioclip_sfx_h0010_jp.ab</v>
       </c>
       <c r="C73">
-        <v>1074573</v>
+        <v>1074574</v>
       </c>
       <c r="D73" t="str">
         <v>Stage_1</v>
@@ -1890,7 +1890,7 @@
         <v>audioclip_sfx_h0013_jp.ab</v>
       </c>
       <c r="C75">
-        <v>940885</v>
+        <v>940883</v>
       </c>
       <c r="D75" t="str">
         <v>Stage_1</v>
@@ -1910,7 +1910,7 @@
         <v>audioclip_sfx_h0014_jp.ab</v>
       </c>
       <c r="C76">
-        <v>446592</v>
+        <v>446593</v>
       </c>
       <c r="D76" t="str">
         <v>Stage_1</v>
@@ -2010,7 +2010,7 @@
         <v>audioclip_sfx_h0022_jp.ab</v>
       </c>
       <c r="C81">
-        <v>985554</v>
+        <v>985555</v>
       </c>
       <c r="D81" t="str">
         <v>Stage_1</v>
@@ -2030,7 +2030,7 @@
         <v>audioclip_sfx_h0023_jp.ab</v>
       </c>
       <c r="C82">
-        <v>1374152</v>
+        <v>1374151</v>
       </c>
       <c r="D82" t="str">
         <v>Stage_1</v>
@@ -2050,7 +2050,7 @@
         <v>audioclip_sfx_h0024_jp.ab</v>
       </c>
       <c r="C83">
-        <v>1572147</v>
+        <v>1572148</v>
       </c>
       <c r="D83" t="str">
         <v>Stage_1</v>
@@ -2130,7 +2130,7 @@
         <v>audioclip_sfx_h0031_jp.ab</v>
       </c>
       <c r="C87">
-        <v>1039749</v>
+        <v>1039751</v>
       </c>
       <c r="D87" t="str">
         <v>Stage_1</v>
@@ -2150,7 +2150,7 @@
         <v>audioclip_sfx_h0035_jp.ab</v>
       </c>
       <c r="C88">
-        <v>785946</v>
+        <v>785947</v>
       </c>
       <c r="D88" t="str">
         <v>Stage_1</v>
@@ -2170,7 +2170,7 @@
         <v>audioclip_sfx_h0036_jp.ab</v>
       </c>
       <c r="C89">
-        <v>743619</v>
+        <v>743620</v>
       </c>
       <c r="D89" t="str">
         <v>Stage_1</v>
@@ -2190,7 +2190,7 @@
         <v>audioclip_sfx_h0038_jp.ab</v>
       </c>
       <c r="C90">
-        <v>611356</v>
+        <v>611358</v>
       </c>
       <c r="D90" t="str">
         <v>Stage_1</v>
@@ -2290,7 +2290,7 @@
         <v>audioclip_sfx_h0044_jp.ab</v>
       </c>
       <c r="C95">
-        <v>619213</v>
+        <v>619212</v>
       </c>
       <c r="D95" t="str">
         <v>Stage_1</v>
@@ -2310,7 +2310,7 @@
         <v>audioclip_sfx_h0045_jp.ab</v>
       </c>
       <c r="C96">
-        <v>538568</v>
+        <v>538569</v>
       </c>
       <c r="D96" t="str">
         <v>Stage_1</v>
@@ -2350,7 +2350,7 @@
         <v>audioclip_sfx_h0048_jp.ab</v>
       </c>
       <c r="C98">
-        <v>1635041</v>
+        <v>1635040</v>
       </c>
       <c r="D98" t="str">
         <v>Stage_1</v>
@@ -2390,7 +2390,7 @@
         <v>audioclip_sfx_h0097_jp.ab</v>
       </c>
       <c r="C100">
-        <v>2057509</v>
+        <v>2057513</v>
       </c>
       <c r="D100" t="str">
         <v>Stage_1</v>
@@ -2430,7 +2430,7 @@
         <v>audioclip_sfx_h0133_jp.ab</v>
       </c>
       <c r="C102">
-        <v>1334023</v>
+        <v>1334022</v>
       </c>
       <c r="D102" t="str">
         <v>Stage_1</v>
@@ -2490,7 +2490,7 @@
         <v>audioclip_sfx_h0136_jp.ab</v>
       </c>
       <c r="C105">
-        <v>1316077</v>
+        <v>1316078</v>
       </c>
       <c r="D105" t="str">
         <v>Stage_1</v>
@@ -2530,7 +2530,7 @@
         <v>audioclip_sfx_h0138_jp.ab</v>
       </c>
       <c r="C107">
-        <v>1236790</v>
+        <v>1236791</v>
       </c>
       <c r="D107" t="str">
         <v>Stage_1</v>
@@ -2550,7 +2550,7 @@
         <v>audioclip_sfx_h0150_jp.ab</v>
       </c>
       <c r="C108">
-        <v>2757251</v>
+        <v>2757248</v>
       </c>
       <c r="D108" t="str">
         <v>Stage_1</v>
@@ -2570,7 +2570,7 @@
         <v>audioclip_sfx_h0151_jp.ab</v>
       </c>
       <c r="C109">
-        <v>1924706</v>
+        <v>1924708</v>
       </c>
       <c r="D109" t="str">
         <v>Stage_1</v>
@@ -2590,7 +2590,7 @@
         <v>audioclip_sfx_h0152_jp.ab</v>
       </c>
       <c r="C110">
-        <v>1987360</v>
+        <v>1987359</v>
       </c>
       <c r="D110" t="str">
         <v>Stage_1</v>
@@ -2630,7 +2630,7 @@
         <v>audioclip_sfx_h0157_jp.ab</v>
       </c>
       <c r="C112">
-        <v>1681371</v>
+        <v>1681370</v>
       </c>
       <c r="D112" t="str">
         <v>Stage_1</v>
@@ -2670,7 +2670,7 @@
         <v>audioclip_sfx_h0161_jp.ab</v>
       </c>
       <c r="C114">
-        <v>1944103</v>
+        <v>1944104</v>
       </c>
       <c r="D114" t="str">
         <v>Stage_1</v>
@@ -2690,7 +2690,7 @@
         <v>audioclip_sfx_h0163_jp.ab</v>
       </c>
       <c r="C115">
-        <v>1305069</v>
+        <v>1305067</v>
       </c>
       <c r="D115" t="str">
         <v>Stage_1</v>
@@ -2710,7 +2710,7 @@
         <v>audioclip_sfx_h0164_jp.ab</v>
       </c>
       <c r="C116">
-        <v>966707</v>
+        <v>966709</v>
       </c>
       <c r="D116" t="str">
         <v>Stage_1</v>
@@ -2750,7 +2750,7 @@
         <v>audioclip_sfx_h0166_jp.ab</v>
       </c>
       <c r="C118">
-        <v>735096</v>
+        <v>735094</v>
       </c>
       <c r="D118" t="str">
         <v>Stage_1</v>
@@ -2770,7 +2770,7 @@
         <v>audioclip_sfx_h0167_jp.ab</v>
       </c>
       <c r="C119">
-        <v>884678</v>
+        <v>884679</v>
       </c>
       <c r="D119" t="str">
         <v>Stage_1</v>
@@ -2830,7 +2830,7 @@
         <v>audioclip_sfx_h0170_jp.ab</v>
       </c>
       <c r="C122">
-        <v>1438188</v>
+        <v>1438190</v>
       </c>
       <c r="D122" t="str">
         <v>Stage_1</v>
@@ -2870,7 +2870,7 @@
         <v>audioclip_sfx_h0172_jp.ab</v>
       </c>
       <c r="C124">
-        <v>1379889</v>
+        <v>1379888</v>
       </c>
       <c r="D124" t="str">
         <v>Stage_1</v>
@@ -2950,7 +2950,7 @@
         <v>audioclip_sfx_h0177_jp.ab</v>
       </c>
       <c r="C128">
-        <v>1465823</v>
+        <v>1465821</v>
       </c>
       <c r="D128" t="str">
         <v>Stage_1</v>
@@ -2970,7 +2970,7 @@
         <v>audioclip_sfx_h0179_jp.ab</v>
       </c>
       <c r="C129">
-        <v>1837989</v>
+        <v>1837990</v>
       </c>
       <c r="D129" t="str">
         <v>Stage_1</v>
@@ -2990,7 +2990,7 @@
         <v>audioclip_sfx_h0183_jp.ab</v>
       </c>
       <c r="C130">
-        <v>2327470</v>
+        <v>2327471</v>
       </c>
       <c r="D130" t="str">
         <v>Stage_1</v>
@@ -3030,7 +3030,7 @@
         <v>audioclip_sfx_h0186_jp.ab</v>
       </c>
       <c r="C132">
-        <v>1892919</v>
+        <v>1892917</v>
       </c>
       <c r="D132" t="str">
         <v>Stage_1</v>
@@ -3050,7 +3050,7 @@
         <v>audioclip_sfx_h0190_jp.ab</v>
       </c>
       <c r="C133">
-        <v>2643058</v>
+        <v>2643059</v>
       </c>
       <c r="D133" t="str">
         <v>Stage_1</v>
@@ -3150,7 +3150,7 @@
         <v>audioclip_sfx_h0196_jp.ab</v>
       </c>
       <c r="C138">
-        <v>1046812</v>
+        <v>1046815</v>
       </c>
       <c r="D138" t="str">
         <v>Stage_1</v>
@@ -3190,7 +3190,7 @@
         <v>audioclip_sfx_h0198_jp.ab</v>
       </c>
       <c r="C140">
-        <v>1081025</v>
+        <v>1081026</v>
       </c>
       <c r="D140" t="str">
         <v>Stage_1</v>
@@ -3210,7 +3210,7 @@
         <v>audioclip_sfx_h0199_jp.ab</v>
       </c>
       <c r="C141">
-        <v>922797</v>
+        <v>922796</v>
       </c>
       <c r="D141" t="str">
         <v>Stage_1</v>
@@ -3250,7 +3250,7 @@
         <v>audioclip_sfx_h0201_jp.ab</v>
       </c>
       <c r="C143">
-        <v>810575</v>
+        <v>810576</v>
       </c>
       <c r="D143" t="str">
         <v>Stage_1</v>
@@ -3270,7 +3270,7 @@
         <v>audioclip_sfx_h0203_jp.ab</v>
       </c>
       <c r="C144">
-        <v>967999</v>
+        <v>967998</v>
       </c>
       <c r="D144" t="str">
         <v>Stage_1</v>
@@ -3290,7 +3290,7 @@
         <v>audioclip_sfx_h0208_jp.ab</v>
       </c>
       <c r="C145">
-        <v>774137</v>
+        <v>774135</v>
       </c>
       <c r="D145" t="str">
         <v>Stage_1</v>
@@ -3450,7 +3450,7 @@
         <v>audioclip_sfx_h0220_jp.ab</v>
       </c>
       <c r="C153">
-        <v>1002160</v>
+        <v>1002159</v>
       </c>
       <c r="D153" t="str">
         <v>Stage_1</v>
@@ -3470,7 +3470,7 @@
         <v>audioclip_sfx_h0221_jp.ab</v>
       </c>
       <c r="C154">
-        <v>1054459</v>
+        <v>1054460</v>
       </c>
       <c r="D154" t="str">
         <v>Stage_1</v>
@@ -3510,7 +3510,7 @@
         <v>audioclip_sfx_h0226_jp.ab</v>
       </c>
       <c r="C156">
-        <v>1134472</v>
+        <v>1134470</v>
       </c>
       <c r="D156" t="str">
         <v>Stage_1</v>
@@ -3550,7 +3550,7 @@
         <v>audioclip_sfx_h0230_jp.ab</v>
       </c>
       <c r="C158">
-        <v>1022962</v>
+        <v>1022961</v>
       </c>
       <c r="D158" t="str">
         <v>Stage_1</v>
@@ -3570,7 +3570,7 @@
         <v>audioclip_sfx_h0232_jp.ab</v>
       </c>
       <c r="C159">
-        <v>1390240</v>
+        <v>1390239</v>
       </c>
       <c r="D159" t="str">
         <v>Stage_1</v>
@@ -3630,7 +3630,7 @@
         <v>audioclip_sfx_h0235_jp.ab</v>
       </c>
       <c r="C162">
-        <v>2384176</v>
+        <v>2384177</v>
       </c>
       <c r="D162" t="str">
         <v>Stage_1</v>
@@ -3650,7 +3650,7 @@
         <v>audioclip_sfx_h0236_jp.ab</v>
       </c>
       <c r="C163">
-        <v>2245978</v>
+        <v>2245975</v>
       </c>
       <c r="D163" t="str">
         <v>Stage_1</v>
@@ -3670,7 +3670,7 @@
         <v>audioclip_sfx_h0237_jp.ab</v>
       </c>
       <c r="C164">
-        <v>2431130</v>
+        <v>2431132</v>
       </c>
       <c r="D164" t="str">
         <v>Stage_1</v>
@@ -3710,7 +3710,7 @@
         <v>audioclip_sfx_h0239_jp.ab</v>
       </c>
       <c r="C166">
-        <v>5844653</v>
+        <v>5844651</v>
       </c>
       <c r="D166" t="str">
         <v>Stage_1</v>
@@ -3730,7 +3730,7 @@
         <v>audioclip_sfx_h0240_jp.ab</v>
       </c>
       <c r="C167">
-        <v>924348</v>
+        <v>924349</v>
       </c>
       <c r="D167" t="str">
         <v>Stage_1</v>
@@ -3750,7 +3750,7 @@
         <v>audioclip_sfx_h0241_jp.ab</v>
       </c>
       <c r="C168">
-        <v>1125056</v>
+        <v>1125057</v>
       </c>
       <c r="D168" t="str">
         <v>Stage_1</v>
@@ -3790,7 +3790,7 @@
         <v>audioclip_sfx_h0244_jp.ab</v>
       </c>
       <c r="C170">
-        <v>1110558</v>
+        <v>1110559</v>
       </c>
       <c r="D170" t="str">
         <v>Stage_1</v>
@@ -3870,7 +3870,7 @@
         <v>audioclip_sfx_h0249_jp.ab</v>
       </c>
       <c r="C174">
-        <v>899107</v>
+        <v>899106</v>
       </c>
       <c r="D174" t="str">
         <v>Stage_1</v>
@@ -3950,7 +3950,7 @@
         <v>audioclip_sfx_h0257_jp.ab</v>
       </c>
       <c r="C178">
-        <v>1131208</v>
+        <v>1131207</v>
       </c>
       <c r="D178" t="str">
         <v>Stage_1</v>
@@ -4150,7 +4150,7 @@
         <v>audioclip_sfx_h0273_jp.ab</v>
       </c>
       <c r="C188">
-        <v>1372807</v>
+        <v>1372808</v>
       </c>
       <c r="D188" t="str">
         <v>Stage_1</v>
@@ -4250,7 +4250,7 @@
         <v>audioclip_sfx_r0034_jp.ab</v>
       </c>
       <c r="C193">
-        <v>1390720</v>
+        <v>1390721</v>
       </c>
       <c r="D193" t="str">
         <v>Stage_1</v>
@@ -4270,7 +4270,7 @@
         <v>audioclip_sfx_r0160_jp.ab</v>
       </c>
       <c r="C194">
-        <v>4141831</v>
+        <v>4141829</v>
       </c>
       <c r="D194" t="str">
         <v>Stage_1</v>
@@ -4290,7 +4290,7 @@
         <v>audioclip_sfx_r0173_jp.ab</v>
       </c>
       <c r="C195">
-        <v>1438363</v>
+        <v>1438364</v>
       </c>
       <c r="D195" t="str">
         <v>Stage_1</v>
@@ -4330,7 +4330,7 @@
         <v>audioclip_sfx_t0017_jp.ab</v>
       </c>
       <c r="C197">
-        <v>883188</v>
+        <v>883186</v>
       </c>
       <c r="D197" t="str">
         <v>Stage_1</v>
@@ -4350,7 +4350,7 @@
         <v>audioclip_sfx_t0026_jp.ab</v>
       </c>
       <c r="C198">
-        <v>903967</v>
+        <v>903966</v>
       </c>
       <c r="D198" t="str">
         <v>Stage_1</v>
@@ -4390,7 +4390,7 @@
         <v>audioclip_sfx_t0032_jp.ab</v>
       </c>
       <c r="C200">
-        <v>995096</v>
+        <v>995097</v>
       </c>
       <c r="D200" t="str">
         <v>Stage_1</v>
@@ -4410,7 +4410,7 @@
         <v>audioclip_sfx_t0033_jp.ab</v>
       </c>
       <c r="C201">
-        <v>1222456</v>
+        <v>1222455</v>
       </c>
       <c r="D201" t="str">
         <v>Stage_1</v>
@@ -4470,7 +4470,7 @@
         <v>audioclip_sfx_t0049_jp.ab</v>
       </c>
       <c r="C204">
-        <v>1950971</v>
+        <v>1950973</v>
       </c>
       <c r="D204" t="str">
         <v>Stage_1</v>
@@ -4590,7 +4590,7 @@
         <v>audioclip_sfx_t0181_jp.ab</v>
       </c>
       <c r="C210">
-        <v>2120059</v>
+        <v>2120060</v>
       </c>
       <c r="D210" t="str">
         <v>Stage_1</v>
@@ -4650,7 +4650,7 @@
         <v>audioclip_sfx_t0187_jp.ab</v>
       </c>
       <c r="C213">
-        <v>2460157</v>
+        <v>2460155</v>
       </c>
       <c r="D213" t="str">
         <v>Stage_1</v>
@@ -4670,7 +4670,7 @@
         <v>audioclip_sfx_t0188_jp.ab</v>
       </c>
       <c r="C214">
-        <v>1973760</v>
+        <v>1973757</v>
       </c>
       <c r="D214" t="str">
         <v>Stage_1</v>
@@ -4830,7 +4830,7 @@
         <v>audioclip_sfx_t0223_jp.ab</v>
       </c>
       <c r="C222">
-        <v>988344</v>
+        <v>988345</v>
       </c>
       <c r="D222" t="str">
         <v>Stage_1</v>
@@ -4870,7 +4870,7 @@
         <v>audioclip_sfx_t0228_jp.ab</v>
       </c>
       <c r="C224">
-        <v>1009845</v>
+        <v>1009843</v>
       </c>
       <c r="D224" t="str">
         <v>Stage_1</v>
@@ -4890,7 +4890,7 @@
         <v>audioclip_sfx_t0229_jp.ab</v>
       </c>
       <c r="C225">
-        <v>1117665</v>
+        <v>1117663</v>
       </c>
       <c r="D225" t="str">
         <v>Stage_1</v>
@@ -4930,7 +4930,7 @@
         <v>audioclip_sfx_t0242_jp.ab</v>
       </c>
       <c r="C227">
-        <v>955690</v>
+        <v>955689</v>
       </c>
       <c r="D227" t="str">
         <v>Stage_1</v>
@@ -5150,7 +5150,7 @@
         <v>audioclip_sfx_t3189_jp.ab</v>
       </c>
       <c r="C238">
-        <v>316225</v>
+        <v>316226</v>
       </c>
       <c r="D238" t="str">
         <v>Stage_1</v>
@@ -5170,7 +5170,7 @@
         <v>audioclip_sfx_t3191_jp.ab</v>
       </c>
       <c r="C239">
-        <v>164051</v>
+        <v>164050</v>
       </c>
       <c r="D239" t="str">
         <v>Stage_1</v>
@@ -5230,7 +5230,7 @@
         <v>audioclip_sfx_t3403_jp.ab</v>
       </c>
       <c r="C242">
-        <v>288968</v>
+        <v>288969</v>
       </c>
       <c r="D242" t="str">
         <v>Stage_1</v>
@@ -5250,7 +5250,7 @@
         <v>audioclip_sfx_t3407_jp.ab</v>
       </c>
       <c r="C243">
-        <v>270580</v>
+        <v>270581</v>
       </c>
       <c r="D243" t="str">
         <v>Stage_1</v>
@@ -5470,7 +5470,7 @@
         <v>character_largeimage_h0003.ab</v>
       </c>
       <c r="C254">
-        <v>3975188</v>
+        <v>3975187</v>
       </c>
       <c r="D254" t="str">
         <v>Stage_1</v>
@@ -5810,7 +5810,7 @@
         <v>character_largeimage_h0024.ab</v>
       </c>
       <c r="C271">
-        <v>3281917</v>
+        <v>3281918</v>
       </c>
       <c r="D271" t="str">
         <v>Stage_1</v>

--- a/client_gamedata/ios/iosExp.xlsx
+++ b/client_gamedata/ios/iosExp.xlsx
@@ -430,7 +430,7 @@
         <v>audioclip_sfx_0_jp.ab</v>
       </c>
       <c r="C2">
-        <v>133115</v>
+        <v>133128</v>
       </c>
       <c r="D2" t="str">
         <v>Stage_1</v>
@@ -439,7 +439,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="str">
-        <v>890e33d92d14059e0179f994483031b11decc8d8593ed95649cd021a969d4ea3</v>
+        <v>a51c1d76f9a8bb7d2f685af61bbb1f28163424f982b30579fe64e060fd825272</v>
       </c>
     </row>
     <row r="3">
@@ -450,7 +450,7 @@
         <v>audioclip_sfx_10_jp.ab</v>
       </c>
       <c r="C3">
-        <v>61210</v>
+        <v>61219</v>
       </c>
       <c r="D3" t="str">
         <v>Stage_1</v>
@@ -459,7 +459,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="str">
-        <v>a161f7e149821f6c4588d25fc0e4044182348ad6d89c237cf154a7d61212d942</v>
+        <v>2d35e11224150080efbe8bbb40b29246047a32f156604d1a32fc3dae5983a376</v>
       </c>
     </row>
     <row r="4">
@@ -470,7 +470,7 @@
         <v>audioclip_sfx_11_jp.ab</v>
       </c>
       <c r="C4">
-        <v>104193</v>
+        <v>104190</v>
       </c>
       <c r="D4" t="str">
         <v>Stage_1</v>
@@ -479,7 +479,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="str">
-        <v>f71c7d64b3557435aa19917b507f2781b741a39bc85db5a8d40ff7c8361ee4a3</v>
+        <v>dde4321f6ea2c183d01ced1d7339b31cb26ee7707324b4b5340cd8eb99c4e3fc</v>
       </c>
     </row>
     <row r="5">
@@ -490,7 +490,7 @@
         <v>audioclip_sfx_12_jp.ab</v>
       </c>
       <c r="C5">
-        <v>67445</v>
+        <v>67448</v>
       </c>
       <c r="D5" t="str">
         <v>Stage_1</v>
@@ -499,7 +499,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="str">
-        <v>eea5c13492a64148547669e3da83d9f999d0c3cce4cf1587bb182e0e14b80695</v>
+        <v>278c55001158dcc8c039a36c7ef9ac220c2f6a37cebcb092a3b23ad57fc82692</v>
       </c>
     </row>
     <row r="6">
@@ -510,7 +510,7 @@
         <v>audioclip_sfx_13_jp.ab</v>
       </c>
       <c r="C6">
-        <v>149034</v>
+        <v>149015</v>
       </c>
       <c r="D6" t="str">
         <v>Stage_1</v>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="str">
-        <v>6e09d91410c90038ae74ae887452fd44c428b0a83d08a3af87f97747a4ba6e75</v>
+        <v>fe4475e9db5e6e0afdf25bd0158e6bb5bcce49fcb5a8052a96f4af7ec85fe506</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>audioclip_sfx_14_jp.ab</v>
       </c>
       <c r="C7">
-        <v>43300</v>
+        <v>43310</v>
       </c>
       <c r="D7" t="str">
         <v>Stage_1</v>
@@ -539,7 +539,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="str">
-        <v>3e5dd5fad421e50edbefe100346cba05e4a9ac0c7c70e528ae77e0d84be8b68f</v>
+        <v>64d4f0d47adbd21777cd094631902dff09abb9b462b8f26e126b2a44e61b91bb</v>
       </c>
     </row>
     <row r="8">
@@ -550,7 +550,7 @@
         <v>audioclip_sfx_15_jp.ab</v>
       </c>
       <c r="C8">
-        <v>88537</v>
+        <v>88542</v>
       </c>
       <c r="D8" t="str">
         <v>Stage_1</v>
@@ -559,7 +559,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="str">
-        <v>c95541bb1417c22250da7380ce5b78c7e844132fbbc24f2943fe09f4ca1e3703</v>
+        <v>a4e9b2854683685e6b7642b35b01e4acaa5658e774338144f219630bb49f67db</v>
       </c>
     </row>
     <row r="9">
@@ -570,7 +570,7 @@
         <v>audioclip_sfx_16_jp.ab</v>
       </c>
       <c r="C9">
-        <v>96170</v>
+        <v>96180</v>
       </c>
       <c r="D9" t="str">
         <v>Stage_1</v>
@@ -579,7 +579,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="str">
-        <v>2ca557d2d20b132e86a5f3a69b87f184b7567f28cdf300802571c584ac2036e7</v>
+        <v>9aa6e4ccafadff8a0547d93e7cb1e23c1cc6bc2472931dbd351eb10ceb4e99e7</v>
       </c>
     </row>
     <row r="10">
@@ -590,7 +590,7 @@
         <v>audioclip_sfx_17_jp.ab</v>
       </c>
       <c r="C10">
-        <v>43759</v>
+        <v>43761</v>
       </c>
       <c r="D10" t="str">
         <v>Stage_1</v>
@@ -599,7 +599,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="str">
-        <v>fb2606e1b32043ff01dd36b98ea5d5d3f17612d6ae8ec13ce42201358399b8e8</v>
+        <v>4b8eca0ef0ddeb68e7416d70396dcb2095fc853bbb614166f5bb25f4e763e608</v>
       </c>
     </row>
     <row r="11">
@@ -610,7 +610,7 @@
         <v>audioclip_sfx_18_jp.ab</v>
       </c>
       <c r="C11">
-        <v>84546</v>
+        <v>84556</v>
       </c>
       <c r="D11" t="str">
         <v>Stage_1</v>
@@ -619,7 +619,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="str">
-        <v>f29c026e180ee7c9175037b0e4559a412bba16b5877a643e9bec130ee1f5f8d2</v>
+        <v>453f0baa48b228b004873c60c3c958346c9980bf8d4819209434bd07b1bb266c</v>
       </c>
     </row>
     <row r="12">
@@ -630,7 +630,7 @@
         <v>audioclip_sfx_19_jp.ab</v>
       </c>
       <c r="C12">
-        <v>77260</v>
+        <v>77268</v>
       </c>
       <c r="D12" t="str">
         <v>Stage_1</v>
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="str">
-        <v>0b580d57e86b11979e2a5d223db7a26834fc03d1af8156a99987d9eac155f43a</v>
+        <v>ef5cd86309ac2536a3d155a3e6ba5878b83a1c4a5a333a2ac385ce2f29022d5f</v>
       </c>
     </row>
     <row r="13">
@@ -650,7 +650,7 @@
         <v>audioclip_sfx_1_jp.ab</v>
       </c>
       <c r="C13">
-        <v>161108</v>
+        <v>161113</v>
       </c>
       <c r="D13" t="str">
         <v>Stage_1</v>
@@ -659,7 +659,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="str">
-        <v>47cf4e5d72f98319dc8eb108861051cb6d1ae586ab677b7a66faa3d89ee77898</v>
+        <v>b712ca58e71dbceff4f60c7b2ff951d54a4e258e6486ae17c781f770554005c6</v>
       </c>
     </row>
     <row r="14">
@@ -670,7 +670,7 @@
         <v>audioclip_sfx_20_jp.ab</v>
       </c>
       <c r="C14">
-        <v>147265</v>
+        <v>147284</v>
       </c>
       <c r="D14" t="str">
         <v>Stage_1</v>
@@ -679,7 +679,7 @@
         <v>0</v>
       </c>
       <c r="F14" t="str">
-        <v>8c576ff7b4357602ab4e2aa893762a835dabac7e3f34673b3c1d2cb42ed70cf7</v>
+        <v>f2dac143234ab5e1ba9af3e1022b242b16f1f87654b148050f06a23b1a22fbbc</v>
       </c>
     </row>
     <row r="15">
@@ -690,7 +690,7 @@
         <v>audioclip_sfx_21_jp.ab</v>
       </c>
       <c r="C15">
-        <v>105516</v>
+        <v>105517</v>
       </c>
       <c r="D15" t="str">
         <v>Stage_1</v>
@@ -699,7 +699,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="str">
-        <v>5e96032b51fc8f19db981aa31444adc017b7321bb9ca8c43e947f05ddd9baf32</v>
+        <v>651bda5fcb65a01a4a57c060ce18a27257c6a28e72dae119e2e40197dd7df612</v>
       </c>
     </row>
     <row r="16">
@@ -710,7 +710,7 @@
         <v>audioclip_sfx_22_jp.ab</v>
       </c>
       <c r="C16">
-        <v>77788</v>
+        <v>77801</v>
       </c>
       <c r="D16" t="str">
         <v>Stage_1</v>
@@ -719,7 +719,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="str">
-        <v>efd13aa03b15bd3cd2981db1514991753e4e171bb5c2c59f540e72f7e852ad9f</v>
+        <v>f7b3da6a650754d7ccff09430e71d261a7f148580c1b649e6e8ca4b11457724e</v>
       </c>
     </row>
     <row r="17">
@@ -730,7 +730,7 @@
         <v>audioclip_sfx_23_jp.ab</v>
       </c>
       <c r="C17">
-        <v>84652</v>
+        <v>84664</v>
       </c>
       <c r="D17" t="str">
         <v>Stage_1</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="str">
-        <v>ef02f66fd410547d9b891e3bba0858d0c2d72bb9165adb0cd065d6fef6b557c4</v>
+        <v>2a640bd9d33e87078d82c415dab378037934c050a8efede23aafe36e604df176</v>
       </c>
     </row>
     <row r="18">
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="F18" t="str">
-        <v>8b445603b39b42c937c2e3e130212a4590907e104788decf29d15ea2f03e2f0a</v>
+        <v>49f367c92f5bea2d16c71b72dbe17f7fc3235d44b844496357d314b9931a4cef</v>
       </c>
     </row>
     <row r="19">
@@ -770,7 +770,7 @@
         <v>audioclip_sfx_25_jp.ab</v>
       </c>
       <c r="C19">
-        <v>135514</v>
+        <v>135524</v>
       </c>
       <c r="D19" t="str">
         <v>Stage_1</v>
@@ -779,7 +779,7 @@
         <v>0</v>
       </c>
       <c r="F19" t="str">
-        <v>70877cba46b595b19ce6a714e26878232ad3c6d949401695f73eeff927927b0a</v>
+        <v>ea79b0efba2af82105807ea39958672fb0458b7be8e12f2d530382e51a5924ae</v>
       </c>
     </row>
     <row r="20">
@@ -790,7 +790,7 @@
         <v>audioclip_sfx_26_jp.ab</v>
       </c>
       <c r="C20">
-        <v>219129</v>
+        <v>219141</v>
       </c>
       <c r="D20" t="str">
         <v>Stage_1</v>
@@ -799,7 +799,7 @@
         <v>0</v>
       </c>
       <c r="F20" t="str">
-        <v>dd10247797195c509f2ac05cbdc9544a669f20b4cc6b318e4c9c4a335f8a3b9c</v>
+        <v>6e6e79616ed2d3257cc244d5a26b5f5afeb4a57ecbe8c13dc0ecd27b79784e15</v>
       </c>
     </row>
     <row r="21">
@@ -810,7 +810,7 @@
         <v>audioclip_sfx_27_jp.ab</v>
       </c>
       <c r="C21">
-        <v>139363</v>
+        <v>139385</v>
       </c>
       <c r="D21" t="str">
         <v>Stage_1</v>
@@ -819,7 +819,7 @@
         <v>0</v>
       </c>
       <c r="F21" t="str">
-        <v>412892d5d5491bacc2e9d44d5b35189408d46782579dcdefaee8caf20dae01ee</v>
+        <v>1c7623f68070b35bfe8b102fc8473c8537318b5ab6102871d9cba4c08ade7910</v>
       </c>
     </row>
     <row r="22">
@@ -830,7 +830,7 @@
         <v>audioclip_sfx_28_jp.ab</v>
       </c>
       <c r="C22">
-        <v>108416</v>
+        <v>108424</v>
       </c>
       <c r="D22" t="str">
         <v>Stage_1</v>
@@ -839,7 +839,7 @@
         <v>0</v>
       </c>
       <c r="F22" t="str">
-        <v>de5866f2f83d4b8604c94740b8a7eb68f8cf0a3b7cf14f64bcd8a0542e5d76a5</v>
+        <v>96e967cb363ca89e299f8b2c6a23913854c98d7a01804b9bff0ba10cac2deebb</v>
       </c>
     </row>
     <row r="23">
@@ -859,7 +859,7 @@
         <v>0</v>
       </c>
       <c r="F23" t="str">
-        <v>5e0f02a17c0995499c87630c91ac8cd5243f7600e2f8b176e68fd88da64b247d</v>
+        <v>998e0e5bc305a59a7b48b4215d4f945cad60e7b3bbb18b264f453715f9e70ff3</v>
       </c>
     </row>
     <row r="24">
@@ -870,7 +870,7 @@
         <v>audioclip_sfx_2_jp.ab</v>
       </c>
       <c r="C24">
-        <v>154649</v>
+        <v>154657</v>
       </c>
       <c r="D24" t="str">
         <v>Stage_1</v>
@@ -879,7 +879,7 @@
         <v>0</v>
       </c>
       <c r="F24" t="str">
-        <v>5bd66eb186de336d595b8d2b996896b108c04ccd94ad331ae24ac24b3276bb86</v>
+        <v>f3c8ea52129ec946aa1d69cf7df0a68732fd115714059e9513b666a5fefa1c55</v>
       </c>
     </row>
     <row r="25">
@@ -899,7 +899,7 @@
         <v>0</v>
       </c>
       <c r="F25" t="str">
-        <v>cf3701dbc43f6057f733452a41098367e782f940fabfa38b2745517456a01f2f</v>
+        <v>1896b747f3af9d86de7ac1e4512bed73d77897cfd325394a3f0c3f243f7a9593</v>
       </c>
     </row>
     <row r="26">
@@ -910,7 +910,7 @@
         <v>audioclip_sfx_31_jp.ab</v>
       </c>
       <c r="C26">
-        <v>92510</v>
+        <v>92521</v>
       </c>
       <c r="D26" t="str">
         <v>Stage_1</v>
@@ -919,7 +919,7 @@
         <v>0</v>
       </c>
       <c r="F26" t="str">
-        <v>594b96e46256e9f45f2c199999fce932398ddf45262411f5a345109beec2a9ad</v>
+        <v>0fc9a0fa0db5b4fb5f7f89dac74c506141bb6a2637901c309757be0bcb32cfc3</v>
       </c>
     </row>
     <row r="27">
@@ -939,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="F27" t="str">
-        <v>4463dc1dbced7de4ed6d6d5c42fdeb28d185f2d5068e2b247f4caa0c9422bb90</v>
+        <v>1708fe7e8b3c5c68e9bff26737dbcf86dc522220bb7aeba15b90f2ad12b1398d</v>
       </c>
     </row>
     <row r="28">
@@ -950,7 +950,7 @@
         <v>audioclip_sfx_33_jp.ab</v>
       </c>
       <c r="C28">
-        <v>64496</v>
+        <v>64499</v>
       </c>
       <c r="D28" t="str">
         <v>Stage_1</v>
@@ -959,7 +959,7 @@
         <v>0</v>
       </c>
       <c r="F28" t="str">
-        <v>a1e06131c71f952c79a7ebffc38db5710032a0e5745d4d3ee35a5d3dfd64d292</v>
+        <v>667f59bd7085f2baf9a843b00633d978c5e9b16ee0e7413312a84733a0402fd8</v>
       </c>
     </row>
     <row r="29">
@@ -970,7 +970,7 @@
         <v>audioclip_sfx_34_jp.ab</v>
       </c>
       <c r="C29">
-        <v>84996</v>
+        <v>85006</v>
       </c>
       <c r="D29" t="str">
         <v>Stage_1</v>
@@ -979,7 +979,7 @@
         <v>0</v>
       </c>
       <c r="F29" t="str">
-        <v>085909aceab020f18df83ed24a23cf055a863b25bd6176ec33b19b5d985a0757</v>
+        <v>effd393a1cb98b426a8d5d0151a8e052e0073be690d2ac687f678929f753cfbb</v>
       </c>
     </row>
     <row r="30">
@@ -990,7 +990,7 @@
         <v>audioclip_sfx_35_jp.ab</v>
       </c>
       <c r="C30">
-        <v>202321</v>
+        <v>202330</v>
       </c>
       <c r="D30" t="str">
         <v>Stage_1</v>
@@ -999,7 +999,7 @@
         <v>0</v>
       </c>
       <c r="F30" t="str">
-        <v>0e36fc4bd38f93180af2a64a60cce7876748da8711e1ff0d396536c3248e1296</v>
+        <v>4575e3a3fd6568d21c0f71182b9e857be47544827fc847aa535fc70ceb119d8a</v>
       </c>
     </row>
     <row r="31">
@@ -1010,7 +1010,7 @@
         <v>audioclip_sfx_36_jp.ab</v>
       </c>
       <c r="C31">
-        <v>104787</v>
+        <v>104789</v>
       </c>
       <c r="D31" t="str">
         <v>Stage_1</v>
@@ -1019,7 +1019,7 @@
         <v>0</v>
       </c>
       <c r="F31" t="str">
-        <v>280bd35bcf98ecde2881f0dbf7e9a13033948660b477e51732e3134a4a47b3f4</v>
+        <v>38f3b2b91ae69c3e607fea2232525cdfa14f8b028abead0ce37be2db1b3cb497</v>
       </c>
     </row>
     <row r="32">
@@ -1030,7 +1030,7 @@
         <v>audioclip_sfx_37_jp.ab</v>
       </c>
       <c r="C32">
-        <v>67922</v>
+        <v>67925</v>
       </c>
       <c r="D32" t="str">
         <v>Stage_1</v>
@@ -1039,7 +1039,7 @@
         <v>0</v>
       </c>
       <c r="F32" t="str">
-        <v>49380d4c9301ac285a45e124e9e58febea9c84ad4f1e1a52c987506447c659cc</v>
+        <v>5164f0faa31857780c88b1a0b86c1e49d5ecb89f79a9be46ad524dbc8cd6a2d3</v>
       </c>
     </row>
     <row r="33">
@@ -1050,7 +1050,7 @@
         <v>audioclip_sfx_38_jp.ab</v>
       </c>
       <c r="C33">
-        <v>68479</v>
+        <v>68476</v>
       </c>
       <c r="D33" t="str">
         <v>Stage_1</v>
@@ -1059,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="F33" t="str">
-        <v>83ad836c51bd3889843337882ed030f846bf51d1f1c76807e2e4b5571279fac3</v>
+        <v>18fb7e8e7389187bc1b4d3ec87d1bc11c16c3323cc18ad3cce7eda36f679527d</v>
       </c>
     </row>
     <row r="34">
@@ -1070,7 +1070,7 @@
         <v>audioclip_sfx_39_jp.ab</v>
       </c>
       <c r="C34">
-        <v>136123</v>
+        <v>136140</v>
       </c>
       <c r="D34" t="str">
         <v>Stage_1</v>
@@ -1079,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="F34" t="str">
-        <v>49af5040246bf34e4574ff8d596a101b293e8f1e1b4f64681b2ea78d2835a9dd</v>
+        <v>691d0c6e9c3b23cfe8a9e6ea202cfa7dd2e4f53e9e75dd2feb40232d098695b8</v>
       </c>
     </row>
     <row r="35">
@@ -1090,7 +1090,7 @@
         <v>audioclip_sfx_3_jp.ab</v>
       </c>
       <c r="C35">
-        <v>137726</v>
+        <v>137732</v>
       </c>
       <c r="D35" t="str">
         <v>Stage_1</v>
@@ -1099,7 +1099,7 @@
         <v>0</v>
       </c>
       <c r="F35" t="str">
-        <v>16c7340f6b17d45c54b6b3a55526e727c010cf872ddb519cac9f6d105374da9e</v>
+        <v>9361bfc40e72b25fe5b5cc7ddba900df5d61a6f15d60280a265e3c6c2f825929</v>
       </c>
     </row>
     <row r="36">
@@ -1110,7 +1110,7 @@
         <v>audioclip_sfx_40_jp.ab</v>
       </c>
       <c r="C36">
-        <v>63225</v>
+        <v>63230</v>
       </c>
       <c r="D36" t="str">
         <v>Stage_1</v>
@@ -1119,7 +1119,7 @@
         <v>0</v>
       </c>
       <c r="F36" t="str">
-        <v>486554aa196492e0e848a439b6a00f07514a6f7538e6e77f56d717509f2296aa</v>
+        <v>4e8d7dc25ae33384305407d964e2f2056cd1da623680f9d0dcd6e597f58f56bf</v>
       </c>
     </row>
     <row r="37">
@@ -1130,7 +1130,7 @@
         <v>audioclip_sfx_41_jp.ab</v>
       </c>
       <c r="C37">
-        <v>75014</v>
+        <v>75025</v>
       </c>
       <c r="D37" t="str">
         <v>Stage_1</v>
@@ -1139,7 +1139,7 @@
         <v>0</v>
       </c>
       <c r="F37" t="str">
-        <v>bb89de55d2eaa45cd37847bbb338534260cde23534b032d9046b0af8c27fbb7f</v>
+        <v>b23837b51060c9d65f037c4fc7b0bddc5e8b4b53a01fa4bc5b64b6447bceae6c</v>
       </c>
     </row>
     <row r="38">
@@ -1150,7 +1150,7 @@
         <v>audioclip_sfx_42_jp.ab</v>
       </c>
       <c r="C38">
-        <v>118445</v>
+        <v>118434</v>
       </c>
       <c r="D38" t="str">
         <v>Stage_1</v>
@@ -1159,7 +1159,7 @@
         <v>0</v>
       </c>
       <c r="F38" t="str">
-        <v>ba0d7c2a8f5929e624f4a10bb2c631d97d9f93cb3f4af42e1cda5c492e0be34b</v>
+        <v>31e8ed3fd2af143738fe94cbe608bae1e0fbe5174ac15e15f14c4ab559c688bb</v>
       </c>
     </row>
     <row r="39">
@@ -1170,7 +1170,7 @@
         <v>audioclip_sfx_43_jp.ab</v>
       </c>
       <c r="C39">
-        <v>23465</v>
+        <v>23471</v>
       </c>
       <c r="D39" t="str">
         <v>Stage_1</v>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="F39" t="str">
-        <v>55a55f76e1f20b64a3f2acad0e6670e8ec21b3ce986fc06dfb4390619e9d6951</v>
+        <v>b5bb56b6b13af8214c650f7b67f4819666b2ffd4ed8cb4e3049c8f1b30efa26f</v>
       </c>
     </row>
     <row r="40">
@@ -1190,7 +1190,7 @@
         <v>audioclip_sfx_44_jp.ab</v>
       </c>
       <c r="C40">
-        <v>123386</v>
+        <v>123390</v>
       </c>
       <c r="D40" t="str">
         <v>Stage_1</v>
@@ -1199,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="F40" t="str">
-        <v>cf44a93898f3aa894abad96bd9255e364684cb29eb8e7c9216c548976aef029b</v>
+        <v>fc565ccf5ce7bc4ee43b5c34152a32499c4914d480bc0baceca70462fd4b5e8f</v>
       </c>
     </row>
     <row r="41">
@@ -1210,7 +1210,7 @@
         <v>audioclip_sfx_45_jp.ab</v>
       </c>
       <c r="C41">
-        <v>75422</v>
+        <v>75423</v>
       </c>
       <c r="D41" t="str">
         <v>Stage_1</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="F41" t="str">
-        <v>78f90e80cab664c0b2f89d6622ffbebd8dcba87d5d7047dc9d1e4c0b32231a9c</v>
+        <v>881ac8ca84630d402cce00e06cdd88d6963acd819c9075c616c1c40058fec010</v>
       </c>
     </row>
     <row r="42">
@@ -1230,7 +1230,7 @@
         <v>audioclip_sfx_46_jp.ab</v>
       </c>
       <c r="C42">
-        <v>38504</v>
+        <v>38511</v>
       </c>
       <c r="D42" t="str">
         <v>Stage_1</v>
@@ -1239,7 +1239,7 @@
         <v>0</v>
       </c>
       <c r="F42" t="str">
-        <v>c5efa43dd93e4d922ca477cdc358f0e88ecbf96ddcfcd710147d4091fa1423ff</v>
+        <v>fe04e358fad8665bb5546456377cef1551b1110d46ac8c3ddb0ba6142938359b</v>
       </c>
     </row>
     <row r="43">
@@ -1250,7 +1250,7 @@
         <v>audioclip_sfx_47_jp.ab</v>
       </c>
       <c r="C43">
-        <v>29284</v>
+        <v>29301</v>
       </c>
       <c r="D43" t="str">
         <v>Stage_1</v>
@@ -1259,7 +1259,7 @@
         <v>0</v>
       </c>
       <c r="F43" t="str">
-        <v>d7106d13ca785a9a39f95810e1fd81a00caffef45a1a8c54a089bb0e0051802e</v>
+        <v>db6f480c9d4288f2910585535c3308093e59853bd0305faf145a3a69c4f0eae6</v>
       </c>
     </row>
     <row r="44">
@@ -1270,7 +1270,7 @@
         <v>audioclip_sfx_48_jp.ab</v>
       </c>
       <c r="C44">
-        <v>88456</v>
+        <v>88463</v>
       </c>
       <c r="D44" t="str">
         <v>Stage_1</v>
@@ -1279,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="F44" t="str">
-        <v>f3fa284ebab08f2e976144b0549a6ecf85cb98f97d00b7c5077da6d28cd8129e</v>
+        <v>a8f7a0818f3dc9903dfa1a72bed054fd47dee5efb8c08e2eecf2422a0c51f5ea</v>
       </c>
     </row>
     <row r="45">
@@ -1290,7 +1290,7 @@
         <v>audioclip_sfx_49_jp.ab</v>
       </c>
       <c r="C45">
-        <v>141539</v>
+        <v>141552</v>
       </c>
       <c r="D45" t="str">
         <v>Stage_1</v>
@@ -1299,7 +1299,7 @@
         <v>0</v>
       </c>
       <c r="F45" t="str">
-        <v>3572df08e735fd70db2564ce46c03bc12db08c099809ef3031e8baba0f5b1b51</v>
+        <v>0b66013fab0ddaf1c5583b2d8b25a4f6449ddabd10385a4b3f47f2234f3d9628</v>
       </c>
     </row>
     <row r="46">
@@ -1310,7 +1310,7 @@
         <v>audioclip_sfx_4_jp.ab</v>
       </c>
       <c r="C46">
-        <v>102717</v>
+        <v>102720</v>
       </c>
       <c r="D46" t="str">
         <v>Stage_1</v>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="F46" t="str">
-        <v>0f92c5523f8520f750968d74c0e7d685b7a45ba7d5505b50eedd9ba4f012f716</v>
+        <v>c177407534ddb1dc9cffc63059ac33c9f83a0ac046a7970130b184524ccaadd6</v>
       </c>
     </row>
     <row r="47">
@@ -1330,7 +1330,7 @@
         <v>audioclip_sfx_5_jp.ab</v>
       </c>
       <c r="C47">
-        <v>118774</v>
+        <v>118783</v>
       </c>
       <c r="D47" t="str">
         <v>Stage_1</v>
@@ -1339,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="F47" t="str">
-        <v>79a9300efbf748a1d33cc6dd6c68e13be4681865621a710867a22cb9c63591ec</v>
+        <v>faf7761e80f7748fad938fea25e086d02bbe50080313bbf3a2fc010b0477d72f</v>
       </c>
     </row>
     <row r="48">
@@ -1350,7 +1350,7 @@
         <v>audioclip_sfx_6_jp.ab</v>
       </c>
       <c r="C48">
-        <v>103527</v>
+        <v>103529</v>
       </c>
       <c r="D48" t="str">
         <v>Stage_1</v>
@@ -1359,7 +1359,7 @@
         <v>0</v>
       </c>
       <c r="F48" t="str">
-        <v>45a30dcef01d78985b03fe87c5514a1385da2ddae219150409533c732bdb6f6c</v>
+        <v>22917d1ea0816d45ad00f65f95822f8fe0a2d6b1955b48024a5b5b68705ab54c</v>
       </c>
     </row>
     <row r="49">
@@ -1370,7 +1370,7 @@
         <v>audioclip_sfx_7_jp.ab</v>
       </c>
       <c r="C49">
-        <v>87150</v>
+        <v>87148</v>
       </c>
       <c r="D49" t="str">
         <v>Stage_1</v>
@@ -1379,7 +1379,7 @@
         <v>0</v>
       </c>
       <c r="F49" t="str">
-        <v>a7ae1d87362c97840abf5f97a9c7330636679fc0077e1a5cc0bb10d10b8c4e93</v>
+        <v>c0b56fbc88fb1653035ad18f7c4460b6b8166a6adf2f21d351d399f7b72dbf94</v>
       </c>
     </row>
     <row r="50">
@@ -1390,7 +1390,7 @@
         <v>audioclip_sfx_8_jp.ab</v>
       </c>
       <c r="C50">
-        <v>61903</v>
+        <v>61912</v>
       </c>
       <c r="D50" t="str">
         <v>Stage_1</v>
@@ -1399,7 +1399,7 @@
         <v>0</v>
       </c>
       <c r="F50" t="str">
-        <v>5e5a794490aad5112aacf96e2a54ae89b87fa39596a30d6a911a0abebb64e083</v>
+        <v>ef9763ac56ee0ecb0443f389644fcacee59ebea167b087de2052f3dee4a75b79</v>
       </c>
     </row>
     <row r="51">
@@ -1410,7 +1410,7 @@
         <v>audioclip_sfx_9_jp.ab</v>
       </c>
       <c r="C51">
-        <v>54584</v>
+        <v>54586</v>
       </c>
       <c r="D51" t="str">
         <v>Stage_1</v>
@@ -1419,7 +1419,7 @@
         <v>0</v>
       </c>
       <c r="F51" t="str">
-        <v>d13235b36e319581aa1beb0d69a2d8751495ba546f11894b346114ca6e89cac3</v>
+        <v>c76c694990214ac1a1e24dde526f1108eedef1bfb79aec9fbb40272a39ba4ba8</v>
       </c>
     </row>
     <row r="52">
@@ -1430,7 +1430,7 @@
         <v>audioclip_sfx_b0001_jp.ab</v>
       </c>
       <c r="C52">
-        <v>63661</v>
+        <v>63665</v>
       </c>
       <c r="D52" t="str">
         <v>Stage_1</v>
@@ -1439,7 +1439,7 @@
         <v>0</v>
       </c>
       <c r="F52" t="str">
-        <v>9c257b0b019e7316c418c6c5812c79c3da690d95d981f2cb5829727f5e2a2242</v>
+        <v>fedf33e57cffd4a9e135e6b72b4fc6daffd4cf924b65d3ef2abc3e0a51e88f22</v>
       </c>
     </row>
     <row r="53">
@@ -1450,7 +1450,7 @@
         <v>audioclip_sfx_b0015_jp.ab</v>
       </c>
       <c r="C53">
-        <v>116862</v>
+        <v>116867</v>
       </c>
       <c r="D53" t="str">
         <v>Stage_1</v>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="F53" t="str">
-        <v>0d55727eff6ab320e7e465a6bee247b8894e186509f82081fc9eb03ad9815e6f</v>
+        <v>47c3cc6c7cfce9da2f99fb23d4bad50bd72d2ba9e9bbc6ae9802519c4c4558fe</v>
       </c>
     </row>
     <row r="54">
@@ -1470,7 +1470,7 @@
         <v>audioclip_sfx_b0028_jp.ab</v>
       </c>
       <c r="C54">
-        <v>875308</v>
+        <v>875319</v>
       </c>
       <c r="D54" t="str">
         <v>Stage_1</v>
@@ -1479,7 +1479,7 @@
         <v>0</v>
       </c>
       <c r="F54" t="str">
-        <v>f41e78f1dc96308d5601037d8daf2ec4d04edcebdf93d7818c00310612af47d2</v>
+        <v>0e7d006346307173a9299f91d63337a856e823aaa01cfd51386cd12618149bd3</v>
       </c>
     </row>
     <row r="55">
@@ -1490,7 +1490,7 @@
         <v>audioclip_sfx_b0037_jp.ab</v>
       </c>
       <c r="C55">
-        <v>2011713</v>
+        <v>2011724</v>
       </c>
       <c r="D55" t="str">
         <v>Stage_1</v>
@@ -1499,7 +1499,7 @@
         <v>0</v>
       </c>
       <c r="F55" t="str">
-        <v>a9d2061d1ff0d76aa12b6549a96d83d7bf0ddcd8a620f9ac8046d2bd3c4aeb86</v>
+        <v>73ea374c429416273e46725642f75e7261c34c6a61850de13af211fc0bf7b0d2</v>
       </c>
     </row>
     <row r="56">
@@ -1510,7 +1510,7 @@
         <v>audioclip_sfx_b0202_jp.ab</v>
       </c>
       <c r="C56">
-        <v>1272282</v>
+        <v>1272356</v>
       </c>
       <c r="D56" t="str">
         <v>Stage_1</v>
@@ -1519,7 +1519,7 @@
         <v>0</v>
       </c>
       <c r="F56" t="str">
-        <v>c69e2ca037763652c03dd9330708f484b0ae7c94befab8d9355e832b3db44a86</v>
+        <v>f66c1e48409a07dab946a838d5d684f944eb8b39934b82e2ee838af0884c369e</v>
       </c>
     </row>
     <row r="57">
@@ -1530,7 +1530,7 @@
         <v>audioclip_sfx_b0260_jp.ab</v>
       </c>
       <c r="C57">
-        <v>1037836</v>
+        <v>1037842</v>
       </c>
       <c r="D57" t="str">
         <v>Stage_1</v>
@@ -1539,7 +1539,7 @@
         <v>0</v>
       </c>
       <c r="F57" t="str">
-        <v>3c1402ca0bdf715ef318d2da6828d055f2b1d7757570fae50e1513cf58b8d8d6</v>
+        <v>56722ace767f9550226bd9649636b0a85d0d337d509616ac26c521438aa8e8e9</v>
       </c>
     </row>
     <row r="58">
@@ -1550,7 +1550,7 @@
         <v>audioclip_sfx_b0267_jp.ab</v>
       </c>
       <c r="C58">
-        <v>1368974</v>
+        <v>1368905</v>
       </c>
       <c r="D58" t="str">
         <v>Stage_1</v>
@@ -1559,7 +1559,7 @@
         <v>0</v>
       </c>
       <c r="F58" t="str">
-        <v>12f9592a14155fd9d1bb1d09ae707af469b1aabca9174c413e503a7823d28b42</v>
+        <v>8497efd4d0649a574f4a462671ae760f0a1af7971b6494edd20303da8956842f</v>
       </c>
     </row>
     <row r="59">
@@ -1570,7 +1570,7 @@
         <v>audioclip_sfx_e0002_jp.ab</v>
       </c>
       <c r="C59">
-        <v>662050</v>
+        <v>662104</v>
       </c>
       <c r="D59" t="str">
         <v>Stage_1</v>
@@ -1579,7 +1579,7 @@
         <v>0</v>
       </c>
       <c r="F59" t="str">
-        <v>adeabd1b5f0bf5bb34af428cd3b35f0a452177a62632266cecd60e5272192235</v>
+        <v>6f50cd2db972afc85127b3ee1d1ab84e92815b52f3743a4374b5a8d4036456ea</v>
       </c>
     </row>
     <row r="60">
@@ -1590,7 +1590,7 @@
         <v>audioclip_sfx_e0046_jp.ab</v>
       </c>
       <c r="C60">
-        <v>3100225</v>
+        <v>3100200</v>
       </c>
       <c r="D60" t="str">
         <v>Stage_1</v>
@@ -1599,7 +1599,7 @@
         <v>0</v>
       </c>
       <c r="F60" t="str">
-        <v>fcec458dcad9b29617768b0faaf871b94d31358645d085e2a1434527f12dbc1a</v>
+        <v>f9ae10f733635ecce5c6e2984e2f22be6913ffddb7824b246239fed3a485693d</v>
       </c>
     </row>
     <row r="61">
@@ -1610,7 +1610,7 @@
         <v>audioclip_sfx_e3489_jp.ab</v>
       </c>
       <c r="C61">
-        <v>356926</v>
+        <v>356943</v>
       </c>
       <c r="D61" t="str">
         <v>Stage_1</v>
@@ -1619,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="F61" t="str">
-        <v>8ff2302352e152d67e1be227662840b0356267debc4fdfb784e57989cf65ea58</v>
+        <v>13b97ecd1bc518daf27707a8c8be8e31cb90248ea9ca1061c158383d808bf6d7</v>
       </c>
     </row>
     <row r="62">
@@ -1630,7 +1630,7 @@
         <v>audioclip_sfx_e3497_jp.ab</v>
       </c>
       <c r="C62">
-        <v>250850</v>
+        <v>250851</v>
       </c>
       <c r="D62" t="str">
         <v>Stage_1</v>
@@ -1639,7 +1639,7 @@
         <v>0</v>
       </c>
       <c r="F62" t="str">
-        <v>7f9a3784be67ddd3d0970fd9cc635703e80e50f6b6a2296ff5b324d2b08aa43d</v>
+        <v>e7f32fa6b037855f334e4bccdf04cb8b15b6629fdf86c6e36d0fd5c40cc6f155</v>
       </c>
     </row>
     <row r="63">
@@ -1650,7 +1650,7 @@
         <v>audioclip_sfx_e3498_jp.ab</v>
       </c>
       <c r="C63">
-        <v>362038</v>
+        <v>362050</v>
       </c>
       <c r="D63" t="str">
         <v>Stage_1</v>
@@ -1659,7 +1659,7 @@
         <v>0</v>
       </c>
       <c r="F63" t="str">
-        <v>8a55a93a8a49010f7f74991d104b76f51687c7d0b5b553213aad268a3491ed5a</v>
+        <v>24843375f3916f975185b49728d321c2fd2221754163eb7cf66d743e294545ec</v>
       </c>
     </row>
     <row r="64">
@@ -1670,7 +1670,7 @@
         <v>audioclip_sfx_e3499_jp.ab</v>
       </c>
       <c r="C64">
-        <v>119661</v>
+        <v>119671</v>
       </c>
       <c r="D64" t="str">
         <v>Stage_1</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="F64" t="str">
-        <v>ee82ccb938b94753a3df70ae2b6638de853c6267f339c80beb144556ad390f08</v>
+        <v>a7c0e24b9c19ed2cda781518d4aa207e3619d9ee4d72417ff43b2ea5054779ee</v>
       </c>
     </row>
     <row r="65">
@@ -1690,7 +1690,7 @@
         <v>audioclip_sfx_e3500_jp.ab</v>
       </c>
       <c r="C65">
-        <v>67579</v>
+        <v>67585</v>
       </c>
       <c r="D65" t="str">
         <v>Stage_1</v>
@@ -1699,7 +1699,7 @@
         <v>0</v>
       </c>
       <c r="F65" t="str">
-        <v>15a3c99a6f4ed868313bd40bf55b9443d3e88339aed6759efa79bae8cab14e01</v>
+        <v>5eb5ff1b48de74baec827819026a23cbe24cec18d02bca1270b5a6eba19f3a4a</v>
       </c>
     </row>
     <row r="66">
@@ -1710,7 +1710,7 @@
         <v>audioclip_sfx_h0003_jp.ab</v>
       </c>
       <c r="C66">
-        <v>643325</v>
+        <v>643321</v>
       </c>
       <c r="D66" t="str">
         <v>Stage_1</v>
@@ -1719,7 +1719,7 @@
         <v>0</v>
       </c>
       <c r="F66" t="str">
-        <v>38cda980665bcc2ee02221f6531dc5c8616bd6dd5292bb823bb91b76379a6756</v>
+        <v>59f82309f613acb6ebc64b8185cb47017a6d137d8fbda5bee9e0d9b950fd9309</v>
       </c>
     </row>
     <row r="67">
@@ -1730,7 +1730,7 @@
         <v>audioclip_sfx_h0004_jp.ab</v>
       </c>
       <c r="C67">
-        <v>1029442</v>
+        <v>1029427</v>
       </c>
       <c r="D67" t="str">
         <v>Stage_1</v>
@@ -1739,7 +1739,7 @@
         <v>0</v>
       </c>
       <c r="F67" t="str">
-        <v>4cdd681196c9041aec808a4eb4510564c5ea7c87471ab68fa5c616bc36ae30e7</v>
+        <v>d2a60c9c5fbee260692e96870eabc105d543a34e1df264d781f6adff4737a5be</v>
       </c>
     </row>
     <row r="68">
@@ -1750,7 +1750,7 @@
         <v>audioclip_sfx_h0005_jp.ab</v>
       </c>
       <c r="C68">
-        <v>872452</v>
+        <v>872461</v>
       </c>
       <c r="D68" t="str">
         <v>Stage_1</v>
@@ -1759,7 +1759,7 @@
         <v>0</v>
       </c>
       <c r="F68" t="str">
-        <v>c248966768838040fbec69b4a486eacf28ab42b45b94f839593822317091ac9c</v>
+        <v>c8c2cdec4a029da6496b9a00a724fb0aaf1039e480b82fd1224ec718f72ae4b3</v>
       </c>
     </row>
     <row r="69">
@@ -1770,7 +1770,7 @@
         <v>audioclip_sfx_h0006_jp.ab</v>
       </c>
       <c r="C69">
-        <v>1013615</v>
+        <v>1013608</v>
       </c>
       <c r="D69" t="str">
         <v>Stage_1</v>
@@ -1779,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="F69" t="str">
-        <v>fe5665d034ec98e1969f6ee708de66c13424fa272415354b0cbc10f61449ab84</v>
+        <v>e638b8027bcd2559256798177b44b56ba3c2b2006c300c38662c009fcc8eb92b</v>
       </c>
     </row>
     <row r="70">
@@ -1790,7 +1790,7 @@
         <v>audioclip_sfx_h0007_jp.ab</v>
       </c>
       <c r="C70">
-        <v>678623</v>
+        <v>678534</v>
       </c>
       <c r="D70" t="str">
         <v>Stage_1</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="F70" t="str">
-        <v>6c6efc850314bcdb8639d5b62dc7fc0b898371bed825864299474cabca00bd2a</v>
+        <v>ae8969f75064ae0a7ae3b80f04193b7d22f4d4584946f6004cbc412f9a34acbf</v>
       </c>
     </row>
     <row r="71">
@@ -1810,7 +1810,7 @@
         <v>audioclip_sfx_h0008_jp.ab</v>
       </c>
       <c r="C71">
-        <v>349413</v>
+        <v>349470</v>
       </c>
       <c r="D71" t="str">
         <v>Stage_1</v>
@@ -1819,7 +1819,7 @@
         <v>0</v>
       </c>
       <c r="F71" t="str">
-        <v>f91653546cf0855966fc35f3cd88cc1e9d49611451d848c903614cd26c8d1e2a</v>
+        <v>a1f64734d0e74b0b06190a6dce1a61dd3ae45b8552277abf4bb0479ab0cf6c08</v>
       </c>
     </row>
     <row r="72">
@@ -1830,7 +1830,7 @@
         <v>audioclip_sfx_h0009_jp.ab</v>
       </c>
       <c r="C72">
-        <v>453780</v>
+        <v>453710</v>
       </c>
       <c r="D72" t="str">
         <v>Stage_1</v>
@@ -1839,7 +1839,7 @@
         <v>0</v>
       </c>
       <c r="F72" t="str">
-        <v>18969559c1f15295cdc2017e4a41934609f3ebfaccc27f49ca018e2cf3429415</v>
+        <v>9904495b2a7d7821797509db16ee42c562c3a05b10b279a6bd451d83050d8b75</v>
       </c>
     </row>
     <row r="73">
@@ -1850,7 +1850,7 @@
         <v>audioclip_sfx_h0010_jp.ab</v>
       </c>
       <c r="C73">
-        <v>1074574</v>
+        <v>1074573</v>
       </c>
       <c r="D73" t="str">
         <v>Stage_1</v>
@@ -1859,7 +1859,7 @@
         <v>0</v>
       </c>
       <c r="F73" t="str">
-        <v>a2e3e7310fd172229dbc8359bdbe5a3e097cb3d916562aa1dcafeb788b84a2b9</v>
+        <v>97ec676ddfe34efc1c0ac6c77c1c3924d86ae572b53b9cfea18f4a5c52ab9908</v>
       </c>
     </row>
     <row r="74">
@@ -1870,7 +1870,7 @@
         <v>audioclip_sfx_h0012_jp.ab</v>
       </c>
       <c r="C74">
-        <v>740116</v>
+        <v>740079</v>
       </c>
       <c r="D74" t="str">
         <v>Stage_1</v>
@@ -1879,7 +1879,7 @@
         <v>0</v>
       </c>
       <c r="F74" t="str">
-        <v>bdd77632d712f23ecda336b8bccd55412f2f06199f32346f7fcdad68ed5ade2c</v>
+        <v>b89cf02e67732326de4f57ab75e54b4cfb9c7fd1a1dcef3fb5d832324a93468f</v>
       </c>
     </row>
     <row r="75">
@@ -1890,7 +1890,7 @@
         <v>audioclip_sfx_h0013_jp.ab</v>
       </c>
       <c r="C75">
-        <v>940883</v>
+        <v>940837</v>
       </c>
       <c r="D75" t="str">
         <v>Stage_1</v>
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="F75" t="str">
-        <v>c3f82328888aee14300bb033d8657e09ac7b65c8e08443da5c31a0974d0718fc</v>
+        <v>1c684133248e39bf4b69e3f9919de3fc5fc9c6584671369b18861e151366dbf8</v>
       </c>
     </row>
     <row r="76">
@@ -1910,7 +1910,7 @@
         <v>audioclip_sfx_h0014_jp.ab</v>
       </c>
       <c r="C76">
-        <v>446593</v>
+        <v>446613</v>
       </c>
       <c r="D76" t="str">
         <v>Stage_1</v>
@@ -1919,7 +1919,7 @@
         <v>0</v>
       </c>
       <c r="F76" t="str">
-        <v>35f5f17eda0d80e254cb565711de1f1ab5782a2453eafe916ff2fc3ef8903a1b</v>
+        <v>0ff0d4cc0aeefdecb0dcce1dd97a6967782008d0d6740d6d9a977f9db56cb2f3</v>
       </c>
     </row>
     <row r="77">
@@ -1930,7 +1930,7 @@
         <v>audioclip_sfx_h0016_jp.ab</v>
       </c>
       <c r="C77">
-        <v>698679</v>
+        <v>698716</v>
       </c>
       <c r="D77" t="str">
         <v>Stage_1</v>
@@ -1939,7 +1939,7 @@
         <v>0</v>
       </c>
       <c r="F77" t="str">
-        <v>33e5c6e86712def040f301e65d532d7650be5293f0f35c767ccf32e5110d99e0</v>
+        <v>72c20383f154e6854e484ad55000abcce6a89f319fb3931b9c0806cfbdf7002c</v>
       </c>
     </row>
     <row r="78">
@@ -1950,7 +1950,7 @@
         <v>audioclip_sfx_h0018_jp.ab</v>
       </c>
       <c r="C78">
-        <v>891813</v>
+        <v>891827</v>
       </c>
       <c r="D78" t="str">
         <v>Stage_1</v>
@@ -1959,7 +1959,7 @@
         <v>0</v>
       </c>
       <c r="F78" t="str">
-        <v>99daea97362cee1dc7bcc7619a57cf95ef560474c2beee51818a9a906d5d8f9a</v>
+        <v>10c2a6bf04ae1cc7f8194b13cff7c88d90a3f008b27180f89a9f7a3324963799</v>
       </c>
     </row>
     <row r="79">
@@ -1970,7 +1970,7 @@
         <v>audioclip_sfx_h0020_jp.ab</v>
       </c>
       <c r="C79">
-        <v>928965</v>
+        <v>928983</v>
       </c>
       <c r="D79" t="str">
         <v>Stage_1</v>
@@ -1979,7 +1979,7 @@
         <v>0</v>
       </c>
       <c r="F79" t="str">
-        <v>af10a421ece4b6b4723db946651144c23c358dc970b69d58db1ed6e80bf56b86</v>
+        <v>dd74bd5b6f34ebc9d3156b7b158d042619993528f7a222937b7be184843793dd</v>
       </c>
     </row>
     <row r="80">
@@ -1990,7 +1990,7 @@
         <v>audioclip_sfx_h0021_jp.ab</v>
       </c>
       <c r="C80">
-        <v>1196248</v>
+        <v>1196306</v>
       </c>
       <c r="D80" t="str">
         <v>Stage_1</v>
@@ -1999,7 +1999,7 @@
         <v>0</v>
       </c>
       <c r="F80" t="str">
-        <v>e4bc105e612fea2c563e47fb9211b0d23649b75e2c9ce15bc5758fc6f49a6623</v>
+        <v>0ad4a3af65ce559f42727de3e6df71a6db52860a350f062db0608ad9485a8a1d</v>
       </c>
     </row>
     <row r="81">
@@ -2010,7 +2010,7 @@
         <v>audioclip_sfx_h0022_jp.ab</v>
       </c>
       <c r="C81">
-        <v>985555</v>
+        <v>985529</v>
       </c>
       <c r="D81" t="str">
         <v>Stage_1</v>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="F81" t="str">
-        <v>403941619aa6b4ec1c545c41af196e706ee31be632f015365946f95a4d99c32f</v>
+        <v>0881d04d36615104f5db60b8dd25f793b253a1efd19544e1db84fbd626536cf7</v>
       </c>
     </row>
     <row r="82">
@@ -2030,7 +2030,7 @@
         <v>audioclip_sfx_h0023_jp.ab</v>
       </c>
       <c r="C82">
-        <v>1374151</v>
+        <v>1374150</v>
       </c>
       <c r="D82" t="str">
         <v>Stage_1</v>
@@ -2039,7 +2039,7 @@
         <v>0</v>
       </c>
       <c r="F82" t="str">
-        <v>33354945932815d98a072bcc88e5faff53b738f7df04e0c6c0eb8a07b6068dc6</v>
+        <v>673ff27320590e9e6c1fce85b6ab2990309e5816498f7f5912f9b8d2e393cee5</v>
       </c>
     </row>
     <row r="83">
@@ -2050,7 +2050,7 @@
         <v>audioclip_sfx_h0024_jp.ab</v>
       </c>
       <c r="C83">
-        <v>1572148</v>
+        <v>1572086</v>
       </c>
       <c r="D83" t="str">
         <v>Stage_1</v>
@@ -2059,7 +2059,7 @@
         <v>0</v>
       </c>
       <c r="F83" t="str">
-        <v>9119409d957f484946d109fa6be78d9d5a71aee8eab53400583aa891f2dff5c9</v>
+        <v>6efeb6dae2c4dde11e67479000ee13adf05bdbcd8b5a16dfe14e6e6e9e668c30</v>
       </c>
     </row>
     <row r="84">
@@ -2070,7 +2070,7 @@
         <v>audioclip_sfx_h0025_jp.ab</v>
       </c>
       <c r="C84">
-        <v>938020</v>
+        <v>938015</v>
       </c>
       <c r="D84" t="str">
         <v>Stage_1</v>
@@ -2079,7 +2079,7 @@
         <v>0</v>
       </c>
       <c r="F84" t="str">
-        <v>7202dbfd6bcc3cb7947c548923d644c4ea84d843ea3ed27920eeb10aa4470dfe</v>
+        <v>57c19e2e0491b0f8d63225b5ac87cc0ef61bd25f71e5b43fa60c1e3ee7eccd1f</v>
       </c>
     </row>
     <row r="85">
@@ -2090,7 +2090,7 @@
         <v>audioclip_sfx_h0029_jp.ab</v>
       </c>
       <c r="C85">
-        <v>1291353</v>
+        <v>1291425</v>
       </c>
       <c r="D85" t="str">
         <v>Stage_1</v>
@@ -2099,7 +2099,7 @@
         <v>0</v>
       </c>
       <c r="F85" t="str">
-        <v>409b575c22378888d40b22fc0c30b7ee216da4ef3885e8a9db9dc42fca78130d</v>
+        <v>724eeae6b9e6ed52769104e0019a3acc6e846afeec5c424b6a004061f7736062</v>
       </c>
     </row>
     <row r="86">
@@ -2110,7 +2110,7 @@
         <v>audioclip_sfx_h0030_jp.ab</v>
       </c>
       <c r="C86">
-        <v>1189229</v>
+        <v>1189238</v>
       </c>
       <c r="D86" t="str">
         <v>Stage_1</v>
@@ -2119,7 +2119,7 @@
         <v>0</v>
       </c>
       <c r="F86" t="str">
-        <v>0ca988613b7f8e0ffbb52895f6e2bbedbfbd69c992fb25e0da33a068abf63fe1</v>
+        <v>1cc69c9337973145a3c8b51ac709aa559ac7f54e1ce19d7e7b928fb6bc5a02c0</v>
       </c>
     </row>
     <row r="87">
@@ -2130,7 +2130,7 @@
         <v>audioclip_sfx_h0031_jp.ab</v>
       </c>
       <c r="C87">
-        <v>1039751</v>
+        <v>1039757</v>
       </c>
       <c r="D87" t="str">
         <v>Stage_1</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="F87" t="str">
-        <v>750ad4d435684553f67d82fa3170ca674d3328b0452f38cc5ec85be69c54148e</v>
+        <v>d8aa840e2f02281eb0f4864119ffcd642361416796d761b3f84d5d94ccebeb44</v>
       </c>
     </row>
     <row r="88">
@@ -2150,7 +2150,7 @@
         <v>audioclip_sfx_h0035_jp.ab</v>
       </c>
       <c r="C88">
-        <v>785947</v>
+        <v>785944</v>
       </c>
       <c r="D88" t="str">
         <v>Stage_1</v>
@@ -2159,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="F88" t="str">
-        <v>14c0f8fe66adffe92f313ce297eab95516e0a7971907c25768525069e0a6db7d</v>
+        <v>61777f9e23b0dbf75dfd9d699549418853ddf73c70beaeba66030541ca438508</v>
       </c>
     </row>
     <row r="89">
@@ -2170,7 +2170,7 @@
         <v>audioclip_sfx_h0036_jp.ab</v>
       </c>
       <c r="C89">
-        <v>743620</v>
+        <v>743634</v>
       </c>
       <c r="D89" t="str">
         <v>Stage_1</v>
@@ -2179,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="F89" t="str">
-        <v>ebc9ec2f8fd0db2084a75c98bf5e78f3560a39031d4e70de22dc6c51a7dae254</v>
+        <v>5fe0bb699867c5d4dda1f34fd9a8ef7a711d33935a498a2966bc39b3a495258e</v>
       </c>
     </row>
     <row r="90">
@@ -2190,7 +2190,7 @@
         <v>audioclip_sfx_h0038_jp.ab</v>
       </c>
       <c r="C90">
-        <v>611358</v>
+        <v>611393</v>
       </c>
       <c r="D90" t="str">
         <v>Stage_1</v>
@@ -2199,7 +2199,7 @@
         <v>0</v>
       </c>
       <c r="F90" t="str">
-        <v>a11a523fb00e0004217c67cec973c963a5d4d854cab28483c4adf3c9b14d08a9</v>
+        <v>c8d963af4018939fb632617cce4869111f70fcfecc52dd5ae0e32139f4a2ab40</v>
       </c>
     </row>
     <row r="91">
@@ -2210,7 +2210,7 @@
         <v>audioclip_sfx_h0040_jp.ab</v>
       </c>
       <c r="C91">
-        <v>587167</v>
+        <v>587188</v>
       </c>
       <c r="D91" t="str">
         <v>Stage_1</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="F91" t="str">
-        <v>e34fa3770191d389fd93e77fd1fd621a5ef3e87987bbcecd0e26e5babad238f8</v>
+        <v>a89a69b7afff1388bb0ae27cb29d3d09a6aa76178572aa424bbb2c4d5c3d3a98</v>
       </c>
     </row>
     <row r="92">
@@ -2230,7 +2230,7 @@
         <v>audioclip_sfx_h0041_jp.ab</v>
       </c>
       <c r="C92">
-        <v>525471</v>
+        <v>525469</v>
       </c>
       <c r="D92" t="str">
         <v>Stage_1</v>
@@ -2239,7 +2239,7 @@
         <v>0</v>
       </c>
       <c r="F92" t="str">
-        <v>daa9a4039aafc609c9f42b8e6f19f9cec548b86ac300a23e108561aece93fcf1</v>
+        <v>aa20e08b7e19c9aad602fb480b73ff912ba9b0f6d503b41db1b10a2be1250a33</v>
       </c>
     </row>
     <row r="93">
@@ -2250,7 +2250,7 @@
         <v>audioclip_sfx_h0042_jp.ab</v>
       </c>
       <c r="C93">
-        <v>955386</v>
+        <v>955327</v>
       </c>
       <c r="D93" t="str">
         <v>Stage_1</v>
@@ -2259,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="F93" t="str">
-        <v>04b7aecda37a086ada634e13ea646e0a62a529f263e288253d7f2698cbd8bd4a</v>
+        <v>574ba4280629bf21ad2291f30a35fec1e1274f49e4090042bb8405b749546d75</v>
       </c>
     </row>
     <row r="94">
@@ -2270,7 +2270,7 @@
         <v>audioclip_sfx_h0043_jp.ab</v>
       </c>
       <c r="C94">
-        <v>2421241</v>
+        <v>2421308</v>
       </c>
       <c r="D94" t="str">
         <v>Stage_1</v>
@@ -2279,7 +2279,7 @@
         <v>0</v>
       </c>
       <c r="F94" t="str">
-        <v>d175374e6bab9b23a69e513fdd83a1b1aeedd66364afc933ac29de3c5691c714</v>
+        <v>73c9efe6a0b5b923c857c6f1f6f96ac6683720718c44e7c6f3492fef6bf877a6</v>
       </c>
     </row>
     <row r="95">
@@ -2290,7 +2290,7 @@
         <v>audioclip_sfx_h0044_jp.ab</v>
       </c>
       <c r="C95">
-        <v>619212</v>
+        <v>619258</v>
       </c>
       <c r="D95" t="str">
         <v>Stage_1</v>
@@ -2299,7 +2299,7 @@
         <v>0</v>
       </c>
       <c r="F95" t="str">
-        <v>5d16f740f777446bcdad7f018c1c1607daf806f181571a7c1c70b43b0e3d42c1</v>
+        <v>b0ce38efb89e31a5e52f59339408c8b7c9bc10fb16af83638ff626193bd353c5</v>
       </c>
     </row>
     <row r="96">
@@ -2310,7 +2310,7 @@
         <v>audioclip_sfx_h0045_jp.ab</v>
       </c>
       <c r="C96">
-        <v>538569</v>
+        <v>538577</v>
       </c>
       <c r="D96" t="str">
         <v>Stage_1</v>
@@ -2319,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="F96" t="str">
-        <v>55cf50bcb056c1951bb7c311b083b7707bc58cabe23721eb397e2a259809c92f</v>
+        <v>205404ed576394b3656fdfa50c52d977240a9794d69fdfee6b65073571b7882f</v>
       </c>
     </row>
     <row r="97">
@@ -2330,7 +2330,7 @@
         <v>audioclip_sfx_h0047_jp.ab</v>
       </c>
       <c r="C97">
-        <v>8510836</v>
+        <v>8510811</v>
       </c>
       <c r="D97" t="str">
         <v>Stage_1</v>
@@ -2339,7 +2339,7 @@
         <v>0</v>
       </c>
       <c r="F97" t="str">
-        <v>4148901efe719a9c838f285e694d6c38be28f187e87aef00f55f28e322b0aa91</v>
+        <v>6ded42b522bd20b81509f112ef9630e992b8ddd76200e930115e927b0eaf78ba</v>
       </c>
     </row>
     <row r="98">
@@ -2350,7 +2350,7 @@
         <v>audioclip_sfx_h0048_jp.ab</v>
       </c>
       <c r="C98">
-        <v>1635040</v>
+        <v>1635034</v>
       </c>
       <c r="D98" t="str">
         <v>Stage_1</v>
@@ -2359,7 +2359,7 @@
         <v>0</v>
       </c>
       <c r="F98" t="str">
-        <v>b4ee10e13e2c3ebee2399b286cfa4a5bac81b7bc70b4d639390e4479e46c03c7</v>
+        <v>c13e93f347f415c5a269b99f1e99ed3da85e6ef218e6cbcee6d44ffa557e098f</v>
       </c>
     </row>
     <row r="99">
@@ -2370,7 +2370,7 @@
         <v>audioclip_sfx_h0073_jp.ab</v>
       </c>
       <c r="C99">
-        <v>276295</v>
+        <v>276321</v>
       </c>
       <c r="D99" t="str">
         <v>Stage_1</v>
@@ -2379,7 +2379,7 @@
         <v>0</v>
       </c>
       <c r="F99" t="str">
-        <v>f84a3ba7c55b027a7694adae501f5afbae9f70113a4f45a917f3c9f4fdc2ca16</v>
+        <v>7e4f49d36b0b4ab0901b6419311d2ddd58e7c1e7233f0445421ce4bd7a094ad8</v>
       </c>
     </row>
     <row r="100">
@@ -2390,7 +2390,7 @@
         <v>audioclip_sfx_h0097_jp.ab</v>
       </c>
       <c r="C100">
-        <v>2057513</v>
+        <v>2057611</v>
       </c>
       <c r="D100" t="str">
         <v>Stage_1</v>
@@ -2399,7 +2399,7 @@
         <v>0</v>
       </c>
       <c r="F100" t="str">
-        <v>315a03e97d996689a7c644ee1a59b1d037ea146c266ae6194c17c26ed31b96b6</v>
+        <v>11ed52c647a1181b13b29c03c9c176ebef39d44aed546eb1a69cbd0ad65d2ad3</v>
       </c>
     </row>
     <row r="101">
@@ -2410,7 +2410,7 @@
         <v>audioclip_sfx_h0128_jp.ab</v>
       </c>
       <c r="C101">
-        <v>29752</v>
+        <v>29753</v>
       </c>
       <c r="D101" t="str">
         <v>Stage_1</v>
@@ -2419,7 +2419,7 @@
         <v>0</v>
       </c>
       <c r="F101" t="str">
-        <v>da1e3516a29e374e62d2ac3127385d51fd5e98315812fc8d4efcdfa1cced77da</v>
+        <v>c6eb2ffa74a2df03b42095936065441b40db1d8b199790319d34fc7fc980c889</v>
       </c>
     </row>
     <row r="102">
@@ -2430,7 +2430,7 @@
         <v>audioclip_sfx_h0133_jp.ab</v>
       </c>
       <c r="C102">
-        <v>1334022</v>
+        <v>1333999</v>
       </c>
       <c r="D102" t="str">
         <v>Stage_1</v>
@@ -2439,7 +2439,7 @@
         <v>0</v>
       </c>
       <c r="F102" t="str">
-        <v>61bbe4809c0a4c470d122e46fa99640ed560c27aa6b2d464523f2e06bea20efc</v>
+        <v>92c2ccac2dfa2c6855833f2fbdbfb593afc794b35e8ec24e9de9a2da178c21c1</v>
       </c>
     </row>
     <row r="103">
@@ -2450,7 +2450,7 @@
         <v>audioclip_sfx_h0134_jp.ab</v>
       </c>
       <c r="C103">
-        <v>1204319</v>
+        <v>1204323</v>
       </c>
       <c r="D103" t="str">
         <v>Stage_1</v>
@@ -2459,7 +2459,7 @@
         <v>0</v>
       </c>
       <c r="F103" t="str">
-        <v>c65dfbcfb0a32ac473562418675ff0d7ab4ad89a9bcd72870254d6a9539cfbaf</v>
+        <v>3479bbe30ca15e2738e7633412b34f29aaaad940227e8c22d47a9c9e0ad94c10</v>
       </c>
     </row>
     <row r="104">
@@ -2470,7 +2470,7 @@
         <v>audioclip_sfx_h0135_jp.ab</v>
       </c>
       <c r="C104">
-        <v>2285418</v>
+        <v>2285400</v>
       </c>
       <c r="D104" t="str">
         <v>Stage_1</v>
@@ -2479,7 +2479,7 @@
         <v>0</v>
       </c>
       <c r="F104" t="str">
-        <v>4b8dce7d7fa2d5bc8277c11d2ad0950d4a7a26d0c4e0abe13aee5e5dac6c108e</v>
+        <v>f17dcba882e1b914519f580937453739d9364410d6222ad790707aefcf4ec96b</v>
       </c>
     </row>
     <row r="105">
@@ -2490,7 +2490,7 @@
         <v>audioclip_sfx_h0136_jp.ab</v>
       </c>
       <c r="C105">
-        <v>1316078</v>
+        <v>1316071</v>
       </c>
       <c r="D105" t="str">
         <v>Stage_1</v>
@@ -2499,7 +2499,7 @@
         <v>0</v>
       </c>
       <c r="F105" t="str">
-        <v>7cd49bbc7ab509252736e2487d822ec9dc7cb9e4e8787803276e4bdfef5ba5fa</v>
+        <v>feda05df05b16c589d0c291cf1ff041322d9a2556056d8b254227ebf048d9960</v>
       </c>
     </row>
     <row r="106">
@@ -2510,7 +2510,7 @@
         <v>audioclip_sfx_h0137_jp.ab</v>
       </c>
       <c r="C106">
-        <v>2046304</v>
+        <v>2046360</v>
       </c>
       <c r="D106" t="str">
         <v>Stage_1</v>
@@ -2519,7 +2519,7 @@
         <v>0</v>
       </c>
       <c r="F106" t="str">
-        <v>d4db8b9f33f7e17e60f704a1720d7bdcec0bf9c7e0f7b935a46f5f932b8674d6</v>
+        <v>5045f0383fbdcbfd9a908a41d00c2f251a864f6c64e74e544409cf19d5d15b1c</v>
       </c>
     </row>
     <row r="107">
@@ -2530,7 +2530,7 @@
         <v>audioclip_sfx_h0138_jp.ab</v>
       </c>
       <c r="C107">
-        <v>1236791</v>
+        <v>1236850</v>
       </c>
       <c r="D107" t="str">
         <v>Stage_1</v>
@@ -2539,7 +2539,7 @@
         <v>0</v>
       </c>
       <c r="F107" t="str">
-        <v>f4510f71a0bdf8dc0074cd49a6c1a199857f5504e91e36a4387e961ed876b58a</v>
+        <v>b1365b29e1c181945bf65626b6c9e21337027d6adb7c7e053b07c173bedc57cc</v>
       </c>
     </row>
     <row r="108">
@@ -2550,7 +2550,7 @@
         <v>audioclip_sfx_h0150_jp.ab</v>
       </c>
       <c r="C108">
-        <v>2757248</v>
+        <v>2757176</v>
       </c>
       <c r="D108" t="str">
         <v>Stage_1</v>
@@ -2559,7 +2559,7 @@
         <v>0</v>
       </c>
       <c r="F108" t="str">
-        <v>ed10788a5b4bb57f608bc8ff9092774c78c773ce39911de61b1a5e223d3c41bf</v>
+        <v>f6cf63aa9a30d97f61ffa8eca51e6ea929273dab57fd2a175bec7e700e9b9340</v>
       </c>
     </row>
     <row r="109">
@@ -2570,7 +2570,7 @@
         <v>audioclip_sfx_h0151_jp.ab</v>
       </c>
       <c r="C109">
-        <v>1924708</v>
+        <v>1924747</v>
       </c>
       <c r="D109" t="str">
         <v>Stage_1</v>
@@ -2579,7 +2579,7 @@
         <v>0</v>
       </c>
       <c r="F109" t="str">
-        <v>1228a4f8efdd7de6eb5361417059f3c9b81b16e919fdb478ca83b1ba5b1eaac5</v>
+        <v>4cb0cc67f6298536d53c6c888bf5adda0053f16cceb97f477cd1fe3695de477b</v>
       </c>
     </row>
     <row r="110">
@@ -2590,7 +2590,7 @@
         <v>audioclip_sfx_h0152_jp.ab</v>
       </c>
       <c r="C110">
-        <v>1987359</v>
+        <v>1987313</v>
       </c>
       <c r="D110" t="str">
         <v>Stage_1</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="F110" t="str">
-        <v>41830d55b2bb2f00c5a9bf4b85d59fe8647f2b3a16fa74242d4535293936b68b</v>
+        <v>0103ea9ab16f6519a38cb95da3a7a7b15fc0fb11d07cbf9861d2b4538f11f18c</v>
       </c>
     </row>
     <row r="111">
@@ -2610,7 +2610,7 @@
         <v>audioclip_sfx_h0154_jp.ab</v>
       </c>
       <c r="C111">
-        <v>1986335</v>
+        <v>1986265</v>
       </c>
       <c r="D111" t="str">
         <v>Stage_1</v>
@@ -2619,7 +2619,7 @@
         <v>0</v>
       </c>
       <c r="F111" t="str">
-        <v>3c419c58c29aca43bc6f5991a9c45b7426608b6e4b495260f4185b9b9d1a929a</v>
+        <v>474b9566a36bf5919784183fe7f25b5c17eb61ccba36542b231a26908c2636c3</v>
       </c>
     </row>
     <row r="112">
@@ -2630,7 +2630,7 @@
         <v>audioclip_sfx_h0157_jp.ab</v>
       </c>
       <c r="C112">
-        <v>1681370</v>
+        <v>1681333</v>
       </c>
       <c r="D112" t="str">
         <v>Stage_1</v>
@@ -2639,7 +2639,7 @@
         <v>0</v>
       </c>
       <c r="F112" t="str">
-        <v>6bf8ea921571ab35978f726263e641cbe60d288bd3eba577a4ccb27306c0e603</v>
+        <v>8e5d875a9ee07c87fb517b61109d3a568d7d17b08395c9f564c04f83f8c1b47d</v>
       </c>
     </row>
     <row r="113">
@@ -2650,7 +2650,7 @@
         <v>audioclip_sfx_h0159_jp.ab</v>
       </c>
       <c r="C113">
-        <v>1893111</v>
+        <v>1893118</v>
       </c>
       <c r="D113" t="str">
         <v>Stage_1</v>
@@ -2659,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="F113" t="str">
-        <v>e5762e77d248b75da3b3c2a85a340d38ce00b4e8451728efc9fccfb564c869b6</v>
+        <v>d5e6c82781443094f2d8f88b0e26f8784ad3742e1a6170c06d230b32e644f5de</v>
       </c>
     </row>
     <row r="114">
@@ -2670,7 +2670,7 @@
         <v>audioclip_sfx_h0161_jp.ab</v>
       </c>
       <c r="C114">
-        <v>1944104</v>
+        <v>1944064</v>
       </c>
       <c r="D114" t="str">
         <v>Stage_1</v>
@@ -2679,7 +2679,7 @@
         <v>0</v>
       </c>
       <c r="F114" t="str">
-        <v>a6a3c7727bc8da7d557a64b3a14d9db538f5195e0d0ce5c77f4e59b83ea46c7a</v>
+        <v>660f212d90e193fc331437482eba0d6078064e8d6849a9bf416d9b51b299d54f</v>
       </c>
     </row>
     <row r="115">
@@ -2690,7 +2690,7 @@
         <v>audioclip_sfx_h0163_jp.ab</v>
       </c>
       <c r="C115">
-        <v>1305067</v>
+        <v>1305134</v>
       </c>
       <c r="D115" t="str">
         <v>Stage_1</v>
@@ -2699,7 +2699,7 @@
         <v>0</v>
       </c>
       <c r="F115" t="str">
-        <v>9131266dbd51ea7c34048d4d037f6f18eb241fc3cdbadb0600b5dc6d348b26ba</v>
+        <v>89a517eef484054460d2db66bbb371224de76aa92cc8de314e8581f25405b624</v>
       </c>
     </row>
     <row r="116">
@@ -2710,7 +2710,7 @@
         <v>audioclip_sfx_h0164_jp.ab</v>
       </c>
       <c r="C116">
-        <v>966709</v>
+        <v>966699</v>
       </c>
       <c r="D116" t="str">
         <v>Stage_1</v>
@@ -2719,7 +2719,7 @@
         <v>0</v>
       </c>
       <c r="F116" t="str">
-        <v>34146bd0a9ef27120b69314da4b7412ac20fd64db230510643a7d3d16de963c4</v>
+        <v>73aa7acf88ed81fba7e0d2341cfe42503343b2289c6f9f4572644c6ee773d590</v>
       </c>
     </row>
     <row r="117">
@@ -2730,7 +2730,7 @@
         <v>audioclip_sfx_h0165_jp.ab</v>
       </c>
       <c r="C117">
-        <v>1022205</v>
+        <v>1022186</v>
       </c>
       <c r="D117" t="str">
         <v>Stage_1</v>
@@ -2739,7 +2739,7 @@
         <v>0</v>
       </c>
       <c r="F117" t="str">
-        <v>6f7b73eff36fcbe18229782a1dd704302b7099692798f6f27e8ccf345e59a9ee</v>
+        <v>af4dd69ee5af5e882da10f354dd2cbf47385a3f9cc6d025ec5c048525b56370e</v>
       </c>
     </row>
     <row r="118">
@@ -2750,7 +2750,7 @@
         <v>audioclip_sfx_h0166_jp.ab</v>
       </c>
       <c r="C118">
-        <v>735094</v>
+        <v>735130</v>
       </c>
       <c r="D118" t="str">
         <v>Stage_1</v>
@@ -2759,7 +2759,7 @@
         <v>0</v>
       </c>
       <c r="F118" t="str">
-        <v>7957019b935106ab080f157aeb3056eaa4e1e5bd0b817658968f76b9f68f90fa</v>
+        <v>5a3781f518474ba6c20db0b6f05e932a2f7c86d8daef1845461c856028d54dc0</v>
       </c>
     </row>
     <row r="119">
@@ -2770,7 +2770,7 @@
         <v>audioclip_sfx_h0167_jp.ab</v>
       </c>
       <c r="C119">
-        <v>884679</v>
+        <v>884652</v>
       </c>
       <c r="D119" t="str">
         <v>Stage_1</v>
@@ -2779,7 +2779,7 @@
         <v>0</v>
       </c>
       <c r="F119" t="str">
-        <v>0bdf0643b3a6e2199b619cf39bc6eb8601c03aeca632afe96f0e7fc86b42df96</v>
+        <v>779a36a544d52a0e66971bfd9cbade689c9f395735d721f7d1e98c43a5dddcec</v>
       </c>
     </row>
     <row r="120">
@@ -2790,7 +2790,7 @@
         <v>audioclip_sfx_h0168_jp.ab</v>
       </c>
       <c r="C120">
-        <v>747236</v>
+        <v>747271</v>
       </c>
       <c r="D120" t="str">
         <v>Stage_1</v>
@@ -2799,7 +2799,7 @@
         <v>0</v>
       </c>
       <c r="F120" t="str">
-        <v>0a148ee36dba2e00613145baf984f53d89c2c4464fa4bf4acb66cf8c0452c116</v>
+        <v>6863ecd4f960e46533b95132f08b5b053e2a1004d3c4c700aa4d9c832e1d7963</v>
       </c>
     </row>
     <row r="121">
@@ -2810,7 +2810,7 @@
         <v>audioclip_sfx_h0169_jp.ab</v>
       </c>
       <c r="C121">
-        <v>929591</v>
+        <v>929653</v>
       </c>
       <c r="D121" t="str">
         <v>Stage_1</v>
@@ -2819,7 +2819,7 @@
         <v>0</v>
       </c>
       <c r="F121" t="str">
-        <v>b01c27758fa0e5b0fdba0d051e47ae4450d2d0db87470db42cff2d2c332cfb7a</v>
+        <v>b5b84e86a62800f16fa0d2745414bf6747204b4edb69e092c02f14d5f0ee3d65</v>
       </c>
     </row>
     <row r="122">
@@ -2830,7 +2830,7 @@
         <v>audioclip_sfx_h0170_jp.ab</v>
       </c>
       <c r="C122">
-        <v>1438190</v>
+        <v>1438224</v>
       </c>
       <c r="D122" t="str">
         <v>Stage_1</v>
@@ -2839,7 +2839,7 @@
         <v>0</v>
       </c>
       <c r="F122" t="str">
-        <v>a5a6e13b828701c18cc4ab0a1aefcdfe26b0dbd575d076e60886494bd137d3e2</v>
+        <v>469ff7642cf794b4ce7466ffd70c2b68f94e04e0aa8e331429f5f98335d850ba</v>
       </c>
     </row>
     <row r="123">
@@ -2850,7 +2850,7 @@
         <v>audioclip_sfx_h0171_jp.ab</v>
       </c>
       <c r="C123">
-        <v>1738273</v>
+        <v>1738208</v>
       </c>
       <c r="D123" t="str">
         <v>Stage_1</v>
@@ -2859,7 +2859,7 @@
         <v>0</v>
       </c>
       <c r="F123" t="str">
-        <v>0a48a089874026a617c92d3149fb5313b33dc3b9c2d21621c5ebcd1d06f0df4a</v>
+        <v>ac9f564558788af5dbb08509cd15f641a61122ac2d16ed373a25540ad9a95c09</v>
       </c>
     </row>
     <row r="124">
@@ -2870,7 +2870,7 @@
         <v>audioclip_sfx_h0172_jp.ab</v>
       </c>
       <c r="C124">
-        <v>1379888</v>
+        <v>1379929</v>
       </c>
       <c r="D124" t="str">
         <v>Stage_1</v>
@@ -2879,7 +2879,7 @@
         <v>0</v>
       </c>
       <c r="F124" t="str">
-        <v>1420127fd1db7990b956039fb1bce3236c87c420d601a54beb857e4727ceabcc</v>
+        <v>488a0c2bab3f2f2bda9bbbf3e67702e9fd9fc7e1383ad144c13cc49cbd4fa75f</v>
       </c>
     </row>
     <row r="125">
@@ -2890,7 +2890,7 @@
         <v>audioclip_sfx_h0174_jp.ab</v>
       </c>
       <c r="C125">
-        <v>1668214</v>
+        <v>1668224</v>
       </c>
       <c r="D125" t="str">
         <v>Stage_1</v>
@@ -2899,7 +2899,7 @@
         <v>0</v>
       </c>
       <c r="F125" t="str">
-        <v>d473cfb3d47b34b4072fed757a235d08b1da54254badf92fed295bdae60dc36b</v>
+        <v>fbc58a59982a1c609942a02696b9033519d104918b48ee81e14462232db287bf</v>
       </c>
     </row>
     <row r="126">
@@ -2910,7 +2910,7 @@
         <v>audioclip_sfx_h0175_jp.ab</v>
       </c>
       <c r="C126">
-        <v>1253486</v>
+        <v>1253515</v>
       </c>
       <c r="D126" t="str">
         <v>Stage_1</v>
@@ -2919,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="F126" t="str">
-        <v>81a7309611f728f29e5c00631b5e0a08b35d74eb20a2d5e4cd7b15e263ad8f7e</v>
+        <v>9201e5d699ef470c8131c1bd2e9f9194f34f003c73a819bb36c3667ee4ea93e7</v>
       </c>
     </row>
     <row r="127">
@@ -2930,7 +2930,7 @@
         <v>audioclip_sfx_h0176_jp.ab</v>
       </c>
       <c r="C127">
-        <v>978059</v>
+        <v>978114</v>
       </c>
       <c r="D127" t="str">
         <v>Stage_1</v>
@@ -2939,7 +2939,7 @@
         <v>0</v>
       </c>
       <c r="F127" t="str">
-        <v>b0db55ebb96cfd8cf7b2564d7b6b75532fc8989f4db04c432a98fe926d047ac3</v>
+        <v>070482dec8a3c17e2f15a57a64a393e8f515051c4ad39a02c2bd08f5d5e44432</v>
       </c>
     </row>
     <row r="128">
@@ -2950,7 +2950,7 @@
         <v>audioclip_sfx_h0177_jp.ab</v>
       </c>
       <c r="C128">
-        <v>1465821</v>
+        <v>1465827</v>
       </c>
       <c r="D128" t="str">
         <v>Stage_1</v>
@@ -2959,7 +2959,7 @@
         <v>0</v>
       </c>
       <c r="F128" t="str">
-        <v>b0a817a1a9005afc751bc1a5087e5c5775c108dbfb89ea5c00747ecafe37e6b8</v>
+        <v>d50633229f8df08c2eb80f6fc6226880995614f764a3029e577aea759fd9904c</v>
       </c>
     </row>
     <row r="129">
@@ -2970,7 +2970,7 @@
         <v>audioclip_sfx_h0179_jp.ab</v>
       </c>
       <c r="C129">
-        <v>1837990</v>
+        <v>1838118</v>
       </c>
       <c r="D129" t="str">
         <v>Stage_1</v>
@@ -2979,7 +2979,7 @@
         <v>0</v>
       </c>
       <c r="F129" t="str">
-        <v>6813d60ca42e0e1e22d63348220ad08c804726b63e82c9517144cf5af794cd05</v>
+        <v>8ea013a942f92521d43f8665e858c766ae21cb64948028b11adb02c60f98e815</v>
       </c>
     </row>
     <row r="130">
@@ -2990,7 +2990,7 @@
         <v>audioclip_sfx_h0183_jp.ab</v>
       </c>
       <c r="C130">
-        <v>2327471</v>
+        <v>2327380</v>
       </c>
       <c r="D130" t="str">
         <v>Stage_1</v>
@@ -2999,7 +2999,7 @@
         <v>0</v>
       </c>
       <c r="F130" t="str">
-        <v>476b25f25ea3680cf684b91a4a8e964551244ef20e7bb6a30c5bb7fd3760fa4c</v>
+        <v>65a6797b89754f53838c441f191af68fa4c7be2b3267f218264f6104fc353580</v>
       </c>
     </row>
     <row r="131">
@@ -3010,7 +3010,7 @@
         <v>audioclip_sfx_h0185_jp.ab</v>
       </c>
       <c r="C131">
-        <v>1563967</v>
+        <v>1563987</v>
       </c>
       <c r="D131" t="str">
         <v>Stage_1</v>
@@ -3019,7 +3019,7 @@
         <v>0</v>
       </c>
       <c r="F131" t="str">
-        <v>677e44364439c03b2643be703ae756e7e78061beaa471e6e3ad23b10dec20b8b</v>
+        <v>4636bb583154e52fbc5b869b4559f54327cec9c2cf0c77c42331ad1fd9450c87</v>
       </c>
     </row>
     <row r="132">
@@ -3030,7 +3030,7 @@
         <v>audioclip_sfx_h0186_jp.ab</v>
       </c>
       <c r="C132">
-        <v>1892917</v>
+        <v>1892941</v>
       </c>
       <c r="D132" t="str">
         <v>Stage_1</v>
@@ -3039,7 +3039,7 @@
         <v>0</v>
       </c>
       <c r="F132" t="str">
-        <v>df19f27bfd0b5259401459e4f18d2afb51c8e78a1140ee638b5d0579c76f1707</v>
+        <v>afb6e2aa3c171447e1cc4027209d3441d05971acb037ed02d79f8baa0509ae21</v>
       </c>
     </row>
     <row r="133">
@@ -3050,7 +3050,7 @@
         <v>audioclip_sfx_h0190_jp.ab</v>
       </c>
       <c r="C133">
-        <v>2643059</v>
+        <v>2642996</v>
       </c>
       <c r="D133" t="str">
         <v>Stage_1</v>
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="F133" t="str">
-        <v>2b49deab28ea069582df30c53cff3f05162b1bdc9a211a313f337da600cc0174</v>
+        <v>d400d5c924bee3ba8dfaad29716388d2cdda4e3b6ad12aa127840ac9125f40d6</v>
       </c>
     </row>
     <row r="134">
@@ -3070,7 +3070,7 @@
         <v>audioclip_sfx_h0191_jp.ab</v>
       </c>
       <c r="C134">
-        <v>573980</v>
+        <v>573986</v>
       </c>
       <c r="D134" t="str">
         <v>Stage_1</v>
@@ -3079,7 +3079,7 @@
         <v>0</v>
       </c>
       <c r="F134" t="str">
-        <v>94e7fa17b3264d905f51cefcc8ff91db036dddedc576fa3d92b08aaf964ef208</v>
+        <v>c5a765e09a5097e8d697b3ef89755f20186fa3d7de1af54eb0caefe91fe6903c</v>
       </c>
     </row>
     <row r="135">
@@ -3090,7 +3090,7 @@
         <v>audioclip_sfx_h0192_jp.ab</v>
       </c>
       <c r="C135">
-        <v>817952</v>
+        <v>817956</v>
       </c>
       <c r="D135" t="str">
         <v>Stage_1</v>
@@ -3099,7 +3099,7 @@
         <v>0</v>
       </c>
       <c r="F135" t="str">
-        <v>fda664a7b0c6a0a5ef51ef1b9d2e68dc187ff2b4282beec74ff77b5bef1c6583</v>
+        <v>187596dab35c5ac23f7d941eb4a7510f261cbd457596a8f739300a183de7c29c</v>
       </c>
     </row>
     <row r="136">
@@ -3110,7 +3110,7 @@
         <v>audioclip_sfx_h0193_jp.ab</v>
       </c>
       <c r="C136">
-        <v>1562440</v>
+        <v>1562391</v>
       </c>
       <c r="D136" t="str">
         <v>Stage_1</v>
@@ -3119,7 +3119,7 @@
         <v>0</v>
       </c>
       <c r="F136" t="str">
-        <v>cd0d43f866594894092bfa72f7c925b6e01e2662eea17335fc6584abd07c8c91</v>
+        <v>5c1e2a4f1e5fe974eea4308527c489529cd843b342f3d60a8b0182db65b8e959</v>
       </c>
     </row>
     <row r="137">
@@ -3130,7 +3130,7 @@
         <v>audioclip_sfx_h0194_jp.ab</v>
       </c>
       <c r="C137">
-        <v>710862</v>
+        <v>710850</v>
       </c>
       <c r="D137" t="str">
         <v>Stage_1</v>
@@ -3139,7 +3139,7 @@
         <v>0</v>
       </c>
       <c r="F137" t="str">
-        <v>ef87d99f4fc6edb7783a7dddcd0ca0e2cb8a65a05962052ce27946e94de30b51</v>
+        <v>d2def99c2635b9aec4dc997b6558d759551f50054d80040868bcb5564c6d7882</v>
       </c>
     </row>
     <row r="138">
@@ -3150,7 +3150,7 @@
         <v>audioclip_sfx_h0196_jp.ab</v>
       </c>
       <c r="C138">
-        <v>1046815</v>
+        <v>1046761</v>
       </c>
       <c r="D138" t="str">
         <v>Stage_1</v>
@@ -3159,7 +3159,7 @@
         <v>0</v>
       </c>
       <c r="F138" t="str">
-        <v>36df798c043b3182a277a897bc26df44edfd4988bc457710d141f3f37dce330f</v>
+        <v>70b3388f4e4313934d976478334c2240bcf3494cc98201f3874bc8a38a8e566d</v>
       </c>
     </row>
     <row r="139">
@@ -3170,7 +3170,7 @@
         <v>audioclip_sfx_h0197_jp.ab</v>
       </c>
       <c r="C139">
-        <v>877462</v>
+        <v>877407</v>
       </c>
       <c r="D139" t="str">
         <v>Stage_1</v>
@@ -3179,7 +3179,7 @@
         <v>0</v>
       </c>
       <c r="F139" t="str">
-        <v>1cd0623cbf20262dcee322c4b462efcbe4a83d69349377baafd77a029ec92999</v>
+        <v>948ad7ff090e33c8407ab4c0a6295bcdba546d7bfed76650bed821fdd27aac5f</v>
       </c>
     </row>
     <row r="140">
@@ -3190,7 +3190,7 @@
         <v>audioclip_sfx_h0198_jp.ab</v>
       </c>
       <c r="C140">
-        <v>1081026</v>
+        <v>1081048</v>
       </c>
       <c r="D140" t="str">
         <v>Stage_1</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="F140" t="str">
-        <v>f65310500a4e202dcedc2243da1d940229e85f0539fe21379ffe8582e2523bd2</v>
+        <v>aea062cf9edda6dd08b70bfec21826046050b9300e4f08faf056fa249f0b5b81</v>
       </c>
     </row>
     <row r="141">
@@ -3210,7 +3210,7 @@
         <v>audioclip_sfx_h0199_jp.ab</v>
       </c>
       <c r="C141">
-        <v>922796</v>
+        <v>922804</v>
       </c>
       <c r="D141" t="str">
         <v>Stage_1</v>
@@ -3219,7 +3219,7 @@
         <v>0</v>
       </c>
       <c r="F141" t="str">
-        <v>ee9f9754b469cddb2593c2a91508b672f428447cc9db7753f3aabb2928d1ea40</v>
+        <v>e52d03fdea2d120ba10992adeccb50e3fe69fa198f4d91aea71dfb8a059530a8</v>
       </c>
     </row>
     <row r="142">
@@ -3230,7 +3230,7 @@
         <v>audioclip_sfx_h0200_jp.ab</v>
       </c>
       <c r="C142">
-        <v>677195</v>
+        <v>677181</v>
       </c>
       <c r="D142" t="str">
         <v>Stage_1</v>
@@ -3239,7 +3239,7 @@
         <v>0</v>
       </c>
       <c r="F142" t="str">
-        <v>7db247d6fabc5ce716729393c6c9a5b645a97cdc9720e11459f7befcfd4e045d</v>
+        <v>46a9b6e7b367143d7c93a40203a96f3762bb025aaa3210cbedca98cf035596e4</v>
       </c>
     </row>
     <row r="143">
@@ -3250,7 +3250,7 @@
         <v>audioclip_sfx_h0201_jp.ab</v>
       </c>
       <c r="C143">
-        <v>810576</v>
+        <v>810554</v>
       </c>
       <c r="D143" t="str">
         <v>Stage_1</v>
@@ -3259,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="F143" t="str">
-        <v>0090c7ade6da67f5b74141a06485a49c378a240de417a4c22636d124121b76de</v>
+        <v>e55b1b860f930f98349096e1d209d09c7c3ab74182aa34d791496fc3eb907ddd</v>
       </c>
     </row>
     <row r="144">
@@ -3270,7 +3270,7 @@
         <v>audioclip_sfx_h0203_jp.ab</v>
       </c>
       <c r="C144">
-        <v>967998</v>
+        <v>968039</v>
       </c>
       <c r="D144" t="str">
         <v>Stage_1</v>
@@ -3279,7 +3279,7 @@
         <v>0</v>
       </c>
       <c r="F144" t="str">
-        <v>217be4bf21d335cb71b55fdb4d31a9a7279d445f0fe85f9cf24c1bef1caf62d4</v>
+        <v>b57f33c7da720489adddf795d5fbb7f332b3c88353ddb19cad42d8734b6b7ba4</v>
       </c>
     </row>
     <row r="145">
@@ -3290,7 +3290,7 @@
         <v>audioclip_sfx_h0208_jp.ab</v>
       </c>
       <c r="C145">
-        <v>774135</v>
+        <v>774146</v>
       </c>
       <c r="D145" t="str">
         <v>Stage_1</v>
@@ -3299,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="F145" t="str">
-        <v>bbfa58683b15e0f13ff91790ddb3e3c89a40a836a21fb5db765bf26c9ced5e65</v>
+        <v>71bdd752d3746c6a48ccd702cafa06037f97581739fe7c76c4154cade2dc759d</v>
       </c>
     </row>
     <row r="146">
@@ -3310,7 +3310,7 @@
         <v>audioclip_sfx_h0209_jp.ab</v>
       </c>
       <c r="C146">
-        <v>1046540</v>
+        <v>1046544</v>
       </c>
       <c r="D146" t="str">
         <v>Stage_1</v>
@@ -3319,7 +3319,7 @@
         <v>0</v>
       </c>
       <c r="F146" t="str">
-        <v>1760ef2f6ba0fbbeed78e2a625e68724d36c698bdc6b96860edd7ef5db67eaa0</v>
+        <v>a5e9c86fd2cb4f0bfea97a38494c4edb089fc9d2d020179ef78eff0295cbc93a</v>
       </c>
     </row>
     <row r="147">
@@ -3330,7 +3330,7 @@
         <v>audioclip_sfx_h0210_jp.ab</v>
       </c>
       <c r="C147">
-        <v>976467</v>
+        <v>976449</v>
       </c>
       <c r="D147" t="str">
         <v>Stage_1</v>
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="F147" t="str">
-        <v>536a0eafaf49dac589a428dc01427c474cbd6c2e042cd154302895731591cd9e</v>
+        <v>9caf2d6eb94e38ed6fecb0ae5ebdb2b3256161bef53a53f5f5a2e125fd3f8de2</v>
       </c>
     </row>
     <row r="148">
@@ -3350,7 +3350,7 @@
         <v>audioclip_sfx_h0213_jp.ab</v>
       </c>
       <c r="C148">
-        <v>1108279</v>
+        <v>1108258</v>
       </c>
       <c r="D148" t="str">
         <v>Stage_1</v>
@@ -3359,7 +3359,7 @@
         <v>0</v>
       </c>
       <c r="F148" t="str">
-        <v>c57d9f9aa94faeeccc5dc0e8541f7bbb2c05bee5cce4211df599ac14eb66f8bf</v>
+        <v>5eb879e63431404c76f279aab72dff424a2c91af88a0bf3eabd86b4a730c8ebe</v>
       </c>
     </row>
     <row r="149">
@@ -3370,7 +3370,7 @@
         <v>audioclip_sfx_h0215_jp.ab</v>
       </c>
       <c r="C149">
-        <v>1225722</v>
+        <v>1225758</v>
       </c>
       <c r="D149" t="str">
         <v>Stage_1</v>
@@ -3379,7 +3379,7 @@
         <v>0</v>
       </c>
       <c r="F149" t="str">
-        <v>454d5ab9e2b2cfea6ab7d81449d4bbe2cf8b238a5ce38f76c4b2f3b539fef92e</v>
+        <v>22e8335eb2b6a3254ce9e5f5c355492d42287e333a6de467b5ba87a53f1956db</v>
       </c>
     </row>
     <row r="150">
@@ -3390,7 +3390,7 @@
         <v>audioclip_sfx_h0216_jp.ab</v>
       </c>
       <c r="C150">
-        <v>1220952</v>
+        <v>1220959</v>
       </c>
       <c r="D150" t="str">
         <v>Stage_1</v>
@@ -3399,7 +3399,7 @@
         <v>0</v>
       </c>
       <c r="F150" t="str">
-        <v>78e22da6aa4588298544512d6e7e380dc1a2a37718643ffaf3167986358f2f99</v>
+        <v>6c86c1954d9fbde5609178ada15b5812a401eb5fcc36c2ef35cd4986c7627e21</v>
       </c>
     </row>
     <row r="151">
@@ -3410,7 +3410,7 @@
         <v>audioclip_sfx_h0217_jp.ab</v>
       </c>
       <c r="C151">
-        <v>974982</v>
+        <v>974984</v>
       </c>
       <c r="D151" t="str">
         <v>Stage_1</v>
@@ -3419,7 +3419,7 @@
         <v>0</v>
       </c>
       <c r="F151" t="str">
-        <v>b7c139fa195fdf9b40fd7e1c8e5d76ea88b3b6da8b86114b5e60509a961f0c08</v>
+        <v>89c28f8c0e4a2cfc807eb4bcbf3b39f34e5ee94ecb92f167daf3af597f3994d3</v>
       </c>
     </row>
     <row r="152">
@@ -3430,7 +3430,7 @@
         <v>audioclip_sfx_h0219_jp.ab</v>
       </c>
       <c r="C152">
-        <v>977561</v>
+        <v>977563</v>
       </c>
       <c r="D152" t="str">
         <v>Stage_1</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="F152" t="str">
-        <v>4acb3205b612aea769180c93ae17da31d2cfe494199e0777510a443e2f35e05e</v>
+        <v>23cb53f13786af0a6dbff5e78bb77271170f100782c37e453840d61151f026d9</v>
       </c>
     </row>
     <row r="153">
@@ -3450,7 +3450,7 @@
         <v>audioclip_sfx_h0220_jp.ab</v>
       </c>
       <c r="C153">
-        <v>1002159</v>
+        <v>1002166</v>
       </c>
       <c r="D153" t="str">
         <v>Stage_1</v>
@@ -3459,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="F153" t="str">
-        <v>cf822740486ee3d6f60df636628b4fdd55d0e35452d4aa071ad977b4e435f9a9</v>
+        <v>58b375c5bd48c37af85be0a2e1b7fc60ed0d87fb9a308a8a4741f1e497475ab5</v>
       </c>
     </row>
     <row r="154">
@@ -3470,7 +3470,7 @@
         <v>audioclip_sfx_h0221_jp.ab</v>
       </c>
       <c r="C154">
-        <v>1054460</v>
+        <v>1054375</v>
       </c>
       <c r="D154" t="str">
         <v>Stage_1</v>
@@ -3479,7 +3479,7 @@
         <v>0</v>
       </c>
       <c r="F154" t="str">
-        <v>86d343e001bdcd963f79a4918f42764020840e169a4127babd4d256b02f0b5b4</v>
+        <v>366a72acd0eb98f5996f9ffed92b6bbeffc6aabeeb66deb21fa4f2d58bb5f867</v>
       </c>
     </row>
     <row r="155">
@@ -3490,7 +3490,7 @@
         <v>audioclip_sfx_h0224_jp.ab</v>
       </c>
       <c r="C155">
-        <v>1031309</v>
+        <v>1031385</v>
       </c>
       <c r="D155" t="str">
         <v>Stage_1</v>
@@ -3499,7 +3499,7 @@
         <v>0</v>
       </c>
       <c r="F155" t="str">
-        <v>76f90c57f1b3b8f107a6a52a4eab7e7733623a4c6adcfdaafa0b2b22298922c7</v>
+        <v>d6e4a1edd111d349ae269395ed196e67d9773a6c6a9f568651b3854eeeab9bc0</v>
       </c>
     </row>
     <row r="156">
@@ -3510,7 +3510,7 @@
         <v>audioclip_sfx_h0226_jp.ab</v>
       </c>
       <c r="C156">
-        <v>1134470</v>
+        <v>1134539</v>
       </c>
       <c r="D156" t="str">
         <v>Stage_1</v>
@@ -3519,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="F156" t="str">
-        <v>bd55288f714ffa1a604086bc4c89238afb248fd2421509659d915715637fa8b2</v>
+        <v>558047ab53ca7c7865f2d7c6dd31a88aefb6cffbfb04878361d3f2d015ebfebb</v>
       </c>
     </row>
     <row r="157">
@@ -3530,7 +3530,7 @@
         <v>audioclip_sfx_h0227_jp.ab</v>
       </c>
       <c r="C157">
-        <v>1040337</v>
+        <v>1040402</v>
       </c>
       <c r="D157" t="str">
         <v>Stage_1</v>
@@ -3539,7 +3539,7 @@
         <v>0</v>
       </c>
       <c r="F157" t="str">
-        <v>6e35359d3dc746289c40e93c7448ff3399ff5d161e36365509b2cc69bc744f7d</v>
+        <v>88c387ff13f2d4095fd7adab453b54669b437e49055814cde2d43f11be4ad81e</v>
       </c>
     </row>
     <row r="158">
@@ -3550,7 +3550,7 @@
         <v>audioclip_sfx_h0230_jp.ab</v>
       </c>
       <c r="C158">
-        <v>1022961</v>
+        <v>1022964</v>
       </c>
       <c r="D158" t="str">
         <v>Stage_1</v>
@@ -3559,7 +3559,7 @@
         <v>0</v>
       </c>
       <c r="F158" t="str">
-        <v>cb87d87d276794017e98533f2d373f1db0f9fe3c0b84632c170df759557928ac</v>
+        <v>1a8d5d67a223593b4069765ff9c63254220f36671c226880077cd5b27d0cafd0</v>
       </c>
     </row>
     <row r="159">
@@ -3570,7 +3570,7 @@
         <v>audioclip_sfx_h0232_jp.ab</v>
       </c>
       <c r="C159">
-        <v>1390239</v>
+        <v>1390266</v>
       </c>
       <c r="D159" t="str">
         <v>Stage_1</v>
@@ -3579,7 +3579,7 @@
         <v>0</v>
       </c>
       <c r="F159" t="str">
-        <v>b7baecc4fcf1876a72169d231b584b62a7febaa95667f0fe67ad0ae7216a78f1</v>
+        <v>79795caa65c37a476a94758c480f8152af98e5791fbe011bbf4c7a03070070d5</v>
       </c>
     </row>
     <row r="160">
@@ -3590,7 +3590,7 @@
         <v>audioclip_sfx_h0233_jp.ab</v>
       </c>
       <c r="C160">
-        <v>1911214</v>
+        <v>1911251</v>
       </c>
       <c r="D160" t="str">
         <v>Stage_1</v>
@@ -3599,7 +3599,7 @@
         <v>0</v>
       </c>
       <c r="F160" t="str">
-        <v>22edb1607a5d8c1b1b848c39fad542cfee030ba5a858f71ce73abb226e7769da</v>
+        <v>62cc7e60803ca42cd71dc66a39a2dbc930e5a0e1d3a29af38133d6478e35dbb5</v>
       </c>
     </row>
     <row r="161">
@@ -3610,7 +3610,7 @@
         <v>audioclip_sfx_h0234_jp.ab</v>
       </c>
       <c r="C161">
-        <v>1859302</v>
+        <v>1859306</v>
       </c>
       <c r="D161" t="str">
         <v>Stage_1</v>
@@ -3619,7 +3619,7 @@
         <v>0</v>
       </c>
       <c r="F161" t="str">
-        <v>7dbd7a286d2e447bdca0849f6b1befed5583672236f82c8b1b68b31f5df11bd3</v>
+        <v>ac618e63887ad37617e00d333e5b5efa30642ade9d3d1e9a87a97073e02e3e2d</v>
       </c>
     </row>
     <row r="162">
@@ -3630,7 +3630,7 @@
         <v>audioclip_sfx_h0235_jp.ab</v>
       </c>
       <c r="C162">
-        <v>2384177</v>
+        <v>2384179</v>
       </c>
       <c r="D162" t="str">
         <v>Stage_1</v>
@@ -3639,7 +3639,7 @@
         <v>0</v>
       </c>
       <c r="F162" t="str">
-        <v>6946e74191b3cba83ad0a1e57e00805cfee6ac3de31b62e38a1487950dfcb4ab</v>
+        <v>7c2c19b4bbf93d4fcc9754a14eb44c1695229be25fd5838e8b3eaa3abcaf86f4</v>
       </c>
     </row>
     <row r="163">
@@ -3650,7 +3650,7 @@
         <v>audioclip_sfx_h0236_jp.ab</v>
       </c>
       <c r="C163">
-        <v>2245975</v>
+        <v>2245969</v>
       </c>
       <c r="D163" t="str">
         <v>Stage_1</v>
@@ -3659,7 +3659,7 @@
         <v>0</v>
       </c>
       <c r="F163" t="str">
-        <v>aff7002ec327dea73b14b732b71b51102f006c7bc536f8d2eaafbdb8af526711</v>
+        <v>0584501a3b50ddae468236c6dad07e1441568fc285bc20f2eab35bbc919719c8</v>
       </c>
     </row>
     <row r="164">
@@ -3670,7 +3670,7 @@
         <v>audioclip_sfx_h0237_jp.ab</v>
       </c>
       <c r="C164">
-        <v>2431132</v>
+        <v>2431046</v>
       </c>
       <c r="D164" t="str">
         <v>Stage_1</v>
@@ -3679,7 +3679,7 @@
         <v>0</v>
       </c>
       <c r="F164" t="str">
-        <v>4fa53f95c47734fb4c441e1343aa0b0c20b0683fbac31c6e79e4715453aab59c</v>
+        <v>9461aa37c70c0efa528e1ac7b5e16f6bbd22e649f5811b7c38ccedcb1e2f75d9</v>
       </c>
     </row>
     <row r="165">
@@ -3690,7 +3690,7 @@
         <v>audioclip_sfx_h0238_jp.ab</v>
       </c>
       <c r="C165">
-        <v>867922</v>
+        <v>867889</v>
       </c>
       <c r="D165" t="str">
         <v>Stage_1</v>
@@ -3699,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="F165" t="str">
-        <v>dd407d7f143de4db0455f9f5fafb92cea85bb015b84aa8a88187e7aa9521959e</v>
+        <v>7f3f867c29668c32fe5d6e217659e1876b4312f428a7dc22b0642d8399fdce42</v>
       </c>
     </row>
     <row r="166">
@@ -3710,7 +3710,7 @@
         <v>audioclip_sfx_h0239_jp.ab</v>
       </c>
       <c r="C166">
-        <v>5844651</v>
+        <v>5844765</v>
       </c>
       <c r="D166" t="str">
         <v>Stage_1</v>
@@ -3719,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="F166" t="str">
-        <v>5ecbb7f695b47f60808c7da0b568b60580ab57403df3b3eca4909cfd43248975</v>
+        <v>004b5d6eeedc4bb0bc41f66cf7f8f763ffe3698e4f64f29063e08ac4fa0850c4</v>
       </c>
     </row>
     <row r="167">
@@ -3730,7 +3730,7 @@
         <v>audioclip_sfx_h0240_jp.ab</v>
       </c>
       <c r="C167">
-        <v>924349</v>
+        <v>924415</v>
       </c>
       <c r="D167" t="str">
         <v>Stage_1</v>
@@ -3739,7 +3739,7 @@
         <v>0</v>
       </c>
       <c r="F167" t="str">
-        <v>d6cacfb89ee8d43ee5b1a873e0d46863a69766df01c69031b8b31e7e86cb55b8</v>
+        <v>3f2eebfeb6acfebc775abff08b7f79a7882b28555c43078c7a6602db3f37e9e3</v>
       </c>
     </row>
     <row r="168">
@@ -3750,7 +3750,7 @@
         <v>audioclip_sfx_h0241_jp.ab</v>
       </c>
       <c r="C168">
-        <v>1125057</v>
+        <v>1125091</v>
       </c>
       <c r="D168" t="str">
         <v>Stage_1</v>
@@ -3759,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="F168" t="str">
-        <v>6aa95d4b324419af4caf29cf9c68b7d98bd1fd822c1860dd6a4a468137a1a3b3</v>
+        <v>8bc4041926e9475db31eb0d67b78671e22a9e14be0e2b0ce31eb95860174d7e7</v>
       </c>
     </row>
     <row r="169">
@@ -3770,7 +3770,7 @@
         <v>audioclip_sfx_h0243_jp.ab</v>
       </c>
       <c r="C169">
-        <v>608160</v>
+        <v>608168</v>
       </c>
       <c r="D169" t="str">
         <v>Stage_1</v>
@@ -3779,7 +3779,7 @@
         <v>0</v>
       </c>
       <c r="F169" t="str">
-        <v>1acca5d8814bbfc23a6b51bcfa7f59958e1032a45a4c0f8ce08dcc35f3c19476</v>
+        <v>c3b841bbff983659e1badddd222bb4424b93a5a08f585ece4227308a64b4a9e9</v>
       </c>
     </row>
     <row r="170">
@@ -3790,7 +3790,7 @@
         <v>audioclip_sfx_h0244_jp.ab</v>
       </c>
       <c r="C170">
-        <v>1110559</v>
+        <v>1110580</v>
       </c>
       <c r="D170" t="str">
         <v>Stage_1</v>
@@ -3799,7 +3799,7 @@
         <v>0</v>
       </c>
       <c r="F170" t="str">
-        <v>155e713aec39971edc4bf23abd4297404d9f05b629382c37889994db8c37e1a1</v>
+        <v>ec8fc9356ab9717be921cb2b06a14309eff5b1ebac14893b114ee72aee2106d9</v>
       </c>
     </row>
     <row r="171">
@@ -3810,7 +3810,7 @@
         <v>audioclip_sfx_h0245_jp.ab</v>
       </c>
       <c r="C171">
-        <v>1354431</v>
+        <v>1354476</v>
       </c>
       <c r="D171" t="str">
         <v>Stage_1</v>
@@ -3819,7 +3819,7 @@
         <v>0</v>
       </c>
       <c r="F171" t="str">
-        <v>071ee9f43965eb6ca632db3bbf8478ea81286141004c84821878d850d78f283e</v>
+        <v>b5c33e093a27e13f2a971856786aafa80a4e0eac338272f3c062f18dee52f739</v>
       </c>
     </row>
     <row r="172">
@@ -3830,7 +3830,7 @@
         <v>audioclip_sfx_h0247_jp.ab</v>
       </c>
       <c r="C172">
-        <v>939767</v>
+        <v>939776</v>
       </c>
       <c r="D172" t="str">
         <v>Stage_1</v>
@@ -3839,7 +3839,7 @@
         <v>0</v>
       </c>
       <c r="F172" t="str">
-        <v>c563c1d35fba9a7bfd0bd8c801cfa6680ddb52ceda9bd90e9ddfddda47463aa4</v>
+        <v>7a4b8c77808f64f7741886fb8deb74e325b80bee4560a70c0e7b2d0d16898e24</v>
       </c>
     </row>
     <row r="173">
@@ -3850,7 +3850,7 @@
         <v>audioclip_sfx_h0248_jp.ab</v>
       </c>
       <c r="C173">
-        <v>1234718</v>
+        <v>1234681</v>
       </c>
       <c r="D173" t="str">
         <v>Stage_1</v>
@@ -3859,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="F173" t="str">
-        <v>17ef73fed5ee585179a5649820d2471d9cbac18000667f2a621bc3cda3621652</v>
+        <v>63fc9d6e19b2f543e08a07f2c58356cae1faa2791e061d047bda0e828fdd17ae</v>
       </c>
     </row>
     <row r="174">
@@ -3870,7 +3870,7 @@
         <v>audioclip_sfx_h0249_jp.ab</v>
       </c>
       <c r="C174">
-        <v>899106</v>
+        <v>899116</v>
       </c>
       <c r="D174" t="str">
         <v>Stage_1</v>
@@ -3879,7 +3879,7 @@
         <v>0</v>
       </c>
       <c r="F174" t="str">
-        <v>cef22b20458d9a8546073050e97baf61aaf1311bb9b0d9a32680d3fecefd92ac</v>
+        <v>a0901dced452dfe825ab300bd898035e6e0f9294b7d8ccb29cf4ec34636b3a85</v>
       </c>
     </row>
     <row r="175">
@@ -3890,7 +3890,7 @@
         <v>audioclip_sfx_h0253_jp.ab</v>
       </c>
       <c r="C175">
-        <v>1011101</v>
+        <v>1011167</v>
       </c>
       <c r="D175" t="str">
         <v>Stage_1</v>
@@ -3899,7 +3899,7 @@
         <v>0</v>
       </c>
       <c r="F175" t="str">
-        <v>48c338b37ad6c5bb8a451791d71d64b8837d013f37472934d328af59f84c38a7</v>
+        <v>5e2f60889e26a8d12b25f80ed9f81e8735a35679fd4e2e7d89b1f025c548bd95</v>
       </c>
     </row>
     <row r="176">
@@ -3910,7 +3910,7 @@
         <v>audioclip_sfx_h0255_jp.ab</v>
       </c>
       <c r="C176">
-        <v>983158</v>
+        <v>983177</v>
       </c>
       <c r="D176" t="str">
         <v>Stage_1</v>
@@ -3919,7 +3919,7 @@
         <v>0</v>
       </c>
       <c r="F176" t="str">
-        <v>a7ff5d0f98a1dd62ae5190e11716ac0239aaa57ca7a2f727ee62edbc04b9b165</v>
+        <v>4552864ef2677297a725dddab03d56b16aa816d7736e17de628e6463d3d026d6</v>
       </c>
     </row>
     <row r="177">
@@ -3930,7 +3930,7 @@
         <v>audioclip_sfx_h0256_jp.ab</v>
       </c>
       <c r="C177">
-        <v>1317836</v>
+        <v>1317826</v>
       </c>
       <c r="D177" t="str">
         <v>Stage_1</v>
@@ -3939,7 +3939,7 @@
         <v>0</v>
       </c>
       <c r="F177" t="str">
-        <v>4dd2dbeafa47a9126d648ae1e287b45ced3859c8786957c9ed1345ac5e67234e</v>
+        <v>d63c4843f9d4b1a8e689916fe3dd1f673ed947410ff8a492c1f49437b1f4c1a6</v>
       </c>
     </row>
     <row r="178">
@@ -3950,7 +3950,7 @@
         <v>audioclip_sfx_h0257_jp.ab</v>
       </c>
       <c r="C178">
-        <v>1131207</v>
+        <v>1131166</v>
       </c>
       <c r="D178" t="str">
         <v>Stage_1</v>
@@ -3959,7 +3959,7 @@
         <v>0</v>
       </c>
       <c r="F178" t="str">
-        <v>ce2a97ebb0ccff50b76fba38d4287320ac6ce63b15c681a3204a1f396fdffc94</v>
+        <v>e05000ce53dba82ccbd944098335d5034f108cca3844aecd952c8377122d47ce</v>
       </c>
     </row>
     <row r="179">
@@ -3970,7 +3970,7 @@
         <v>audioclip_sfx_h0259_jp.ab</v>
       </c>
       <c r="C179">
-        <v>1446712</v>
+        <v>1446658</v>
       </c>
       <c r="D179" t="str">
         <v>Stage_1</v>
@@ -3979,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="F179" t="str">
-        <v>54c06eff4ff4c3553541d47dc4995d0832ff5e51c2428d1a0c8f08e330568659</v>
+        <v>13fa726310883c9c09f86f60e4578b0fc0483b1f46e12aa37c00a140ba3f312d</v>
       </c>
     </row>
     <row r="180">
@@ -3990,7 +3990,7 @@
         <v>audioclip_sfx_h0261_jp.ab</v>
       </c>
       <c r="C180">
-        <v>1220852</v>
+        <v>1220858</v>
       </c>
       <c r="D180" t="str">
         <v>Stage_1</v>
@@ -3999,7 +3999,7 @@
         <v>0</v>
       </c>
       <c r="F180" t="str">
-        <v>d068cdce37e2f25589c80a88251e5f20a3f1479718192a8938d37f4c436f9de2</v>
+        <v>bb62ee7542b1cef843a7c89acc8c67809536e3301e4363147e77d354224d11b3</v>
       </c>
     </row>
     <row r="181">
@@ -4010,7 +4010,7 @@
         <v>audioclip_sfx_h0262_jp.ab</v>
       </c>
       <c r="C181">
-        <v>1140808</v>
+        <v>1140806</v>
       </c>
       <c r="D181" t="str">
         <v>Stage_1</v>
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="F181" t="str">
-        <v>25d7d3a23455f14c5e75dc7b70b7d31503c90f0d94c29436174fa96fb869a2a5</v>
+        <v>9a224462af69cd85529649cc0e87dfa7d758b16782d8623802baa1b9a40ae4ba</v>
       </c>
     </row>
     <row r="182">
@@ -4030,7 +4030,7 @@
         <v>audioclip_sfx_h0264_jp.ab</v>
       </c>
       <c r="C182">
-        <v>973033</v>
+        <v>973011</v>
       </c>
       <c r="D182" t="str">
         <v>Stage_1</v>
@@ -4039,7 +4039,7 @@
         <v>0</v>
       </c>
       <c r="F182" t="str">
-        <v>0448a14211f66d92c46f8d0430373d1b36713c5875506be5502af3cf690292ac</v>
+        <v>e5c3adee4c2101215cd7b6d17b87087c0a8fde49898eb8ff5eeaff198c058046</v>
       </c>
     </row>
     <row r="183">
@@ -4050,7 +4050,7 @@
         <v>audioclip_sfx_h0265_jp.ab</v>
       </c>
       <c r="C183">
-        <v>1201262</v>
+        <v>1201268</v>
       </c>
       <c r="D183" t="str">
         <v>Stage_1</v>
@@ -4059,7 +4059,7 @@
         <v>0</v>
       </c>
       <c r="F183" t="str">
-        <v>36b01de1a2b39e0f7de44d7edc242d5029eb8cac21ed3a33604ec185dc118d8a</v>
+        <v>f6c808926aa525de36191e24ba0cda7fef489e249d50748bb3f0f2995ad4b949</v>
       </c>
     </row>
     <row r="184">
@@ -4070,7 +4070,7 @@
         <v>audioclip_sfx_h0266_jp.ab</v>
       </c>
       <c r="C184">
-        <v>1292356</v>
+        <v>1292329</v>
       </c>
       <c r="D184" t="str">
         <v>Stage_1</v>
@@ -4079,7 +4079,7 @@
         <v>0</v>
       </c>
       <c r="F184" t="str">
-        <v>585c7fcd0fe3b15fc204e0f74dbd7c90ca5ee1b899777f0a277b3b578729a20e</v>
+        <v>03e67759683411c6df3b8a01f1ce2acb5d342adecf9e50213e795aba52f6dd5b</v>
       </c>
     </row>
     <row r="185">
@@ -4090,7 +4090,7 @@
         <v>audioclip_sfx_h0268_jp.ab</v>
       </c>
       <c r="C185">
-        <v>1234505</v>
+        <v>1234454</v>
       </c>
       <c r="D185" t="str">
         <v>Stage_1</v>
@@ -4099,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="F185" t="str">
-        <v>30be21d1ba7b9fdf687f1625c700051c4f08754991a59be3a4ca26455124eebe</v>
+        <v>2c95d47ea417e0243b1cc0893a1856b59e89046075f04464cb99f7a51cb14896</v>
       </c>
     </row>
     <row r="186">
@@ -4110,7 +4110,7 @@
         <v>audioclip_sfx_h0270_jp.ab</v>
       </c>
       <c r="C186">
-        <v>1391873</v>
+        <v>1391808</v>
       </c>
       <c r="D186" t="str">
         <v>Stage_1</v>
@@ -4119,7 +4119,7 @@
         <v>0</v>
       </c>
       <c r="F186" t="str">
-        <v>97d24d0fb39e9c99882381fffa21f2b65603391fa5f4b4bfbc96e43926731f38</v>
+        <v>2ccc8e169cb64878f528a56e75e7a04fcdb0338ac2f2cfb10f479019e2ba0c55</v>
       </c>
     </row>
     <row r="187">
@@ -4130,7 +4130,7 @@
         <v>audioclip_sfx_h0271_jp.ab</v>
       </c>
       <c r="C187">
-        <v>1584336</v>
+        <v>1584314</v>
       </c>
       <c r="D187" t="str">
         <v>Stage_1</v>
@@ -4139,7 +4139,7 @@
         <v>0</v>
       </c>
       <c r="F187" t="str">
-        <v>fe6cb7b3ffa1d73d7394443c9ba60ca8d28358c796d1588f9a064e8a8db621f6</v>
+        <v>bae8423fa0bf9033ac6803b7780d7e134f6e3c5535ca93c8c4fa4b1ddd6e0c58</v>
       </c>
     </row>
     <row r="188">
@@ -4150,7 +4150,7 @@
         <v>audioclip_sfx_h0273_jp.ab</v>
       </c>
       <c r="C188">
-        <v>1372808</v>
+        <v>1372816</v>
       </c>
       <c r="D188" t="str">
         <v>Stage_1</v>
@@ -4159,7 +4159,7 @@
         <v>0</v>
       </c>
       <c r="F188" t="str">
-        <v>5fff5d907859c6321942ad5db651650d340e8a3ff72cd16eb8ec3f2c60d41c6c</v>
+        <v>fd90b170daf42558de551e28aeef9aa740f0f128eb825ef38a1eada66dd64a78</v>
       </c>
     </row>
     <row r="189">
@@ -4170,7 +4170,7 @@
         <v>audioclip_sfx_h0274_jp.ab</v>
       </c>
       <c r="C189">
-        <v>1539698</v>
+        <v>1539762</v>
       </c>
       <c r="D189" t="str">
         <v>Stage_1</v>
@@ -4179,7 +4179,7 @@
         <v>0</v>
       </c>
       <c r="F189" t="str">
-        <v>1af040bd1788fa17e98eb02c87f15e5ada55e3a2e5a70b2e56b505e3c5d85090</v>
+        <v>532ec3d831c37f88d1618e105002895ad8e6a1e7a9bcc12c8fb5cc17801d3b22</v>
       </c>
     </row>
     <row r="190">
@@ -4190,7 +4190,7 @@
         <v>audioclip_sfx_h3190_jp.ab</v>
       </c>
       <c r="C190">
-        <v>274141</v>
+        <v>274144</v>
       </c>
       <c r="D190" t="str">
         <v>Stage_1</v>
@@ -4199,7 +4199,7 @@
         <v>0</v>
       </c>
       <c r="F190" t="str">
-        <v>9eb4ecd3f3e085f0324fe131b664b0dd4662b72c3dc2fcf9d07102bf21c32b72</v>
+        <v>ba5bd6dc62387f130eaecd28ac8316fccba26967d7fd29b452e924065f6673f9</v>
       </c>
     </row>
     <row r="191">
@@ -4210,7 +4210,7 @@
         <v>audioclip_sfx_h3401_jp.ab</v>
       </c>
       <c r="C191">
-        <v>220278</v>
+        <v>220294</v>
       </c>
       <c r="D191" t="str">
         <v>Stage_1</v>
@@ -4219,7 +4219,7 @@
         <v>0</v>
       </c>
       <c r="F191" t="str">
-        <v>bfd1e4e5ecfbe76670e0cbcf8e995505ad8e5878e9a9dd0d01716b8b487c88c9</v>
+        <v>0bb50ec4cb8feea3fc49195737f6cdade648041a7be8c64637927d57b3bc694e</v>
       </c>
     </row>
     <row r="192">
@@ -4230,7 +4230,7 @@
         <v>audioclip_sfx_m0011_jp.ab</v>
       </c>
       <c r="C192">
-        <v>95939</v>
+        <v>95941</v>
       </c>
       <c r="D192" t="str">
         <v>Stage_1</v>
@@ -4239,7 +4239,7 @@
         <v>0</v>
       </c>
       <c r="F192" t="str">
-        <v>3b4b8786386c69943f0f359fc0ea0779db199f5f19ebc3f5248302686bd825f1</v>
+        <v>e87301d01e417419853558e8e2a0722aa4087161fbc845d9344f4c9272e0e9cf</v>
       </c>
     </row>
     <row r="193">
@@ -4250,7 +4250,7 @@
         <v>audioclip_sfx_r0034_jp.ab</v>
       </c>
       <c r="C193">
-        <v>1390721</v>
+        <v>1390751</v>
       </c>
       <c r="D193" t="str">
         <v>Stage_1</v>
@@ -4259,7 +4259,7 @@
         <v>0</v>
       </c>
       <c r="F193" t="str">
-        <v>4f71edf4bbd4c86e2d9f0bb49f2ef5275cd707aec9e30de127252d2bc84be384</v>
+        <v>7ca6307107308eada91f00e5b188051013037fb08fd4ff88dd189bf5d761d568</v>
       </c>
     </row>
     <row r="194">
@@ -4270,7 +4270,7 @@
         <v>audioclip_sfx_r0160_jp.ab</v>
       </c>
       <c r="C194">
-        <v>4141829</v>
+        <v>4141853</v>
       </c>
       <c r="D194" t="str">
         <v>Stage_1</v>
@@ -4279,7 +4279,7 @@
         <v>0</v>
       </c>
       <c r="F194" t="str">
-        <v>53250ee3484ea26304c0a7fd112d551545735fdbe124452cac32da923cf3eccb</v>
+        <v>31a57aea69da2eb94bc13277875412012bdf5f4a5c34980feb777789daaa9324</v>
       </c>
     </row>
     <row r="195">
@@ -4290,7 +4290,7 @@
         <v>audioclip_sfx_r0173_jp.ab</v>
       </c>
       <c r="C195">
-        <v>1438364</v>
+        <v>1438329</v>
       </c>
       <c r="D195" t="str">
         <v>Stage_1</v>
@@ -4299,7 +4299,7 @@
         <v>0</v>
       </c>
       <c r="F195" t="str">
-        <v>9ecc97c123ddd9aacf2f6ba002eabbbdf3b77e8dd505913f1ed17f488c97a29a</v>
+        <v>8cd6d21234e7e5ae58d8f6f23c1cc9664fbba1badb8a075d21cba2a6c69bb0cf</v>
       </c>
     </row>
     <row r="196">
@@ -4310,7 +4310,7 @@
         <v>audioclip_sfx_r0205_jp.ab</v>
       </c>
       <c r="C196">
-        <v>1066358</v>
+        <v>1066400</v>
       </c>
       <c r="D196" t="str">
         <v>Stage_1</v>
@@ -4319,7 +4319,7 @@
         <v>0</v>
       </c>
       <c r="F196" t="str">
-        <v>c92555b7120ac235346b35f30da6753a28158b9840ca72b3cac3d7a23cecdfc2</v>
+        <v>9114e83fdedcd821019f065e2ddf34c49ca66262176a93b8bcdc46f9de3844d6</v>
       </c>
     </row>
     <row r="197">
@@ -4330,7 +4330,7 @@
         <v>audioclip_sfx_t0017_jp.ab</v>
       </c>
       <c r="C197">
-        <v>883186</v>
+        <v>883212</v>
       </c>
       <c r="D197" t="str">
         <v>Stage_1</v>
@@ -4339,7 +4339,7 @@
         <v>0</v>
       </c>
       <c r="F197" t="str">
-        <v>b70487cba84494f69cee47573fab52e375c8bd92af04044cfdc5818cbe84153d</v>
+        <v>bd7d233702f81e1ec9935e8123a8d9d2247df81dad54747af2d1fed433067d51</v>
       </c>
     </row>
     <row r="198">
@@ -4350,7 +4350,7 @@
         <v>audioclip_sfx_t0026_jp.ab</v>
       </c>
       <c r="C198">
-        <v>903966</v>
+        <v>903935</v>
       </c>
       <c r="D198" t="str">
         <v>Stage_1</v>
@@ -4359,7 +4359,7 @@
         <v>0</v>
       </c>
       <c r="F198" t="str">
-        <v>2e9997e9cbd488446ab8e1dd429e313dc921fd5412e0eab5332297122bd1ca26</v>
+        <v>aacc490472b06835e6dd21fe5e78f5c3951b677a3b4684583a50a933aa9f10ac</v>
       </c>
     </row>
     <row r="199">
@@ -4370,7 +4370,7 @@
         <v>audioclip_sfx_t0027_jp.ab</v>
       </c>
       <c r="C199">
-        <v>1396255</v>
+        <v>1396284</v>
       </c>
       <c r="D199" t="str">
         <v>Stage_1</v>
@@ -4379,7 +4379,7 @@
         <v>0</v>
       </c>
       <c r="F199" t="str">
-        <v>b15bdd7b76908dfea388b149103cb7a3bb8ddedb9d0b66e61a9bbdb4ed76c6bb</v>
+        <v>b022aa0ac21aea81edd179afbeed4f5fdb9754bc06c4fe483ac5a766c6ab2936</v>
       </c>
     </row>
     <row r="200">
@@ -4390,7 +4390,7 @@
         <v>audioclip_sfx_t0032_jp.ab</v>
       </c>
       <c r="C200">
-        <v>995097</v>
+        <v>995113</v>
       </c>
       <c r="D200" t="str">
         <v>Stage_1</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="F200" t="str">
-        <v>ba41a2a25880e9c9c32992a8d12134f3417542a623ef5796438664487de2dd84</v>
+        <v>c571bdddbf82f9a5cedabc53814749b74d5606014bc4b0b8e5bf7c3e8d3623c9</v>
       </c>
     </row>
     <row r="201">
@@ -4410,7 +4410,7 @@
         <v>audioclip_sfx_t0033_jp.ab</v>
       </c>
       <c r="C201">
-        <v>1222455</v>
+        <v>1222415</v>
       </c>
       <c r="D201" t="str">
         <v>Stage_1</v>
@@ -4419,7 +4419,7 @@
         <v>0</v>
       </c>
       <c r="F201" t="str">
-        <v>63963c9efe4a35bd1f713e9096337f19fd65c782f6a42ffe70e44f4b05fc8e64</v>
+        <v>8c22572d3746bd8151b045186082268704a2e0cec82278fb4e9cde986e92d295</v>
       </c>
     </row>
     <row r="202">
@@ -4430,7 +4430,7 @@
         <v>audioclip_sfx_t0039_jp.ab</v>
       </c>
       <c r="C202">
-        <v>694991</v>
+        <v>695023</v>
       </c>
       <c r="D202" t="str">
         <v>Stage_1</v>
@@ -4439,7 +4439,7 @@
         <v>0</v>
       </c>
       <c r="F202" t="str">
-        <v>a2e4375cd3ec14e8de1240ada61ea4bd86a4168a0f7da338bdf3289a455ace8d</v>
+        <v>ae594d89400e7f4228220ebbae7c39fdc1a4950f1fcfd82be93a50a79f929040</v>
       </c>
     </row>
     <row r="203">
@@ -4450,7 +4450,7 @@
         <v>audioclip_sfx_t0044_jp.ab</v>
       </c>
       <c r="C203">
-        <v>3841908</v>
+        <v>3841923</v>
       </c>
       <c r="D203" t="str">
         <v>Stage_1</v>
@@ -4459,7 +4459,7 @@
         <v>0</v>
       </c>
       <c r="F203" t="str">
-        <v>91288f2a2fcc8e9d38b2516a9a0c2fc5655d888dbc2e871df9f5a39a9ffce823</v>
+        <v>1e807b3fa79e8fa3bc5c21bb3d709f48c51817bce97e89b199e0d1f013141efd</v>
       </c>
     </row>
     <row r="204">
@@ -4470,7 +4470,7 @@
         <v>audioclip_sfx_t0049_jp.ab</v>
       </c>
       <c r="C204">
-        <v>1950973</v>
+        <v>1950994</v>
       </c>
       <c r="D204" t="str">
         <v>Stage_1</v>
@@ -4479,7 +4479,7 @@
         <v>0</v>
       </c>
       <c r="F204" t="str">
-        <v>67f07047bfa16f49fbf64d39e131045c4144ba87694de4e7f992355b9c299351</v>
+        <v>f1d7a965b59e7af272684fd74e267500e248c68b053796dbb4cfa4a5c345ff2e</v>
       </c>
     </row>
     <row r="205">
@@ -4490,7 +4490,7 @@
         <v>audioclip_sfx_t0153_jp.ab</v>
       </c>
       <c r="C205">
-        <v>2974172</v>
+        <v>2974191</v>
       </c>
       <c r="D205" t="str">
         <v>Stage_1</v>
@@ -4499,7 +4499,7 @@
         <v>0</v>
       </c>
       <c r="F205" t="str">
-        <v>15235b6c85359ae5ee7667d431699e6c187e2ed3e93cf47a2a46349be09b4179</v>
+        <v>bf8c1f99e9b2abc29429af8604f84d9934cb0aa94e404f059954b587e4efbd9c</v>
       </c>
     </row>
     <row r="206">
@@ -4510,7 +4510,7 @@
         <v>audioclip_sfx_t0155_jp.ab</v>
       </c>
       <c r="C206">
-        <v>1992961</v>
+        <v>1992884</v>
       </c>
       <c r="D206" t="str">
         <v>Stage_1</v>
@@ -4519,7 +4519,7 @@
         <v>0</v>
       </c>
       <c r="F206" t="str">
-        <v>7c84d1990a85f4779a7eda24c273846c81610aa0fe2813d34e8445ed38b16296</v>
+        <v>743953c129a1fe5e9a05fa06d416decf330e89b30679a3d33497b67aaf55a419</v>
       </c>
     </row>
     <row r="207">
@@ -4530,7 +4530,7 @@
         <v>audioclip_sfx_t0156_jp.ab</v>
       </c>
       <c r="C207">
-        <v>2340708</v>
+        <v>2340702</v>
       </c>
       <c r="D207" t="str">
         <v>Stage_1</v>
@@ -4539,7 +4539,7 @@
         <v>0</v>
       </c>
       <c r="F207" t="str">
-        <v>5c7114173bcc2aa7765ceeec641470a3748cba8820707c60590b601ffa9e7055</v>
+        <v>57fcb7414520e85e7cb37cc4e56824651fe91b20abb1168913d6e861e32963bc</v>
       </c>
     </row>
     <row r="208">
@@ -4550,7 +4550,7 @@
         <v>audioclip_sfx_t0158_jp.ab</v>
       </c>
       <c r="C208">
-        <v>1950991</v>
+        <v>1951194</v>
       </c>
       <c r="D208" t="str">
         <v>Stage_1</v>
@@ -4559,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="F208" t="str">
-        <v>e52de1bdb54e58c7e3ff0ad2ab16da9e6f5d9cc50b81d89beace7a56e732346d</v>
+        <v>2498f79d30e887849d14212eed99a9af4ecb9540479c7badfa8cb4229116b867</v>
       </c>
     </row>
     <row r="209">
@@ -4570,7 +4570,7 @@
         <v>audioclip_sfx_t0180_jp.ab</v>
       </c>
       <c r="C209">
-        <v>2527578</v>
+        <v>2527530</v>
       </c>
       <c r="D209" t="str">
         <v>Stage_1</v>
@@ -4579,7 +4579,7 @@
         <v>0</v>
       </c>
       <c r="F209" t="str">
-        <v>6f31b6b3134e7be9114828c534a1bd1df6311033e5cde7af58e453a261307349</v>
+        <v>5a1ac7f74419517682870ab7ac14de7c0e680edd7c0fecac3e88e79ddf4e677f</v>
       </c>
     </row>
     <row r="210">
@@ -4590,7 +4590,7 @@
         <v>audioclip_sfx_t0181_jp.ab</v>
       </c>
       <c r="C210">
-        <v>2120060</v>
+        <v>2120055</v>
       </c>
       <c r="D210" t="str">
         <v>Stage_1</v>
@@ -4599,7 +4599,7 @@
         <v>0</v>
       </c>
       <c r="F210" t="str">
-        <v>dafa9dbdf2f8f8a22b7186d59bc97ac7a5c45f7bd8f4b5d0a6060d3a7f0b9375</v>
+        <v>f7d6cd60cb681b9c0407ceeb035d69240953d629767c9448ef04f8ac525f38ff</v>
       </c>
     </row>
     <row r="211">
@@ -4610,7 +4610,7 @@
         <v>audioclip_sfx_t0182_jp.ab</v>
       </c>
       <c r="C211">
-        <v>1952767</v>
+        <v>1952779</v>
       </c>
       <c r="D211" t="str">
         <v>Stage_1</v>
@@ -4619,7 +4619,7 @@
         <v>0</v>
       </c>
       <c r="F211" t="str">
-        <v>c6062de6ae2cba59cbcc0cdb17d71b682a4cf7097952355c293ec991ad67657f</v>
+        <v>f11dac9b7da49dfbc4cab00524ba5ab608905e383be6cf91735051a85bfcb431</v>
       </c>
     </row>
     <row r="212">
@@ -4630,7 +4630,7 @@
         <v>audioclip_sfx_t0184_jp.ab</v>
       </c>
       <c r="C212">
-        <v>1736024</v>
+        <v>1735993</v>
       </c>
       <c r="D212" t="str">
         <v>Stage_1</v>
@@ -4639,7 +4639,7 @@
         <v>0</v>
       </c>
       <c r="F212" t="str">
-        <v>fac1fce0fd7de8c885aff7abb736d9580d0d9c03c7bcb811dda4c341e27b0b63</v>
+        <v>fdb8fa6c5895f522c63b75126f3c8c83c5af87043ee24ed46f33de866406e6e9</v>
       </c>
     </row>
     <row r="213">
@@ -4650,7 +4650,7 @@
         <v>audioclip_sfx_t0187_jp.ab</v>
       </c>
       <c r="C213">
-        <v>2460155</v>
+        <v>2460117</v>
       </c>
       <c r="D213" t="str">
         <v>Stage_1</v>
@@ -4659,7 +4659,7 @@
         <v>0</v>
       </c>
       <c r="F213" t="str">
-        <v>c7515df8ff510981f8f8cf8b1ee59f740db4c11b7342c41539e5299ad250d8a2</v>
+        <v>8c229e9181cac4b5b20d5814ef22e74f6f6d4ae6e101202b3ea684346529ca5e</v>
       </c>
     </row>
     <row r="214">
@@ -4670,7 +4670,7 @@
         <v>audioclip_sfx_t0188_jp.ab</v>
       </c>
       <c r="C214">
-        <v>1973757</v>
+        <v>1973765</v>
       </c>
       <c r="D214" t="str">
         <v>Stage_1</v>
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="F214" t="str">
-        <v>29e965dcc6fc00f674215baf4b928c70be3f541088a6a5b986f879c73f5a5d42</v>
+        <v>7420750ec1fc5f1b1bd5b20bf58d5b4fb67c0e0876750966df08f3bcd5812b79</v>
       </c>
     </row>
     <row r="215">
@@ -4690,7 +4690,7 @@
         <v>audioclip_sfx_t0189_jp.ab</v>
       </c>
       <c r="C215">
-        <v>2403910</v>
+        <v>2403907</v>
       </c>
       <c r="D215" t="str">
         <v>Stage_1</v>
@@ -4699,7 +4699,7 @@
         <v>0</v>
       </c>
       <c r="F215" t="str">
-        <v>b16c0ca313216b564f4b1e6eccb6e954925af42df5760bd9437c91e0a2061922</v>
+        <v>eb555d75f9c4b048f079aef2aed74b3f8bf986fc8e7c2b2be3295a3897e57879</v>
       </c>
     </row>
     <row r="216">
@@ -4710,7 +4710,7 @@
         <v>audioclip_sfx_t0204_jp.ab</v>
       </c>
       <c r="C216">
-        <v>1290319</v>
+        <v>1290298</v>
       </c>
       <c r="D216" t="str">
         <v>Stage_1</v>
@@ -4719,7 +4719,7 @@
         <v>0</v>
       </c>
       <c r="F216" t="str">
-        <v>3cd8c7dae7a51d1482da70e02c1ec32b0e9414370658e14b4e45fc0e0665a4e9</v>
+        <v>041e655d0f864dce82e0b6e0d5bd1420cf74eec4a5d036f7eaa70bce23081c52</v>
       </c>
     </row>
     <row r="217">
@@ -4730,7 +4730,7 @@
         <v>audioclip_sfx_t0207_jp.ab</v>
       </c>
       <c r="C217">
-        <v>940739</v>
+        <v>940751</v>
       </c>
       <c r="D217" t="str">
         <v>Stage_1</v>
@@ -4739,7 +4739,7 @@
         <v>0</v>
       </c>
       <c r="F217" t="str">
-        <v>6093f9e47c57dd3fc24f60af5f7622e81bacab91f35c0dacb54fcc1e2d36c7cf</v>
+        <v>46b1bfd6fdee35096b9b13fe596ba70b94c8f945d8fa35479968743641df4938</v>
       </c>
     </row>
     <row r="218">
@@ -4750,7 +4750,7 @@
         <v>audioclip_sfx_t0212_jp.ab</v>
       </c>
       <c r="C218">
-        <v>1484342</v>
+        <v>1484300</v>
       </c>
       <c r="D218" t="str">
         <v>Stage_1</v>
@@ -4759,7 +4759,7 @@
         <v>0</v>
       </c>
       <c r="F218" t="str">
-        <v>e73e76ba60cbcfda52306bf47a263f3be4e0c31663be4278b999cff99d452011</v>
+        <v>dea03e7f44893ba00cd5efe4c891827456888cd841181b49429bdd683b229005</v>
       </c>
     </row>
     <row r="219">
@@ -4770,7 +4770,7 @@
         <v>audioclip_sfx_t0214_jp.ab</v>
       </c>
       <c r="C219">
-        <v>1202868</v>
+        <v>1202940</v>
       </c>
       <c r="D219" t="str">
         <v>Stage_1</v>
@@ -4779,7 +4779,7 @@
         <v>0</v>
       </c>
       <c r="F219" t="str">
-        <v>8d2f29e299d4c8d0cb34579b5ae0b2de70efd1d3d394e38a5323bfbe75a553e7</v>
+        <v>5650d1e013f83fd55f9a4371aa615708659afb0cf5df01d53e12c8b668fa509c</v>
       </c>
     </row>
     <row r="220">
@@ -4790,7 +4790,7 @@
         <v>audioclip_sfx_t0218_jp.ab</v>
       </c>
       <c r="C220">
-        <v>619268</v>
+        <v>619274</v>
       </c>
       <c r="D220" t="str">
         <v>Stage_1</v>
@@ -4799,7 +4799,7 @@
         <v>0</v>
       </c>
       <c r="F220" t="str">
-        <v>76c2f395f7dd3e6968171d854f1a945ff726837685d2a94e2a19c1fe8c217be8</v>
+        <v>fd158d15410f475f6d106b1ff7ef844dea191315592eb4aaf7b5dc2c477964b7</v>
       </c>
     </row>
     <row r="221">
@@ -4810,7 +4810,7 @@
         <v>audioclip_sfx_t0222_jp.ab</v>
       </c>
       <c r="C221">
-        <v>781279</v>
+        <v>781288</v>
       </c>
       <c r="D221" t="str">
         <v>Stage_1</v>
@@ -4819,7 +4819,7 @@
         <v>0</v>
       </c>
       <c r="F221" t="str">
-        <v>c1be58c088b69a1fd1f997ba5f0d043bb187c8feb06162a49a38b291cde93ed5</v>
+        <v>9533b4decac5eb1723228908908892afd3d56b64bedb87ee97da84493bb67309</v>
       </c>
     </row>
     <row r="222">
@@ -4830,7 +4830,7 @@
         <v>audioclip_sfx_t0223_jp.ab</v>
       </c>
       <c r="C222">
-        <v>988345</v>
+        <v>988382</v>
       </c>
       <c r="D222" t="str">
         <v>Stage_1</v>
@@ -4839,7 +4839,7 @@
         <v>0</v>
       </c>
       <c r="F222" t="str">
-        <v>1f449da36a5721d749c0a977bfc07acd9568c1e47886840b5d6eca12d7ba7911</v>
+        <v>b197424052f89584b2e8c8416e5184c4b7564fb31f898b39a44c5f0c5913e689</v>
       </c>
     </row>
     <row r="223">
@@ -4850,7 +4850,7 @@
         <v>audioclip_sfx_t0225_jp.ab</v>
       </c>
       <c r="C223">
-        <v>867411</v>
+        <v>867331</v>
       </c>
       <c r="D223" t="str">
         <v>Stage_1</v>
@@ -4859,7 +4859,7 @@
         <v>0</v>
       </c>
       <c r="F223" t="str">
-        <v>2403978508b152e347b3f46dda625a4f30324882f2594dd64dcade93354bca03</v>
+        <v>776c7b563f6249da3d5be270f70a651f29991b7fb68f136d2ff0eb228fd05988</v>
       </c>
     </row>
     <row r="224">
@@ -4870,7 +4870,7 @@
         <v>audioclip_sfx_t0228_jp.ab</v>
       </c>
       <c r="C224">
-        <v>1009843</v>
+        <v>1009849</v>
       </c>
       <c r="D224" t="str">
         <v>Stage_1</v>
@@ -4879,7 +4879,7 @@
         <v>0</v>
       </c>
       <c r="F224" t="str">
-        <v>c501f9ab00ed7a5a51aa0e3f5e6c69e2f59abe0a18f0989109e95f748974c93b</v>
+        <v>69c4845a8123c61c24d08d235a9fc86b4a6a01c00d25914720ba2d7d5aed79d5</v>
       </c>
     </row>
     <row r="225">
@@ -4890,7 +4890,7 @@
         <v>audioclip_sfx_t0229_jp.ab</v>
       </c>
       <c r="C225">
-        <v>1117663</v>
+        <v>1117639</v>
       </c>
       <c r="D225" t="str">
         <v>Stage_1</v>
@@ -4899,7 +4899,7 @@
         <v>0</v>
       </c>
       <c r="F225" t="str">
-        <v>9f7f6b1d211cc28e51714ec88ca1c3e39dd93ff9915f15d9f74be6b519c65ede</v>
+        <v>9ec2ac61d0119e70a7923cf09e21b1cdcfcf7ed7ed52ee01a124b7ce0d2d4c2d</v>
       </c>
     </row>
     <row r="226">
@@ -4910,7 +4910,7 @@
         <v>audioclip_sfx_t0231_jp.ab</v>
       </c>
       <c r="C226">
-        <v>1242758</v>
+        <v>1242671</v>
       </c>
       <c r="D226" t="str">
         <v>Stage_1</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="F226" t="str">
-        <v>ce08981162e66466b4ee4e4da78ceb0ffc741426c58cd5e7fd42f26741c67bfb</v>
+        <v>a967ed1d87e5e244c175ec7272885ed63fd46912e279d7e426e0d38d2c479021</v>
       </c>
     </row>
     <row r="227">
@@ -4930,7 +4930,7 @@
         <v>audioclip_sfx_t0242_jp.ab</v>
       </c>
       <c r="C227">
-        <v>955689</v>
+        <v>955700</v>
       </c>
       <c r="D227" t="str">
         <v>Stage_1</v>
@@ -4939,7 +4939,7 @@
         <v>0</v>
       </c>
       <c r="F227" t="str">
-        <v>b7ace3ce40220f62e3d18d05ec7660b190503c1030c184741d45181e67939878</v>
+        <v>ef6a337dc7282d90fe802fd418fd04e81b9064da0824f7eda5a995d84dda68b6</v>
       </c>
     </row>
     <row r="228">
@@ -4950,7 +4950,7 @@
         <v>audioclip_sfx_t0246_jp.ab</v>
       </c>
       <c r="C228">
-        <v>890771</v>
+        <v>890763</v>
       </c>
       <c r="D228" t="str">
         <v>Stage_1</v>
@@ -4959,7 +4959,7 @@
         <v>0</v>
       </c>
       <c r="F228" t="str">
-        <v>983311ac98117dad253ea5b6a92e1c836692f5f1be8f54da5e2c61e3f0085062</v>
+        <v>c386377e4cac1f29155fea13c280febbf1b11321035e6703e084341fe7f47fbe</v>
       </c>
     </row>
     <row r="229">
@@ -4970,7 +4970,7 @@
         <v>audioclip_sfx_t0250_jp.ab</v>
       </c>
       <c r="C229">
-        <v>1509664</v>
+        <v>1509638</v>
       </c>
       <c r="D229" t="str">
         <v>Stage_1</v>
@@ -4979,7 +4979,7 @@
         <v>0</v>
       </c>
       <c r="F229" t="str">
-        <v>1af58272bb08ddde51eb1ba60f0704e4df9b5465bdfeeac1ff193ce56384bdb3</v>
+        <v>36ace86418516d7cded8861bd3f829008fbca7e36b88d4e3c6aeefd293f53ea9</v>
       </c>
     </row>
     <row r="230">
@@ -4990,7 +4990,7 @@
         <v>audioclip_sfx_t0251_jp.ab</v>
       </c>
       <c r="C230">
-        <v>1812579</v>
+        <v>1812593</v>
       </c>
       <c r="D230" t="str">
         <v>Stage_1</v>
@@ -4999,7 +4999,7 @@
         <v>0</v>
       </c>
       <c r="F230" t="str">
-        <v>83103a7a033808c88ac06462bb696421ca4aefe89e7096d385cd786c89d83f7e</v>
+        <v>30550f2b2a40bc79bc273809e87d0400f0e17beb5bb18172c2ee382f2b597dcd</v>
       </c>
     </row>
     <row r="231">
@@ -5010,7 +5010,7 @@
         <v>audioclip_sfx_t0252_jp.ab</v>
       </c>
       <c r="C231">
-        <v>2885317</v>
+        <v>2885294</v>
       </c>
       <c r="D231" t="str">
         <v>Stage_1</v>
@@ -5019,7 +5019,7 @@
         <v>0</v>
       </c>
       <c r="F231" t="str">
-        <v>148649f548044e6098a6642c2fa9ad1b9ff8e00150a71f5809dda3927fe4701f</v>
+        <v>ada0adff76f7ca6295fbdde275da07d73c2e5371556f3d553b0778b381df9027</v>
       </c>
     </row>
     <row r="232">
@@ -5030,7 +5030,7 @@
         <v>audioclip_sfx_t0254_jp.ab</v>
       </c>
       <c r="C232">
-        <v>1288917</v>
+        <v>1288936</v>
       </c>
       <c r="D232" t="str">
         <v>Stage_1</v>
@@ -5039,7 +5039,7 @@
         <v>0</v>
       </c>
       <c r="F232" t="str">
-        <v>d904be8b981ba87777b1f00a5a758bc50493dacb6f15c975bde4aebd7d563ca8</v>
+        <v>db3a77880bda109d2d38d4d65cd86ed2939a80a669197a313a059092830cfae8</v>
       </c>
     </row>
     <row r="233">
@@ -5050,7 +5050,7 @@
         <v>audioclip_sfx_t0258_jp.ab</v>
       </c>
       <c r="C233">
-        <v>1912958</v>
+        <v>1912976</v>
       </c>
       <c r="D233" t="str">
         <v>Stage_1</v>
@@ -5059,7 +5059,7 @@
         <v>0</v>
       </c>
       <c r="F233" t="str">
-        <v>b5c1c04a2837264abf5aabfdb7cd0e6b28f8d9c1552e191d433be8dedb7018db</v>
+        <v>c2cfe0b36468e4f0833cae067590617d0681c1e5d5cd1045c5ff9b9b5b748124</v>
       </c>
     </row>
     <row r="234">
@@ -5070,7 +5070,7 @@
         <v>audioclip_sfx_t0263_jp.ab</v>
       </c>
       <c r="C234">
-        <v>1741544</v>
+        <v>1741593</v>
       </c>
       <c r="D234" t="str">
         <v>Stage_1</v>
@@ -5079,7 +5079,7 @@
         <v>0</v>
       </c>
       <c r="F234" t="str">
-        <v>a16fb8288cca9c4e0172e756e8f7970aebe0a540486a0136a7e7471ffb57dac4</v>
+        <v>58e0a82ac9c16d9acdc17c1bba376c2ac2b3cadcd8d7b00e26ff70c6da3dbdc6</v>
       </c>
     </row>
     <row r="235">
@@ -5090,7 +5090,7 @@
         <v>audioclip_sfx_t0269_jp.ab</v>
       </c>
       <c r="C235">
-        <v>1231700</v>
+        <v>1231721</v>
       </c>
       <c r="D235" t="str">
         <v>Stage_1</v>
@@ -5099,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="F235" t="str">
-        <v>75159c8704f153ca9e4407ce585f5b2e6e24c82349549f6da9d7c7f66d5da6f2</v>
+        <v>904347efd427659308c752cdcb7e1bd9d40e90c110fbaa7be112de652085526e</v>
       </c>
     </row>
     <row r="236">
@@ -5110,7 +5110,7 @@
         <v>audioclip_sfx_t0272_jp.ab</v>
       </c>
       <c r="C236">
-        <v>1436659</v>
+        <v>1436668</v>
       </c>
       <c r="D236" t="str">
         <v>Stage_1</v>
@@ -5119,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="F236" t="str">
-        <v>3fbd499f369d479453c63104e49451bb58ffc5a320809a8764e869742fe3e29b</v>
+        <v>f0da41c4d0d5eda5640e3912bef5020a5ac2497e84e9015c418b80186db7c08d</v>
       </c>
     </row>
     <row r="237">
@@ -5130,7 +5130,7 @@
         <v>audioclip_sfx_t0275_jp.ab</v>
       </c>
       <c r="C237">
-        <v>1172442</v>
+        <v>1172489</v>
       </c>
       <c r="D237" t="str">
         <v>Stage_1</v>
@@ -5139,7 +5139,7 @@
         <v>0</v>
       </c>
       <c r="F237" t="str">
-        <v>b6f6edf00466592028c60ce90e74dd406334954362231570834a3b4eef0603ed</v>
+        <v>54c308dfbe0de74ce47f0e655ec90809d1d9e9e37f299cbd6ed37d1b7c017ca7</v>
       </c>
     </row>
     <row r="238">
@@ -5150,7 +5150,7 @@
         <v>audioclip_sfx_t3189_jp.ab</v>
       </c>
       <c r="C238">
-        <v>316226</v>
+        <v>316239</v>
       </c>
       <c r="D238" t="str">
         <v>Stage_1</v>
@@ -5159,7 +5159,7 @@
         <v>0</v>
       </c>
       <c r="F238" t="str">
-        <v>01cdfbbf9f77a918a2016333f70e047b3087ef54fd0477a4cbb298f6a9eb631d</v>
+        <v>1d1e9ae7cb7b6834ebc141019d715580c557fdb9fca495d18ebb8ed65742e135</v>
       </c>
     </row>
     <row r="239">
@@ -5170,7 +5170,7 @@
         <v>audioclip_sfx_t3191_jp.ab</v>
       </c>
       <c r="C239">
-        <v>164050</v>
+        <v>164060</v>
       </c>
       <c r="D239" t="str">
         <v>Stage_1</v>
@@ -5179,7 +5179,7 @@
         <v>0</v>
       </c>
       <c r="F239" t="str">
-        <v>8abe3d521ebcb185fcce96a49bbc96df07257c26e4d0764e87c1936ced63e4b5</v>
+        <v>039ad69d46bcbaf3b050b3a796ff097456e0013c3cf75180c4cfdaab30d5c3ae</v>
       </c>
     </row>
     <row r="240">
@@ -5190,7 +5190,7 @@
         <v>audioclip_sfx_t3259_jp.ab</v>
       </c>
       <c r="C240">
-        <v>214579</v>
+        <v>214599</v>
       </c>
       <c r="D240" t="str">
         <v>Stage_1</v>
@@ -5199,7 +5199,7 @@
         <v>0</v>
       </c>
       <c r="F240" t="str">
-        <v>d3418a4d00e7826aeec3b5f55296ba67194159666952d4f5645a7a3e3959bd33</v>
+        <v>93aac7a5ec8b8d9d9d6a852cffc388bc9fee16555efdcd183c0ca32e7bcaaaea</v>
       </c>
     </row>
     <row r="241">
@@ -5210,7 +5210,7 @@
         <v>audioclip_sfx_t3260_jp.ab</v>
       </c>
       <c r="C241">
-        <v>310407</v>
+        <v>310413</v>
       </c>
       <c r="D241" t="str">
         <v>Stage_1</v>
@@ -5219,7 +5219,7 @@
         <v>0</v>
       </c>
       <c r="F241" t="str">
-        <v>7922b41fbe5ace431e852e608c627644145a3374e7c72b17c7eb99e87d8a75f0</v>
+        <v>43434b007126360f4896b3f63c23af1105e66912b3af759e99db4017b75345a6</v>
       </c>
     </row>
     <row r="242">
@@ -5230,7 +5230,7 @@
         <v>audioclip_sfx_t3403_jp.ab</v>
       </c>
       <c r="C242">
-        <v>288969</v>
+        <v>288999</v>
       </c>
       <c r="D242" t="str">
         <v>Stage_1</v>
@@ -5239,7 +5239,7 @@
         <v>0</v>
       </c>
       <c r="F242" t="str">
-        <v>318ed1740220025f770750eae32fd2966f4ee57185327d8b16d06272c6fb1b72</v>
+        <v>25209767720edf6c020f26a762b8fe8c8fa4fa594faa4aa6a9ef84f1d4c91dd7</v>
       </c>
     </row>
     <row r="243">
@@ -5250,7 +5250,7 @@
         <v>audioclip_sfx_t3407_jp.ab</v>
       </c>
       <c r="C243">
-        <v>270581</v>
+        <v>270574</v>
       </c>
       <c r="D243" t="str">
         <v>Stage_1</v>
@@ -5259,7 +5259,7 @@
         <v>0</v>
       </c>
       <c r="F243" t="str">
-        <v>d6d2fac1b1df16b394e326376d1b0328ebf898c00bfa98e4d483d55222f879a7</v>
+        <v>23684fde6983e60363d2a6a1e44af850c4913ab3d93c9a91988edafac0b413c4</v>
       </c>
     </row>
     <row r="244">
@@ -5270,7 +5270,7 @@
         <v>character_largeimage_b0001.ab</v>
       </c>
       <c r="C244">
-        <v>3127774</v>
+        <v>3139566</v>
       </c>
       <c r="D244" t="str">
         <v>Stage_1</v>
@@ -5279,7 +5279,7 @@
         <v>0</v>
       </c>
       <c r="F244" t="str">
-        <v>78e784ceac79715e6f390d5b83f7fb527e8cb5b0404a6f1be45b313a5ba02dc1</v>
+        <v>974f09b8d133e6ea2c6b9bb2e779297787860d23dade0bc8719638287102331a</v>
       </c>
     </row>
     <row r="245">
@@ -5290,7 +5290,7 @@
         <v>character_largeimage_b0015.ab</v>
       </c>
       <c r="C245">
-        <v>3331653</v>
+        <v>3462894</v>
       </c>
       <c r="D245" t="str">
         <v>Stage_1</v>
@@ -5299,7 +5299,7 @@
         <v>0</v>
       </c>
       <c r="F245" t="str">
-        <v>dd04ef36d2763124089134dbe7458b80907450a71e52752c5290f0de6f4e7eae</v>
+        <v>3eccb04f7b6938d8a407cb03d67c3306f38994bb7664406851c8adb8de67b1ff</v>
       </c>
     </row>
     <row r="246">
@@ -5310,7 +5310,7 @@
         <v>character_largeimage_b0028.ab</v>
       </c>
       <c r="C246">
-        <v>3412887</v>
+        <v>3458728</v>
       </c>
       <c r="D246" t="str">
         <v>Stage_1</v>
@@ -5319,7 +5319,7 @@
         <v>0</v>
       </c>
       <c r="F246" t="str">
-        <v>24f9a0b1ca8b96b3da27e0f1d94e381499f584471f56b3c2a7241ae4f6141d8c</v>
+        <v>1a5903dc08bd7af04ba147dad24f427a6474245f47a1f2cde3bb3c757b5e73e9</v>
       </c>
     </row>
     <row r="247">
@@ -5330,7 +5330,7 @@
         <v>character_largeimage_b0037.ab</v>
       </c>
       <c r="C247">
-        <v>4001030</v>
+        <v>4029942</v>
       </c>
       <c r="D247" t="str">
         <v>Stage_1</v>
@@ -5339,7 +5339,7 @@
         <v>0</v>
       </c>
       <c r="F247" t="str">
-        <v>1bb8cecd4d65d3465875868908bde0e58a0c63eb9afd917907feb7180b3b8914</v>
+        <v>7f338066817f9c7924a614cf759d9058099f46651684c68be6314609a6bbda63</v>
       </c>
     </row>
     <row r="248">
@@ -5350,7 +5350,7 @@
         <v>character_largeimage_b0202.ab</v>
       </c>
       <c r="C248">
-        <v>790826</v>
+        <v>795638</v>
       </c>
       <c r="D248" t="str">
         <v>Stage_1</v>
@@ -5359,7 +5359,7 @@
         <v>0</v>
       </c>
       <c r="F248" t="str">
-        <v>be4310c123d2b37d7bdd180f406795da17db9276c2abcf6d33c7f2d834798ba0</v>
+        <v>b8455e6c61f8d2dd1db9f50ec69e6bfefcaade236e64fa83f20dda0ffae910fd</v>
       </c>
     </row>
     <row r="249">
@@ -5370,7 +5370,7 @@
         <v>character_largeimage_b0260.ab</v>
       </c>
       <c r="C249">
-        <v>809446</v>
+        <v>819352</v>
       </c>
       <c r="D249" t="str">
         <v>Stage_1</v>
@@ -5379,7 +5379,7 @@
         <v>0</v>
       </c>
       <c r="F249" t="str">
-        <v>5545e61f9af50ea439bb9425d49679c265b4b04153e748be9d8dff61b7f46113</v>
+        <v>0ffa388ea9edffae44e8a33b3308e6b93ab6217f1719be03fc5796cbddc8778d</v>
       </c>
     </row>
     <row r="250">
@@ -5390,7 +5390,7 @@
         <v>character_largeimage_b0267.ab</v>
       </c>
       <c r="C250">
-        <v>789052</v>
+        <v>791244</v>
       </c>
       <c r="D250" t="str">
         <v>Stage_1</v>
@@ -5399,7 +5399,7 @@
         <v>0</v>
       </c>
       <c r="F250" t="str">
-        <v>d2c5fdd38d13a1a6a6c8f4f19e0f84caaa156ea51ae041433dfd645d0b8e59f8</v>
+        <v>9544dcf1b4e2dc9e060ec3d1080ab7ba5481256146b08d80b22cec5fc38cbaef</v>
       </c>
     </row>
     <row r="251">
@@ -5410,7 +5410,7 @@
         <v>character_largeimage_e0002.ab</v>
       </c>
       <c r="C251">
-        <v>3558177</v>
+        <v>3722344</v>
       </c>
       <c r="D251" t="str">
         <v>Stage_1</v>
@@ -5419,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="F251" t="str">
-        <v>a51d1503e3559c8ce675afeeed8f729155eed27a8fbebb35148b3dc87f8492e1</v>
+        <v>f89f4bf64b146f56adb434c21c1d48fb40140b1f2d36315faa6daf895744785c</v>
       </c>
     </row>
     <row r="252">
@@ -5430,7 +5430,7 @@
         <v>character_largeimage_e0046.ab</v>
       </c>
       <c r="C252">
-        <v>797567</v>
+        <v>802833</v>
       </c>
       <c r="D252" t="str">
         <v>Stage_1</v>
@@ -5439,7 +5439,7 @@
         <v>0</v>
       </c>
       <c r="F252" t="str">
-        <v>a59b46fa5f54c534a9098787a6bf734026c5260a26fe4ed54fab45eb22d26dd3</v>
+        <v>6cf8515dfd200a57151e1d2ecfb69b95f5844a3314ea652a5a5268ee21462413</v>
       </c>
     </row>
     <row r="253">
@@ -5450,7 +5450,7 @@
         <v>character_largeimage_h0000.ab</v>
       </c>
       <c r="C253">
-        <v>208090</v>
+        <v>209115</v>
       </c>
       <c r="D253" t="str">
         <v>Stage_1</v>
@@ -5459,7 +5459,7 @@
         <v>0</v>
       </c>
       <c r="F253" t="str">
-        <v>a83767d3a6a982d3509d5ed4c329a744963271116b14d342654d3bd0bc612c66</v>
+        <v>9ecab0c6268b961e7ed3f7afe2749dfc468d2f5e6be7e1feca8765f564085117</v>
       </c>
     </row>
     <row r="254">
@@ -5470,7 +5470,7 @@
         <v>character_largeimage_h0003.ab</v>
       </c>
       <c r="C254">
-        <v>3975187</v>
+        <v>4082707</v>
       </c>
       <c r="D254" t="str">
         <v>Stage_1</v>
@@ -5479,7 +5479,7 @@
         <v>0</v>
       </c>
       <c r="F254" t="str">
-        <v>c7a8bfc4a28e3f884b3fd89a9d5988d4b86952038ef16422caddaee083cf9588</v>
+        <v>a09418e104021c955035c2e8500a7be7c71a347cd9c36d3eba684fdcc9ba68d0</v>
       </c>
     </row>
     <row r="255">
@@ -5490,7 +5490,7 @@
         <v>character_largeimage_h0004.ab</v>
       </c>
       <c r="C255">
-        <v>4306043</v>
+        <v>4501079</v>
       </c>
       <c r="D255" t="str">
         <v>Stage_1</v>
@@ -5499,7 +5499,7 @@
         <v>0</v>
       </c>
       <c r="F255" t="str">
-        <v>8b2ed468e2fcba7d477e3da1fe08a3c2d69c7a5b700f1e557d14a5b1a72ba120</v>
+        <v>c580b7d921f339bbdf7a1a808137555adc3341b6f88e85326577d88a6c5807ff</v>
       </c>
     </row>
     <row r="256">
@@ -5510,7 +5510,7 @@
         <v>character_largeimage_h0005.ab</v>
       </c>
       <c r="C256">
-        <v>3547758</v>
+        <v>3698165</v>
       </c>
       <c r="D256" t="str">
         <v>Stage_1</v>
@@ -5519,7 +5519,7 @@
         <v>0</v>
       </c>
       <c r="F256" t="str">
-        <v>e3fca3c426d6ee0a3cf9dd6f304f8f25d2fef2a9b1ae6de05627d3db37e3fc6a</v>
+        <v>f644717ba851e1c71c2931191f5941bb331d43f4d5c9cd95235d9cb0f90913d6</v>
       </c>
     </row>
     <row r="257">
@@ -5530,7 +5530,7 @@
         <v>character_largeimage_h0006.ab</v>
       </c>
       <c r="C257">
-        <v>3671173</v>
+        <v>3876694</v>
       </c>
       <c r="D257" t="str">
         <v>Stage_1</v>
@@ -5539,7 +5539,7 @@
         <v>0</v>
       </c>
       <c r="F257" t="str">
-        <v>b5b543aee2a4ed561a42e5107bbea10ef79b2ad93842b832eb235533f7ca4f99</v>
+        <v>c038be63651d08b799d6d7599344579632b8b4e11ce9f66c0fa969bfa26c227d</v>
       </c>
     </row>
     <row r="258">
@@ -5550,7 +5550,7 @@
         <v>character_largeimage_h0007.ab</v>
       </c>
       <c r="C258">
-        <v>803840</v>
+        <v>806835</v>
       </c>
       <c r="D258" t="str">
         <v>Stage_1</v>
@@ -5559,7 +5559,7 @@
         <v>0</v>
       </c>
       <c r="F258" t="str">
-        <v>e7a218ee7d7a55f01a0e251a424c46bcf384be8b50176d5cac868f9da0dde6d7</v>
+        <v>b753749d2cde667bf3d5342e48a8d8a9ea592600d6dbaed8888cabe49d5d83a5</v>
       </c>
     </row>
     <row r="259">
@@ -5570,7 +5570,7 @@
         <v>character_largeimage_h0008.ab</v>
       </c>
       <c r="C259">
-        <v>713224</v>
+        <v>720293</v>
       </c>
       <c r="D259" t="str">
         <v>Stage_1</v>
@@ -5579,7 +5579,7 @@
         <v>0</v>
       </c>
       <c r="F259" t="str">
-        <v>bbc9c213346cd9c77b113965f05ffa7d0b05ac187f68681435bf67674b00e146</v>
+        <v>dfcb36c1eabf073d85f6ca66a81215732d12b0c8716b2624f9bf7850e3757d3c</v>
       </c>
     </row>
     <row r="260">
@@ -5590,7 +5590,7 @@
         <v>character_largeimage_h0009.ab</v>
       </c>
       <c r="C260">
-        <v>831282</v>
+        <v>835304</v>
       </c>
       <c r="D260" t="str">
         <v>Stage_1</v>
@@ -5599,7 +5599,7 @@
         <v>0</v>
       </c>
       <c r="F260" t="str">
-        <v>c38406c3168894ab382175e94b7976eb5ea0caf4f1d7a22fe7b3860d8dc0759e</v>
+        <v>bfaeae6d8d1ee88b605d18b0985ff8fb45e9f4d4d68119425905a1c6f02c4331</v>
       </c>
     </row>
     <row r="261">
@@ -5610,7 +5610,7 @@
         <v>character_largeimage_h0010.ab</v>
       </c>
       <c r="C261">
-        <v>4679298</v>
+        <v>4718109</v>
       </c>
       <c r="D261" t="str">
         <v>Stage_1</v>
@@ -5619,7 +5619,7 @@
         <v>0</v>
       </c>
       <c r="F261" t="str">
-        <v>6f4c0ef7a8999f67fbe814d23dd3f4bdd1d22cc0f44a0f13a9953615ce2d6580</v>
+        <v>2aa814768c7c16c60b7cb1ba30953ea26a88da5af37c63c8a812c0780bd8f690</v>
       </c>
     </row>
     <row r="262">
@@ -5630,7 +5630,7 @@
         <v>character_largeimage_h0012.ab</v>
       </c>
       <c r="C262">
-        <v>823851</v>
+        <v>829443</v>
       </c>
       <c r="D262" t="str">
         <v>Stage_1</v>
@@ -5639,7 +5639,7 @@
         <v>0</v>
       </c>
       <c r="F262" t="str">
-        <v>8ce801de023c56fbb01494c4ca701ac2a955973683af0de63eb113c470fe54c3</v>
+        <v>5234fb998c4818dcc2fec4f106853aca8accfb82f06b06937032f0e58aa44762</v>
       </c>
     </row>
     <row r="263">
@@ -5650,7 +5650,7 @@
         <v>character_largeimage_h0013.ab</v>
       </c>
       <c r="C263">
-        <v>730593</v>
+        <v>732340</v>
       </c>
       <c r="D263" t="str">
         <v>Stage_1</v>
@@ -5659,7 +5659,7 @@
         <v>0</v>
       </c>
       <c r="F263" t="str">
-        <v>70018ef62ee1aa1a3b56fd711fb01a33ba58f72ed71b0ee34e169894cad9a529</v>
+        <v>34ed3871f9f12b47c56d1544fc1ba4433bf43f9f35bd91fe9a2088de9234beb4</v>
       </c>
     </row>
     <row r="264">
@@ -5670,7 +5670,7 @@
         <v>character_largeimage_h0014.ab</v>
       </c>
       <c r="C264">
-        <v>808031</v>
+        <v>814927</v>
       </c>
       <c r="D264" t="str">
         <v>Stage_1</v>
@@ -5679,7 +5679,7 @@
         <v>0</v>
       </c>
       <c r="F264" t="str">
-        <v>da212d22735b71006f7bbebd8d2cf847ddf21d859344229cddf9f6ccf80c5372</v>
+        <v>00dc0a4c1b8377acaf7f6966a89e336ac4513ad273757d81affe25cc295600c9</v>
       </c>
     </row>
     <row r="265">
@@ -5690,7 +5690,7 @@
         <v>character_largeimage_h0016.ab</v>
       </c>
       <c r="C265">
-        <v>758977</v>
+        <v>764558</v>
       </c>
       <c r="D265" t="str">
         <v>Stage_1</v>
@@ -5699,7 +5699,7 @@
         <v>0</v>
       </c>
       <c r="F265" t="str">
-        <v>8b88365c69bb5344a0f0022c3e0ae2283422666aca080b856f449d7397992782</v>
+        <v>1f26bbb70fc95d89c6c443ef24ff61ca661bdb2481d622d7471c1288d78352bb</v>
       </c>
     </row>
     <row r="266">
@@ -5710,7 +5710,7 @@
         <v>character_largeimage_h0018.ab</v>
       </c>
       <c r="C266">
-        <v>4615070</v>
+        <v>4901347</v>
       </c>
       <c r="D266" t="str">
         <v>Stage_1</v>
@@ -5719,7 +5719,7 @@
         <v>0</v>
       </c>
       <c r="F266" t="str">
-        <v>78559c267f1b3412982acc007d76441d8b75e93eb4bfcdb0e95485e9ecd87318</v>
+        <v>8d4387964125d3764663bc45e1c9162fa38574d0a5a20e9737b4e15f77660d42</v>
       </c>
     </row>
     <row r="267">
@@ -5730,7 +5730,7 @@
         <v>character_largeimage_h0020.ab</v>
       </c>
       <c r="C267">
-        <v>3928747</v>
+        <v>4171655</v>
       </c>
       <c r="D267" t="str">
         <v>Stage_1</v>
@@ -5739,7 +5739,7 @@
         <v>0</v>
       </c>
       <c r="F267" t="str">
-        <v>649021775c3d944ec66710dc2833a8df8f6e11c44878c62f3b931ff660a3c2da</v>
+        <v>2d81dc99e4e5b6e0d85a10f0a35f26180d64451d8e8b0060fcb20df75755124f</v>
       </c>
     </row>
     <row r="268">
@@ -5750,7 +5750,7 @@
         <v>character_largeimage_h0021.ab</v>
       </c>
       <c r="C268">
-        <v>4234934</v>
+        <v>4410542</v>
       </c>
       <c r="D268" t="str">
         <v>Stage_1</v>
@@ -5759,7 +5759,7 @@
         <v>0</v>
       </c>
       <c r="F268" t="str">
-        <v>95f82d1cb182f0d594eb6125d7b4f828b8e2b54c03c6a9b2a8a2688ae2b427ef</v>
+        <v>1d572e25f61eeb19f3d1dcdb7a5c686e03f2706ff3db6c4e88b65bf52888427d</v>
       </c>
     </row>
     <row r="269">
@@ -5770,7 +5770,7 @@
         <v>character_largeimage_h0022.ab</v>
       </c>
       <c r="C269">
-        <v>4332457</v>
+        <v>4409642</v>
       </c>
       <c r="D269" t="str">
         <v>Stage_1</v>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="F269" t="str">
-        <v>4d633e8de21a01527f9364d84f44895010d4a5dec9f0ede8402c19749280609a</v>
+        <v>03cacebf56732e0029abf6b93346680f2e9a60ccd17342dfebbc5fb07fe05c32</v>
       </c>
     </row>
     <row r="270">
@@ -5790,7 +5790,7 @@
         <v>character_largeimage_h0023.ab</v>
       </c>
       <c r="C270">
-        <v>3265010</v>
+        <v>3285961</v>
       </c>
       <c r="D270" t="str">
         <v>Stage_1</v>
@@ -5799,7 +5799,7 @@
         <v>0</v>
       </c>
       <c r="F270" t="str">
-        <v>ffdbdb5c7c3a5f8aec334500f40226b14d82ac63ff43d51fa83131e6be67c680</v>
+        <v>b29dc8e23ae7577614fd48ea089c68739e619e9c192a34251e505ed307bbafff</v>
       </c>
     </row>
     <row r="271">
@@ -5810,7 +5810,7 @@
         <v>character_largeimage_h0024.ab</v>
       </c>
       <c r="C271">
-        <v>3281918</v>
+        <v>3324743</v>
       </c>
       <c r="D271" t="str">
         <v>Stage_1</v>
@@ -5819,7 +5819,7 @@
         <v>0</v>
       </c>
       <c r="F271" t="str">
-        <v>055d98eaa385323f6b431d57d9158c227ec5ff8f3fa628b8fdac15595b44a475</v>
+        <v>3bbc8f10e186a186e2069857259bea949507fbb4d5a8e7d099df2af3a17ce757</v>
       </c>
     </row>
     <row r="272">
@@ -5830,7 +5830,7 @@
         <v>character_largeimage_h0025.ab</v>
       </c>
       <c r="C272">
-        <v>3268737</v>
+        <v>3291677</v>
       </c>
       <c r="D272" t="str">
         <v>Stage_1</v>
@@ -5839,7 +5839,7 @@
         <v>0</v>
       </c>
       <c r="F272" t="str">
-        <v>2a72b0b0d6249cd756219728440dca77f1388f67427663ba12f8ddac14f3a5c5</v>
+        <v>a49276599a0a90a6b3b2dff3dfe04e905c01c38ce67b59413f1d67378f5af49e</v>
       </c>
     </row>
     <row r="273">
@@ -5850,7 +5850,7 @@
         <v>character_largeimage_h0029.ab</v>
       </c>
       <c r="C273">
-        <v>3878944</v>
+        <v>3926292</v>
       </c>
       <c r="D273" t="str">
         <v>Stage_1</v>
@@ -5859,7 +5859,7 @@
         <v>0</v>
       </c>
       <c r="F273" t="str">
-        <v>4d62229cbd284aa9391c2ae5728483edcdd7c3664570bc6980b143987362b95d</v>
+        <v>e6720656fdf86846b2af4a9bc16d970a65de4d95c32b4e5e18e8fb9d71b3fcac</v>
       </c>
     </row>
     <row r="274">
@@ -5870,7 +5870,7 @@
         <v>character_largeimage_h0030.ab</v>
       </c>
       <c r="C274">
-        <v>3068963</v>
+        <v>3108918</v>
       </c>
       <c r="D274" t="str">
         <v>Stage_1</v>
@@ -5879,7 +5879,7 @@
         <v>0</v>
       </c>
       <c r="F274" t="str">
-        <v>d43431a351343bcce91b2b6839f9998d1c36be4e3f4f103a9b7bed45056690a6</v>
+        <v>8576e1cdce0ca29e34fb8809251012eec24d75c4ee249fbb0f86bdf9abcff8e3</v>
       </c>
     </row>
     <row r="275">
@@ -5890,7 +5890,7 @@
         <v>character_largeimage_h0031.ab</v>
       </c>
       <c r="C275">
-        <v>3311210</v>
+        <v>3386930</v>
       </c>
       <c r="D275" t="str">
         <v>Stage_1</v>
@@ -5899,7 +5899,7 @@
         <v>0</v>
       </c>
       <c r="F275" t="str">
-        <v>f844caa4342233c882176f4b3d3b5df3aa38df5704837c4e17b36f772a18fe85</v>
+        <v>9b57a21b59f0d456310c77d1f3ae679df2a7e96c89351b78134639a27218219f</v>
       </c>
     </row>
     <row r="276">
@@ -5910,7 +5910,7 @@
         <v>character_largeimage_h0035.ab</v>
       </c>
       <c r="C276">
-        <v>3958978</v>
+        <v>4064674</v>
       </c>
       <c r="D276" t="str">
         <v>Stage_1</v>
@@ -5919,7 +5919,7 @@
         <v>0</v>
       </c>
       <c r="F276" t="str">
-        <v>5a7f4c68dffa0013111cececfe93648f43ea44a9d2ecc2f353cf7b7c8cb8f59c</v>
+        <v>bf7753395a84dd762f014eb7f933b6028a5e87ea894944e6e2297830ea8c3ee3</v>
       </c>
     </row>
     <row r="277">
@@ -5930,7 +5930,7 @@
         <v>character_largeimage_h0036.ab</v>
       </c>
       <c r="C277">
-        <v>2916298</v>
+        <v>2986356</v>
       </c>
       <c r="D277" t="str">
         <v>Stage_1</v>
@@ -5939,7 +5939,7 @@
         <v>0</v>
       </c>
       <c r="F277" t="str">
-        <v>b9696daa9252dec4261611f1f256637ee51cb3b8b33d0b92cfd3bba149001c6e</v>
+        <v>b16b0157ce0f04ca16b0e389f025fadc7bffa54321b655797e645f79b4662bac</v>
       </c>
     </row>
     <row r="278">
@@ -5950,7 +5950,7 @@
         <v>character_largeimage_h0038.ab</v>
       </c>
       <c r="C278">
-        <v>855003</v>
+        <v>862605</v>
       </c>
       <c r="D278" t="str">
         <v>Stage_1</v>
@@ -5959,7 +5959,7 @@
         <v>0</v>
       </c>
       <c r="F278" t="str">
-        <v>289b0ed905365cd5e8cb89fe42ac33d47e5f572cfc93a7419bb99f39ea7341d1</v>
+        <v>ecd058a02a1aefa7c6a263296ee0c21dfb9345aab55b94a893fa77178b944737</v>
       </c>
     </row>
     <row r="279">
@@ -5970,7 +5970,7 @@
         <v>character_largeimage_h0040.ab</v>
       </c>
       <c r="C279">
-        <v>834045</v>
+        <v>840562</v>
       </c>
       <c r="D279" t="str">
         <v>Stage_1</v>
@@ -5979,7 +5979,7 @@
         <v>0</v>
       </c>
       <c r="F279" t="str">
-        <v>6b42ad4bbc2598a1f1702e175d9bf9f511e485fa19f3fa86a86c22eb8cc7f23e</v>
+        <v>dfc4f3875de0851154d137b7b85dc7a1c00d5f60c98fa971565e89fc8104b682</v>
       </c>
     </row>
     <row r="280">
@@ -5990,7 +5990,7 @@
         <v>character_largeimage_h0041.ab</v>
       </c>
       <c r="C280">
-        <v>799261</v>
+        <v>803611</v>
       </c>
       <c r="D280" t="str">
         <v>Stage_1</v>
@@ -5999,7 +5999,7 @@
         <v>0</v>
       </c>
       <c r="F280" t="str">
-        <v>5f1d547ddd7b8ce59a4e005ebe350bdc99957ad7f687d685d31014cccf81c0fc</v>
+        <v>53edbc457a6281624c16958297cb7ef498cb7f00543b1e3c36568a5555127501</v>
       </c>
     </row>
     <row r="281">
@@ -6010,7 +6010,7 @@
         <v>character_largeimage_h0042.ab</v>
       </c>
       <c r="C281">
-        <v>777116</v>
+        <v>783684</v>
       </c>
       <c r="D281" t="str">
         <v>Stage_1</v>
@@ -6019,7 +6019,7 @@
         <v>0</v>
       </c>
       <c r="F281" t="str">
-        <v>ec22258063c80e1c82446b8a02dd46be8a92091df93f324eb9cf423dbee75c4a</v>
+        <v>7d27f42cf90b7427f2be2a9642d6745a2013e9d339c611a5b6a61669f69267ce</v>
       </c>
     </row>
     <row r="282">
@@ -6030,7 +6030,7 @@
         <v>character_largeimage_h0043.ab</v>
       </c>
       <c r="C282">
-        <v>4131491</v>
+        <v>4207233</v>
       </c>
       <c r="D282" t="str">
         <v>Stage_1</v>
@@ -6039,7 +6039,7 @@
         <v>0</v>
       </c>
       <c r="F282" t="str">
-        <v>2e3087d8674c5bff6c4f6a7957f7b459bfefc77083b6fa9050da6c234e5fcd06</v>
+        <v>ff8f2e750b0724f585c1d748dc06170ff2ed3958fe092d64f629c1ae0f9b97b2</v>
       </c>
     </row>
     <row r="283">
@@ -6050,7 +6050,7 @@
         <v>character_largeimage_h0045.ab</v>
       </c>
       <c r="C283">
-        <v>806083</v>
+        <v>814525</v>
       </c>
       <c r="D283" t="str">
         <v>Stage_1</v>
@@ -6059,7 +6059,7 @@
         <v>0</v>
       </c>
       <c r="F283" t="str">
-        <v>75ea8ae022a44b3b64d866c990239078893ea0883aa85a84522e0d99fff85500</v>
+        <v>dae2ccec890c4b4e5dc29705ee34d77a82700c93c3e2f84d215e776d4d5d32be</v>
       </c>
     </row>
     <row r="284">
@@ -6070,7 +6070,7 @@
         <v>character_largeimage_h0047.ab</v>
       </c>
       <c r="C284">
-        <v>4289279</v>
+        <v>4344899</v>
       </c>
       <c r="D284" t="str">
         <v>Stage_1</v>
@@ -6079,7 +6079,7 @@
         <v>0</v>
       </c>
       <c r="F284" t="str">
-        <v>3f3f9d99623d7683093487b65cfd461be53bd2b8153a9419bb9880bf3086fee3</v>
+        <v>b75ba36d12466d04ee80f52876fe94d08f29fde1ef8c4b266209ea68362667c5</v>
       </c>
     </row>
     <row r="285">
@@ -6090,7 +6090,7 @@
         <v>character_largeimage_h0048.ab</v>
       </c>
       <c r="C285">
-        <v>3816882</v>
+        <v>3885667</v>
       </c>
       <c r="D285" t="str">
         <v>Stage_1</v>
@@ -6099,7 +6099,7 @@
         <v>0</v>
       </c>
       <c r="F285" t="str">
-        <v>e342bcc9d451f54427e9e676142ce9d3e42283c78c64adf074fd6754f8b711c9</v>
+        <v>d1e4c55e7d85b1d55b310a477e7dc15cc5d811a11d85055141e8b7d93fe60180</v>
       </c>
     </row>
     <row r="286">
@@ -6110,7 +6110,7 @@
         <v>character_largeimage_h0097.ab</v>
       </c>
       <c r="C286">
-        <v>5051199</v>
+        <v>5310116</v>
       </c>
       <c r="D286" t="str">
         <v>Stage_1</v>
@@ -6119,7 +6119,7 @@
         <v>0</v>
       </c>
       <c r="F286" t="str">
-        <v>a85ef6c19ca8f47ed76b9c9f22aa8d48512b3d1dc156cdb37fdebe8d80ff9e1a</v>
+        <v>dc6a5326663bace5aa6a1b5d89b1a4002f7d8a99222418f573de38181b44e4c6</v>
       </c>
     </row>
     <row r="287">
@@ -6130,7 +6130,7 @@
         <v>character_largeimage_h0133.ab</v>
       </c>
       <c r="C287">
-        <v>4176002</v>
+        <v>4271410</v>
       </c>
       <c r="D287" t="str">
         <v>Stage_1</v>
@@ -6139,7 +6139,7 @@
         <v>0</v>
       </c>
       <c r="F287" t="str">
-        <v>206d98bef7c96e960896ee8ee4a7b90e71f4c30bd73f9833cbe46d246c450f78</v>
+        <v>867845e752c27d3a00840331cb9c065c0d48a13e4f27398844ec4a057783d37c</v>
       </c>
     </row>
     <row r="288">
@@ -6150,7 +6150,7 @@
         <v>character_largeimage_h0134.ab</v>
       </c>
       <c r="C288">
-        <v>4242518</v>
+        <v>4321328</v>
       </c>
       <c r="D288" t="str">
         <v>Stage_1</v>
@@ -6159,7 +6159,7 @@
         <v>0</v>
       </c>
       <c r="F288" t="str">
-        <v>824b86c0e40aefc0770c167f978bc2fd4c1925a9efe1e9691c60a2eb5122c14e</v>
+        <v>f991a900453c8393e93987f9b6c3bacbba8ff7bf33d3f8cd138f2bbbed1c2bf2</v>
       </c>
     </row>
     <row r="289">
@@ -6170,7 +6170,7 @@
         <v>character_largeimage_h0135.ab</v>
       </c>
       <c r="C289">
-        <v>3266671</v>
+        <v>3301944</v>
       </c>
       <c r="D289" t="str">
         <v>Stage_1</v>
@@ -6179,7 +6179,7 @@
         <v>0</v>
       </c>
       <c r="F289" t="str">
-        <v>6242bc0a6af6955ac2a0a8d31fee0a742dd006425a34614572a0ff0a6cf3ac30</v>
+        <v>00861e17161778fc3bdd3ba9d6e2ffff239eb1228b5594bced7e8ead1abe7c3d</v>
       </c>
     </row>
     <row r="290">
@@ -6190,7 +6190,7 @@
         <v>character_largeimage_h0136.ab</v>
       </c>
       <c r="C290">
-        <v>3395405</v>
+        <v>3445363</v>
       </c>
       <c r="D290" t="str">
         <v>Stage_1</v>
@@ -6199,7 +6199,7 @@
         <v>0</v>
       </c>
       <c r="F290" t="str">
-        <v>c07b0a8e238a880228b5a27ac66e50bd4cd42ef64dd35769fbadb7ef4f9419aa</v>
+        <v>5a053b3abb2998a0adbce34c738ef08f4bef62f61fb88e12ee0361bea65ce70c</v>
       </c>
     </row>
     <row r="291">
@@ -6210,7 +6210,7 @@
         <v>character_largeimage_h0137.ab</v>
       </c>
       <c r="C291">
-        <v>5218305</v>
+        <v>5284419</v>
       </c>
       <c r="D291" t="str">
         <v>Stage_1</v>
@@ -6219,7 +6219,7 @@
         <v>0</v>
       </c>
       <c r="F291" t="str">
-        <v>0202ec87f638f3fd76d7a98dd5eb291a5d0c8125ded3ecb47f078dccd09f3a0b</v>
+        <v>3e7c4e489929a9ea8e2b078d863e93b64c6a7cd14b70735c8e372c5289801168</v>
       </c>
     </row>
     <row r="292">
@@ -6230,7 +6230,7 @@
         <v>character_largeimage_h0138.ab</v>
       </c>
       <c r="C292">
-        <v>4004656</v>
+        <v>4051724</v>
       </c>
       <c r="D292" t="str">
         <v>Stage_1</v>
@@ -6239,7 +6239,7 @@
         <v>0</v>
       </c>
       <c r="F292" t="str">
-        <v>61e12aaabe2c59ab60d879b18a7d8b89b7ddf9a8a71498e190e883353f7167c5</v>
+        <v>951279005f0d77a3d2ee3c8c62eb22bbf3e269cf8e43cef2a8ea52814cd52f6a</v>
       </c>
     </row>
     <row r="293">
@@ -6250,7 +6250,7 @@
         <v>character_largeimage_h0150.ab</v>
       </c>
       <c r="C293">
-        <v>4037956</v>
+        <v>4107766</v>
       </c>
       <c r="D293" t="str">
         <v>Stage_1</v>
@@ -6259,7 +6259,7 @@
         <v>0</v>
       </c>
       <c r="F293" t="str">
-        <v>d7d2064c4b7799f6f05c0bea7820d77879988674b6cbb863fc6ffff294516853</v>
+        <v>0f078156caaa525e93483c0225a5eab714f6954d88090396756a527b1bfe9626</v>
       </c>
     </row>
     <row r="294">
@@ -6270,7 +6270,7 @@
         <v>character_largeimage_h0151.ab</v>
       </c>
       <c r="C294">
-        <v>2589817</v>
+        <v>2819780</v>
       </c>
       <c r="D294" t="str">
         <v>Stage_1</v>
@@ -6279,7 +6279,7 @@
         <v>0</v>
       </c>
       <c r="F294" t="str">
-        <v>e319306d4c24fd23c4a7473ad0c6218a96d6abcbf8062198b2d17c4362a88c65</v>
+        <v>8a1325a32d2cd5312e8e113574be0a64fb03a96033dc64bab52f2eb6a8e8a988</v>
       </c>
     </row>
     <row r="295">
@@ -6290,7 +6290,7 @@
         <v>character_largeimage_h0152.ab</v>
       </c>
       <c r="C295">
-        <v>3232149</v>
+        <v>3342856</v>
       </c>
       <c r="D295" t="str">
         <v>Stage_1</v>
@@ -6299,7 +6299,7 @@
         <v>0</v>
       </c>
       <c r="F295" t="str">
-        <v>3d27bb9df8d360989f595c83964e2a94d8e5fd22b8f7a6c1193e7c4cc257a6dd</v>
+        <v>54d1397152473611eda4a1e39c50f549058ad929f9fdd6feba6e11cd14b1fe4b</v>
       </c>
     </row>
     <row r="296">
@@ -6310,7 +6310,7 @@
         <v>character_largeimage_h0154.ab</v>
       </c>
       <c r="C296">
-        <v>3117108</v>
+        <v>3159727</v>
       </c>
       <c r="D296" t="str">
         <v>Stage_1</v>
@@ -6319,7 +6319,7 @@
         <v>0</v>
       </c>
       <c r="F296" t="str">
-        <v>2ce3ea84a16615d2d212b5c34a99171686d2a4e36cff83cf509ebbfb367e0b2d</v>
+        <v>368e1a69e00b818bd037415c1f980a0dc6b131eeaa2385d5c1d67b5266fb17e8</v>
       </c>
     </row>
     <row r="297">
@@ -6330,7 +6330,7 @@
         <v>character_largeimage_h0157.ab</v>
       </c>
       <c r="C297">
-        <v>4175238</v>
+        <v>4298377</v>
       </c>
       <c r="D297" t="str">
         <v>Stage_1</v>
@@ -6339,7 +6339,7 @@
         <v>0</v>
       </c>
       <c r="F297" t="str">
-        <v>54cf04627438a03b859ddb2f4687af86522a3814168449e0f183e1fc0bb2a847</v>
+        <v>8e0a801b9373c4e836c966292d149d49cce065255ab5d3bc21fecee55d5ca052</v>
       </c>
     </row>
     <row r="298">
@@ -6350,7 +6350,7 @@
         <v>character_largeimage_h0159.ab</v>
       </c>
       <c r="C298">
-        <v>3438941</v>
+        <v>3507202</v>
       </c>
       <c r="D298" t="str">
         <v>Stage_1</v>
@@ -6359,7 +6359,7 @@
         <v>0</v>
       </c>
       <c r="F298" t="str">
-        <v>69896b88d7b878ed3a9ae0ccaac412a1dcead089da47686152318321fd1de238</v>
+        <v>ece817db78b026802e23cd361a328fdfc04c5e0877455dfec144ea11733088e0</v>
       </c>
     </row>
     <row r="299">
@@ -6370,7 +6370,7 @@
         <v>character_largeimage_h0161.ab</v>
       </c>
       <c r="C299">
-        <v>4097341</v>
+        <v>4138913</v>
       </c>
       <c r="D299" t="str">
         <v>Stage_1</v>
@@ -6379,7 +6379,7 @@
         <v>0</v>
       </c>
       <c r="F299" t="str">
-        <v>a660b7d68977f955ba7ceced1adadab138e4fc76cc5208da43d9369b9dc59e23</v>
+        <v>f4ead470b434cdccdb9815c0e7e9f0bae3aecc725ca9a0372dd65197cae12ab9</v>
       </c>
     </row>
     <row r="300">
@@ -6390,7 +6390,7 @@
         <v>character_largeimage_h0162.ab</v>
       </c>
       <c r="C300">
-        <v>750978</v>
+        <v>754225</v>
       </c>
       <c r="D300" t="str">
         <v>Stage_1</v>
@@ -6399,7 +6399,7 @@
         <v>0</v>
       </c>
       <c r="F300" t="str">
-        <v>38de7487f089a655ef8ef162c0d101525d83e7f406dabf459b3a9c8390380122</v>
+        <v>5bd0247f2a6db043bda85f276ec10fc744e4b14b081f804ec906cba6c419f092</v>
       </c>
     </row>
     <row r="301">
@@ -6410,7 +6410,7 @@
         <v>character_largeimage_h0163.ab</v>
       </c>
       <c r="C301">
-        <v>2078410</v>
+        <v>2086379</v>
       </c>
       <c r="D301" t="str">
         <v>Stage_1</v>
@@ -6419,7 +6419,7 @@
         <v>0</v>
       </c>
       <c r="F301" t="str">
-        <v>6cb30643d3b6c9be725cce1f64f07b98426ba01da9ad3e9b127862d8b8dbccf8</v>
+        <v>a6834fcbea342b855747af107409d1e463fe05972262bc8241666b3ad8688197</v>
       </c>
     </row>
     <row r="302">
@@ -6430,7 +6430,7 @@
         <v>character_largeimage_h0164.ab</v>
       </c>
       <c r="C302">
-        <v>562150</v>
+        <v>570685</v>
       </c>
       <c r="D302" t="str">
         <v>Stage_1</v>
@@ -6439,7 +6439,7 @@
         <v>0</v>
       </c>
       <c r="F302" t="str">
-        <v>8950a764fe423f950c36d8d8c330f207f071139213a0be60bebb3ded5fe329cd</v>
+        <v>5ec3ee0a67e827f7a4f39dc1e14401b0a3dfb8ae7ce2b00fa603ea92c4518a15</v>
       </c>
     </row>
     <row r="303">
@@ -6450,7 +6450,7 @@
         <v>character_largeimage_h0165.ab</v>
       </c>
       <c r="C303">
-        <v>796221</v>
+        <v>808465</v>
       </c>
       <c r="D303" t="str">
         <v>Stage_1</v>
@@ -6459,7 +6459,7 @@
         <v>0</v>
       </c>
       <c r="F303" t="str">
-        <v>1e0a607d278479f68829b034dc3e31e3ff73f88dee2ff778c5c4398d845d97e6</v>
+        <v>f7d29014b00ed7d13067dfe998157ee085a6841a0b97cc6a1685f7064f46eb30</v>
       </c>
     </row>
     <row r="304">
@@ -6470,7 +6470,7 @@
         <v>character_largeimage_h0166.ab</v>
       </c>
       <c r="C304">
-        <v>770702</v>
+        <v>779788</v>
       </c>
       <c r="D304" t="str">
         <v>Stage_1</v>
@@ -6479,7 +6479,7 @@
         <v>0</v>
       </c>
       <c r="F304" t="str">
-        <v>e434b87a3241dae1f7d81acd86f8102e93895ec6ab30272f57fd9721c6d1bcfa</v>
+        <v>9f245c6bb17ea8e1ddc730ed1d0e8401e00609f627cc065193ae82a746fc1553</v>
       </c>
     </row>
     <row r="305">
@@ -6490,7 +6490,7 @@
         <v>character_largeimage_h0167.ab</v>
       </c>
       <c r="C305">
-        <v>820636</v>
+        <v>836821</v>
       </c>
       <c r="D305" t="str">
         <v>Stage_1</v>
@@ -6499,7 +6499,7 @@
         <v>0</v>
       </c>
       <c r="F305" t="str">
-        <v>c5d28976c731cae2d777b0675466878565052af34c557d71d7009162fbe813e8</v>
+        <v>2f4d94a8947fbc1d5157c8c6a1c8c8fb740555b87d865d644b085e9e7e0a7589</v>
       </c>
     </row>
     <row r="306">
@@ -6510,7 +6510,7 @@
         <v>character_largeimage_h0168.ab</v>
       </c>
       <c r="C306">
-        <v>817925</v>
+        <v>830222</v>
       </c>
       <c r="D306" t="str">
         <v>Stage_1</v>
@@ -6519,7 +6519,7 @@
         <v>0</v>
       </c>
       <c r="F306" t="str">
-        <v>d596388ecc3145e4279aed0ec7f8b25c8a5abbfeaf17c76560902f42fd6fd46c</v>
+        <v>1ee0d2ea76c558612948def7d01901529e2d0f0c21a0c245093dff0a123c5817</v>
       </c>
     </row>
     <row r="307">
@@ -6530,7 +6530,7 @@
         <v>character_largeimage_h0169.ab</v>
       </c>
       <c r="C307">
-        <v>830548</v>
+        <v>839535</v>
       </c>
       <c r="D307" t="str">
         <v>Stage_1</v>
@@ -6539,7 +6539,7 @@
         <v>0</v>
       </c>
       <c r="F307" t="str">
-        <v>694f5ecefeccf73e0d79fcbde42e9a7552d32c2dc69d3894af27e1b92e9c9327</v>
+        <v>8784aca63a4c2dc8c4de8d78782567cb852a07cab7fbcb3a95acd63577e06628</v>
       </c>
     </row>
     <row r="308">
@@ -6550,7 +6550,7 @@
         <v>character_largeimage_h0170.ab</v>
       </c>
       <c r="C308">
-        <v>802577</v>
+        <v>810872</v>
       </c>
       <c r="D308" t="str">
         <v>Stage_1</v>
@@ -6559,7 +6559,7 @@
         <v>0</v>
       </c>
       <c r="F308" t="str">
-        <v>22ce1b1174d04d190ad9105ae99b8268e4b5b4bce7d43dbd7bac3a6930162aa5</v>
+        <v>d8c20e4a9038880762acf8181d60001a74eadb87b875dc8e9bfd32101675b5d7</v>
       </c>
     </row>
     <row r="309">
@@ -6570,7 +6570,7 @@
         <v>character_largeimage_h0171.ab</v>
       </c>
       <c r="C309">
-        <v>782755</v>
+        <v>787286</v>
       </c>
       <c r="D309" t="str">
         <v>Stage_1</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="F309" t="str">
-        <v>fa33b1b6747266a27a42f0fe654fadc5c45d1b7ca97b1b8f2d52b3b0d3c7c647</v>
+        <v>db26a7a8221837bcb8d25dc865fab19d6da0cb87ab8b7d8756e236c6990523f1</v>
       </c>
     </row>
     <row r="310">
@@ -6590,7 +6590,7 @@
         <v>character_largeimage_h0172.ab</v>
       </c>
       <c r="C310">
-        <v>783966</v>
+        <v>784571</v>
       </c>
       <c r="D310" t="str">
         <v>Stage_1</v>
@@ -6599,7 +6599,7 @@
         <v>0</v>
       </c>
       <c r="F310" t="str">
-        <v>6c80e0e30faa685a6e8861942e4283309563a109980a7b43ad0f6c8f7b3fd812</v>
+        <v>0bc39452899835996739dd976e9d551b34b1242d9bb93103ffdd3926e3c7aa7c</v>
       </c>
     </row>
     <row r="311">
@@ -6610,7 +6610,7 @@
         <v>character_largeimage_h0174.ab</v>
       </c>
       <c r="C311">
-        <v>818586</v>
+        <v>822130</v>
       </c>
       <c r="D311" t="str">
         <v>Stage_1</v>
@@ -6619,7 +6619,7 @@
         <v>0</v>
       </c>
       <c r="F311" t="str">
-        <v>4189f28a4927c0faa536e86f0b2978390507c7e2a3f7182854f18827713a9ae6</v>
+        <v>6556cfa1a36ae7f9877eb6f735c39f67810aa6343b29bcf11f7281da664e2669</v>
       </c>
     </row>
     <row r="312">
@@ -6630,7 +6630,7 @@
         <v>character_largeimage_h0175.ab</v>
       </c>
       <c r="C312">
-        <v>804643</v>
+        <v>812319</v>
       </c>
       <c r="D312" t="str">
         <v>Stage_1</v>
@@ -6639,7 +6639,7 @@
         <v>0</v>
       </c>
       <c r="F312" t="str">
-        <v>5779e4f64a588b7ba406c3f77cbe5a7623a881612f260d82d0fdd015454ce4e5</v>
+        <v>ffb4bfcc2a2a493a696aa850275fc0fb8ace6d95381caaed6371b28ee3561265</v>
       </c>
     </row>
     <row r="313">
@@ -6650,7 +6650,7 @@
         <v>character_largeimage_h0176.ab</v>
       </c>
       <c r="C313">
-        <v>815725</v>
+        <v>832083</v>
       </c>
       <c r="D313" t="str">
         <v>Stage_1</v>
@@ -6659,7 +6659,7 @@
         <v>0</v>
       </c>
       <c r="F313" t="str">
-        <v>670e37924a1dc65b3257f7ea9ea57af53ef77c50e363aa558450edda73a3971e</v>
+        <v>b2b06cf735b412596f554663060c48a8a49bae9f616d38038d68fc0839aff1fd</v>
       </c>
     </row>
     <row r="314">
@@ -6670,7 +6670,7 @@
         <v>character_largeimage_h0177.ab</v>
       </c>
       <c r="C314">
-        <v>787384</v>
+        <v>793852</v>
       </c>
       <c r="D314" t="str">
         <v>Stage_1</v>
@@ -6679,7 +6679,7 @@
         <v>0</v>
       </c>
       <c r="F314" t="str">
-        <v>72c7aa064bb39180b9f70c05d799875beb09b87e0863e05312f2b613f6296aaa</v>
+        <v>b3c38ff4669b9a7c5430333cf7cd8b6438a0da6a57bfff3aa7202b1b03a545f0</v>
       </c>
     </row>
     <row r="315">
@@ -6690,7 +6690,7 @@
         <v>character_largeimage_h0179.ab</v>
       </c>
       <c r="C315">
-        <v>3226990</v>
+        <v>3287095</v>
       </c>
       <c r="D315" t="str">
         <v>Stage_1</v>
@@ -6699,7 +6699,7 @@
         <v>0</v>
       </c>
       <c r="F315" t="str">
-        <v>78cff653adce00a0271b9b386462b605c5155aa5328a916a2c1e7472ef53800b</v>
+        <v>2fd545a1e8137450f41fe2818b0bed7e6bced7d455a907f5b3709e3d62c976b8</v>
       </c>
     </row>
     <row r="316">
@@ -6710,7 +6710,7 @@
         <v>character_largeimage_h0183.ab</v>
       </c>
       <c r="C316">
-        <v>3520720</v>
+        <v>3611626</v>
       </c>
       <c r="D316" t="str">
         <v>Stage_1</v>
@@ -6719,7 +6719,7 @@
         <v>0</v>
       </c>
       <c r="F316" t="str">
-        <v>f0b995ef5d339afb76d7292b967c27ba26b3f240505eddecf275b18d014acabe</v>
+        <v>4d0a46d67983e01e2f68f3175dbfd05920ccd0cacef5b6f1da91df45958c4091</v>
       </c>
     </row>
     <row r="317">
@@ -6730,7 +6730,7 @@
         <v>character_largeimage_h0185.ab</v>
       </c>
       <c r="C317">
-        <v>2771089</v>
+        <v>2887814</v>
       </c>
       <c r="D317" t="str">
         <v>Stage_1</v>
@@ -6739,7 +6739,7 @@
         <v>0</v>
       </c>
       <c r="F317" t="str">
-        <v>bfa55cdf6f0750acee979cdf5cdc7840f4de769c34b7e38431644cf7a21ae6ba</v>
+        <v>a353d592fd1186f66c97fb8e5f02767935db28f3aaece7d7aeaf527baf565473</v>
       </c>
     </row>
     <row r="318">
@@ -6750,7 +6750,7 @@
         <v>character_largeimage_h0186.ab</v>
       </c>
       <c r="C318">
-        <v>3669448</v>
+        <v>3782998</v>
       </c>
       <c r="D318" t="str">
         <v>Stage_1</v>
@@ -6759,7 +6759,7 @@
         <v>0</v>
       </c>
       <c r="F318" t="str">
-        <v>d9f408df598bbed9f98731ebbbc24dd54c87d8faf6db4f9f6ed0bbdc627164f9</v>
+        <v>e887bdaac2712c347080e0c78e9ce0da806e59b5864813964d5b3e8d56556a4b</v>
       </c>
     </row>
     <row r="319">
@@ -6770,7 +6770,7 @@
         <v>character_largeimage_h0190.ab</v>
       </c>
       <c r="C319">
-        <v>3422472</v>
+        <v>3523302</v>
       </c>
       <c r="D319" t="str">
         <v>Stage_1</v>
@@ -6779,7 +6779,7 @@
         <v>0</v>
       </c>
       <c r="F319" t="str">
-        <v>6a96ed9bc7dae9b6a94560a7a2a2c4c968aa9c666608866700784adbd28efe9e</v>
+        <v>c37471e3d841326c3f81f95f362e5916ea1e8a2bde90c76aad81d5a54ae77f0a</v>
       </c>
     </row>
     <row r="320">
@@ -6790,7 +6790,7 @@
         <v>character_largeimage_h0191.ab</v>
       </c>
       <c r="C320">
-        <v>808827</v>
+        <v>815465</v>
       </c>
       <c r="D320" t="str">
         <v>Stage_1</v>
@@ -6799,7 +6799,7 @@
         <v>0</v>
       </c>
       <c r="F320" t="str">
-        <v>b849caca8249392ed9cb5fbc69ad00daebd22a57c5dbe8dd0ef8e36a983745d0</v>
+        <v>861381d75e29da73fdd1a7425e4199b9463d9a17e8579610d4554fafc84f2dd5</v>
       </c>
     </row>
     <row r="321">
@@ -6810,7 +6810,7 @@
         <v>character_largeimage_h0192.ab</v>
       </c>
       <c r="C321">
-        <v>792810</v>
+        <v>799276</v>
       </c>
       <c r="D321" t="str">
         <v>Stage_1</v>
@@ -6819,7 +6819,7 @@
         <v>0</v>
       </c>
       <c r="F321" t="str">
-        <v>2b02b549d1958dcd7765bd6847f70978d863dd130ffa8e646f5fdc031cdc8351</v>
+        <v>88ad69b50e3eea76d778cd77c3603bc9642e6ef526171388f499c17a7243c8a3</v>
       </c>
     </row>
     <row r="322">
@@ -6830,7 +6830,7 @@
         <v>character_largeimage_h0193.ab</v>
       </c>
       <c r="C322">
-        <v>725025</v>
+        <v>728883</v>
       </c>
       <c r="D322" t="str">
         <v>Stage_1</v>
@@ -6839,7 +6839,7 @@
         <v>0</v>
       </c>
       <c r="F322" t="str">
-        <v>c54d37a9842bc35f6a53430f7b78bf25398c17e364d4fd7af908f2f9e6a41a4a</v>
+        <v>1b1c1582957557248ec735a4e70a7293b403c5e97f92d1fc7bafb5d8b66443a1</v>
       </c>
     </row>
     <row r="323">
@@ -6850,7 +6850,7 @@
         <v>character_largeimage_h0194.ab</v>
       </c>
       <c r="C323">
-        <v>785465</v>
+        <v>789936</v>
       </c>
       <c r="D323" t="str">
         <v>Stage_1</v>
@@ -6859,7 +6859,7 @@
         <v>0</v>
       </c>
       <c r="F323" t="str">
-        <v>36cc8950d881f726e02b7e855085ff44ade33666176018a788d9faec4f87090f</v>
+        <v>1bc2f401429d59a8b25f651646b9cf6fda92718b1228316a7c79a85cf7f9fec3</v>
       </c>
     </row>
     <row r="324">
@@ -6870,7 +6870,7 @@
         <v>character_largeimage_h0196.ab</v>
       </c>
       <c r="C324">
-        <v>815412</v>
+        <v>824494</v>
       </c>
       <c r="D324" t="str">
         <v>Stage_1</v>
@@ -6879,7 +6879,7 @@
         <v>0</v>
       </c>
       <c r="F324" t="str">
-        <v>6a6748aa0319948886214cb8c63c8cec143ea660d596ef8d6d978fdd3511b82a</v>
+        <v>a8a0f4ede88d582f8bd9c1c52c65873bf1e26591a2b886fe46bf879b95a2c4bf</v>
       </c>
     </row>
     <row r="325">
@@ -6890,7 +6890,7 @@
         <v>character_largeimage_h0197.ab</v>
       </c>
       <c r="C325">
-        <v>798179</v>
+        <v>804734</v>
       </c>
       <c r="D325" t="str">
         <v>Stage_1</v>
@@ -6899,7 +6899,7 @@
         <v>0</v>
       </c>
       <c r="F325" t="str">
-        <v>c7d74889421f50783e19f16bfee0461d528a543471b9b45ae4aa772b774876c0</v>
+        <v>145e233e1a2bc394f6434bd4a9c868d7ac98206e4d3635b6bf1a5ce240472d82</v>
       </c>
     </row>
     <row r="326">
@@ -6910,7 +6910,7 @@
         <v>character_largeimage_h0198.ab</v>
       </c>
       <c r="C326">
-        <v>781740</v>
+        <v>790099</v>
       </c>
       <c r="D326" t="str">
         <v>Stage_1</v>
@@ -6919,7 +6919,7 @@
         <v>0</v>
       </c>
       <c r="F326" t="str">
-        <v>2055d9937e4e0b0a8811536085a0478651eb0f01fc6dfec0c170ac2391a1d44b</v>
+        <v>041dc1bebe7698ec8b12add414348eb307b1389077740befed68668804cc5498</v>
       </c>
     </row>
     <row r="327">
@@ -6930,7 +6930,7 @@
         <v>character_largeimage_h0199.ab</v>
       </c>
       <c r="C327">
-        <v>723932</v>
+        <v>726753</v>
       </c>
       <c r="D327" t="str">
         <v>Stage_1</v>
@@ -6939,7 +6939,7 @@
         <v>0</v>
       </c>
       <c r="F327" t="str">
-        <v>54fb809610bab1d842ba2f6c9092c659035994f46801d54970375ee2ea3c5dac</v>
+        <v>1c269f49dcf9264a1de0e05d63f85cd548a783412405942cb46510d2f838287e</v>
       </c>
     </row>
     <row r="328">
@@ -6950,7 +6950,7 @@
         <v>character_largeimage_h0200.ab</v>
       </c>
       <c r="C328">
-        <v>817588</v>
+        <v>827990</v>
       </c>
       <c r="D328" t="str">
         <v>Stage_1</v>
@@ -6959,7 +6959,7 @@
         <v>0</v>
       </c>
       <c r="F328" t="str">
-        <v>b19a3f8eb2a00ec2e2fafcdb4ae347a5e27c5d935a48a989071d64f8daa7c711</v>
+        <v>91087b50bd2580ded288d7205d57a3bc5cddc78a391babbb46b98274166d6ef5</v>
       </c>
     </row>
     <row r="329">
@@ -6970,7 +6970,7 @@
         <v>character_largeimage_h0201.ab</v>
       </c>
       <c r="C329">
-        <v>835275</v>
+        <v>841759</v>
       </c>
       <c r="D329" t="str">
         <v>Stage_1</v>
@@ -6979,7 +6979,7 @@
         <v>0</v>
       </c>
       <c r="F329" t="str">
-        <v>976aa2fcf5e09deb4a3ab659fb8a8e9afc3c27bbb832920dde15ea1cb2d990db</v>
+        <v>179a0195c61777cccb0eee3fac46e1aa1600fe16c383001d535fe039e6529f0d</v>
       </c>
     </row>
     <row r="330">
@@ -6990,7 +6990,7 @@
         <v>character_largeimage_h0203.ab</v>
       </c>
       <c r="C330">
-        <v>810774</v>
+        <v>822144</v>
       </c>
       <c r="D330" t="str">
         <v>Stage_1</v>
@@ -6999,7 +6999,7 @@
         <v>0</v>
       </c>
       <c r="F330" t="str">
-        <v>8a135d2928943c0ee8f93db24bb041ac0925554dfa5e69c1d8ed784c1517bab2</v>
+        <v>a80104425e4ab86cec6a8b44b10e33d121f06f849fdeb851fb5c7412b76bc3a3</v>
       </c>
     </row>
     <row r="331">
@@ -7010,7 +7010,7 @@
         <v>character_largeimage_h0208.ab</v>
       </c>
       <c r="C331">
-        <v>782587</v>
+        <v>791388</v>
       </c>
       <c r="D331" t="str">
         <v>Stage_1</v>
@@ -7019,7 +7019,7 @@
         <v>0</v>
       </c>
       <c r="F331" t="str">
-        <v>c8b75ce568e328d85fb21c02c1ab9c4309d261e1771ad612854e065b528e80b6</v>
+        <v>f7e06078e8d7aafb507d9d52ab4b786d15fd16de64f37319169c4d250b5f37d7</v>
       </c>
     </row>
     <row r="332">
@@ -7030,7 +7030,7 @@
         <v>character_largeimage_h0209.ab</v>
       </c>
       <c r="C332">
-        <v>832318</v>
+        <v>839927</v>
       </c>
       <c r="D332" t="str">
         <v>Stage_1</v>
@@ -7039,7 +7039,7 @@
         <v>0</v>
       </c>
       <c r="F332" t="str">
-        <v>551c9d38c10aaa35dc668fa95d4ab634ea90021e999ec43e3b3692a33f37308c</v>
+        <v>1870f4c4b20c4069b56afedc46a61e48ae092c8bee2c22b827d3aeaec5367cc4</v>
       </c>
     </row>
     <row r="333">
@@ -7050,7 +7050,7 @@
         <v>character_largeimage_h0210.ab</v>
       </c>
       <c r="C333">
-        <v>825127</v>
+        <v>836781</v>
       </c>
       <c r="D333" t="str">
         <v>Stage_1</v>
@@ -7059,7 +7059,7 @@
         <v>0</v>
       </c>
       <c r="F333" t="str">
-        <v>8589c6aa5e2a1402cd077069b6a7c5b7963e4990bf24ef1ae425fa5b6fe77851</v>
+        <v>1d29f0f5e2407558c303354f9bb9bab64602432c6e06105deacd9e0bb4db8ac3</v>
       </c>
     </row>
     <row r="334">
@@ -7070,7 +7070,7 @@
         <v>character_largeimage_h0213.ab</v>
       </c>
       <c r="C334">
-        <v>765539</v>
+        <v>775664</v>
       </c>
       <c r="D334" t="str">
         <v>Stage_1</v>
@@ -7079,7 +7079,7 @@
         <v>0</v>
       </c>
       <c r="F334" t="str">
-        <v>7ceaafb884feff69f0cad1625495c0b9623b4abcdb13918dee5ec9782b9e7c6f</v>
+        <v>994975a57ab2adcf55bfd1f661b8bd16939492c932c8c7b1582aebc3bbf62d90</v>
       </c>
     </row>
     <row r="335">
@@ -7090,7 +7090,7 @@
         <v>character_largeimage_h0215.ab</v>
       </c>
       <c r="C335">
-        <v>759394</v>
+        <v>763689</v>
       </c>
       <c r="D335" t="str">
         <v>Stage_1</v>
@@ -7099,7 +7099,7 @@
         <v>0</v>
       </c>
       <c r="F335" t="str">
-        <v>8e6f4b217298f11e5493e50b5f41aefd8b49f8f0d3d68747e30ebde5fcb495af</v>
+        <v>193cadf68600b899b6d2ebf52e9165d311f0a8dd7d506aa9439b6803449c6bd8</v>
       </c>
     </row>
     <row r="336">
@@ -7110,7 +7110,7 @@
         <v>character_largeimage_h0216.ab</v>
       </c>
       <c r="C336">
-        <v>736440</v>
+        <v>742027</v>
       </c>
       <c r="D336" t="str">
         <v>Stage_1</v>
@@ -7119,7 +7119,7 @@
         <v>0</v>
       </c>
       <c r="F336" t="str">
-        <v>1ba74f46cf112a8fbabd9dbe94f3e47c6b8fae0f59caf2cbd33d263176d536eb</v>
+        <v>4e7021fe0993db1b8ed3c72ad70656bd0c7dd43e536d7ff72c1b806826437427</v>
       </c>
     </row>
     <row r="337">
@@ -7130,7 +7130,7 @@
         <v>character_largeimage_h0217.ab</v>
       </c>
       <c r="C337">
-        <v>828877</v>
+        <v>832922</v>
       </c>
       <c r="D337" t="str">
         <v>Stage_1</v>
@@ -7139,7 +7139,7 @@
         <v>0</v>
       </c>
       <c r="F337" t="str">
-        <v>84f2c50e0b0f149fc2a5da0a87b10af733ba6c544daf4e3f9dd4c2c2e702fe60</v>
+        <v>09b3b2ea5b513ba3782d57a1ff07b360935324cf4280ca91382fa051fe159df3</v>
       </c>
     </row>
     <row r="338">
@@ -7150,7 +7150,7 @@
         <v>character_largeimage_h0219.ab</v>
       </c>
       <c r="C338">
-        <v>817529</v>
+        <v>822380</v>
       </c>
       <c r="D338" t="str">
         <v>Stage_1</v>
@@ -7159,7 +7159,7 @@
         <v>0</v>
       </c>
       <c r="F338" t="str">
-        <v>87101cadb86464c4b19e924805d524f2a1700367f5a505fb1ae5f7bc289886f2</v>
+        <v>a88e28af6f067b331262ad9a8ee4a077506b585378095113a38efc764fe9f55c</v>
       </c>
     </row>
     <row r="339">
@@ -7170,7 +7170,7 @@
         <v>character_largeimage_h0220.ab</v>
       </c>
       <c r="C339">
-        <v>689304</v>
+        <v>698469</v>
       </c>
       <c r="D339" t="str">
         <v>Stage_1</v>
@@ -7179,7 +7179,7 @@
         <v>0</v>
       </c>
       <c r="F339" t="str">
-        <v>0838c201cac6aa71480937da9424b05a4dfbe7d617bb0811c64a08f8fbc44329</v>
+        <v>ef62ee264fbffd71e2b53882cef79c1f1a497ca8d4cf8ea2de1168387e72f913</v>
       </c>
     </row>
     <row r="340">
@@ -7190,7 +7190,7 @@
         <v>character_largeimage_h0221.ab</v>
       </c>
       <c r="C340">
-        <v>774852</v>
+        <v>778961</v>
       </c>
       <c r="D340" t="str">
         <v>Stage_1</v>
@@ -7199,7 +7199,7 @@
         <v>0</v>
       </c>
       <c r="F340" t="str">
-        <v>260c6ef2907458fb0b24e79b4fdc8f2daf248b54e954c202b89e87fa45a79917</v>
+        <v>29e4f3612029c5cc01c1b0edc87744cfb2f17752e92a407453e421fef7a9b29c</v>
       </c>
     </row>
     <row r="341">
@@ -7210,7 +7210,7 @@
         <v>character_largeimage_h0224.ab</v>
       </c>
       <c r="C341">
-        <v>734210</v>
+        <v>737722</v>
       </c>
       <c r="D341" t="str">
         <v>Stage_1</v>
@@ -7219,7 +7219,7 @@
         <v>0</v>
       </c>
       <c r="F341" t="str">
-        <v>8f88f1319c7298174ac3aa8a82b6986761610cbb74ef14c82c7e1ede1fc0b15d</v>
+        <v>db65350b6783802e475a4982ac8b337cee82401f6a48d58e3da9cc09ba285930</v>
       </c>
     </row>
     <row r="342">
@@ -7230,7 +7230,7 @@
         <v>character_largeimage_h0226.ab</v>
       </c>
       <c r="C342">
-        <v>761235</v>
+        <v>764757</v>
       </c>
       <c r="D342" t="str">
         <v>Stage_1</v>
@@ -7239,7 +7239,7 @@
         <v>0</v>
       </c>
       <c r="F342" t="str">
-        <v>6bc4336199b83047446c82c6a230574f05b6e130a41d9f33770766aeac9436f2</v>
+        <v>432f241690d55bfccbc4f2518565eff071bf11f62f4ac9e693845d3390259c55</v>
       </c>
     </row>
     <row r="343">
@@ -7250,7 +7250,7 @@
         <v>character_largeimage_h0227.ab</v>
       </c>
       <c r="C343">
-        <v>786760</v>
+        <v>790503</v>
       </c>
       <c r="D343" t="str">
         <v>Stage_1</v>
@@ -7259,7 +7259,7 @@
         <v>0</v>
       </c>
       <c r="F343" t="str">
-        <v>0ec3a2ddea2c5f14762b1d53cf2a6c9b959342b7c2d7cb8c53f5de78389a1a9f</v>
+        <v>8c8a74a30cbfe4d572794775b409667601eef4713ad51f372516b7e33e2f41da</v>
       </c>
     </row>
     <row r="344">
@@ -7270,7 +7270,7 @@
         <v>character_largeimage_h0230.ab</v>
       </c>
       <c r="C344">
-        <v>795281</v>
+        <v>798854</v>
       </c>
       <c r="D344" t="str">
         <v>Stage_1</v>
@@ -7279,7 +7279,7 @@
         <v>0</v>
       </c>
       <c r="F344" t="str">
-        <v>29ca1d6c0d021948d89276ee888dd3f034a0a0efe30c90a4af695d44e14e409d</v>
+        <v>432046e5cb84e92192b56d3837c402a8dd045328a3ed642a370cca17d2fe1bf9</v>
       </c>
     </row>
     <row r="345">
@@ -7290,7 +7290,7 @@
         <v>character_largeimage_h0232.ab</v>
       </c>
       <c r="C345">
-        <v>2084078</v>
+        <v>2091051</v>
       </c>
       <c r="D345" t="str">
         <v>Stage_1</v>
@@ -7299,7 +7299,7 @@
         <v>0</v>
       </c>
       <c r="F345" t="str">
-        <v>dfe3d19d68019845ae4ece6c9574a5495c0a7e2d7b2bd5731672a07a39334105</v>
+        <v>6a556cee1be460b56ffdd6407da14115a367f0d40901d3aca1d029857fc6733a</v>
       </c>
     </row>
     <row r="346">
@@ -7310,7 +7310,7 @@
         <v>character_largeimage_h0233.ab</v>
       </c>
       <c r="C346">
-        <v>3216689</v>
+        <v>3246146</v>
       </c>
       <c r="D346" t="str">
         <v>Stage_1</v>
@@ -7319,7 +7319,7 @@
         <v>0</v>
       </c>
       <c r="F346" t="str">
-        <v>aef3828cf7528b7b93a7e0d7408ad22b191692c1de64519b9f768867bc7b11a4</v>
+        <v>696d0c22e038c0eb4964d13e844322c7db7d84e1650e77ba3cd8f25b6d0764b6</v>
       </c>
     </row>
     <row r="347">
@@ -7330,7 +7330,7 @@
         <v>character_largeimage_h0234.ab</v>
       </c>
       <c r="C347">
-        <v>3069501</v>
+        <v>3085993</v>
       </c>
       <c r="D347" t="str">
         <v>Stage_1</v>
@@ -7339,7 +7339,7 @@
         <v>0</v>
       </c>
       <c r="F347" t="str">
-        <v>b2537f99faf6708c1597ef8c25e62f4355e6f32459e915e721ed323c337327f5</v>
+        <v>88cd8ed981def631367e0540dd47053faec8826f2e82686cc0399ffe1eefc3f2</v>
       </c>
     </row>
     <row r="348">
@@ -7350,7 +7350,7 @@
         <v>character_largeimage_h0235.ab</v>
       </c>
       <c r="C348">
-        <v>2226899</v>
+        <v>2241883</v>
       </c>
       <c r="D348" t="str">
         <v>Stage_1</v>
@@ -7359,7 +7359,7 @@
         <v>0</v>
       </c>
       <c r="F348" t="str">
-        <v>465a56a4e220bd39de58cf59e525a9aa2450c8f08870c2d8368c8fd7339d7ac1</v>
+        <v>e67544a26a7a0a03f4a3d70819dd6dee3a3f40e3f827a85594e2ad40c92786be</v>
       </c>
     </row>
     <row r="349">
@@ -7370,7 +7370,7 @@
         <v>character_largeimage_h0236.ab</v>
       </c>
       <c r="C349">
-        <v>2098839</v>
+        <v>2121603</v>
       </c>
       <c r="D349" t="str">
         <v>Stage_1</v>
@@ -7379,7 +7379,7 @@
         <v>0</v>
       </c>
       <c r="F349" t="str">
-        <v>861fe308f08e7ddd65e35b46d651cf70e0bf5a6ece93c69910f51b1910bc60b5</v>
+        <v>3d6024b8e33fbc5476bd84d781ddcbd787c703915354d4d5e8db938243dd90c1</v>
       </c>
     </row>
     <row r="350">
@@ -7390,7 +7390,7 @@
         <v>character_largeimage_h0237.ab</v>
       </c>
       <c r="C350">
-        <v>2342886</v>
+        <v>2353969</v>
       </c>
       <c r="D350" t="str">
         <v>Stage_1</v>
@@ -7399,7 +7399,7 @@
         <v>0</v>
       </c>
       <c r="F350" t="str">
-        <v>8e06426b9ef92077864f5f81f17f7da0e94162e7d8d2e1b0da5e5b0492ef2638</v>
+        <v>574ac8f6ab62535e14bfd73f3b6f5c095ef64ff52c9d899b9f52ee9ec0eda963</v>
       </c>
     </row>
     <row r="351">
@@ -7410,7 +7410,7 @@
         <v>character_largeimage_h0238.ab</v>
       </c>
       <c r="C351">
-        <v>848742</v>
+        <v>853052</v>
       </c>
       <c r="D351" t="str">
         <v>Stage_1</v>
@@ -7419,7 +7419,7 @@
         <v>0</v>
       </c>
       <c r="F351" t="str">
-        <v>eebcd817999436e6de65383cf189412ca4c12f9058f159cae52fef68555ccbbe</v>
+        <v>0193a5f8bda431bb7b8b604c3096a56eee38e02a18110ec0798cf3fc5a38a355</v>
       </c>
     </row>
     <row r="352">
@@ -7430,7 +7430,7 @@
         <v>character_largeimage_h0239.ab</v>
       </c>
       <c r="C352">
-        <v>812643</v>
+        <v>817584</v>
       </c>
       <c r="D352" t="str">
         <v>Stage_1</v>
@@ -7439,7 +7439,7 @@
         <v>0</v>
       </c>
       <c r="F352" t="str">
-        <v>a53f4a28d98d240b9ebf9ab9a21802b22ca3f01a9cbe43c7605471e8b69e8c22</v>
+        <v>150dfad8e872fa7eb8b883cf69bc3e553bcc81f10e478647fa0708d9cd976531</v>
       </c>
     </row>
     <row r="353">
@@ -7450,7 +7450,7 @@
         <v>character_largeimage_h0240.ab</v>
       </c>
       <c r="C353">
-        <v>819235</v>
+        <v>830373</v>
       </c>
       <c r="D353" t="str">
         <v>Stage_1</v>
@@ -7459,7 +7459,7 @@
         <v>0</v>
       </c>
       <c r="F353" t="str">
-        <v>416f932b7f7a15646a65e059ebb8f7a18b000b78fcdbdf6f5b0f6e99feee60a4</v>
+        <v>656ff6bffc2dcbb184bf843c5d38594ef0e76f60eef9a6f1501fb2a9bc7d3a8e</v>
       </c>
     </row>
     <row r="354">
@@ -7470,7 +7470,7 @@
         <v>character_largeimage_h0241.ab</v>
       </c>
       <c r="C354">
-        <v>824553</v>
+        <v>828429</v>
       </c>
       <c r="D354" t="str">
         <v>Stage_1</v>
@@ -7479,7 +7479,7 @@
         <v>0</v>
       </c>
       <c r="F354" t="str">
-        <v>0b513268be4ebfb7b998c19702c89e727831fcc9a6c44799632362eae33a7917</v>
+        <v>c2919c075f844e7ccca5f2d2d54a7d6792db9fc190edf883ee9fcb6c99d68704</v>
       </c>
     </row>
     <row r="355">
@@ -7490,7 +7490,7 @@
         <v>character_largeimage_h0243.ab</v>
       </c>
       <c r="C355">
-        <v>810706</v>
+        <v>817759</v>
       </c>
       <c r="D355" t="str">
         <v>Stage_1</v>
@@ -7499,7 +7499,7 @@
         <v>0</v>
       </c>
       <c r="F355" t="str">
-        <v>cb1bfb37585c135009aab9b0583e3d251dabfdd75817f9cb75d7b54ab1d86778</v>
+        <v>dca9a44b45f14dfa403e1eb841c66765e55ff84aa6b7c5567c3f31f4b1a36e2a</v>
       </c>
     </row>
     <row r="356">
@@ -7510,7 +7510,7 @@
         <v>character_largeimage_h0244.ab</v>
       </c>
       <c r="C356">
-        <v>778524</v>
+        <v>791076</v>
       </c>
       <c r="D356" t="str">
         <v>Stage_1</v>
@@ -7519,7 +7519,7 @@
         <v>0</v>
       </c>
       <c r="F356" t="str">
-        <v>41a7d16ec3600f10cab4dee7f9c437082021de8e22902f3b82af1db8c5b220fb</v>
+        <v>387f94e41dc18fc894f86423a1314188c70221c86640a6bf46353595d793098c</v>
       </c>
     </row>
     <row r="357">
@@ -7530,7 +7530,7 @@
         <v>character_largeimage_h0245.ab</v>
       </c>
       <c r="C357">
-        <v>795404</v>
+        <v>812553</v>
       </c>
       <c r="D357" t="str">
         <v>Stage_1</v>
@@ -7539,7 +7539,7 @@
         <v>0</v>
       </c>
       <c r="F357" t="str">
-        <v>22925c8d03dde32eb604d7ecfd799e03d9032c974272d0823790b7d6b18967ba</v>
+        <v>28863dd5c2b81bc5356ca9f0dd5e1eac8fed203fb49f4b210e922ecb03193f6e</v>
       </c>
     </row>
     <row r="358">
@@ -7550,7 +7550,7 @@
         <v>character_largeimage_h0247.ab</v>
       </c>
       <c r="C358">
-        <v>837487</v>
+        <v>839343</v>
       </c>
       <c r="D358" t="str">
         <v>Stage_1</v>
@@ -7559,7 +7559,7 @@
         <v>0</v>
       </c>
       <c r="F358" t="str">
-        <v>ef401029e4a4b055b381ebbe633554d5daf4a3e23b60c62b852b185c4c663bf5</v>
+        <v>5357905b7239aed4aa345f0d8858dc18667b357d6ba43913b006c846889cce66</v>
       </c>
     </row>
     <row r="359">
@@ -7570,7 +7570,7 @@
         <v>character_largeimage_h0248.ab</v>
       </c>
       <c r="C359">
-        <v>836258</v>
+        <v>840807</v>
       </c>
       <c r="D359" t="str">
         <v>Stage_1</v>
@@ -7579,7 +7579,7 @@
         <v>0</v>
       </c>
       <c r="F359" t="str">
-        <v>f8dc41278c1bfbb1635e74efb4ceb293b4de54b87f0626cf7e2b6c0f4972b150</v>
+        <v>14fa397376c5c41166de1118ceafb55efe73cb2c5cc5b60bbce04b5d2246a8f9</v>
       </c>
     </row>
     <row r="360">
@@ -7590,7 +7590,7 @@
         <v>character_largeimage_h0249.ab</v>
       </c>
       <c r="C360">
-        <v>839134</v>
+        <v>845501</v>
       </c>
       <c r="D360" t="str">
         <v>Stage_1</v>
@@ -7599,7 +7599,7 @@
         <v>0</v>
       </c>
       <c r="F360" t="str">
-        <v>9b91af750de18d7afe93e1d3cba66a0bdd3c7db49a03c5ebcf3b8c44fee32fc4</v>
+        <v>39f9c7e94cddf548a58df76d68d9f3cf23f4a9e15f78d0acbb4520a83292ab51</v>
       </c>
     </row>
     <row r="361">
@@ -7610,7 +7610,7 @@
         <v>character_largeimage_h0253.ab</v>
       </c>
       <c r="C361">
-        <v>823722</v>
+        <v>828894</v>
       </c>
       <c r="D361" t="str">
         <v>Stage_1</v>
@@ -7619,7 +7619,7 @@
         <v>0</v>
       </c>
       <c r="F361" t="str">
-        <v>9c5c84a37c920c2e4b79f9013c9c5db129735e6375cc195a90117b4cf7802999</v>
+        <v>8d198c57924574ee3a201b394f17cb87d6e18677d306c7b7b817e1d3f9bacc9b</v>
       </c>
     </row>
     <row r="362">
@@ -7630,7 +7630,7 @@
         <v>character_largeimage_h0255.ab</v>
       </c>
       <c r="C362">
-        <v>800474</v>
+        <v>806083</v>
       </c>
       <c r="D362" t="str">
         <v>Stage_1</v>
@@ -7639,7 +7639,7 @@
         <v>0</v>
       </c>
       <c r="F362" t="str">
-        <v>450ab00dbd5b8f991797ab6c83f3ee7cb54290e9971ebd6d51273ff327ed5e15</v>
+        <v>5bd390944bcc93c73e4b44d171934f62938807da3dd2399995b638d9ac300554</v>
       </c>
     </row>
     <row r="363">
@@ -7650,7 +7650,7 @@
         <v>character_largeimage_h0256.ab</v>
       </c>
       <c r="C363">
-        <v>805509</v>
+        <v>813116</v>
       </c>
       <c r="D363" t="str">
         <v>Stage_1</v>
@@ -7659,7 +7659,7 @@
         <v>0</v>
       </c>
       <c r="F363" t="str">
-        <v>297c419fbd877b05bfc9add448ff76132757333cae20eccc028647aea7da7255</v>
+        <v>45a7cff70fc29d9013433edfe90c21ff00348d78109c0678d5f479573f6c5d17</v>
       </c>
     </row>
     <row r="364">
@@ -7670,7 +7670,7 @@
         <v>character_largeimage_h0257.ab</v>
       </c>
       <c r="C364">
-        <v>808381</v>
+        <v>817015</v>
       </c>
       <c r="D364" t="str">
         <v>Stage_1</v>
@@ -7679,7 +7679,7 @@
         <v>0</v>
       </c>
       <c r="F364" t="str">
-        <v>d05147b2b6be03ef2ce9c9de4dec8d3ff71bd96053222a4f476707092d75fa72</v>
+        <v>e94b5b576ddbde56aeb3f2f9b8cbea033580820f9c8d17507af6cc208d8939e8</v>
       </c>
     </row>
     <row r="365">
@@ -7690,7 +7690,7 @@
         <v>character_largeimage_h0259.ab</v>
       </c>
       <c r="C365">
-        <v>810068</v>
+        <v>818096</v>
       </c>
       <c r="D365" t="str">
         <v>Stage_1</v>
@@ -7699,7 +7699,7 @@
         <v>0</v>
       </c>
       <c r="F365" t="str">
-        <v>172c2c74277241aa72cedda739d55d17e54f6959a7474b0780a9ed33d03daa33</v>
+        <v>9eb7e0b7ff643f061ccad10a00ddf1f4a4d9a75555fa343d23bc164ec4eec25d</v>
       </c>
     </row>
     <row r="366">
@@ -7710,7 +7710,7 @@
         <v>character_largeimage_h0261.ab</v>
       </c>
       <c r="C366">
-        <v>785275</v>
+        <v>792915</v>
       </c>
       <c r="D366" t="str">
         <v>Stage_1</v>
@@ -7719,7 +7719,7 @@
         <v>0</v>
       </c>
       <c r="F366" t="str">
-        <v>03b89947a2d5dbfe670810747d52ec50f06c25e91ffe38907f479d65efb03148</v>
+        <v>c86b86ed367ebddf4ae097466d2b7d7362b3e59a68254c4366ded96ab91c4cc2</v>
       </c>
     </row>
     <row r="367">
@@ -7730,7 +7730,7 @@
         <v>character_largeimage_h0262.ab</v>
       </c>
       <c r="C367">
-        <v>847775</v>
+        <v>856984</v>
       </c>
       <c r="D367" t="str">
         <v>Stage_1</v>
@@ -7739,7 +7739,7 @@
         <v>0</v>
       </c>
       <c r="F367" t="str">
-        <v>42dc7a9aeedfb2f6754bbff5a20c0649221fbd710df2fb2229837dbf798d580a</v>
+        <v>d2dc039c603a31ceba28b5453d5a35827663ebeeba89251d86bfebfe04c18b4d</v>
       </c>
     </row>
     <row r="368">
@@ -7750,7 +7750,7 @@
         <v>character_largeimage_h0264.ab</v>
       </c>
       <c r="C368">
-        <v>718190</v>
+        <v>725019</v>
       </c>
       <c r="D368" t="str">
         <v>Stage_1</v>
@@ -7759,7 +7759,7 @@
         <v>0</v>
       </c>
       <c r="F368" t="str">
-        <v>ab84d41ed01d417a5c5cd0109bca96e438f4f56f3472560b99958ac4137677ca</v>
+        <v>11f6c768dd0a203c02200d132d7436ed82264211f7f46d539ed047901ede8fa7</v>
       </c>
     </row>
     <row r="369">
@@ -7770,7 +7770,7 @@
         <v>character_largeimage_h0265.ab</v>
       </c>
       <c r="C369">
-        <v>795432</v>
+        <v>802205</v>
       </c>
       <c r="D369" t="str">
         <v>Stage_1</v>
@@ -7779,7 +7779,7 @@
         <v>0</v>
       </c>
       <c r="F369" t="str">
-        <v>43942d89eafcb8381ae779ac97b86df469078014bca34c2803baa9d16040a97e</v>
+        <v>7b450a7966a09a2ca9516193c26994495af092a1afc8897b070f4143a028acc4</v>
       </c>
     </row>
     <row r="370">
@@ -7790,7 +7790,7 @@
         <v>character_largeimage_h0266.ab</v>
       </c>
       <c r="C370">
-        <v>808588</v>
+        <v>816759</v>
       </c>
       <c r="D370" t="str">
         <v>Stage_1</v>
@@ -7799,7 +7799,7 @@
         <v>0</v>
       </c>
       <c r="F370" t="str">
-        <v>ed1bd287702b2f736b9ad9fb7524ec06f5777b21a9511818d78a3ad00dc9d423</v>
+        <v>54c77486e93f91d5ed2b98194ad692ed3101698ac2f7065a507ce3fd3b9171de</v>
       </c>
     </row>
     <row r="371">
@@ -7810,7 +7810,7 @@
         <v>character_largeimage_h0268.ab</v>
       </c>
       <c r="C371">
-        <v>778224</v>
+        <v>782708</v>
       </c>
       <c r="D371" t="str">
         <v>Stage_1</v>
@@ -7819,7 +7819,7 @@
         <v>0</v>
       </c>
       <c r="F371" t="str">
-        <v>8c545650dd20c9e32120149543dd24e79058d125aa0ccf95c1033e80b8078919</v>
+        <v>c82e7dd946895fc505347e85732219fe31e12ec21909c1f52eb93a17190cca66</v>
       </c>
     </row>
     <row r="372">
@@ -7830,7 +7830,7 @@
         <v>character_largeimage_h0270.ab</v>
       </c>
       <c r="C372">
-        <v>789665</v>
+        <v>797348</v>
       </c>
       <c r="D372" t="str">
         <v>Stage_1</v>
@@ -7839,7 +7839,7 @@
         <v>0</v>
       </c>
       <c r="F372" t="str">
-        <v>1061859969e3ff3ae1b28bcaa8c6e3a8aa5203c6699e037ab0a1a30dd0ea1e6d</v>
+        <v>2105131bbf28ad85364804fb3c82c722cc9b215ee79ed6aff40cff8397bcb0b4</v>
       </c>
     </row>
     <row r="373">
@@ -7850,7 +7850,7 @@
         <v>character_largeimage_h0271.ab</v>
       </c>
       <c r="C373">
-        <v>820733</v>
+        <v>830364</v>
       </c>
       <c r="D373" t="str">
         <v>Stage_1</v>
@@ -7859,7 +7859,7 @@
         <v>0</v>
       </c>
       <c r="F373" t="str">
-        <v>04260aa0eb4d75fb007447059b3aaed6316a2c062babec302361c33db8578284</v>
+        <v>823f054038b500471607dab0573d0a1e6d9b02e93302b33b20ca41d8d03dbf81</v>
       </c>
     </row>
     <row r="374">
@@ -7870,7 +7870,7 @@
         <v>character_largeimage_h0273.ab</v>
       </c>
       <c r="C374">
-        <v>757725</v>
+        <v>760653</v>
       </c>
       <c r="D374" t="str">
         <v>Stage_1</v>
@@ -7879,7 +7879,7 @@
         <v>0</v>
       </c>
       <c r="F374" t="str">
-        <v>e451b622796765d79eda9a2e06ffe4673623d79ed334b834b1f3fbfa33e59da7</v>
+        <v>da5354f82abc33454ac8f11cb0f54c046f68ab7dc86e67afe77270d2bbda272d</v>
       </c>
     </row>
     <row r="375">
@@ -7890,7 +7890,7 @@
         <v>character_largeimage_h0274.ab</v>
       </c>
       <c r="C375">
-        <v>786408</v>
+        <v>787453</v>
       </c>
       <c r="D375" t="str">
         <v>Stage_1</v>
@@ -7899,7 +7899,7 @@
         <v>0</v>
       </c>
       <c r="F375" t="str">
-        <v>380ab4b4093260b3f77f48c03c65173f484970d7e9d7a55b9067faa0eb6b662d</v>
+        <v>4efc835e8d39f56bbf178063cda8ee05ea29080b46a8c00fbd92048c524a68e2</v>
       </c>
     </row>
     <row r="376">
@@ -7910,7 +7910,7 @@
         <v>character_largeimage_m0011.ab</v>
       </c>
       <c r="C376">
-        <v>3645563</v>
+        <v>3815659</v>
       </c>
       <c r="D376" t="str">
         <v>Stage_1</v>
@@ -7919,7 +7919,7 @@
         <v>0</v>
       </c>
       <c r="F376" t="str">
-        <v>6d163c0aa3de03702199280db17c4bbe2fddeea97fa709543044a1864c59ac4e</v>
+        <v>ece9e6414d11958a483849e584d3ed7effe4955aa6334fcf76502d4632980bbe</v>
       </c>
     </row>
     <row r="377">
@@ -7930,7 +7930,7 @@
         <v>character_largeimage_r0034.ab</v>
       </c>
       <c r="C377">
-        <v>3192016</v>
+        <v>3235567</v>
       </c>
       <c r="D377" t="str">
         <v>Stage_1</v>
@@ -7939,7 +7939,7 @@
         <v>0</v>
       </c>
       <c r="F377" t="str">
-        <v>a95c21cd1ab779a63db9047ad68d79e913fce1d1229cd60959433c515fa2b15f</v>
+        <v>c08d2b8c1d6f2ee2c3b1b285af7148d296bf0a717628dc1aa5c31b710f90cc27</v>
       </c>
     </row>
     <row r="378">
@@ -7950,7 +7950,7 @@
         <v>character_largeimage_r0160.ab</v>
       </c>
       <c r="C378">
-        <v>4547639</v>
+        <v>4612271</v>
       </c>
       <c r="D378" t="str">
         <v>Stage_1</v>
@@ -7959,7 +7959,7 @@
         <v>0</v>
       </c>
       <c r="F378" t="str">
-        <v>964ea8e902241d88c58f2ac99db9982703da97b02c7609af5438b4a03a8a0efe</v>
+        <v>eb93c981846b2a54d940a05d3def4e89a721f70bea2edd51e4c78f28f92360b8</v>
       </c>
     </row>
     <row r="379">
@@ -7970,7 +7970,7 @@
         <v>character_largeimage_r0173.ab</v>
       </c>
       <c r="C379">
-        <v>783778</v>
+        <v>796924</v>
       </c>
       <c r="D379" t="str">
         <v>Stage_1</v>
@@ -7979,7 +7979,7 @@
         <v>0</v>
       </c>
       <c r="F379" t="str">
-        <v>8195c3708ce8e882a3d95cb265160b057eb3bf5d286f64493dab9ff905fdaab6</v>
+        <v>4ec0161ab3d23c2f252d99578986617acf053f1a41f7bc326b63e8ab3d42ddaa</v>
       </c>
     </row>
     <row r="380">
@@ -7990,7 +7990,7 @@
         <v>character_largeimage_r0205.ab</v>
       </c>
       <c r="C380">
-        <v>835262</v>
+        <v>844428</v>
       </c>
       <c r="D380" t="str">
         <v>Stage_1</v>
@@ -7999,7 +7999,7 @@
         <v>0</v>
       </c>
       <c r="F380" t="str">
-        <v>527e90522ce04f745056b9caedcb86a53d46219da877b5661b2d167770d26dcb</v>
+        <v>77542217dfbb763287a67c4a89a743a0bc1b5c9d7032d46ddbde3890d8c35032</v>
       </c>
     </row>
     <row r="381">
@@ -8010,7 +8010,7 @@
         <v>character_largeimage_t0017.ab</v>
       </c>
       <c r="C381">
-        <v>5048467</v>
+        <v>5237326</v>
       </c>
       <c r="D381" t="str">
         <v>Stage_1</v>
@@ -8019,7 +8019,7 @@
         <v>0</v>
       </c>
       <c r="F381" t="str">
-        <v>569f2fd821c168371bd7ba0fad110a99c067d9153288ec5b7dc7dba7fadbef87</v>
+        <v>3b46c7c3716d00b6ff611cbe69ceba0b3530e7d32751d03b33ed335ccfcb8d86</v>
       </c>
     </row>
     <row r="382">
@@ -8030,7 +8030,7 @@
         <v>character_largeimage_t0026.ab</v>
       </c>
       <c r="C382">
-        <v>3324659</v>
+        <v>3362496</v>
       </c>
       <c r="D382" t="str">
         <v>Stage_1</v>
@@ -8039,7 +8039,7 @@
         <v>0</v>
       </c>
       <c r="F382" t="str">
-        <v>3f68cff42a6b9b5f70e4727bbbc4ca79a4b5e3f36eabee4e6ac677e471042212</v>
+        <v>5d841bf9766a0f53042eae4be6f12d3e3983d334258eaf2c189681125d420393</v>
       </c>
     </row>
     <row r="383">
@@ -8050,7 +8050,7 @@
         <v>character_largeimage_t0027.ab</v>
       </c>
       <c r="C383">
-        <v>3241554</v>
+        <v>3449660</v>
       </c>
       <c r="D383" t="str">
         <v>Stage_1</v>
@@ -8059,7 +8059,7 @@
         <v>0</v>
       </c>
       <c r="F383" t="str">
-        <v>5c1ed78edf2589ba18b2fd63c792819e2092273556283005ee4e832864ad3852</v>
+        <v>c9621fe141e6662013eca19d893c4916ef63ae02e9f28bbd2d979f244bf7bcc5</v>
       </c>
     </row>
     <row r="384">
@@ -8070,7 +8070,7 @@
         <v>character_largeimage_t0032.ab</v>
       </c>
       <c r="C384">
-        <v>3632341</v>
+        <v>3730204</v>
       </c>
       <c r="D384" t="str">
         <v>Stage_1</v>
@@ -8079,7 +8079,7 @@
         <v>0</v>
       </c>
       <c r="F384" t="str">
-        <v>3f275335ed88fbd6088516a978efb3cd60af951a07bbdb0cd82a834ccaccbc07</v>
+        <v>5e1dc1cd937aa31054f8dcdb451b0b999d597fb5457b383f201447f89de9382e</v>
       </c>
     </row>
     <row r="385">
@@ -8090,7 +8090,7 @@
         <v>character_largeimage_t0033.ab</v>
       </c>
       <c r="C385">
-        <v>3771149</v>
+        <v>3801701</v>
       </c>
       <c r="D385" t="str">
         <v>Stage_1</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="F385" t="str">
-        <v>26a7366f49bb32607c93b69268e6fc0693e08fef6296452290871b2fb08fc2c7</v>
+        <v>bc796ec22a60218361399d6abecc4d14bee5d451d4817c08638d226729c23d87</v>
       </c>
     </row>
     <row r="386">
@@ -8110,7 +8110,7 @@
         <v>character_largeimage_t0039.ab</v>
       </c>
       <c r="C386">
-        <v>813283</v>
+        <v>815207</v>
       </c>
       <c r="D386" t="str">
         <v>Stage_1</v>
@@ -8119,7 +8119,7 @@
         <v>0</v>
       </c>
       <c r="F386" t="str">
-        <v>5350ab84baed9d974062a833ee3cabfdea3208b429a787505b7863cd88d02e59</v>
+        <v>787d08afaf9495577645a27a0f557ffc4f50f58f605bc466e49ee5025c977e92</v>
       </c>
     </row>
     <row r="387">
@@ -8130,7 +8130,7 @@
         <v>character_largeimage_t0044.ab</v>
       </c>
       <c r="C387">
-        <v>791961</v>
+        <v>797516</v>
       </c>
       <c r="D387" t="str">
         <v>Stage_1</v>
@@ -8139,7 +8139,7 @@
         <v>0</v>
       </c>
       <c r="F387" t="str">
-        <v>eb3fb4c4fbec62853ced6c63348bda093239167910e1975c24786721e5c36945</v>
+        <v>86a9f8572f81e70b8ab18626bd3351c19de23fd28b80bbfce97bfbbf1ecc1877</v>
       </c>
     </row>
     <row r="388">
@@ -8150,7 +8150,7 @@
         <v>character_largeimage_t0049.ab</v>
       </c>
       <c r="C388">
-        <v>2772613</v>
+        <v>2773067</v>
       </c>
       <c r="D388" t="str">
         <v>Stage_1</v>
@@ -8159,7 +8159,7 @@
         <v>0</v>
       </c>
       <c r="F388" t="str">
-        <v>95bcb0bd9154f014e06084d19d720ac2bac3315b2829a51f748bab806188e50e</v>
+        <v>e864e23665cf82e428ddc4e61c4c808c8a3ef417948673de2cb773f02b4448da</v>
       </c>
     </row>
     <row r="389">
@@ -8170,7 +8170,7 @@
         <v>character_largeimage_t0153.ab</v>
       </c>
       <c r="C389">
-        <v>2756611</v>
+        <v>2806303</v>
       </c>
       <c r="D389" t="str">
         <v>Stage_1</v>
@@ -8179,7 +8179,7 @@
         <v>0</v>
       </c>
       <c r="F389" t="str">
-        <v>3c97d4a5953e712f3dfdd8ab30d02f527616fcb3d801dd8b86b3c0cf522a0eef</v>
+        <v>c5a5bb34de6805f8f98b3cbc449e0949441098977f4acb208a3b47120ea12a8e</v>
       </c>
     </row>
     <row r="390">
@@ -8190,7 +8190,7 @@
         <v>character_largeimage_t0155.ab</v>
       </c>
       <c r="C390">
-        <v>4381513</v>
+        <v>4432999</v>
       </c>
       <c r="D390" t="str">
         <v>Stage_1</v>
@@ -8199,7 +8199,7 @@
         <v>0</v>
       </c>
       <c r="F390" t="str">
-        <v>38ad3eaafbadfa98327d0d5542f2f0d88f7f31f659055e6d5d7f5d8ecadaaf25</v>
+        <v>c9fe5c4237d3a91aab24b2f8c797c56572e3edd903e3829355978ae19a449604</v>
       </c>
     </row>
     <row r="391">
@@ -8210,7 +8210,7 @@
         <v>character_largeimage_t0156.ab</v>
       </c>
       <c r="C391">
-        <v>2462163</v>
+        <v>2656080</v>
       </c>
       <c r="D391" t="str">
         <v>Stage_1</v>
@@ -8219,7 +8219,7 @@
         <v>0</v>
       </c>
       <c r="F391" t="str">
-        <v>d47db6ea8061d6508d44fdbc8629a568db3385a88c1f450c53188c37a306fbd1</v>
+        <v>ac1b9e34282714a51d58cf78f6b64da3b0e38b0efbab3f90a79b9a27231d7c61</v>
       </c>
     </row>
     <row r="392">
@@ -8230,7 +8230,7 @@
         <v>character_largeimage_t0158.ab</v>
       </c>
       <c r="C392">
-        <v>5260995</v>
+        <v>5326790</v>
       </c>
       <c r="D392" t="str">
         <v>Stage_1</v>
@@ -8239,7 +8239,7 @@
         <v>0</v>
       </c>
       <c r="F392" t="str">
-        <v>60e32e2c51b82894f308157ead5044b1e8a536bc973703711b4f8eb6ab332f30</v>
+        <v>8604c6757311de6420a6addd258335d73db3a654535327d2b0bc97a36d474162</v>
       </c>
     </row>
     <row r="393">
@@ -8250,7 +8250,7 @@
         <v>character_largeimage_t0180.ab</v>
       </c>
       <c r="C393">
-        <v>2585585</v>
+        <v>2626294</v>
       </c>
       <c r="D393" t="str">
         <v>Stage_1</v>
@@ -8259,7 +8259,7 @@
         <v>0</v>
       </c>
       <c r="F393" t="str">
-        <v>c5811705c032100ad1a16583021dca2fb02a11ed596ad6f58b79f2775150edc1</v>
+        <v>935b7f4c8c9f2fef6f048e9c6b0038eedc73d0886d60f9586bd47110ae454408</v>
       </c>
     </row>
     <row r="394">
@@ -8270,7 +8270,7 @@
         <v>character_largeimage_t0181.ab</v>
       </c>
       <c r="C394">
-        <v>3294655</v>
+        <v>3323819</v>
       </c>
       <c r="D394" t="str">
         <v>Stage_1</v>
@@ -8279,7 +8279,7 @@
         <v>0</v>
       </c>
       <c r="F394" t="str">
-        <v>3ce7bff8c5c6bff24697ac51035be274c30bba43c89704245ba4d5ece12532a8</v>
+        <v>8c331b21412fa6b650637d4fbd497f68dd9d26770e8abfbca3bd84d27c398a68</v>
       </c>
     </row>
     <row r="395">
@@ -8290,7 +8290,7 @@
         <v>character_largeimage_t0182.ab</v>
       </c>
       <c r="C395">
-        <v>2283005</v>
+        <v>2324431</v>
       </c>
       <c r="D395" t="str">
         <v>Stage_1</v>
@@ -8299,7 +8299,7 @@
         <v>0</v>
       </c>
       <c r="F395" t="str">
-        <v>f08896641300c346a1e73ed169d426147c629133d6b99fc0d0b053d6f89dea33</v>
+        <v>08f1dc4a804b238f1a0915c1539ecd591e54f3d2a968f9b0edffd29bc31acbf1</v>
       </c>
     </row>
     <row r="396">
@@ -8310,7 +8310,7 @@
         <v>character_largeimage_t0184.ab</v>
       </c>
       <c r="C396">
-        <v>2289827</v>
+        <v>2299363</v>
       </c>
       <c r="D396" t="str">
         <v>Stage_1</v>
@@ -8319,7 +8319,7 @@
         <v>0</v>
       </c>
       <c r="F396" t="str">
-        <v>aa09e9c0a10976e05321eeed5a37397f867e1377acd71dc4e3d2d5d1417daf28</v>
+        <v>bf9d2301fade1acdada22a0d0b6edba9aca7bfd95e4295565ba9343793e8819f</v>
       </c>
     </row>
     <row r="397">
@@ -8330,7 +8330,7 @@
         <v>character_largeimage_t0187.ab</v>
       </c>
       <c r="C397">
-        <v>2887185</v>
+        <v>2916663</v>
       </c>
       <c r="D397" t="str">
         <v>Stage_1</v>
@@ -8339,7 +8339,7 @@
         <v>0</v>
       </c>
       <c r="F397" t="str">
-        <v>84cffe40a80fe5c71df8f44503bbdce8bbffb4c01dc57012fb621fc40fd4230d</v>
+        <v>fa50123e679a8398a94251f4261e19a754f1a33abfea77ac6c714dffd1e6d18e</v>
       </c>
     </row>
     <row r="398">
@@ -8350,7 +8350,7 @@
         <v>character_largeimage_t0188.ab</v>
       </c>
       <c r="C398">
-        <v>2744938</v>
+        <v>2795521</v>
       </c>
       <c r="D398" t="str">
         <v>Stage_1</v>
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="F398" t="str">
-        <v>4f854b7d0c3b92905dd2311a69ab83cea017de02730b719a6608464f27e269d4</v>
+        <v>587416a791d7ef87f35c67adc36082a2820851f2c88dbdfa8a05d416ea468f33</v>
       </c>
     </row>
     <row r="399">
@@ -8370,7 +8370,7 @@
         <v>character_largeimage_t0189.ab</v>
       </c>
       <c r="C399">
-        <v>4473711</v>
+        <v>4521740</v>
       </c>
       <c r="D399" t="str">
         <v>Stage_1</v>
@@ -8379,7 +8379,7 @@
         <v>0</v>
       </c>
       <c r="F399" t="str">
-        <v>8fc73aa493d889c8325fbef52adf15dac0c8ee19e212564b6ae16b08b266144f</v>
+        <v>4769d118144b2236a3920b3590b78e1d5328b02a28e26e8906c79126f1f800dd</v>
       </c>
     </row>
     <row r="400">
@@ -8390,7 +8390,7 @@
         <v>character_largeimage_t0204.ab</v>
       </c>
       <c r="C400">
-        <v>839510</v>
+        <v>849147</v>
       </c>
       <c r="D400" t="str">
         <v>Stage_1</v>
@@ -8399,7 +8399,7 @@
         <v>0</v>
       </c>
       <c r="F400" t="str">
-        <v>3339401d70ded15a0020af038f486a0d2a6e2bf7e4ca29d2fc52483eba92f982</v>
+        <v>78669d6c64b4b4679563635bfe1cfef5ac0189338b1f524c713569b0655f099b</v>
       </c>
     </row>
     <row r="401">
@@ -8410,7 +8410,7 @@
         <v>character_largeimage_t0207.ab</v>
       </c>
       <c r="C401">
-        <v>788109</v>
+        <v>792341</v>
       </c>
       <c r="D401" t="str">
         <v>Stage_1</v>
@@ -8419,7 +8419,7 @@
         <v>0</v>
       </c>
       <c r="F401" t="str">
-        <v>884a61acb6fc59583fb23f817ab1ee2aad0b3edba982eb01c5e3d4409e1db73f</v>
+        <v>9503b1db9b456094ab75a8c113bfd8b532da352f149c6f212c4729d03fd86304</v>
       </c>
     </row>
     <row r="402">
@@ -8430,7 +8430,7 @@
         <v>character_largeimage_t0212.ab</v>
       </c>
       <c r="C402">
-        <v>843123</v>
+        <v>848727</v>
       </c>
       <c r="D402" t="str">
         <v>Stage_1</v>
@@ -8439,7 +8439,7 @@
         <v>0</v>
       </c>
       <c r="F402" t="str">
-        <v>e442a6b286187dcc18ca56751536e1758d5953d5b913e759d2ed412148611a38</v>
+        <v>3d7c6dae804b092d4e26fc250d506e8d50554c4d93f3598c4072e2182c93f16d</v>
       </c>
     </row>
     <row r="403">
@@ -8450,7 +8450,7 @@
         <v>character_largeimage_t0214.ab</v>
       </c>
       <c r="C403">
-        <v>828387</v>
+        <v>835624</v>
       </c>
       <c r="D403" t="str">
         <v>Stage_1</v>
@@ -8459,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="F403" t="str">
-        <v>342fd529c964664d600e232cd94bd8b1675ded9c1b64945ef103993a6b5b300c</v>
+        <v>a5c2725db06676a17073fa47982b8b5e3ea90c51f357a0ceee13c887a90156c5</v>
       </c>
     </row>
     <row r="404">
@@ -8470,7 +8470,7 @@
         <v>character_largeimage_t0218.ab</v>
       </c>
       <c r="C404">
-        <v>811612</v>
+        <v>819695</v>
       </c>
       <c r="D404" t="str">
         <v>Stage_1</v>
@@ -8479,7 +8479,7 @@
         <v>0</v>
       </c>
       <c r="F404" t="str">
-        <v>bda0c6f7dc7407f7c344f85b171a48370f75519c50e728784f647c83169bd94c</v>
+        <v>e1e11a0e18f75446e58853e0666382a0b70442f53696742f7654c55aa2ae5fc6</v>
       </c>
     </row>
     <row r="405">
@@ -8490,7 +8490,7 @@
         <v>character_largeimage_t0222.ab</v>
       </c>
       <c r="C405">
-        <v>774259</v>
+        <v>780845</v>
       </c>
       <c r="D405" t="str">
         <v>Stage_1</v>
@@ -8499,7 +8499,7 @@
         <v>0</v>
       </c>
       <c r="F405" t="str">
-        <v>8ab646da7e9d3f088d7b6a87436ba651ca2f50198534bb4838143a45e096932e</v>
+        <v>94806acd5bc81256cc69a0ce2ee8bfac15df1ff54a271cbbed4d37d2caba5915</v>
       </c>
     </row>
     <row r="406">
@@ -8510,7 +8510,7 @@
         <v>character_largeimage_t0223.ab</v>
       </c>
       <c r="C406">
-        <v>844248</v>
+        <v>851233</v>
       </c>
       <c r="D406" t="str">
         <v>Stage_1</v>
@@ -8519,7 +8519,7 @@
         <v>0</v>
       </c>
       <c r="F406" t="str">
-        <v>18c1161759d4a71ed98ffc241b6626b1e001387f1a6c5ce54150f250abf64248</v>
+        <v>90ee019f21368d7aa6055fcbeb9c86023e7d8f43f98ff302e8472b537a638ded</v>
       </c>
     </row>
     <row r="407">
@@ -8530,7 +8530,7 @@
         <v>character_largeimage_t0225.ab</v>
       </c>
       <c r="C407">
-        <v>815023</v>
+        <v>822322</v>
       </c>
       <c r="D407" t="str">
         <v>Stage_1</v>
@@ -8539,7 +8539,7 @@
         <v>0</v>
       </c>
       <c r="F407" t="str">
-        <v>f2a096a766a2689633f4d106cf0a6a439a759aea742a118791bd76a6648f267d</v>
+        <v>1aa6aeb4640e99079fa0d7ac41790b66916841c477ccbd10d47c535b16667471</v>
       </c>
     </row>
     <row r="408">
@@ -8550,7 +8550,7 @@
         <v>character_largeimage_t0228.ab</v>
       </c>
       <c r="C408">
-        <v>829894</v>
+        <v>836203</v>
       </c>
       <c r="D408" t="str">
         <v>Stage_1</v>
@@ -8559,7 +8559,7 @@
         <v>0</v>
       </c>
       <c r="F408" t="str">
-        <v>94f3e6cc4c0a6a79f10a543d83f614303bc3a05333d39f4403ef896f4dcf07f5</v>
+        <v>407569038ef6420c0cb1e4506d19167df815123959962c9b21bbd99897fe4ccf</v>
       </c>
     </row>
     <row r="409">
@@ -8570,7 +8570,7 @@
         <v>character_largeimage_t0229.ab</v>
       </c>
       <c r="C409">
-        <v>1662213</v>
+        <v>1673615</v>
       </c>
       <c r="D409" t="str">
         <v>Stage_1</v>
@@ -8579,7 +8579,7 @@
         <v>0</v>
       </c>
       <c r="F409" t="str">
-        <v>69e6216c55eeaaab8fd283f59f25c316734a73644b13941d4d1fe1e1c31f8c1f</v>
+        <v>7dbe3117eda9a192907af6b5d915e1e8d5d5863d5ee9ee0890f0f80a7ac9f717</v>
       </c>
     </row>
     <row r="410">
@@ -8590,7 +8590,7 @@
         <v>character_largeimage_t0231.ab</v>
       </c>
       <c r="C410">
-        <v>823425</v>
+        <v>834972</v>
       </c>
       <c r="D410" t="str">
         <v>Stage_1</v>
@@ -8599,7 +8599,7 @@
         <v>0</v>
       </c>
       <c r="F410" t="str">
-        <v>3cb4f02d9303d1a2b5fc53ad0acd0aa27db034c6c97e9bef02dacf3febc0eee6</v>
+        <v>37e21a4dc89ef6d00464654bed2d1409db1f1bad078fe9654d74351f667a3728</v>
       </c>
     </row>
     <row r="411">
@@ -8610,7 +8610,7 @@
         <v>character_largeimage_t0242.ab</v>
       </c>
       <c r="C411">
-        <v>777670</v>
+        <v>783235</v>
       </c>
       <c r="D411" t="str">
         <v>Stage_1</v>
@@ -8619,7 +8619,7 @@
         <v>0</v>
       </c>
       <c r="F411" t="str">
-        <v>7c281124753083a4db690ee47b450f4f89e3d56fc805d995ace8e49efa5bc50f</v>
+        <v>a689a4203b4d2ae4198c335651845704851964c5a71096c76f74f71512bf22c3</v>
       </c>
     </row>
     <row r="412">
@@ -8630,7 +8630,7 @@
         <v>character_largeimage_t0246.ab</v>
       </c>
       <c r="C412">
-        <v>819675</v>
+        <v>826861</v>
       </c>
       <c r="D412" t="str">
         <v>Stage_1</v>
@@ -8639,7 +8639,7 @@
         <v>0</v>
       </c>
       <c r="F412" t="str">
-        <v>c9ff420c4cd5404f687592c9851a9c3c9b90d6aba4ec3215e4213794c4ec8651</v>
+        <v>0efbe3fca37e5b49193f01329415a3422993494311427b4e1bcebab87f797e13</v>
       </c>
     </row>
     <row r="413">
@@ -8650,7 +8650,7 @@
         <v>character_largeimage_t0250.ab</v>
       </c>
       <c r="C413">
-        <v>835064</v>
+        <v>840665</v>
       </c>
       <c r="D413" t="str">
         <v>Stage_1</v>
@@ -8659,7 +8659,7 @@
         <v>0</v>
       </c>
       <c r="F413" t="str">
-        <v>cabd53f65c1283e0ac5773bc89f0d3baf8df60f587a2629bb61ff5df5f38e998</v>
+        <v>bebcc064143ea17da4597d6bb5d9776da0cd7b0099e980b535cfc950888c02b6</v>
       </c>
     </row>
     <row r="414">
@@ -8670,7 +8670,7 @@
         <v>character_largeimage_t0251.ab</v>
       </c>
       <c r="C414">
-        <v>817439</v>
+        <v>822122</v>
       </c>
       <c r="D414" t="str">
         <v>Stage_1</v>
@@ -8679,7 +8679,7 @@
         <v>0</v>
       </c>
       <c r="F414" t="str">
-        <v>35de9505e776e1b88eff26e7adc6f554d89c0d74424c46ac4d6b966cac281dae</v>
+        <v>5765b7d7037fd8080b6cadcf07d11827781ee1387a102a02ede1a7b09b9f5cd7</v>
       </c>
     </row>
     <row r="415">
@@ -8690,7 +8690,7 @@
         <v>character_largeimage_t0252.ab</v>
       </c>
       <c r="C415">
-        <v>3182222</v>
+        <v>3204821</v>
       </c>
       <c r="D415" t="str">
         <v>Stage_1</v>
@@ -8699,7 +8699,7 @@
         <v>0</v>
       </c>
       <c r="F415" t="str">
-        <v>041e2f53d9fa84b5baeb43cbf5b681fe1c1a09fc422e5db7e8abc8f70bc26348</v>
+        <v>206869d1e761df16eb266df1dfe7a7d656ea25a88716e4d697fa24e643be0c41</v>
       </c>
     </row>
     <row r="416">
@@ -8710,7 +8710,7 @@
         <v>character_largeimage_t0254.ab</v>
       </c>
       <c r="C416">
-        <v>821577</v>
+        <v>829656</v>
       </c>
       <c r="D416" t="str">
         <v>Stage_1</v>
@@ -8719,7 +8719,7 @@
         <v>0</v>
       </c>
       <c r="F416" t="str">
-        <v>0ec094e49c6f0bef8aeec78857eeaae95127b56d79ef9f59be4ec966f8258c66</v>
+        <v>bea1c9474f8e2bd2d98f6c7685aee7aa7f6dfddad97fa9aec368a06056c08543</v>
       </c>
     </row>
     <row r="417">
@@ -8730,7 +8730,7 @@
         <v>character_largeimage_t0258.ab</v>
       </c>
       <c r="C417">
-        <v>799096</v>
+        <v>808339</v>
       </c>
       <c r="D417" t="str">
         <v>Stage_1</v>
@@ -8739,7 +8739,7 @@
         <v>0</v>
       </c>
       <c r="F417" t="str">
-        <v>18672ae7cdd8fbc33c3c3fb113d9cc3cb1797d9336d487d7d2cc71564bb4a621</v>
+        <v>441eeeca9c231f13bba46857369c41027113991efc9516e9cd196dec341ea2a3</v>
       </c>
     </row>
     <row r="418">
@@ -8750,7 +8750,7 @@
         <v>character_largeimage_t0263.ab</v>
       </c>
       <c r="C418">
-        <v>819892</v>
+        <v>822766</v>
       </c>
       <c r="D418" t="str">
         <v>Stage_1</v>
@@ -8759,7 +8759,7 @@
         <v>0</v>
       </c>
       <c r="F418" t="str">
-        <v>e8bb91ba644af38d3523e9355cc207668ab626f2304399ef855def2eeb181356</v>
+        <v>dbce1b703954a35f00ecb8b6499cc858038621ca5f72d604dae0ffb4500dd7f4</v>
       </c>
     </row>
     <row r="419">
@@ -8770,7 +8770,7 @@
         <v>character_largeimage_t0269.ab</v>
       </c>
       <c r="C419">
-        <v>814551</v>
+        <v>817986</v>
       </c>
       <c r="D419" t="str">
         <v>Stage_1</v>
@@ -8779,7 +8779,7 @@
         <v>0</v>
       </c>
       <c r="F419" t="str">
-        <v>5775eef9664188e2989b7a33985a416e66fca83d2960305dab4744621708d1e0</v>
+        <v>0b562def1880e98aeca9e8f512b30b0951e29cfc34dbdbd337d6f09fc3f91f31</v>
       </c>
     </row>
     <row r="420">
@@ -8790,7 +8790,7 @@
         <v>character_largeimage_t0272.ab</v>
       </c>
       <c r="C420">
-        <v>760703</v>
+        <v>766550</v>
       </c>
       <c r="D420" t="str">
         <v>Stage_1</v>
@@ -8799,7 +8799,7 @@
         <v>0</v>
       </c>
       <c r="F420" t="str">
-        <v>04b23476caf6f2275bb0febbf34b0f90581a1b778c8e54f1dd604efcb8283da8</v>
+        <v>ee1d17c7f6740d38388eaa5eadf46c77e2b8c63569efd8745c42a87ed038489e</v>
       </c>
     </row>
     <row r="421">
@@ -8810,7 +8810,7 @@
         <v>character_largeimage_t0275.ab</v>
       </c>
       <c r="C421">
-        <v>761709</v>
+        <v>762774</v>
       </c>
       <c r="D421" t="str">
         <v>Stage_1</v>
@@ -8819,7 +8819,7 @@
         <v>0</v>
       </c>
       <c r="F421" t="str">
-        <v>8350830bdc61d2345550fec850c1f0b08043d91988e717e7291fc6ff4633abfa</v>
+        <v>cc11bfc0b65dd92cf0728a9e3b53c668de271ad8455e5f30eaa75fe376b82444</v>
       </c>
     </row>
     <row r="422">
@@ -8830,7 +8830,7 @@
         <v>character_largeimage_uncategorized_0.ab</v>
       </c>
       <c r="C422">
-        <v>173461</v>
+        <v>173957</v>
       </c>
       <c r="D422" t="str">
         <v>Stage_1</v>
@@ -8839,7 +8839,7 @@
         <v>0</v>
       </c>
       <c r="F422" t="str">
-        <v>9c40f907ab459375c76b4a51919f83aa971bac3c394a4d64e8e549d7879abebf</v>
+        <v>2c2beaf88b035c85d770cde28b8f928cde5511b162590621cfd7b98956b94253</v>
       </c>
     </row>
     <row r="423">
@@ -8850,7 +8850,7 @@
         <v>character_largeimage_uncategorized_3.ab</v>
       </c>
       <c r="C423">
-        <v>214292</v>
+        <v>234749</v>
       </c>
       <c r="D423" t="str">
         <v>Stage_1</v>
@@ -8859,7 +8859,7 @@
         <v>0</v>
       </c>
       <c r="F423" t="str">
-        <v>baa10ce33b3b4d5a88452011578fd5a338303e27f2f7e58822f6cbbf2f359f10</v>
+        <v>e7c577ac771a0141fd16afeba0ecfa3ff4cab7a7ea5c00388e72e51e2117f9f9</v>
       </c>
     </row>
   </sheetData>
